--- a/site/exports/hit-seie.xlsx
+++ b/site/exports/hit-seie.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R1541479fcf034dc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R87ae7f63e6ca40b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rb648aae6d66c4b01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R11a1b6e5e9cf4de6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R957fa6374b9b4563"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re2532eb5601b446d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R3673877d0ca14e62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rda79ee985c174a4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R9274e9a79892498f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R0639878522ed414e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T1_0" displayName="T1_0" ref="A1:G84" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T1_0" displayName="T1_0" ref="A1:G104" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T1_1" displayName="T1_1" ref="A1:Q657" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T1_1" displayName="T1_1" ref="A1:Q773" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -179,7 +179,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T1_2" displayName="T1_2" ref="A1:J22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T1_2" displayName="T1_2" ref="A1:J29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="导师姓名"/>
@@ -197,7 +197,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T1_3" displayName="T1_3" ref="A1:J176" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T1_3" displayName="T1_3" ref="A1:J214" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -215,7 +215,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T1_4" displayName="T1_4" ref="A1:E268" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T1_4" displayName="T1_4" ref="A1:E366" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -2363,10 +2363,470 @@
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
     </x:row>
+    <x:row r="85" ht="64" customHeight="1">
+      <x:c r="A85" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B85" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C85" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D85" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/weidebao?lang=zh</x:v>
+      </x:c>
+      <x:c r="E85" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F85" s="6" t="str">
+        <x:v>仅记录已读来源明确披露的公开职业信息，不宣称完整终身履历。；本人导师须有明确关系证据；合著、团队成员、相关链接、招生导师资格均不推断为本人的导师。；学位、访学、博士后与任职分型；机构地域不代表国籍。；论文为至多3篇官网精选，不是完整成果清单；登记元数据核验不等于文章落地页已可访问。；未披露完整任职时间线、当前研究员任命起始日期及公开访问/博士后经历。；已检索姓名与导师、博士论文词组，未确认本人导师；乔立岩课题组归属与联合指导招生模式不是魏德宝自身师承证据。；来源差异（appointments.current_title）：中文页头及正文为研究员，英文页头为Professor而正文为Research Professor；当前职称保留中文研究员，不另设教授任命。</x:v>
+      </x:c>
+      <x:c r="G85" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="64" customHeight="1">
+      <x:c r="A86" s="6" t="str">
+        <x:v>刘晓东</x:v>
+      </x:c>
+      <x:c r="B86" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C86" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D86" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuxiaodong?lang=zh</x:v>
+      </x:c>
+      <x:c r="E86" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F86" s="6" t="str">
+        <x:v>仅记录已读来源明确披露的公开职业信息，不宣称完整终身履历。；本人导师须有明确关系证据；合著、团队成员、相关链接、招生导师资格均不推断为本人的导师。；学位、访学、博士后与任职分型；机构地域不代表国籍。；论文为至多3篇官网精选，不是完整成果清单；登记元数据核验不等于文章落地页已可访问。；本科、硕士、博士入学时间、访学/博士后及完整任职时间线未披露。；已读官方中英文内容并定向检索本人博士/导师，未确认导师；杨京礼团队归属及合著不作师承。；来源差异（appointments.current_title）：中文及英文正文均为副教授/associate professor；英文页头同时列Associate Professor和assistant professor。保留副教授并保留页头标签冲突，不新增助理教授任职。；来源差异（publications.hybrid_title_and_venue）：官网题名为Analogue Circuits且刊名为IEEE Transactions on Instrument and Measurement；Crossref登记正式期刊文章使用Analog Circuits及Instrumentation and Measurement。采用登记书目并保留原文差异。</x:v>
+      </x:c>
+      <x:c r="G86" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="64" customHeight="1">
+      <x:c r="A87" s="6" t="str">
+        <x:v>孙震</x:v>
+      </x:c>
+      <x:c r="B87" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C87" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D87" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/sunzhen?lang=zh</x:v>
+      </x:c>
+      <x:c r="E87" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F87" s="6" t="str">
+        <x:v>仅记录已读来源明确披露的公开职业信息，不宣称完整终身履历。；本人导师须有明确关系证据；合著、团队成员、相关链接、招生导师资格均不推断为本人的导师。；学位、访学、博士后与任职分型；机构地域不代表国籍。；论文为至多3篇官网精选，不是完整成果清单；登记元数据核验不等于文章落地页已可访问。；本科、硕士、博士起止时间及专业、访问/博士后经历未披露。；已读本人中英文主页并检索博士/学位论文/导师，未取得本人导师的明确证据；同名外校学者和研究团队列表不并入。；已读官方主页未列具体论文书目，仅有论文数量概述，publications保留空数组。</x:v>
+      </x:c>
+      <x:c r="G87" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="64" customHeight="1">
+      <x:c r="A88" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B88" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C88" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D88" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ljzsylmy?lang=zh</x:v>
+      </x:c>
+      <x:c r="E88" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F88" s="6" t="str">
+        <x:v>仅记录已读来源明确披露的公开职业信息，不宣称完整终身履历。；本人导师须有明确关系证据；合著、团队成员、相关链接、招生导师资格均不推断为本人的导师。；学位、访学、博士后与任职分型；机构地域不代表国籍。；论文为至多3篇官网精选，不是完整成果清单；登记元数据核验不等于文章落地页已可访问。；已定向检索博士及导师，未确认本人的学位导师；彭喜元、彭宇团队负责关系与合作教师不是其本人导师证据。；主页讲师任职从2001-02开始，硕士教育到2001-07结束，原文时间重叠保留，不自行纠正。；未披露本人访学或博士后经历；合作教师介绍中的访学/博士后经历属于其他人，不采入本人的履历。；来源差异（publications.correlation_pages）：官网44(8):553-554，Crossref同题同作者登记553-555；页码采用Crossref，差异未声称独立消除。</x:v>
+      </x:c>
+      <x:c r="G88" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="64" customHeight="1">
+      <x:c r="A89" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B89" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C89" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D89" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+      <x:c r="E89" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F89" s="6" t="str">
+        <x:v>仅记录已读来源明确披露的公开职业信息，不宣称完整终身履历。；本人导师须有明确关系证据；合著、团队成员、相关链接、招生导师资格均不推断为本人的导师。；学位、访学、博士后与任职分型；机构地域不代表国籍。；论文为至多3篇官网精选，不是完整成果清单；登记元数据核验不等于文章落地页已可访问。；1994年硕士结束至1998年讲师开始之间的职业经历、1998年前任职和博士后合作导师未披露。；本科及硕士授位状态未另有明确授位叙述，保留null；博士后不计学位。；未取得本科导师陈陆君可消歧的独立官方个人简介或当前任职状态，保留未知，不与同名者合并。</x:v>
+      </x:c>
+      <x:c r="G89" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="64" customHeight="1">
+      <x:c r="A90" s="6" t="str">
+        <x:v>尹洪涛</x:v>
+      </x:c>
+      <x:c r="B90" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C90" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D90" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yinhongtao</x:v>
+      </x:c>
+      <x:c r="E90" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F90" s="6" t="str">
+        <x:v>本硕履历、博士学校专业年份、全部导师均未披露。所属付平团队不等于师承。；原网页仅披露成果总量未逐篇列示；本批仅补可核共同作者官方书目，不代表无论文。；精选成果不是全部论文全集；原始缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G90" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="64" customHeight="1">
+      <x:c r="A91" s="6" t="str">
+        <x:v>马云彤</x:v>
+      </x:c>
+      <x:c r="B91" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C91" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D91" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mayuntong</x:v>
+      </x:c>
+      <x:c r="E91" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F91" s="6" t="str">
+        <x:v>本科、硕士授位院校专业年份、博士经历是否存在、全部导师及分段任职未知。；同名期刊编辑/图情领域马云彤不能合并；未采用其硕士信息。当前工学硕士来自本校研究所本人简介。；精选成果不是全部论文全集；原始缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G91" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="64" customHeight="1">
+      <x:c r="A92" s="6" t="str">
+        <x:v>刘兆庆</x:v>
+      </x:c>
+      <x:c r="B92" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C92" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D92" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuzhaoqing</x:v>
+      </x:c>
+      <x:c r="E92" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F92" s="6" t="str">
+        <x:v>本硕授位与各阶段专业、本人导师未确证，乔立岩团队关系不作师承。；助理研究员结束原文42003.07无效保留；不能据相邻讲师起点擅称准确结束日期。；研究所/本人官网未逐项论文列表，另核1篇DOAJ书目；ATML候选原期刊返回420未作为已读论文加入。；精选成果不是全部论文全集；原始缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G92" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="64" customHeight="1">
+      <x:c r="A93" s="6" t="str">
+        <x:v>刘旺</x:v>
+      </x:c>
+      <x:c r="B93" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C93" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D93" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuwang</x:v>
+      </x:c>
+      <x:c r="E93" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F93" s="6" t="str">
+        <x:v>本人本硕授位明确性、各阶段及博士后导师无直接证据；孙圣和合著不是本人导师证明。；博士后结束月、讲师及副教授开始月中英文不一致，当前取中文不称无争议日期。；精选成果不是全部论文全集；原始缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G93" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="64" customHeight="1">
+      <x:c r="A94" s="6" t="str">
+        <x:v>邹昕光</x:v>
+      </x:c>
+      <x:c r="B94" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C94" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D94" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zouxinguang</x:v>
+      </x:c>
+      <x:c r="E94" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F94" s="6" t="str">
+        <x:v>本硕授位明确性、学位导师、分段任职日期尚未公开核实；周荻为合著者不自动作为导师。；精选成果不是全部论文全集；原始缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G94" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="64" customHeight="1">
+      <x:c r="A95" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B95" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C95" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D95" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/songyuchen</x:v>
+      </x:c>
+      <x:c r="E95" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F95" s="6" t="str">
+        <x:v>没有独立硕士学历条目，不填造硕士经历。博士学习结束、毕业与英文授位年不同保留。；精选成果不是全部论文全集；原始缓存不公开。；博士日期口径：中文学习结束为2021-11，导师名录毕业年为2021，英文授位年为2022；分别保留，不将学习结束日当作授位日。</x:v>
+      </x:c>
+      <x:c r="G95" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="64" customHeight="1">
+      <x:c r="A96" s="6" t="str">
+        <x:v>王本宽</x:v>
+      </x:c>
+      <x:c r="B96" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C96" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D96" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangbenkuan</x:v>
+      </x:c>
+      <x:c r="E96" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F96" s="6" t="str">
+        <x:v>仅公布成果总量和ResearchGate入口，无逐篇书目；导师未直接披露，彭宇和刘大同为团队负责人不等于学位导师。；精选成果不是全部论文全集；原始缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G96" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="64" customHeight="1">
+      <x:c r="A97" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B97" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C97" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D97" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaotianyu</x:v>
+      </x:c>
+      <x:c r="E97" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F97" s="6" t="str">
+        <x:v>杨京礼官方已毕业博士生列表列本人2018–2023；未明确主导师/共同指导，作为候选保留不入师承主图。；精选成果不是全部论文全集；原始缓存不公开。；首篇中文论文Crossref请求429未重试；仅保留官网书目，不称DOI独立核验。；待核指导关系（不计师承）：杨京礼；教师官网已毕业博士生列表列本人及论文/毕业期，但未明确该条主导师或联合指导角色，暂不纳入已核导师。；成果年份差异：Analog Circuit Test Point Selection Method for Fault Diagnosis Based on Deep Reinforcement Learning；官网年份2025，Crossref 登记日期2026-01，差异原因未核实。</x:v>
+      </x:c>
+      <x:c r="G97" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="64" customHeight="1">
+      <x:c r="A98" s="6" t="str">
+        <x:v>尉志良</x:v>
+      </x:c>
+      <x:c r="B98" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C98" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D98" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WeiZhiliang</x:v>
+      </x:c>
+      <x:c r="E98" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F98" s="6" t="str">
+        <x:v>无硕士经历不补造；本科学位授予、学位导师和逐篇论文未知。隶属彭喜元/乔立岩课题组不等于师承。；精选成果不是全部论文全集；原始缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G98" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="64" customHeight="1">
+      <x:c r="A99" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B99" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C99" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D99" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/changyongqi</x:v>
+      </x:c>
+      <x:c r="E99" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F99" s="6" t="str">
+        <x:v>学位与联合培养导师未明确；不得从沈毅/合著者推导师。；精选成果不是全部论文全集；原始缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G99" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="64" customHeight="1">
+      <x:c r="A100" s="6" t="str">
+        <x:v>王俊凯</x:v>
+      </x:c>
+      <x:c r="B100" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C100" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D100" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WangJunkai</x:v>
+      </x:c>
+      <x:c r="E100" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F100" s="6" t="str">
+        <x:v>本科硕士经历未披露；林连雷博士生栏列本人2025届博士论文，指导角色未明确，候选不入主图。；精选成果不是全部论文全集；原始缓存不公开。；待核指导关系（不计师承）：林连雷；教师官网博士生栏目列本人及论文/毕业期，但未明确该条主导师或联合指导角色，暂不纳入已核导师。；主页身份映射：名录原链接为同名空白学院条目；独立本人主页姓名、HIT电信测控单位与研究所教师目录一致，未声称两个URL互相重定向。</x:v>
+      </x:c>
+      <x:c r="G100" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="64" customHeight="1">
+      <x:c r="A101" s="6" t="str">
+        <x:v>姚博文</x:v>
+      </x:c>
+      <x:c r="B101" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C101" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D101" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yaobowen</x:v>
+      </x:c>
+      <x:c r="E101" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F101" s="6" t="str">
+        <x:v>总述三个学位持有已披露，但逐项授位院校/年仅按学习序列暂对应，确证状态留空；未披露导师或逐篇论文。；精选成果不是全部论文全集；原始缓存不公开。；主页身份映射：名录原链接为同名空白学院条目；独立本人主页姓名、HIT电信测控单位与研究所教师目录一致，未声称两个URL互相重定向。；学士、硕士、博士层次仅由总述与学习顺序暂对应，三条授位状态均未知；不参与已核本科985、硕士或博士地域筛选。</x:v>
+      </x:c>
+      <x:c r="G101" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="64" customHeight="1">
+      <x:c r="A102" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B102" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C102" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D102" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangchangdong</x:v>
+      </x:c>
+      <x:c r="E102" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F102" s="6" t="str">
+        <x:v>本科硕士未知；博士专业、NTU联合培养起讫、两次访问起讫、博士后起讫均未知；NTU不统计为国外博士授位。；精选成果不是全部论文全集；原始缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G102" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="64" customHeight="1">
+      <x:c r="A103" s="6" t="str">
+        <x:v>吴艳</x:v>
+      </x:c>
+      <x:c r="B103" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C103" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D103" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WuYan</x:v>
+      </x:c>
+      <x:c r="E103" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F103" s="6" t="str">
+        <x:v>本硕授位明确性和导师未知；没有博士经历，不补造。教材第二条题名疑似字误未修猜。；精选成果不是全部论文全集；原始缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G103" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="64" customHeight="1">
+      <x:c r="A104" s="6" t="str">
+        <x:v>郑文斌</x:v>
+      </x:c>
+      <x:c r="B104" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C104" s="6" t="str">
+        <x:v>电子与信息工程学院·测控工程系</x:v>
+      </x:c>
+      <x:c r="D104" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhengwenbin</x:v>
+      </x:c>
+      <x:c r="E104" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F104" s="6" t="str">
+        <x:v>学位导师和分段任职未知；付平仅团队负责人不作导师。官方仅书籍逐项元数据，无逐篇论文，论文总量不等于可逐篇核验。；精选成果不是全部论文全集；原始缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G104" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda1c1d8997ea481e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8293c13b76e848a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28857,10 +29317,4602 @@
         <x:v>https://homepage.hit.edu.cn/zhangjingchao</x:v>
       </x:c>
     </x:row>
+    <x:row r="658" ht="64" customHeight="1">
+      <x:c r="A658" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B658" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C658" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D658" s="6" t="str">
+        <x:v>哈尔滨工业大学（威海）</x:v>
+      </x:c>
+      <x:c r="E658" s="6" t="str">
+        <x:v>2005-08</x:v>
+      </x:c>
+      <x:c r="F658" s="6" t="str">
+        <x:v>2009-07</x:v>
+      </x:c>
+      <x:c r="G658" s="6" t="str">
+        <x:v>测控技术与仪器</x:v>
+      </x:c>
+      <x:c r="H658" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I658" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J658" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K658" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L658" s="6" t="str"/>
+      <x:c r="M658" s="7" t="str"/>
+      <x:c r="N658" s="6" t="str"/>
+      <x:c r="O658" s="6" t="str">
+        <x:v>教育经历仅列学士标签，未读到明确授位叙述，授位null。</x:v>
+      </x:c>
+      <x:c r="P658" s="6" t="str">
+        <x:v>按机构所在地标准化，不代表国籍；访学、博士后不计学位。</x:v>
+      </x:c>
+      <x:c r="Q658" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/weidebao?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="659" ht="64" customHeight="1">
+      <x:c r="A659" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B659" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C659" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D659" s="6" t="str">
+        <x:v>哈尔滨工业大学（威海）</x:v>
+      </x:c>
+      <x:c r="E659" s="6" t="str">
+        <x:v>2009-09</x:v>
+      </x:c>
+      <x:c r="F659" s="6" t="str">
+        <x:v>2011-07</x:v>
+      </x:c>
+      <x:c r="G659" s="6" t="str">
+        <x:v>电气工程</x:v>
+      </x:c>
+      <x:c r="H659" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I659" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J659" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K659" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L659" s="6" t="str"/>
+      <x:c r="M659" s="7" t="str"/>
+      <x:c r="N659" s="6" t="str"/>
+      <x:c r="O659" s="6" t="str">
+        <x:v>官方注明保送；教育经历仅列硕士标签，授位null。</x:v>
+      </x:c>
+      <x:c r="P659" s="6" t="str">
+        <x:v>按机构所在地标准化，不代表国籍；访学、博士后不计学位。</x:v>
+      </x:c>
+      <x:c r="Q659" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/weidebao?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="660" ht="64" customHeight="1">
+      <x:c r="A660" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B660" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C660" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D660" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E660" s="6" t="str">
+        <x:v>2011-09</x:v>
+      </x:c>
+      <x:c r="F660" s="6" t="str">
+        <x:v>2016-06</x:v>
+      </x:c>
+      <x:c r="G660" s="6" t="str">
+        <x:v>仪器科学与技术</x:v>
+      </x:c>
+      <x:c r="H660" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I660" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J660" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K660" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L660" s="6" t="str"/>
+      <x:c r="M660" s="7" t="str"/>
+      <x:c r="N660" s="6" t="str"/>
+      <x:c r="O660" s="6" t="str">
+        <x:v>官方注明推博；中英文简介为工学博士/Ph.D. in Engineering标签，未读到明确received/holds语句，保守授位null。</x:v>
+      </x:c>
+      <x:c r="P660" s="6" t="str">
+        <x:v>按机构所在地标准化，不代表国籍；访学、博士后不计学位。</x:v>
+      </x:c>
+      <x:c r="Q660" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/weidebao?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="661" ht="64" customHeight="1">
+      <x:c r="A661" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B661" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C661" s="6" t="str">
+        <x:v>研究员</x:v>
+      </x:c>
+      <x:c r="D661" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E661" s="6" t="str"/>
+      <x:c r="F661" s="6" t="str"/>
+      <x:c r="G661" s="6" t="str"/>
+      <x:c r="H661" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I661" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J661" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K661" s="6" t="str"/>
+      <x:c r="L661" s="6" t="str"/>
+      <x:c r="M661" s="7" t="str"/>
+      <x:c r="N661" s="6" t="str"/>
+      <x:c r="O661" s="6" t="str"/>
+      <x:c r="P661" s="6" t="str"/>
+      <x:c r="Q661" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/weidebao?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="662" ht="64" customHeight="1">
+      <x:c r="A662" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B662" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C662" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D662" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E662" s="6" t="str"/>
+      <x:c r="F662" s="6" t="str"/>
+      <x:c r="G662" s="6" t="str"/>
+      <x:c r="H662" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I662" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J662" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K662" s="6" t="str"/>
+      <x:c r="L662" s="6" t="str"/>
+      <x:c r="M662" s="7" t="str"/>
+      <x:c r="N662" s="6" t="str"/>
+      <x:c r="O662" s="6" t="str"/>
+      <x:c r="P662" s="6" t="str"/>
+      <x:c r="Q662" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/weidebao?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="663" ht="64" customHeight="1">
+      <x:c r="A663" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B663" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C663" s="6" t="str">
+        <x:v>副所长</x:v>
+      </x:c>
+      <x:c r="D663" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院自动化测试与控制研究所</x:v>
+      </x:c>
+      <x:c r="E663" s="6" t="str"/>
+      <x:c r="F663" s="6" t="str"/>
+      <x:c r="G663" s="6" t="str"/>
+      <x:c r="H663" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I663" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J663" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K663" s="6" t="str"/>
+      <x:c r="L663" s="6" t="str"/>
+      <x:c r="M663" s="7" t="str"/>
+      <x:c r="N663" s="6" t="str"/>
+      <x:c r="O663" s="6" t="str"/>
+      <x:c r="P663" s="6" t="str"/>
+      <x:c r="Q663" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/weidebao?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="664" ht="64" customHeight="1">
+      <x:c r="A664" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B664" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C664" s="6" t="str">
+        <x:v>副主任</x:v>
+      </x:c>
+      <x:c r="D664" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院测控工程系</x:v>
+      </x:c>
+      <x:c r="E664" s="6" t="str"/>
+      <x:c r="F664" s="6" t="str"/>
+      <x:c r="G664" s="6" t="str"/>
+      <x:c r="H664" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I664" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J664" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K664" s="6" t="str"/>
+      <x:c r="L664" s="6" t="str"/>
+      <x:c r="M664" s="7" t="str"/>
+      <x:c r="N664" s="6" t="str"/>
+      <x:c r="O664" s="6" t="str">
+        <x:v>分管研究生工作；开始日期未披露。</x:v>
+      </x:c>
+      <x:c r="P664" s="6" t="str"/>
+      <x:c r="Q664" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/weidebao?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="665" ht="64" customHeight="1">
+      <x:c r="A665" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B665" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C665" s="6" t="str">
+        <x:v>副研究员</x:v>
+      </x:c>
+      <x:c r="D665" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E665" s="6" t="str"/>
+      <x:c r="F665" s="6" t="str"/>
+      <x:c r="G665" s="6" t="str"/>
+      <x:c r="H665" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I665" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J665" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K665" s="6" t="str"/>
+      <x:c r="L665" s="6" t="str"/>
+      <x:c r="M665" s="7" t="str"/>
+      <x:c r="N665" s="6" t="str"/>
+      <x:c r="O665" s="6" t="str">
+        <x:v>2023-06-12学院新闻当时职称；准确任职起止日期未披露，不把新闻日期当入职或离职日期。</x:v>
+      </x:c>
+      <x:c r="P665" s="6" t="str"/>
+      <x:c r="Q665" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/2023/0612/c9262a313766/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="666" ht="64" customHeight="1">
+      <x:c r="A666" s="6" t="str">
+        <x:v>刘晓东</x:v>
+      </x:c>
+      <x:c r="B666" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C666" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D666" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E666" s="6" t="str"/>
+      <x:c r="F666" s="6" t="str">
+        <x:v>2003</x:v>
+      </x:c>
+      <x:c r="G666" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H666" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I666" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J666" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K666" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L666" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M666" s="7" t="str"/>
+      <x:c r="N666" s="6" t="str"/>
+      <x:c r="O666" s="6" t="str">
+        <x:v>英文Basic Information明确He received the Ph.D. degree ... from the Harbin Institute of Technology ... in 2003；起始日期未披露。</x:v>
+      </x:c>
+      <x:c r="P666" s="6" t="str">
+        <x:v>按机构所在地标准化，不代表国籍；访学、博士后不计学位。</x:v>
+      </x:c>
+      <x:c r="Q666" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuxiaodong?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="667" ht="64" customHeight="1">
+      <x:c r="A667" s="6" t="str">
+        <x:v>刘晓东</x:v>
+      </x:c>
+      <x:c r="B667" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C667" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D667" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E667" s="6" t="str"/>
+      <x:c r="F667" s="6" t="str"/>
+      <x:c r="G667" s="6" t="str"/>
+      <x:c r="H667" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I667" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J667" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K667" s="6" t="str"/>
+      <x:c r="L667" s="6" t="str"/>
+      <x:c r="M667" s="7" t="str"/>
+      <x:c r="N667" s="6" t="str"/>
+      <x:c r="O667" s="6" t="str"/>
+      <x:c r="P667" s="6" t="str"/>
+      <x:c r="Q667" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuxiaodong?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="668" ht="64" customHeight="1">
+      <x:c r="A668" s="6" t="str">
+        <x:v>刘晓东</x:v>
+      </x:c>
+      <x:c r="B668" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C668" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D668" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E668" s="6" t="str"/>
+      <x:c r="F668" s="6" t="str"/>
+      <x:c r="G668" s="6" t="str"/>
+      <x:c r="H668" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I668" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J668" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K668" s="6" t="str"/>
+      <x:c r="L668" s="6" t="str"/>
+      <x:c r="M668" s="7" t="str"/>
+      <x:c r="N668" s="6" t="str"/>
+      <x:c r="O668" s="6" t="str"/>
+      <x:c r="P668" s="6" t="str"/>
+      <x:c r="Q668" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuxiaodong?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="669" ht="64" customHeight="1">
+      <x:c r="A669" s="6" t="str">
+        <x:v>孙震</x:v>
+      </x:c>
+      <x:c r="B669" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C669" s="6" t="str">
+        <x:v>工学博士</x:v>
+      </x:c>
+      <x:c r="D669" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E669" s="6" t="str"/>
+      <x:c r="F669" s="6" t="str"/>
+      <x:c r="G669" s="6" t="str"/>
+      <x:c r="H669" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I669" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J669" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K669" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L669" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M669" s="7" t="str"/>
+      <x:c r="N669" s="6" t="str"/>
+      <x:c r="O669" s="6" t="str">
+        <x:v>英文Basic Information明确holds a Doctor of Engineering degree from Harbin Institute of Technology；学科、起止日期及更早学历未披露，不借当前学科补专业。</x:v>
+      </x:c>
+      <x:c r="P669" s="6" t="str">
+        <x:v>按机构所在地标准化，不代表国籍；访学、博士后不计学位。</x:v>
+      </x:c>
+      <x:c r="Q669" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/sunzhen?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="670" ht="64" customHeight="1">
+      <x:c r="A670" s="6" t="str">
+        <x:v>孙震</x:v>
+      </x:c>
+      <x:c r="B670" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C670" s="6" t="str">
+        <x:v>助教、讲师、副教授（历任）</x:v>
+      </x:c>
+      <x:c r="D670" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E670" s="6" t="str">
+        <x:v>1994-07</x:v>
+      </x:c>
+      <x:c r="F670" s="6" t="str"/>
+      <x:c r="G670" s="6" t="str"/>
+      <x:c r="H670" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I670" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J670" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K670" s="6" t="str"/>
+      <x:c r="L670" s="6" t="str"/>
+      <x:c r="M670" s="7" t="str"/>
+      <x:c r="N670" s="6" t="str"/>
+      <x:c r="O670" s="6" t="str">
+        <x:v>官方将1994.07至今合并列历任三种职称；不拆分未知晋升日期。</x:v>
+      </x:c>
+      <x:c r="P670" s="6" t="str"/>
+      <x:c r="Q670" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/sunzhen?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="671" ht="64" customHeight="1">
+      <x:c r="A671" s="6" t="str">
+        <x:v>孙震</x:v>
+      </x:c>
+      <x:c r="B671" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C671" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D671" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E671" s="6" t="str"/>
+      <x:c r="F671" s="6" t="str"/>
+      <x:c r="G671" s="6" t="str"/>
+      <x:c r="H671" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I671" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J671" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K671" s="6" t="str"/>
+      <x:c r="L671" s="6" t="str"/>
+      <x:c r="M671" s="7" t="str"/>
+      <x:c r="N671" s="6" t="str"/>
+      <x:c r="O671" s="6" t="str">
+        <x:v>当前职称在简介明确，职称起始日期未知；不把1994-07认定为副教授起始。</x:v>
+      </x:c>
+      <x:c r="P671" s="6" t="str"/>
+      <x:c r="Q671" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/sunzhen?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="672" ht="64" customHeight="1">
+      <x:c r="A672" s="6" t="str">
+        <x:v>孙震</x:v>
+      </x:c>
+      <x:c r="B672" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C672" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D672" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E672" s="6" t="str"/>
+      <x:c r="F672" s="6" t="str"/>
+      <x:c r="G672" s="6" t="str"/>
+      <x:c r="H672" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I672" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J672" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K672" s="6" t="str"/>
+      <x:c r="L672" s="6" t="str"/>
+      <x:c r="M672" s="7" t="str"/>
+      <x:c r="N672" s="6" t="str"/>
+      <x:c r="O672" s="6" t="str"/>
+      <x:c r="P672" s="6" t="str"/>
+      <x:c r="Q672" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/sunzhen?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="673" ht="64" customHeight="1">
+      <x:c r="A673" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B673" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C673" s="6" t="str">
+        <x:v>工学学士</x:v>
+      </x:c>
+      <x:c r="D673" s="6" t="str">
+        <x:v>重庆大学</x:v>
+      </x:c>
+      <x:c r="E673" s="6" t="str">
+        <x:v>1989-09</x:v>
+      </x:c>
+      <x:c r="F673" s="6" t="str">
+        <x:v>1993-07</x:v>
+      </x:c>
+      <x:c r="G673" s="6" t="str">
+        <x:v>无线电技术</x:v>
+      </x:c>
+      <x:c r="H673" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I673" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J673" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K673" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L673" s="6" t="str"/>
+      <x:c r="M673" s="7" t="str"/>
+      <x:c r="N673" s="6" t="str"/>
+      <x:c r="O673" s="6" t="str">
+        <x:v>教育经历仅列学士，缺明确授位叙述，授位null。</x:v>
+      </x:c>
+      <x:c r="P673" s="6" t="str">
+        <x:v>按机构所在地标准化，不代表国籍；访学、博士后不计学位。</x:v>
+      </x:c>
+      <x:c r="Q673" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ljzsylmy?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="674" ht="64" customHeight="1">
+      <x:c r="A674" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B674" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C674" s="6" t="str">
+        <x:v>工学硕士</x:v>
+      </x:c>
+      <x:c r="D674" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E674" s="6" t="str">
+        <x:v>1998-09</x:v>
+      </x:c>
+      <x:c r="F674" s="6" t="str">
+        <x:v>2001-07</x:v>
+      </x:c>
+      <x:c r="G674" s="6" t="str">
+        <x:v>测试计量技术及仪器</x:v>
+      </x:c>
+      <x:c r="H674" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I674" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J674" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K674" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L674" s="6" t="str"/>
+      <x:c r="M674" s="7" t="str"/>
+      <x:c r="N674" s="6" t="str"/>
+      <x:c r="O674" s="6" t="str">
+        <x:v>教育经历仅列硕士，缺明确授位叙述，授位null。</x:v>
+      </x:c>
+      <x:c r="P674" s="6" t="str">
+        <x:v>按机构所在地标准化，不代表国籍；访学、博士后不计学位。</x:v>
+      </x:c>
+      <x:c r="Q674" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ljzsylmy?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="675" ht="64" customHeight="1">
+      <x:c r="A675" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B675" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C675" s="6" t="str">
+        <x:v>工学博士</x:v>
+      </x:c>
+      <x:c r="D675" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E675" s="6" t="str">
+        <x:v>2005-08</x:v>
+      </x:c>
+      <x:c r="F675" s="6" t="str">
+        <x:v>2009-07</x:v>
+      </x:c>
+      <x:c r="G675" s="6" t="str">
+        <x:v>测试计量技术及仪器</x:v>
+      </x:c>
+      <x:c r="H675" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I675" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J675" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K675" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L675" s="6" t="str"/>
+      <x:c r="M675" s="7" t="str"/>
+      <x:c r="N675" s="6" t="str"/>
+      <x:c r="O675" s="6" t="str">
+        <x:v>教育经历和简介列工学博士/Doctor of Engineering，英文页头又为Eng.D；未将学位标签当作明确授位证明，授位null，英文学位缩写不擅自改成Ph.D。</x:v>
+      </x:c>
+      <x:c r="P675" s="6" t="str">
+        <x:v>按机构所在地标准化，不代表国籍；访学、博士后不计学位。</x:v>
+      </x:c>
+      <x:c r="Q675" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ljzsylmy?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="676" ht="64" customHeight="1">
+      <x:c r="A676" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B676" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C676" s="6" t="str">
+        <x:v>技术员</x:v>
+      </x:c>
+      <x:c r="D676" s="6" t="str">
+        <x:v>哈尔滨市无线电通信有限公司</x:v>
+      </x:c>
+      <x:c r="E676" s="6" t="str">
+        <x:v>1993-07</x:v>
+      </x:c>
+      <x:c r="F676" s="6" t="str">
+        <x:v>1998-07</x:v>
+      </x:c>
+      <x:c r="G676" s="6" t="str"/>
+      <x:c r="H676" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I676" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J676" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K676" s="6" t="str"/>
+      <x:c r="L676" s="6" t="str"/>
+      <x:c r="M676" s="7" t="str"/>
+      <x:c r="N676" s="6" t="str"/>
+      <x:c r="O676" s="6" t="str">
+        <x:v>只保留雇主名称，省略原文街道地址。</x:v>
+      </x:c>
+      <x:c r="P676" s="6" t="str"/>
+      <x:c r="Q676" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ljzsylmy?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="677" ht="64" customHeight="1">
+      <x:c r="A677" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B677" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C677" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D677" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E677" s="6" t="str">
+        <x:v>2001-02</x:v>
+      </x:c>
+      <x:c r="F677" s="6" t="str">
+        <x:v>2008-07</x:v>
+      </x:c>
+      <x:c r="G677" s="6" t="str"/>
+      <x:c r="H677" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I677" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J677" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K677" s="6" t="str"/>
+      <x:c r="L677" s="6" t="str"/>
+      <x:c r="M677" s="7" t="str"/>
+      <x:c r="N677" s="6" t="str"/>
+      <x:c r="O677" s="6" t="str"/>
+      <x:c r="P677" s="6" t="str"/>
+      <x:c r="Q677" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ljzsylmy?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="678" ht="64" customHeight="1">
+      <x:c r="A678" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B678" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C678" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D678" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E678" s="6" t="str">
+        <x:v>2008-07</x:v>
+      </x:c>
+      <x:c r="F678" s="6" t="str"/>
+      <x:c r="G678" s="6" t="str"/>
+      <x:c r="H678" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I678" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J678" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K678" s="6" t="str"/>
+      <x:c r="L678" s="6" t="str"/>
+      <x:c r="M678" s="7" t="str"/>
+      <x:c r="N678" s="6" t="str"/>
+      <x:c r="O678" s="6" t="str">
+        <x:v>官方自2008-07即采用现学院名称，按原文保留，不据学院改组时间改写。</x:v>
+      </x:c>
+      <x:c r="P678" s="6" t="str"/>
+      <x:c r="Q678" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ljzsylmy?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="679" ht="64" customHeight="1">
+      <x:c r="A679" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B679" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C679" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D679" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E679" s="6" t="str">
+        <x:v>2008-07</x:v>
+      </x:c>
+      <x:c r="F679" s="6" t="str"/>
+      <x:c r="G679" s="6" t="str"/>
+      <x:c r="H679" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I679" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J679" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K679" s="6" t="str"/>
+      <x:c r="L679" s="6" t="str"/>
+      <x:c r="M679" s="7" t="str"/>
+      <x:c r="N679" s="6" t="str"/>
+      <x:c r="O679" s="6" t="str"/>
+      <x:c r="P679" s="6" t="str"/>
+      <x:c r="Q679" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ljzsylmy?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="680" ht="64" customHeight="1">
+      <x:c r="A680" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B680" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C680" s="6" t="str">
+        <x:v>副所长</x:v>
+      </x:c>
+      <x:c r="D680" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院自动化测试与控制研究所</x:v>
+      </x:c>
+      <x:c r="E680" s="6" t="str"/>
+      <x:c r="F680" s="6" t="str"/>
+      <x:c r="G680" s="6" t="str"/>
+      <x:c r="H680" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I680" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J680" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K680" s="6" t="str"/>
+      <x:c r="L680" s="6" t="str"/>
+      <x:c r="M680" s="7" t="str"/>
+      <x:c r="N680" s="6" t="str"/>
+      <x:c r="O680" s="6" t="str"/>
+      <x:c r="P680" s="6" t="str"/>
+      <x:c r="Q680" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ljzsylmy?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="681" ht="64" customHeight="1">
+      <x:c r="A681" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B681" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C681" s="6" t="str">
+        <x:v>副所长</x:v>
+      </x:c>
+      <x:c r="D681" s="6" t="str">
+        <x:v>哈尔滨工业大学郑州研究院智能测控研究所</x:v>
+      </x:c>
+      <x:c r="E681" s="6" t="str"/>
+      <x:c r="F681" s="6" t="str"/>
+      <x:c r="G681" s="6" t="str"/>
+      <x:c r="H681" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I681" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J681" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K681" s="6" t="str"/>
+      <x:c r="L681" s="6" t="str"/>
+      <x:c r="M681" s="7" t="str"/>
+      <x:c r="N681" s="6" t="str"/>
+      <x:c r="O681" s="6" t="str"/>
+      <x:c r="P681" s="6" t="str"/>
+      <x:c r="Q681" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ljzsylmy?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="682" ht="64" customHeight="1">
+      <x:c r="A682" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B682" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C682" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D682" s="6" t="str">
+        <x:v>西安电子科技大学</x:v>
+      </x:c>
+      <x:c r="E682" s="6" t="str">
+        <x:v>1987-09</x:v>
+      </x:c>
+      <x:c r="F682" s="6" t="str">
+        <x:v>1991-07</x:v>
+      </x:c>
+      <x:c r="G682" s="6" t="str">
+        <x:v>物理学</x:v>
+      </x:c>
+      <x:c r="H682" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I682" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J682" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K682" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L682" s="6" t="str"/>
+      <x:c r="M682" s="7" t="str"/>
+      <x:c r="N682" s="6" t="str"/>
+      <x:c r="O682" s="6" t="str">
+        <x:v>只列学士教育标签，授位null；本科导师陈陆君为原文明确。</x:v>
+      </x:c>
+      <x:c r="P682" s="6" t="str">
+        <x:v>按机构所在地标准化，不代表国籍；访学、博士后不计学位。</x:v>
+      </x:c>
+      <x:c r="Q682" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="683" ht="64" customHeight="1">
+      <x:c r="A683" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B683" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C683" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D683" s="6" t="str">
+        <x:v>西安电子科技大学</x:v>
+      </x:c>
+      <x:c r="E683" s="6" t="str">
+        <x:v>1991-09</x:v>
+      </x:c>
+      <x:c r="F683" s="6" t="str">
+        <x:v>1994-03</x:v>
+      </x:c>
+      <x:c r="G683" s="6" t="str">
+        <x:v>无线电物理学</x:v>
+      </x:c>
+      <x:c r="H683" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I683" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J683" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K683" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L683" s="6" t="str"/>
+      <x:c r="M683" s="7" t="str"/>
+      <x:c r="N683" s="6" t="str"/>
+      <x:c r="O683" s="6" t="str">
+        <x:v>只列硕士教育标签，授位null；硕士导师王一平为原文明确。</x:v>
+      </x:c>
+      <x:c r="P683" s="6" t="str">
+        <x:v>按机构所在地标准化，不代表国籍；访学、博士后不计学位。</x:v>
+      </x:c>
+      <x:c r="Q683" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="684" ht="64" customHeight="1">
+      <x:c r="A684" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B684" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C684" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D684" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E684" s="6" t="str">
+        <x:v>2002-09</x:v>
+      </x:c>
+      <x:c r="F684" s="6" t="str">
+        <x:v>2007-07</x:v>
+      </x:c>
+      <x:c r="G684" s="6" t="str">
+        <x:v>仪器科学与技术</x:v>
+      </x:c>
+      <x:c r="H684" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I684" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J684" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K684" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L684" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M684" s="7" t="str"/>
+      <x:c r="N684" s="6" t="str"/>
+      <x:c r="O684" s="6" t="str">
+        <x:v>英文Basic Information明确with a PhD in Engineering，与唯一博士教育经历对应；官网另列本人2007年学位论文。日期仍是教育阶段起止，不声称精确学位授予日。</x:v>
+      </x:c>
+      <x:c r="P684" s="6" t="str">
+        <x:v>按机构所在地标准化，不代表国籍；访学、博士后不计学位。</x:v>
+      </x:c>
+      <x:c r="Q684" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="685" ht="64" customHeight="1">
+      <x:c r="A685" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B685" s="6" t="str">
+        <x:v>postdoctoral_research</x:v>
+      </x:c>
+      <x:c r="C685" s="6" t="str"/>
+      <x:c r="D685" s="6" t="str">
+        <x:v>中国科学院电子学研究所</x:v>
+      </x:c>
+      <x:c r="E685" s="6" t="str">
+        <x:v>2008-01</x:v>
+      </x:c>
+      <x:c r="F685" s="6" t="str">
+        <x:v>2011-09</x:v>
+      </x:c>
+      <x:c r="G685" s="6" t="str"/>
+      <x:c r="H685" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I685" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J685" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K685" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L685" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M685" s="7" t="str"/>
+      <x:c r="N685" s="6" t="str"/>
+      <x:c r="O685" s="6" t="str">
+        <x:v>工作经历明确博士后，非授位事件；未披露博士后合作导师。</x:v>
+      </x:c>
+      <x:c r="P685" s="6" t="str">
+        <x:v>按机构所在地标准化，不代表国籍；访学、博士后不计学位。</x:v>
+      </x:c>
+      <x:c r="Q685" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="686" ht="64" customHeight="1">
+      <x:c r="A686" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B686" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C686" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D686" s="6" t="str">
+        <x:v>哈尔滨工业大学电气工程及自动化学院</x:v>
+      </x:c>
+      <x:c r="E686" s="6" t="str">
+        <x:v>1998-02</x:v>
+      </x:c>
+      <x:c r="F686" s="6" t="str">
+        <x:v>2004-11</x:v>
+      </x:c>
+      <x:c r="G686" s="6" t="str"/>
+      <x:c r="H686" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I686" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J686" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K686" s="6" t="str"/>
+      <x:c r="L686" s="6" t="str"/>
+      <x:c r="M686" s="7" t="str"/>
+      <x:c r="N686" s="6" t="str"/>
+      <x:c r="O686" s="6" t="str"/>
+      <x:c r="P686" s="6" t="str"/>
+      <x:c r="Q686" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="687" ht="64" customHeight="1">
+      <x:c r="A687" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B687" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C687" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D687" s="6" t="str">
+        <x:v>哈尔滨工业大学电气工程及自动化学院</x:v>
+      </x:c>
+      <x:c r="E687" s="6" t="str">
+        <x:v>2004-12</x:v>
+      </x:c>
+      <x:c r="F687" s="6" t="str">
+        <x:v>2018-09</x:v>
+      </x:c>
+      <x:c r="G687" s="6" t="str"/>
+      <x:c r="H687" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I687" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J687" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K687" s="6" t="str"/>
+      <x:c r="L687" s="6" t="str"/>
+      <x:c r="M687" s="7" t="str"/>
+      <x:c r="N687" s="6" t="str"/>
+      <x:c r="O687" s="6" t="str"/>
+      <x:c r="P687" s="6" t="str"/>
+      <x:c r="Q687" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="688" ht="64" customHeight="1">
+      <x:c r="A688" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B688" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C688" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D688" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E688" s="6" t="str">
+        <x:v>2018-10</x:v>
+      </x:c>
+      <x:c r="F688" s="6" t="str"/>
+      <x:c r="G688" s="6" t="str"/>
+      <x:c r="H688" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I688" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J688" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K688" s="6" t="str"/>
+      <x:c r="L688" s="6" t="str"/>
+      <x:c r="M688" s="7" t="str"/>
+      <x:c r="N688" s="6" t="str"/>
+      <x:c r="O688" s="6" t="str"/>
+      <x:c r="P688" s="6" t="str"/>
+      <x:c r="Q688" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="689" ht="64" customHeight="1">
+      <x:c r="A689" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B689" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C689" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D689" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E689" s="6" t="str"/>
+      <x:c r="F689" s="6" t="str"/>
+      <x:c r="G689" s="6" t="str"/>
+      <x:c r="H689" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I689" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J689" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K689" s="6" t="str"/>
+      <x:c r="L689" s="6" t="str"/>
+      <x:c r="M689" s="7" t="str"/>
+      <x:c r="N689" s="6" t="str"/>
+      <x:c r="O689" s="6" t="str"/>
+      <x:c r="P689" s="6" t="str"/>
+      <x:c r="Q689" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="690" ht="64" customHeight="1">
+      <x:c r="A690" s="6" t="str">
+        <x:v>尹洪涛</x:v>
+      </x:c>
+      <x:c r="B690" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C690" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D690" s="6" t="str"/>
+      <x:c r="E690" s="6" t="str"/>
+      <x:c r="F690" s="6" t="str"/>
+      <x:c r="G690" s="6" t="str"/>
+      <x:c r="H690" s="6" t="str"/>
+      <x:c r="I690" s="6" t="str"/>
+      <x:c r="J690" s="6" t="str"/>
+      <x:c r="K690" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L690" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M690" s="7" t="str"/>
+      <x:c r="N690" s="6" t="str"/>
+      <x:c r="O690" s="6" t="str">
+        <x:v>本人中英文简介明确工学博士，但授位院校、年份、专业未披露，不用现任院校代填。</x:v>
+      </x:c>
+      <x:c r="P690" s="6" t="str">
+        <x:v>授位学校未知，国家地区和洲未知，不以现任单位补全。</x:v>
+      </x:c>
+      <x:c r="Q690" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yinhongtao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="691" ht="64" customHeight="1">
+      <x:c r="A691" s="6" t="str">
+        <x:v>尹洪涛</x:v>
+      </x:c>
+      <x:c r="B691" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C691" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D691" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E691" s="6" t="str"/>
+      <x:c r="F691" s="6" t="str"/>
+      <x:c r="G691" s="6" t="str"/>
+      <x:c r="H691" s="6" t="str"/>
+      <x:c r="I691" s="6" t="str"/>
+      <x:c r="J691" s="6" t="str"/>
+      <x:c r="K691" s="6" t="str"/>
+      <x:c r="L691" s="6" t="str"/>
+      <x:c r="M691" s="7" t="str"/>
+      <x:c r="N691" s="6" t="str"/>
+      <x:c r="O691" s="6" t="str"/>
+      <x:c r="P691" s="6" t="str"/>
+      <x:c r="Q691" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/2023/0227/c16426a289552/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="692" ht="64" customHeight="1">
+      <x:c r="A692" s="6" t="str">
+        <x:v>马云彤</x:v>
+      </x:c>
+      <x:c r="B692" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C692" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D692" s="6" t="str"/>
+      <x:c r="E692" s="6" t="str"/>
+      <x:c r="F692" s="6" t="str"/>
+      <x:c r="G692" s="6" t="str"/>
+      <x:c r="H692" s="6" t="str"/>
+      <x:c r="I692" s="6" t="str"/>
+      <x:c r="J692" s="6" t="str"/>
+      <x:c r="K692" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L692" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M692" s="7" t="str"/>
+      <x:c r="N692" s="6" t="str"/>
+      <x:c r="O692" s="6" t="str">
+        <x:v>研究所官网明确工学硕士；授位学校、专业和时间未知，不从HIT任职推学历机构。</x:v>
+      </x:c>
+      <x:c r="P692" s="6" t="str">
+        <x:v>授位学校未知，国家地区和洲未知，不以现任单位补全。</x:v>
+      </x:c>
+      <x:c r="Q692" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/2023/0227/c16426a289585/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="693" ht="64" customHeight="1">
+      <x:c r="A693" s="6" t="str">
+        <x:v>马云彤</x:v>
+      </x:c>
+      <x:c r="B693" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C693" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D693" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E693" s="6" t="str"/>
+      <x:c r="F693" s="6" t="str"/>
+      <x:c r="G693" s="6" t="str"/>
+      <x:c r="H693" s="6" t="str"/>
+      <x:c r="I693" s="6" t="str"/>
+      <x:c r="J693" s="6" t="str"/>
+      <x:c r="K693" s="6" t="str"/>
+      <x:c r="L693" s="6" t="str"/>
+      <x:c r="M693" s="7" t="str"/>
+      <x:c r="N693" s="6" t="str"/>
+      <x:c r="O693" s="6" t="str">
+        <x:v>本人中英文主页和研究所官方当前简介均列副教授，开始时间未披露。</x:v>
+      </x:c>
+      <x:c r="P693" s="6" t="str"/>
+      <x:c r="Q693" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mayuntong</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="694" ht="64" customHeight="1">
+      <x:c r="A694" s="6" t="str">
+        <x:v>刘兆庆</x:v>
+      </x:c>
+      <x:c r="B694" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C694" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D694" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E694" s="6" t="str">
+        <x:v>1993-09</x:v>
+      </x:c>
+      <x:c r="F694" s="6" t="str">
+        <x:v>1997-07</x:v>
+      </x:c>
+      <x:c r="G694" s="6" t="str"/>
+      <x:c r="H694" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I694" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J694" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K694" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L694" s="6" t="str"/>
+      <x:c r="M694" s="7" t="str"/>
+      <x:c r="N694" s="6" t="str"/>
+      <x:c r="O694" s="6" t="str">
+        <x:v>教育履历列学士，尚未进一步明确授位。</x:v>
+      </x:c>
+      <x:c r="P694" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q694" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuzhaoqing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="695" ht="64" customHeight="1">
+      <x:c r="A695" s="6" t="str">
+        <x:v>刘兆庆</x:v>
+      </x:c>
+      <x:c r="B695" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C695" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D695" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E695" s="6" t="str">
+        <x:v>2001-09</x:v>
+      </x:c>
+      <x:c r="F695" s="6" t="str">
+        <x:v>2003-07</x:v>
+      </x:c>
+      <x:c r="G695" s="6" t="str"/>
+      <x:c r="H695" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I695" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J695" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K695" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L695" s="6" t="str"/>
+      <x:c r="M695" s="7" t="str"/>
+      <x:c r="N695" s="6" t="str"/>
+      <x:c r="O695" s="6" t="str">
+        <x:v>教育履历列硕士，尚未进一步明确授位。</x:v>
+      </x:c>
+      <x:c r="P695" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q695" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuzhaoqing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="696" ht="64" customHeight="1">
+      <x:c r="A696" s="6" t="str">
+        <x:v>刘兆庆</x:v>
+      </x:c>
+      <x:c r="B696" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C696" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D696" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E696" s="6" t="str">
+        <x:v>2007-09</x:v>
+      </x:c>
+      <x:c r="F696" s="6" t="str">
+        <x:v>2013-04</x:v>
+      </x:c>
+      <x:c r="G696" s="6" t="str"/>
+      <x:c r="H696" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I696" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J696" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K696" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L696" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M696" s="7" t="str"/>
+      <x:c r="N696" s="6" t="str"/>
+      <x:c r="O696" s="6" t="str">
+        <x:v>本人英文明确holds a PhD in Engineering；专业未披露。</x:v>
+      </x:c>
+      <x:c r="P696" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q696" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuzhaoqing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="697" ht="64" customHeight="1">
+      <x:c r="A697" s="6" t="str">
+        <x:v>刘兆庆</x:v>
+      </x:c>
+      <x:c r="B697" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C697" s="6" t="str">
+        <x:v>助理研究员</x:v>
+      </x:c>
+      <x:c r="D697" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E697" s="6" t="str">
+        <x:v>1997-07</x:v>
+      </x:c>
+      <x:c r="F697" s="6" t="str"/>
+      <x:c r="G697" s="6" t="str"/>
+      <x:c r="H697" s="6" t="str"/>
+      <x:c r="I697" s="6" t="str"/>
+      <x:c r="J697" s="6" t="str"/>
+      <x:c r="K697" s="6" t="str"/>
+      <x:c r="L697" s="6" t="str"/>
+      <x:c r="M697" s="7" t="str"/>
+      <x:c r="N697" s="6" t="str"/>
+      <x:c r="O697" s="6" t="str">
+        <x:v>原文终点42003.07无效，不静默修正为2003.07；此为历史任职并非仍任。</x:v>
+      </x:c>
+      <x:c r="P697" s="6" t="str"/>
+      <x:c r="Q697" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuzhaoqing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="698" ht="64" customHeight="1">
+      <x:c r="A698" s="6" t="str">
+        <x:v>刘兆庆</x:v>
+      </x:c>
+      <x:c r="B698" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C698" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D698" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E698" s="6" t="str">
+        <x:v>2003-07</x:v>
+      </x:c>
+      <x:c r="F698" s="6" t="str">
+        <x:v>2014-12</x:v>
+      </x:c>
+      <x:c r="G698" s="6" t="str"/>
+      <x:c r="H698" s="6" t="str"/>
+      <x:c r="I698" s="6" t="str"/>
+      <x:c r="J698" s="6" t="str"/>
+      <x:c r="K698" s="6" t="str"/>
+      <x:c r="L698" s="6" t="str"/>
+      <x:c r="M698" s="7" t="str"/>
+      <x:c r="N698" s="6" t="str"/>
+      <x:c r="O698" s="6" t="str"/>
+      <x:c r="P698" s="6" t="str"/>
+      <x:c r="Q698" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuzhaoqing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="699" ht="64" customHeight="1">
+      <x:c r="A699" s="6" t="str">
+        <x:v>刘兆庆</x:v>
+      </x:c>
+      <x:c r="B699" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C699" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D699" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E699" s="6" t="str">
+        <x:v>2015-01</x:v>
+      </x:c>
+      <x:c r="F699" s="6" t="str"/>
+      <x:c r="G699" s="6" t="str"/>
+      <x:c r="H699" s="6" t="str"/>
+      <x:c r="I699" s="6" t="str"/>
+      <x:c r="J699" s="6" t="str"/>
+      <x:c r="K699" s="6" t="str"/>
+      <x:c r="L699" s="6" t="str"/>
+      <x:c r="M699" s="7" t="str"/>
+      <x:c r="N699" s="6" t="str"/>
+      <x:c r="O699" s="6" t="str"/>
+      <x:c r="P699" s="6" t="str"/>
+      <x:c r="Q699" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuzhaoqing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="700" ht="64" customHeight="1">
+      <x:c r="A700" s="6" t="str">
+        <x:v>刘旺</x:v>
+      </x:c>
+      <x:c r="B700" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C700" s="6" t="str">
+        <x:v>本科</x:v>
+      </x:c>
+      <x:c r="D700" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E700" s="6" t="str">
+        <x:v>1995-09</x:v>
+      </x:c>
+      <x:c r="F700" s="6" t="str">
+        <x:v>1999-07</x:v>
+      </x:c>
+      <x:c r="G700" s="6" t="str">
+        <x:v>测控技术</x:v>
+      </x:c>
+      <x:c r="H700" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I700" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J700" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K700" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L700" s="6" t="str"/>
+      <x:c r="M700" s="7" t="str"/>
+      <x:c r="N700" s="6" t="str"/>
+      <x:c r="O700" s="6" t="str">
+        <x:v>中文本科、英文B.S.教育栏，尚无额外授位陈述；中学经历不纳入职业学术档案。</x:v>
+      </x:c>
+      <x:c r="P700" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q700" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuwang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="701" ht="64" customHeight="1">
+      <x:c r="A701" s="6" t="str">
+        <x:v>刘旺</x:v>
+      </x:c>
+      <x:c r="B701" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C701" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D701" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E701" s="6" t="str">
+        <x:v>1999-09</x:v>
+      </x:c>
+      <x:c r="F701" s="6" t="str">
+        <x:v>2001-07</x:v>
+      </x:c>
+      <x:c r="G701" s="6" t="str">
+        <x:v>测试计量技术及仪器</x:v>
+      </x:c>
+      <x:c r="H701" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I701" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J701" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K701" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L701" s="6" t="str"/>
+      <x:c r="M701" s="7" t="str"/>
+      <x:c r="N701" s="6" t="str"/>
+      <x:c r="O701" s="6" t="str">
+        <x:v>英文专业Instrumentation Science and Technology，保留中文细分专业。</x:v>
+      </x:c>
+      <x:c r="P701" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q701" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuwang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="702" ht="64" customHeight="1">
+      <x:c r="A702" s="6" t="str">
+        <x:v>刘旺</x:v>
+      </x:c>
+      <x:c r="B702" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C702" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D702" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E702" s="6" t="str">
+        <x:v>2001-09</x:v>
+      </x:c>
+      <x:c r="F702" s="6" t="str">
+        <x:v>2005-12</x:v>
+      </x:c>
+      <x:c r="G702" s="6" t="str">
+        <x:v>仪器科学与技术</x:v>
+      </x:c>
+      <x:c r="H702" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I702" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J702" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K702" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L702" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M702" s="7" t="str"/>
+      <x:c r="N702" s="6" t="str"/>
+      <x:c r="O702" s="6" t="str">
+        <x:v>本人简介明确工学博士。</x:v>
+      </x:c>
+      <x:c r="P702" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q702" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuwang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="703" ht="64" customHeight="1">
+      <x:c r="A703" s="6" t="str">
+        <x:v>刘旺</x:v>
+      </x:c>
+      <x:c r="B703" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="C703" s="6" t="str"/>
+      <x:c r="D703" s="6" t="str">
+        <x:v>哈尔滨工程大学</x:v>
+      </x:c>
+      <x:c r="E703" s="6" t="str">
+        <x:v>2006-09</x:v>
+      </x:c>
+      <x:c r="F703" s="6" t="str">
+        <x:v>2009-09</x:v>
+      </x:c>
+      <x:c r="G703" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H703" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I703" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J703" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K703" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L703" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M703" s="7" t="str"/>
+      <x:c r="N703" s="6" t="str"/>
+      <x:c r="O703" s="6" t="str">
+        <x:v>中文结束2009.09，英文两处均Dec.2009，当前end取中文并保留冲突。</x:v>
+      </x:c>
+      <x:c r="P703" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q703" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuwang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="704" ht="64" customHeight="1">
+      <x:c r="A704" s="6" t="str">
+        <x:v>刘旺</x:v>
+      </x:c>
+      <x:c r="B704" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C704" s="6" t="str">
+        <x:v>助教</x:v>
+      </x:c>
+      <x:c r="D704" s="6" t="str">
+        <x:v>哈尔滨工业大学自动化测试与控制研究所</x:v>
+      </x:c>
+      <x:c r="E704" s="6" t="str">
+        <x:v>2000-08</x:v>
+      </x:c>
+      <x:c r="F704" s="6" t="str">
+        <x:v>2003-07</x:v>
+      </x:c>
+      <x:c r="G704" s="6" t="str"/>
+      <x:c r="H704" s="6" t="str"/>
+      <x:c r="I704" s="6" t="str"/>
+      <x:c r="J704" s="6" t="str"/>
+      <x:c r="K704" s="6" t="str"/>
+      <x:c r="L704" s="6" t="str"/>
+      <x:c r="M704" s="7" t="str"/>
+      <x:c r="N704" s="6" t="str"/>
+      <x:c r="O704" s="6" t="str"/>
+      <x:c r="P704" s="6" t="str"/>
+      <x:c r="Q704" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuwang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="705" ht="64" customHeight="1">
+      <x:c r="A705" s="6" t="str">
+        <x:v>刘旺</x:v>
+      </x:c>
+      <x:c r="B705" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C705" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D705" s="6" t="str">
+        <x:v>哈尔滨工业大学自动化测试与控制研究所</x:v>
+      </x:c>
+      <x:c r="E705" s="6" t="str">
+        <x:v>2003-08</x:v>
+      </x:c>
+      <x:c r="F705" s="6" t="str">
+        <x:v>2007-07</x:v>
+      </x:c>
+      <x:c r="G705" s="6" t="str"/>
+      <x:c r="H705" s="6" t="str"/>
+      <x:c r="I705" s="6" t="str"/>
+      <x:c r="J705" s="6" t="str"/>
+      <x:c r="K705" s="6" t="str"/>
+      <x:c r="L705" s="6" t="str"/>
+      <x:c r="M705" s="7" t="str"/>
+      <x:c r="N705" s="6" t="str"/>
+      <x:c r="O705" s="6" t="str">
+        <x:v>英文起点Jul.2003，中文2003.08冲突，当前取中文。</x:v>
+      </x:c>
+      <x:c r="P705" s="6" t="str"/>
+      <x:c r="Q705" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuwang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="706" ht="64" customHeight="1">
+      <x:c r="A706" s="6" t="str">
+        <x:v>刘旺</x:v>
+      </x:c>
+      <x:c r="B706" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C706" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D706" s="6" t="str">
+        <x:v>哈尔滨工业大学自动化测试与控制研究所</x:v>
+      </x:c>
+      <x:c r="E706" s="6" t="str">
+        <x:v>2007-08</x:v>
+      </x:c>
+      <x:c r="F706" s="6" t="str"/>
+      <x:c r="G706" s="6" t="str"/>
+      <x:c r="H706" s="6" t="str"/>
+      <x:c r="I706" s="6" t="str"/>
+      <x:c r="J706" s="6" t="str"/>
+      <x:c r="K706" s="6" t="str"/>
+      <x:c r="L706" s="6" t="str"/>
+      <x:c r="M706" s="7" t="str"/>
+      <x:c r="N706" s="6" t="str"/>
+      <x:c r="O706" s="6" t="str">
+        <x:v>英文起点Jul.2007，中文2007.08冲突，当前取中文。</x:v>
+      </x:c>
+      <x:c r="P706" s="6" t="str"/>
+      <x:c r="Q706" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuwang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="707" ht="64" customHeight="1">
+      <x:c r="A707" s="6" t="str">
+        <x:v>邹昕光</x:v>
+      </x:c>
+      <x:c r="B707" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C707" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D707" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E707" s="6" t="str">
+        <x:v>1993-09</x:v>
+      </x:c>
+      <x:c r="F707" s="6" t="str">
+        <x:v>1997-07</x:v>
+      </x:c>
+      <x:c r="G707" s="6" t="str">
+        <x:v>通信与信息系统</x:v>
+      </x:c>
+      <x:c r="H707" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I707" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J707" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K707" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L707" s="6" t="str"/>
+      <x:c r="M707" s="7" t="str"/>
+      <x:c r="N707" s="6" t="str"/>
+      <x:c r="O707" s="6" t="str">
+        <x:v>英文Bachelor’s Degree教育栏，未进一步明确授位。</x:v>
+      </x:c>
+      <x:c r="P707" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q707" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zouxinguang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="708" ht="64" customHeight="1">
+      <x:c r="A708" s="6" t="str">
+        <x:v>邹昕光</x:v>
+      </x:c>
+      <x:c r="B708" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C708" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D708" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E708" s="6" t="str">
+        <x:v>1997-09</x:v>
+      </x:c>
+      <x:c r="F708" s="6" t="str">
+        <x:v>1999-07</x:v>
+      </x:c>
+      <x:c r="G708" s="6" t="str">
+        <x:v>通信与信息系统</x:v>
+      </x:c>
+      <x:c r="H708" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I708" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J708" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K708" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L708" s="6" t="str"/>
+      <x:c r="M708" s="7" t="str"/>
+      <x:c r="N708" s="6" t="str"/>
+      <x:c r="O708" s="6" t="str">
+        <x:v>英文Master’s Degree教育栏，未进一步明确授位。</x:v>
+      </x:c>
+      <x:c r="P708" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q708" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zouxinguang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="709" ht="64" customHeight="1">
+      <x:c r="A709" s="6" t="str">
+        <x:v>邹昕光</x:v>
+      </x:c>
+      <x:c r="B709" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C709" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D709" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E709" s="6" t="str">
+        <x:v>1999-09</x:v>
+      </x:c>
+      <x:c r="F709" s="6" t="str">
+        <x:v>2002-06</x:v>
+      </x:c>
+      <x:c r="G709" s="6" t="str">
+        <x:v>通信与信息系统</x:v>
+      </x:c>
+      <x:c r="H709" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I709" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J709" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K709" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L709" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M709" s="7" t="str"/>
+      <x:c r="N709" s="6" t="str"/>
+      <x:c r="O709" s="6" t="str">
+        <x:v>研究所官方本人简介明确工学博士，主页提供博士学习学校和日期。</x:v>
+      </x:c>
+      <x:c r="P709" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q709" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zouxinguang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="710" ht="64" customHeight="1">
+      <x:c r="A710" s="6" t="str">
+        <x:v>邹昕光</x:v>
+      </x:c>
+      <x:c r="B710" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C710" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D710" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E710" s="6" t="str"/>
+      <x:c r="F710" s="6" t="str"/>
+      <x:c r="G710" s="6" t="str"/>
+      <x:c r="H710" s="6" t="str"/>
+      <x:c r="I710" s="6" t="str"/>
+      <x:c r="J710" s="6" t="str"/>
+      <x:c r="K710" s="6" t="str"/>
+      <x:c r="L710" s="6" t="str"/>
+      <x:c r="M710" s="7" t="str"/>
+      <x:c r="N710" s="6" t="str"/>
+      <x:c r="O710" s="6" t="str">
+        <x:v>研究所官方简介确证，个人主页正文未列分段任职。</x:v>
+      </x:c>
+      <x:c r="P710" s="6" t="str"/>
+      <x:c r="Q710" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/2023/0227/c16426a289583/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="711" ht="64" customHeight="1">
+      <x:c r="A711" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B711" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C711" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D711" s="6" t="str">
+        <x:v>电子科技大学</x:v>
+      </x:c>
+      <x:c r="E711" s="6" t="str">
+        <x:v>2011-09</x:v>
+      </x:c>
+      <x:c r="F711" s="6" t="str">
+        <x:v>2015-07</x:v>
+      </x:c>
+      <x:c r="G711" s="6" t="str">
+        <x:v>测控技术与仪器</x:v>
+      </x:c>
+      <x:c r="H711" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I711" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J711" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K711" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L711" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M711" s="7" t="str"/>
+      <x:c r="N711" s="6" t="str"/>
+      <x:c r="O711" s="6" t="str">
+        <x:v>英文明确received BSc in2015，与中文学校专业起讫对应。</x:v>
+      </x:c>
+      <x:c r="P711" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q711" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/songyuchen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="712" ht="64" customHeight="1">
+      <x:c r="A712" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B712" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C712" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D712" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E712" s="6" t="str">
+        <x:v>2015-09</x:v>
+      </x:c>
+      <x:c r="F712" s="6" t="str">
+        <x:v>2021-11</x:v>
+      </x:c>
+      <x:c r="G712" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H712" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I712" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J712" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K712" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L712" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M712" s="7" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="N712" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/songyuchen</x:v>
+      </x:c>
+      <x:c r="O712" s="6" t="str">
+        <x:v>中文学习结束2021.11；英文明确received PhD in2022；彭宇毕业名录写2021。不同日期并列保留，不假定授位与毕业同日。</x:v>
+      </x:c>
+      <x:c r="P712" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q712" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/songyuchen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="713" ht="64" customHeight="1">
+      <x:c r="A713" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B713" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C713" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D713" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E713" s="6" t="str">
+        <x:v>2024-02</x:v>
+      </x:c>
+      <x:c r="F713" s="6" t="str"/>
+      <x:c r="G713" s="6" t="str"/>
+      <x:c r="H713" s="6" t="str"/>
+      <x:c r="I713" s="6" t="str"/>
+      <x:c r="J713" s="6" t="str"/>
+      <x:c r="K713" s="6" t="str"/>
+      <x:c r="L713" s="6" t="str"/>
+      <x:c r="M713" s="7" t="str"/>
+      <x:c r="N713" s="6" t="str"/>
+      <x:c r="O713" s="6" t="str"/>
+      <x:c r="P713" s="6" t="str"/>
+      <x:c r="Q713" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/songyuchen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="714" ht="64" customHeight="1">
+      <x:c r="A714" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B714" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C714" s="6" t="str">
+        <x:v>助理教授</x:v>
+      </x:c>
+      <x:c r="D714" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E714" s="6" t="str">
+        <x:v>2022-01</x:v>
+      </x:c>
+      <x:c r="F714" s="6" t="str">
+        <x:v>2024-02</x:v>
+      </x:c>
+      <x:c r="G714" s="6" t="str"/>
+      <x:c r="H714" s="6" t="str"/>
+      <x:c r="I714" s="6" t="str"/>
+      <x:c r="J714" s="6" t="str"/>
+      <x:c r="K714" s="6" t="str"/>
+      <x:c r="L714" s="6" t="str"/>
+      <x:c r="M714" s="7" t="str"/>
+      <x:c r="N714" s="6" t="str"/>
+      <x:c r="O714" s="6" t="str"/>
+      <x:c r="P714" s="6" t="str"/>
+      <x:c r="Q714" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/songyuchen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="715" ht="64" customHeight="1">
+      <x:c r="A715" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B715" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C715" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D715" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E715" s="6" t="str">
+        <x:v>2024-03</x:v>
+      </x:c>
+      <x:c r="F715" s="6" t="str"/>
+      <x:c r="G715" s="6" t="str"/>
+      <x:c r="H715" s="6" t="str"/>
+      <x:c r="I715" s="6" t="str"/>
+      <x:c r="J715" s="6" t="str"/>
+      <x:c r="K715" s="6" t="str"/>
+      <x:c r="L715" s="6" t="str"/>
+      <x:c r="M715" s="7" t="str"/>
+      <x:c r="N715" s="6" t="str"/>
+      <x:c r="O715" s="6" t="str"/>
+      <x:c r="P715" s="6" t="str"/>
+      <x:c r="Q715" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/songyuchen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="716" ht="64" customHeight="1">
+      <x:c r="A716" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B716" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C716" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D716" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E716" s="6" t="str">
+        <x:v>2023-03</x:v>
+      </x:c>
+      <x:c r="F716" s="6" t="str"/>
+      <x:c r="G716" s="6" t="str"/>
+      <x:c r="H716" s="6" t="str"/>
+      <x:c r="I716" s="6" t="str"/>
+      <x:c r="J716" s="6" t="str"/>
+      <x:c r="K716" s="6" t="str"/>
+      <x:c r="L716" s="6" t="str"/>
+      <x:c r="M716" s="7" t="str"/>
+      <x:c r="N716" s="6" t="str"/>
+      <x:c r="O716" s="6" t="str"/>
+      <x:c r="P716" s="6" t="str"/>
+      <x:c r="Q716" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/songyuchen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="717" ht="64" customHeight="1">
+      <x:c r="A717" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B717" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C717" s="6" t="str">
+        <x:v>副总研究师、技术中心副主任（挂职）</x:v>
+      </x:c>
+      <x:c r="D717" s="6" t="str">
+        <x:v>上海航天精密机械研究所</x:v>
+      </x:c>
+      <x:c r="E717" s="6" t="str">
+        <x:v>2025-12</x:v>
+      </x:c>
+      <x:c r="F717" s="6" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="G717" s="6" t="str"/>
+      <x:c r="H717" s="6" t="str"/>
+      <x:c r="I717" s="6" t="str"/>
+      <x:c r="J717" s="6" t="str"/>
+      <x:c r="K717" s="6" t="str"/>
+      <x:c r="L717" s="6" t="str"/>
+      <x:c r="M717" s="7" t="str"/>
+      <x:c r="N717" s="6" t="str"/>
+      <x:c r="O717" s="6" t="str">
+        <x:v>官方给出未来计划结束月，当前日期尚未届满，不能标历史已结束。</x:v>
+      </x:c>
+      <x:c r="P717" s="6" t="str"/>
+      <x:c r="Q717" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/songyuchen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="718" ht="64" customHeight="1">
+      <x:c r="A718" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B718" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C718" s="6" t="str">
+        <x:v>副主任</x:v>
+      </x:c>
+      <x:c r="D718" s="6" t="str">
+        <x:v>自动测试及仪器技术教育部工程研究中心</x:v>
+      </x:c>
+      <x:c r="E718" s="6" t="str"/>
+      <x:c r="F718" s="6" t="str"/>
+      <x:c r="G718" s="6" t="str"/>
+      <x:c r="H718" s="6" t="str"/>
+      <x:c r="I718" s="6" t="str"/>
+      <x:c r="J718" s="6" t="str"/>
+      <x:c r="K718" s="6" t="str"/>
+      <x:c r="L718" s="6" t="str"/>
+      <x:c r="M718" s="7" t="str"/>
+      <x:c r="N718" s="6" t="str"/>
+      <x:c r="O718" s="6" t="str"/>
+      <x:c r="P718" s="6" t="str"/>
+      <x:c r="Q718" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/songyuchen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="719" ht="64" customHeight="1">
+      <x:c r="A719" s="6" t="str">
+        <x:v>王本宽</x:v>
+      </x:c>
+      <x:c r="B719" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C719" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D719" s="6" t="str">
+        <x:v>哈尔滨工业大学（威海）</x:v>
+      </x:c>
+      <x:c r="E719" s="6" t="str">
+        <x:v>2009-09</x:v>
+      </x:c>
+      <x:c r="F719" s="6" t="str">
+        <x:v>2013-07</x:v>
+      </x:c>
+      <x:c r="G719" s="6" t="str">
+        <x:v>测控技术与仪器</x:v>
+      </x:c>
+      <x:c r="H719" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I719" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J719" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K719" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L719" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M719" s="7" t="str"/>
+      <x:c r="N719" s="6" t="str"/>
+      <x:c r="O719" s="6" t="str">
+        <x:v>英文Degrees Held明确持有B.S.；校区据中文。</x:v>
+      </x:c>
+      <x:c r="P719" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q719" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangbenkuan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="720" ht="64" customHeight="1">
+      <x:c r="A720" s="6" t="str">
+        <x:v>王本宽</x:v>
+      </x:c>
+      <x:c r="B720" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C720" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D720" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E720" s="6" t="str">
+        <x:v>2013-09</x:v>
+      </x:c>
+      <x:c r="F720" s="6" t="str">
+        <x:v>2015-07</x:v>
+      </x:c>
+      <x:c r="G720" s="6" t="str">
+        <x:v>仪器仪表工程</x:v>
+      </x:c>
+      <x:c r="H720" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I720" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J720" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K720" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L720" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M720" s="7" t="str"/>
+      <x:c r="N720" s="6" t="str"/>
+      <x:c r="O720" s="6" t="str">
+        <x:v>英文Degrees Held明确持有M.S.。</x:v>
+      </x:c>
+      <x:c r="P720" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q720" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangbenkuan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="721" ht="64" customHeight="1">
+      <x:c r="A721" s="6" t="str">
+        <x:v>王本宽</x:v>
+      </x:c>
+      <x:c r="B721" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C721" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D721" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E721" s="6" t="str">
+        <x:v>2015-09</x:v>
+      </x:c>
+      <x:c r="F721" s="6" t="str">
+        <x:v>2021-12</x:v>
+      </x:c>
+      <x:c r="G721" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H721" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I721" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J721" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K721" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L721" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M721" s="7" t="str"/>
+      <x:c r="N721" s="6" t="str"/>
+      <x:c r="O721" s="6" t="str">
+        <x:v>英文Degrees Held明确持有Ph.D.。</x:v>
+      </x:c>
+      <x:c r="P721" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q721" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangbenkuan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="722" ht="64" customHeight="1">
+      <x:c r="A722" s="6" t="str">
+        <x:v>王本宽</x:v>
+      </x:c>
+      <x:c r="B722" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C722" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D722" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E722" s="6" t="str">
+        <x:v>2024-12</x:v>
+      </x:c>
+      <x:c r="F722" s="6" t="str"/>
+      <x:c r="G722" s="6" t="str"/>
+      <x:c r="H722" s="6" t="str"/>
+      <x:c r="I722" s="6" t="str"/>
+      <x:c r="J722" s="6" t="str"/>
+      <x:c r="K722" s="6" t="str"/>
+      <x:c r="L722" s="6" t="str"/>
+      <x:c r="M722" s="7" t="str"/>
+      <x:c r="N722" s="6" t="str"/>
+      <x:c r="O722" s="6" t="str"/>
+      <x:c r="P722" s="6" t="str"/>
+      <x:c r="Q722" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangbenkuan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="723" ht="64" customHeight="1">
+      <x:c r="A723" s="6" t="str">
+        <x:v>王本宽</x:v>
+      </x:c>
+      <x:c r="B723" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C723" s="6" t="str">
+        <x:v>助理教授</x:v>
+      </x:c>
+      <x:c r="D723" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E723" s="6" t="str">
+        <x:v>2022-01</x:v>
+      </x:c>
+      <x:c r="F723" s="6" t="str">
+        <x:v>2024-12</x:v>
+      </x:c>
+      <x:c r="G723" s="6" t="str"/>
+      <x:c r="H723" s="6" t="str"/>
+      <x:c r="I723" s="6" t="str"/>
+      <x:c r="J723" s="6" t="str"/>
+      <x:c r="K723" s="6" t="str"/>
+      <x:c r="L723" s="6" t="str"/>
+      <x:c r="M723" s="7" t="str"/>
+      <x:c r="N723" s="6" t="str"/>
+      <x:c r="O723" s="6" t="str"/>
+      <x:c r="P723" s="6" t="str"/>
+      <x:c r="Q723" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangbenkuan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="724" ht="64" customHeight="1">
+      <x:c r="A724" s="6" t="str">
+        <x:v>王本宽</x:v>
+      </x:c>
+      <x:c r="B724" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C724" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D724" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E724" s="6" t="str">
+        <x:v>2025-03</x:v>
+      </x:c>
+      <x:c r="F724" s="6" t="str"/>
+      <x:c r="G724" s="6" t="str"/>
+      <x:c r="H724" s="6" t="str"/>
+      <x:c r="I724" s="6" t="str"/>
+      <x:c r="J724" s="6" t="str"/>
+      <x:c r="K724" s="6" t="str"/>
+      <x:c r="L724" s="6" t="str"/>
+      <x:c r="M724" s="7" t="str"/>
+      <x:c r="N724" s="6" t="str"/>
+      <x:c r="O724" s="6" t="str"/>
+      <x:c r="P724" s="6" t="str"/>
+      <x:c r="Q724" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangbenkuan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="725" ht="64" customHeight="1">
+      <x:c r="A725" s="6" t="str">
+        <x:v>王本宽</x:v>
+      </x:c>
+      <x:c r="B725" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C725" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D725" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E725" s="6" t="str">
+        <x:v>2023-03</x:v>
+      </x:c>
+      <x:c r="F725" s="6" t="str"/>
+      <x:c r="G725" s="6" t="str"/>
+      <x:c r="H725" s="6" t="str"/>
+      <x:c r="I725" s="6" t="str"/>
+      <x:c r="J725" s="6" t="str"/>
+      <x:c r="K725" s="6" t="str"/>
+      <x:c r="L725" s="6" t="str"/>
+      <x:c r="M725" s="7" t="str"/>
+      <x:c r="N725" s="6" t="str"/>
+      <x:c r="O725" s="6" t="str"/>
+      <x:c r="P725" s="6" t="str"/>
+      <x:c r="Q725" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangbenkuan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="726" ht="64" customHeight="1">
+      <x:c r="A726" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B726" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C726" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D726" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E726" s="6" t="str">
+        <x:v>2012-09</x:v>
+      </x:c>
+      <x:c r="F726" s="6" t="str">
+        <x:v>2016-07</x:v>
+      </x:c>
+      <x:c r="G726" s="6" t="str">
+        <x:v>测控技术与仪器</x:v>
+      </x:c>
+      <x:c r="H726" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I726" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J726" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K726" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L726" s="6" t="str"/>
+      <x:c r="M726" s="7" t="str"/>
+      <x:c r="N726" s="6" t="str"/>
+      <x:c r="O726" s="6" t="str">
+        <x:v>中英文教育栏为学位标签及日期，未独立核实具体授位。</x:v>
+      </x:c>
+      <x:c r="P726" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q726" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaotianyu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="727" ht="64" customHeight="1">
+      <x:c r="A727" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B727" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C727" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D727" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E727" s="6" t="str">
+        <x:v>2016-09</x:v>
+      </x:c>
+      <x:c r="F727" s="6" t="str">
+        <x:v>2018-07</x:v>
+      </x:c>
+      <x:c r="G727" s="6" t="str">
+        <x:v>仪器科学与技术</x:v>
+      </x:c>
+      <x:c r="H727" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I727" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J727" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K727" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L727" s="6" t="str"/>
+      <x:c r="M727" s="7" t="str"/>
+      <x:c r="N727" s="6" t="str"/>
+      <x:c r="O727" s="6" t="str"/>
+      <x:c r="P727" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q727" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaotianyu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="728" ht="64" customHeight="1">
+      <x:c r="A728" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B728" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C728" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D728" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E728" s="6" t="str">
+        <x:v>2018-09</x:v>
+      </x:c>
+      <x:c r="F728" s="6" t="str">
+        <x:v>2023-06</x:v>
+      </x:c>
+      <x:c r="G728" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H728" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I728" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J728" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K728" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L728" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M728" s="7" t="str"/>
+      <x:c r="N728" s="6" t="str"/>
+      <x:c r="O728" s="6" t="str">
+        <x:v>本人简介明确PhD inEngineering。</x:v>
+      </x:c>
+      <x:c r="P728" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q728" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaotianyu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="729" ht="64" customHeight="1">
+      <x:c r="A729" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B729" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="C729" s="6" t="str"/>
+      <x:c r="D729" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E729" s="6" t="str"/>
+      <x:c r="F729" s="6" t="str"/>
+      <x:c r="G729" s="6" t="str"/>
+      <x:c r="H729" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I729" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J729" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K729" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L729" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M729" s="7" t="str"/>
+      <x:c r="N729" s="6" t="str"/>
+      <x:c r="O729" s="6" t="str">
+        <x:v>英文现任postdoctoral associate researcher，研究所名录亦博士后副研究员；仅职称晋升时间明确，博士后完整起讫未知。</x:v>
+      </x:c>
+      <x:c r="P729" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q729" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/16427/list.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="730" ht="64" customHeight="1">
+      <x:c r="A730" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B730" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C730" s="6" t="str">
+        <x:v>副研究员</x:v>
+      </x:c>
+      <x:c r="D730" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E730" s="6" t="str">
+        <x:v>2024-12</x:v>
+      </x:c>
+      <x:c r="F730" s="6" t="str"/>
+      <x:c r="G730" s="6" t="str"/>
+      <x:c r="H730" s="6" t="str"/>
+      <x:c r="I730" s="6" t="str"/>
+      <x:c r="J730" s="6" t="str"/>
+      <x:c r="K730" s="6" t="str"/>
+      <x:c r="L730" s="6" t="str"/>
+      <x:c r="M730" s="7" t="str"/>
+      <x:c r="N730" s="6" t="str"/>
+      <x:c r="O730" s="6" t="str">
+        <x:v>英文Postdoctoral Associate Researcher，博士后性质另列非授位事件。</x:v>
+      </x:c>
+      <x:c r="P730" s="6" t="str"/>
+      <x:c r="Q730" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaotianyu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="731" ht="64" customHeight="1">
+      <x:c r="A731" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B731" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C731" s="6" t="str">
+        <x:v>助理教授</x:v>
+      </x:c>
+      <x:c r="D731" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E731" s="6" t="str">
+        <x:v>2023-07</x:v>
+      </x:c>
+      <x:c r="F731" s="6" t="str">
+        <x:v>2024-12</x:v>
+      </x:c>
+      <x:c r="G731" s="6" t="str"/>
+      <x:c r="H731" s="6" t="str"/>
+      <x:c r="I731" s="6" t="str"/>
+      <x:c r="J731" s="6" t="str"/>
+      <x:c r="K731" s="6" t="str"/>
+      <x:c r="L731" s="6" t="str"/>
+      <x:c r="M731" s="7" t="str"/>
+      <x:c r="N731" s="6" t="str"/>
+      <x:c r="O731" s="6" t="str"/>
+      <x:c r="P731" s="6" t="str"/>
+      <x:c r="Q731" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaotianyu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="732" ht="64" customHeight="1">
+      <x:c r="A732" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B732" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C732" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D732" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E732" s="6" t="str">
+        <x:v>2024-03</x:v>
+      </x:c>
+      <x:c r="F732" s="6" t="str"/>
+      <x:c r="G732" s="6" t="str"/>
+      <x:c r="H732" s="6" t="str"/>
+      <x:c r="I732" s="6" t="str"/>
+      <x:c r="J732" s="6" t="str"/>
+      <x:c r="K732" s="6" t="str"/>
+      <x:c r="L732" s="6" t="str"/>
+      <x:c r="M732" s="7" t="str"/>
+      <x:c r="N732" s="6" t="str"/>
+      <x:c r="O732" s="6" t="str"/>
+      <x:c r="P732" s="6" t="str"/>
+      <x:c r="Q732" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaotianyu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="733" ht="64" customHeight="1">
+      <x:c r="A733" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B733" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C733" s="6" t="str">
+        <x:v>所长助理</x:v>
+      </x:c>
+      <x:c r="D733" s="6" t="str">
+        <x:v>哈尔滨工业大学自动化测试与控制研究所</x:v>
+      </x:c>
+      <x:c r="E733" s="6" t="str"/>
+      <x:c r="F733" s="6" t="str"/>
+      <x:c r="G733" s="6" t="str"/>
+      <x:c r="H733" s="6" t="str"/>
+      <x:c r="I733" s="6" t="str"/>
+      <x:c r="J733" s="6" t="str"/>
+      <x:c r="K733" s="6" t="str"/>
+      <x:c r="L733" s="6" t="str"/>
+      <x:c r="M733" s="7" t="str"/>
+      <x:c r="N733" s="6" t="str"/>
+      <x:c r="O733" s="6" t="str"/>
+      <x:c r="P733" s="6" t="str"/>
+      <x:c r="Q733" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaotianyu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="734" ht="64" customHeight="1">
+      <x:c r="A734" s="6" t="str">
+        <x:v>尉志良</x:v>
+      </x:c>
+      <x:c r="B734" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C734" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D734" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E734" s="6" t="str">
+        <x:v>2013-09</x:v>
+      </x:c>
+      <x:c r="F734" s="6" t="str">
+        <x:v>2017-06</x:v>
+      </x:c>
+      <x:c r="G734" s="6" t="str">
+        <x:v>测控技术与仪器</x:v>
+      </x:c>
+      <x:c r="H734" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I734" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J734" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K734" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L734" s="6" t="str"/>
+      <x:c r="M734" s="7" t="str"/>
+      <x:c r="N734" s="6" t="str"/>
+      <x:c r="O734" s="6" t="str"/>
+      <x:c r="P734" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q734" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WeiZhiliang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="735" ht="64" customHeight="1">
+      <x:c r="A735" s="6" t="str">
+        <x:v>尉志良</x:v>
+      </x:c>
+      <x:c r="B735" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C735" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D735" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E735" s="6" t="str">
+        <x:v>2017-09</x:v>
+      </x:c>
+      <x:c r="F735" s="6" t="str">
+        <x:v>2023-09</x:v>
+      </x:c>
+      <x:c r="G735" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H735" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I735" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J735" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K735" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L735" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M735" s="7" t="str"/>
+      <x:c r="N735" s="6" t="str"/>
+      <x:c r="O735" s="6" t="str">
+        <x:v>中英文简介明确工学博士。</x:v>
+      </x:c>
+      <x:c r="P735" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q735" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WeiZhiliang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="736" ht="64" customHeight="1">
+      <x:c r="A736" s="6" t="str">
+        <x:v>尉志良</x:v>
+      </x:c>
+      <x:c r="B736" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="C736" s="6" t="str"/>
+      <x:c r="D736" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E736" s="6" t="str"/>
+      <x:c r="F736" s="6" t="str"/>
+      <x:c r="G736" s="6" t="str"/>
+      <x:c r="H736" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I736" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J736" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K736" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L736" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M736" s="7" t="str"/>
+      <x:c r="N736" s="6" t="str"/>
+      <x:c r="O736" s="6" t="str">
+        <x:v>研究所官方目录明确博士后副研究员，完整起讫与合作导师未知。</x:v>
+      </x:c>
+      <x:c r="P736" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q736" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/16427/list.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="737" ht="64" customHeight="1">
+      <x:c r="A737" s="6" t="str">
+        <x:v>尉志良</x:v>
+      </x:c>
+      <x:c r="B737" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C737" s="6" t="str">
+        <x:v>副研究员</x:v>
+      </x:c>
+      <x:c r="D737" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E737" s="6" t="str">
+        <x:v>2025-01</x:v>
+      </x:c>
+      <x:c r="F737" s="6" t="str"/>
+      <x:c r="G737" s="6" t="str"/>
+      <x:c r="H737" s="6" t="str"/>
+      <x:c r="I737" s="6" t="str"/>
+      <x:c r="J737" s="6" t="str"/>
+      <x:c r="K737" s="6" t="str"/>
+      <x:c r="L737" s="6" t="str"/>
+      <x:c r="M737" s="7" t="str"/>
+      <x:c r="N737" s="6" t="str"/>
+      <x:c r="O737" s="6" t="str"/>
+      <x:c r="P737" s="6" t="str"/>
+      <x:c r="Q737" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WeiZhiliang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="738" ht="64" customHeight="1">
+      <x:c r="A738" s="6" t="str">
+        <x:v>尉志良</x:v>
+      </x:c>
+      <x:c r="B738" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C738" s="6" t="str">
+        <x:v>助理教授</x:v>
+      </x:c>
+      <x:c r="D738" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E738" s="6" t="str">
+        <x:v>2023-10</x:v>
+      </x:c>
+      <x:c r="F738" s="6" t="str">
+        <x:v>2024-12</x:v>
+      </x:c>
+      <x:c r="G738" s="6" t="str"/>
+      <x:c r="H738" s="6" t="str"/>
+      <x:c r="I738" s="6" t="str"/>
+      <x:c r="J738" s="6" t="str"/>
+      <x:c r="K738" s="6" t="str"/>
+      <x:c r="L738" s="6" t="str"/>
+      <x:c r="M738" s="7" t="str"/>
+      <x:c r="N738" s="6" t="str"/>
+      <x:c r="O738" s="6" t="str"/>
+      <x:c r="P738" s="6" t="str"/>
+      <x:c r="Q738" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WeiZhiliang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="739" ht="64" customHeight="1">
+      <x:c r="A739" s="6" t="str">
+        <x:v>尉志良</x:v>
+      </x:c>
+      <x:c r="B739" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C739" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D739" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E739" s="6" t="str">
+        <x:v>2024-03</x:v>
+      </x:c>
+      <x:c r="F739" s="6" t="str"/>
+      <x:c r="G739" s="6" t="str"/>
+      <x:c r="H739" s="6" t="str"/>
+      <x:c r="I739" s="6" t="str"/>
+      <x:c r="J739" s="6" t="str"/>
+      <x:c r="K739" s="6" t="str"/>
+      <x:c r="L739" s="6" t="str"/>
+      <x:c r="M739" s="7" t="str"/>
+      <x:c r="N739" s="6" t="str"/>
+      <x:c r="O739" s="6" t="str"/>
+      <x:c r="P739" s="6" t="str"/>
+      <x:c r="Q739" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WeiZhiliang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="740" ht="64" customHeight="1">
+      <x:c r="A740" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B740" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C740" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D740" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E740" s="6" t="str">
+        <x:v>2014-09</x:v>
+      </x:c>
+      <x:c r="F740" s="6" t="str">
+        <x:v>2018-07</x:v>
+      </x:c>
+      <x:c r="G740" s="6" t="str">
+        <x:v>测控技术与仪器</x:v>
+      </x:c>
+      <x:c r="H740" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I740" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J740" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K740" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L740" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M740" s="7" t="str"/>
+      <x:c r="N740" s="6" t="str"/>
+      <x:c r="O740" s="6" t="str">
+        <x:v>英文received BEng in2018，英文专业概称instrument science andengineering；取中文细专业并保留原文差别。</x:v>
+      </x:c>
+      <x:c r="P740" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q740" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/changyongqi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="741" ht="64" customHeight="1">
+      <x:c r="A741" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B741" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C741" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D741" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E741" s="6" t="str">
+        <x:v>2018-09</x:v>
+      </x:c>
+      <x:c r="F741" s="6" t="str">
+        <x:v>2020-07</x:v>
+      </x:c>
+      <x:c r="G741" s="6" t="str">
+        <x:v>仪器科学与技术</x:v>
+      </x:c>
+      <x:c r="H741" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I741" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J741" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K741" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L741" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M741" s="7" t="str"/>
+      <x:c r="N741" s="6" t="str"/>
+      <x:c r="O741" s="6" t="str">
+        <x:v>英文明确received MEng in2020。</x:v>
+      </x:c>
+      <x:c r="P741" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q741" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/changyongqi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="742" ht="64" customHeight="1">
+      <x:c r="A742" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B742" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C742" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D742" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E742" s="6" t="str">
+        <x:v>2021-03</x:v>
+      </x:c>
+      <x:c r="F742" s="6" t="str">
+        <x:v>2024-12</x:v>
+      </x:c>
+      <x:c r="G742" s="6" t="str">
+        <x:v>控制科学与工程</x:v>
+      </x:c>
+      <x:c r="H742" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I742" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J742" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K742" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L742" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M742" s="7" t="str"/>
+      <x:c r="N742" s="6" t="str"/>
+      <x:c r="O742" s="6" t="str">
+        <x:v>英文明确received PhD in2024。</x:v>
+      </x:c>
+      <x:c r="P742" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q742" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/changyongqi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="743" ht="64" customHeight="1">
+      <x:c r="A743" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B743" s="6" t="str">
+        <x:v>joint_training</x:v>
+      </x:c>
+      <x:c r="C743" s="6" t="str"/>
+      <x:c r="D743" s="6" t="str">
+        <x:v>南洋理工大学</x:v>
+      </x:c>
+      <x:c r="E743" s="6" t="str">
+        <x:v>2023-03</x:v>
+      </x:c>
+      <x:c r="F743" s="6" t="str">
+        <x:v>2024-03</x:v>
+      </x:c>
+      <x:c r="G743" s="6" t="str">
+        <x:v>电气与电子工程</x:v>
+      </x:c>
+      <x:c r="H743" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="I743" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="J743" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K743" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L743" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M743" s="7" t="str"/>
+      <x:c r="N743" s="6" t="str"/>
+      <x:c r="O743" s="6" t="str">
+        <x:v>中文博士联合培养，英文Visiting Student，不是NTU授位。</x:v>
+      </x:c>
+      <x:c r="P743" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q743" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/changyongqi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="744" ht="64" customHeight="1">
+      <x:c r="A744" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B744" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="C744" s="6" t="str"/>
+      <x:c r="D744" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E744" s="6" t="str"/>
+      <x:c r="F744" s="6" t="str"/>
+      <x:c r="G744" s="6" t="str"/>
+      <x:c r="H744" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I744" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J744" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K744" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L744" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M744" s="7" t="str"/>
+      <x:c r="N744" s="6" t="str"/>
+      <x:c r="O744" s="6" t="str">
+        <x:v>研究所官方目录明确博士后副研究员，完整起讫与合作导师未知。</x:v>
+      </x:c>
+      <x:c r="P744" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q744" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/16427/list.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="745" ht="64" customHeight="1">
+      <x:c r="A745" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B745" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C745" s="6" t="str">
+        <x:v>副研究员</x:v>
+      </x:c>
+      <x:c r="D745" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E745" s="6" t="str">
+        <x:v>2025-03</x:v>
+      </x:c>
+      <x:c r="F745" s="6" t="str"/>
+      <x:c r="G745" s="6" t="str"/>
+      <x:c r="H745" s="6" t="str"/>
+      <x:c r="I745" s="6" t="str"/>
+      <x:c r="J745" s="6" t="str"/>
+      <x:c r="K745" s="6" t="str"/>
+      <x:c r="L745" s="6" t="str"/>
+      <x:c r="M745" s="7" t="str"/>
+      <x:c r="N745" s="6" t="str"/>
+      <x:c r="O745" s="6" t="str">
+        <x:v>另条2026.09副研究员/硕导与该条重叠，合并副研究员任职并将硕导单列；英文AssociateProfessor与中文副研究员职称差别保留。</x:v>
+      </x:c>
+      <x:c r="P745" s="6" t="str"/>
+      <x:c r="Q745" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/changyongqi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="746" ht="64" customHeight="1">
+      <x:c r="A746" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B746" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C746" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D746" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E746" s="6" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="F746" s="6" t="str"/>
+      <x:c r="G746" s="6" t="str"/>
+      <x:c r="H746" s="6" t="str"/>
+      <x:c r="I746" s="6" t="str"/>
+      <x:c r="J746" s="6" t="str"/>
+      <x:c r="K746" s="6" t="str"/>
+      <x:c r="L746" s="6" t="str"/>
+      <x:c r="M746" s="7" t="str"/>
+      <x:c r="N746" s="6" t="str"/>
+      <x:c r="O746" s="6" t="str"/>
+      <x:c r="P746" s="6" t="str"/>
+      <x:c r="Q746" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/changyongqi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="747" ht="64" customHeight="1">
+      <x:c r="A747" s="6" t="str">
+        <x:v>王俊凯</x:v>
+      </x:c>
+      <x:c r="B747" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C747" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D747" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E747" s="6" t="str">
+        <x:v>2020-09</x:v>
+      </x:c>
+      <x:c r="F747" s="6" t="str">
+        <x:v>2025-12</x:v>
+      </x:c>
+      <x:c r="G747" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H747" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I747" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J747" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K747" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L747" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M747" s="7" t="str"/>
+      <x:c r="N747" s="6" t="str"/>
+      <x:c r="O747" s="6" t="str">
+        <x:v>本人英文明确2025 received PhD。</x:v>
+      </x:c>
+      <x:c r="P747" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q747" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WangJunkai</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="748" ht="64" customHeight="1">
+      <x:c r="A748" s="6" t="str">
+        <x:v>王俊凯</x:v>
+      </x:c>
+      <x:c r="B748" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="C748" s="6" t="str"/>
+      <x:c r="D748" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E748" s="6" t="str"/>
+      <x:c r="F748" s="6" t="str"/>
+      <x:c r="G748" s="6" t="str"/>
+      <x:c r="H748" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I748" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J748" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K748" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L748" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M748" s="7" t="str"/>
+      <x:c r="N748" s="6" t="str"/>
+      <x:c r="O748" s="6" t="str">
+        <x:v>研究所名录明确博士后副研究员，未将副研究员晋升日期当博士后入站。</x:v>
+      </x:c>
+      <x:c r="P748" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q748" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/16427/list.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="749" ht="64" customHeight="1">
+      <x:c r="A749" s="6" t="str">
+        <x:v>王俊凯</x:v>
+      </x:c>
+      <x:c r="B749" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C749" s="6" t="str">
+        <x:v>副研究员</x:v>
+      </x:c>
+      <x:c r="D749" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E749" s="6" t="str">
+        <x:v>2026-01</x:v>
+      </x:c>
+      <x:c r="F749" s="6" t="str"/>
+      <x:c r="G749" s="6" t="str"/>
+      <x:c r="H749" s="6" t="str"/>
+      <x:c r="I749" s="6" t="str"/>
+      <x:c r="J749" s="6" t="str"/>
+      <x:c r="K749" s="6" t="str"/>
+      <x:c r="L749" s="6" t="str"/>
+      <x:c r="M749" s="7" t="str"/>
+      <x:c r="N749" s="6" t="str"/>
+      <x:c r="O749" s="6" t="str"/>
+      <x:c r="P749" s="6" t="str"/>
+      <x:c r="Q749" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WangJunkai</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="750" ht="64" customHeight="1">
+      <x:c r="A750" s="6" t="str">
+        <x:v>王俊凯</x:v>
+      </x:c>
+      <x:c r="B750" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C750" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D750" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E750" s="6" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="F750" s="6" t="str"/>
+      <x:c r="G750" s="6" t="str"/>
+      <x:c r="H750" s="6" t="str"/>
+      <x:c r="I750" s="6" t="str"/>
+      <x:c r="J750" s="6" t="str"/>
+      <x:c r="K750" s="6" t="str"/>
+      <x:c r="L750" s="6" t="str"/>
+      <x:c r="M750" s="7" t="str"/>
+      <x:c r="N750" s="6" t="str"/>
+      <x:c r="O750" s="6" t="str"/>
+      <x:c r="P750" s="6" t="str"/>
+      <x:c r="Q750" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WangJunkai</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="751" ht="64" customHeight="1">
+      <x:c r="A751" s="6" t="str">
+        <x:v>姚博文</x:v>
+      </x:c>
+      <x:c r="B751" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C751" s="6" t="str">
+        <x:v>学士（层次暂对应，未核实）</x:v>
+      </x:c>
+      <x:c r="D751" s="6" t="str">
+        <x:v>哈尔滨理工大学</x:v>
+      </x:c>
+      <x:c r="E751" s="6" t="str">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="F751" s="6" t="str">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="G751" s="6" t="str">
+        <x:v>微电子学</x:v>
+      </x:c>
+      <x:c r="H751" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I751" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J751" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K751" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L751" s="6" t="str"/>
+      <x:c r="M751" s="7" t="str"/>
+      <x:c r="N751" s="6" t="str"/>
+      <x:c r="O751" s="6" t="str">
+        <x:v>本人总述持理学学士/工学硕士/工学博士，三个学习阶段按同段顺序暂对应；逐条未明确学位字段，授位学校与年份待单独直接证明，不用顺序推断作已确证授位。</x:v>
+      </x:c>
+      <x:c r="P751" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q751" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yaobowen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="752" ht="64" customHeight="1">
+      <x:c r="A752" s="6" t="str">
+        <x:v>姚博文</x:v>
+      </x:c>
+      <x:c r="B752" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C752" s="6" t="str">
+        <x:v>硕士（层次暂对应，未核实）</x:v>
+      </x:c>
+      <x:c r="D752" s="6" t="str">
+        <x:v>哈尔滨理工大学</x:v>
+      </x:c>
+      <x:c r="E752" s="6" t="str">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="F752" s="6" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="G752" s="6" t="str">
+        <x:v>电子科学与技术</x:v>
+      </x:c>
+      <x:c r="H752" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I752" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J752" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K752" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L752" s="6" t="str"/>
+      <x:c r="M752" s="7" t="str"/>
+      <x:c r="N752" s="6" t="str"/>
+      <x:c r="O752" s="6" t="str">
+        <x:v>本人总述持理学学士/工学硕士/工学博士，三个学习阶段按同段顺序暂对应；逐条未明确学位字段，授位学校与年份待单独直接证明，不用顺序推断作已确证授位。</x:v>
+      </x:c>
+      <x:c r="P752" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q752" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yaobowen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="753" ht="64" customHeight="1">
+      <x:c r="A753" s="6" t="str">
+        <x:v>姚博文</x:v>
+      </x:c>
+      <x:c r="B753" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C753" s="6" t="str">
+        <x:v>博士（层次暂对应，未核实）</x:v>
+      </x:c>
+      <x:c r="D753" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E753" s="6" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="F753" s="6" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="G753" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H753" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I753" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J753" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K753" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L753" s="6" t="str"/>
+      <x:c r="M753" s="7" t="str"/>
+      <x:c r="N753" s="6" t="str"/>
+      <x:c r="O753" s="6" t="str">
+        <x:v>本人总述持理学学士/工学硕士/工学博士，三个学习阶段按同段顺序暂对应；逐条未明确学位字段，授位学校与年份待单独直接证明，不用顺序推断作已确证授位。</x:v>
+      </x:c>
+      <x:c r="P753" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q753" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yaobowen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="754" ht="64" customHeight="1">
+      <x:c r="A754" s="6" t="str">
+        <x:v>姚博文</x:v>
+      </x:c>
+      <x:c r="B754" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="C754" s="6" t="str"/>
+      <x:c r="D754" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E754" s="6" t="str"/>
+      <x:c r="F754" s="6" t="str"/>
+      <x:c r="G754" s="6" t="str"/>
+      <x:c r="H754" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I754" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J754" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K754" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L754" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M754" s="7" t="str"/>
+      <x:c r="N754" s="6" t="str"/>
+      <x:c r="O754" s="6" t="str">
+        <x:v>本人英文及研究所官方目录明确博士后助理研究员。</x:v>
+      </x:c>
+      <x:c r="P754" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q754" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/16427/list.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="755" ht="64" customHeight="1">
+      <x:c r="A755" s="6" t="str">
+        <x:v>姚博文</x:v>
+      </x:c>
+      <x:c r="B755" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C755" s="6" t="str">
+        <x:v>助理研究员</x:v>
+      </x:c>
+      <x:c r="D755" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E755" s="6" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="F755" s="6" t="str"/>
+      <x:c r="G755" s="6" t="str"/>
+      <x:c r="H755" s="6" t="str"/>
+      <x:c r="I755" s="6" t="str"/>
+      <x:c r="J755" s="6" t="str"/>
+      <x:c r="K755" s="6" t="str"/>
+      <x:c r="L755" s="6" t="str"/>
+      <x:c r="M755" s="7" t="str"/>
+      <x:c r="N755" s="6" t="str"/>
+      <x:c r="O755" s="6" t="str"/>
+      <x:c r="P755" s="6" t="str"/>
+      <x:c r="Q755" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yaobowen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="756" ht="64" customHeight="1">
+      <x:c r="A756" s="6" t="str">
+        <x:v>姚博文</x:v>
+      </x:c>
+      <x:c r="B756" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C756" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D756" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E756" s="6" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="F756" s="6" t="str"/>
+      <x:c r="G756" s="6" t="str"/>
+      <x:c r="H756" s="6" t="str"/>
+      <x:c r="I756" s="6" t="str"/>
+      <x:c r="J756" s="6" t="str"/>
+      <x:c r="K756" s="6" t="str"/>
+      <x:c r="L756" s="6" t="str"/>
+      <x:c r="M756" s="7" t="str"/>
+      <x:c r="N756" s="6" t="str"/>
+      <x:c r="O756" s="6" t="str"/>
+      <x:c r="P756" s="6" t="str"/>
+      <x:c r="Q756" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yaobowen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="757" ht="64" customHeight="1">
+      <x:c r="A757" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B757" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C757" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D757" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E757" s="6" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="F757" s="6" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="G757" s="6" t="str"/>
+      <x:c r="H757" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I757" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J757" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K757" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L757" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M757" s="7" t="str"/>
+      <x:c r="N757" s="6" t="str"/>
+      <x:c r="O757" s="6" t="str">
+        <x:v>本人简介明确PhD和HIT-NTU联合培养；杨京礼官方已毕业博士生2022–2026列本人，并写留校工作，日期来自导师页。</x:v>
+      </x:c>
+      <x:c r="P757" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q757" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yangjingli</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="758" ht="64" customHeight="1">
+      <x:c r="A758" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B758" s="6" t="str">
+        <x:v>joint_training</x:v>
+      </x:c>
+      <x:c r="C758" s="6" t="str"/>
+      <x:c r="D758" s="6" t="str">
+        <x:v>南洋理工大学</x:v>
+      </x:c>
+      <x:c r="E758" s="6" t="str"/>
+      <x:c r="F758" s="6" t="str"/>
+      <x:c r="G758" s="6" t="str"/>
+      <x:c r="H758" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="I758" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="J758" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K758" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L758" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M758" s="7" t="str"/>
+      <x:c r="N758" s="6" t="str"/>
+      <x:c r="O758" s="6" t="str">
+        <x:v>本人中英文均联合培养，没有NTU独立授位证据。</x:v>
+      </x:c>
+      <x:c r="P758" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q758" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangchangdong</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="759" ht="64" customHeight="1">
+      <x:c r="A759" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B759" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="C759" s="6" t="str"/>
+      <x:c r="D759" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E759" s="6" t="str"/>
+      <x:c r="F759" s="6" t="str"/>
+      <x:c r="G759" s="6" t="str"/>
+      <x:c r="H759" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I759" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J759" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K759" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L759" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M759" s="7" t="str"/>
+      <x:c r="N759" s="6" t="str"/>
+      <x:c r="O759" s="6" t="str">
+        <x:v>本人中文明确博后导师李惠；完整起讫未披露。</x:v>
+      </x:c>
+      <x:c r="P759" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q759" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangchangdong</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="760" ht="64" customHeight="1">
+      <x:c r="A760" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B760" s="6" t="str">
+        <x:v>visiting_study</x:v>
+      </x:c>
+      <x:c r="C760" s="6" t="str"/>
+      <x:c r="D760" s="6" t="str">
+        <x:v>牛津大学</x:v>
+      </x:c>
+      <x:c r="E760" s="6" t="str"/>
+      <x:c r="F760" s="6" t="str"/>
+      <x:c r="G760" s="6" t="str"/>
+      <x:c r="H760" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="I760" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="J760" s="6" t="str">
+        <x:v>欧洲</x:v>
+      </x:c>
+      <x:c r="K760" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L760" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M760" s="7" t="str"/>
+      <x:c r="N760" s="6" t="str"/>
+      <x:c r="O760" s="6" t="str">
+        <x:v>本人英文visited andstudied，无时长、学位或指导人。</x:v>
+      </x:c>
+      <x:c r="P760" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q760" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangchangdong</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="761" ht="64" customHeight="1">
+      <x:c r="A761" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B761" s="6" t="str">
+        <x:v>visiting_study</x:v>
+      </x:c>
+      <x:c r="C761" s="6" t="str"/>
+      <x:c r="D761" s="6" t="str">
+        <x:v>东京大学</x:v>
+      </x:c>
+      <x:c r="E761" s="6" t="str"/>
+      <x:c r="F761" s="6" t="str"/>
+      <x:c r="G761" s="6" t="str"/>
+      <x:c r="H761" s="6" t="str">
+        <x:v>日本</x:v>
+      </x:c>
+      <x:c r="I761" s="6" t="str">
+        <x:v>日本</x:v>
+      </x:c>
+      <x:c r="J761" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K761" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L761" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M761" s="7" t="str"/>
+      <x:c r="N761" s="6" t="str"/>
+      <x:c r="O761" s="6" t="str">
+        <x:v>本人英文visited andstudied，无时长、学位或指导人。</x:v>
+      </x:c>
+      <x:c r="P761" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q761" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangchangdong</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="762" ht="64" customHeight="1">
+      <x:c r="A762" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B762" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C762" s="6" t="str">
+        <x:v>副研究员、硕士生导师</x:v>
+      </x:c>
+      <x:c r="D762" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E762" s="6" t="str"/>
+      <x:c r="F762" s="6" t="str"/>
+      <x:c r="G762" s="6" t="str"/>
+      <x:c r="H762" s="6" t="str"/>
+      <x:c r="I762" s="6" t="str"/>
+      <x:c r="J762" s="6" t="str"/>
+      <x:c r="K762" s="6" t="str"/>
+      <x:c r="L762" s="6" t="str"/>
+      <x:c r="M762" s="7" t="str"/>
+      <x:c r="N762" s="6" t="str"/>
+      <x:c r="O762" s="6" t="str"/>
+      <x:c r="P762" s="6" t="str"/>
+      <x:c r="Q762" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangchangdong</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="763" ht="64" customHeight="1">
+      <x:c r="A763" s="6" t="str">
+        <x:v>吴艳</x:v>
+      </x:c>
+      <x:c r="B763" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C763" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D763" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E763" s="6" t="str">
+        <x:v>2002</x:v>
+      </x:c>
+      <x:c r="F763" s="6" t="str">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="G763" s="6" t="str">
+        <x:v>测控技术与仪器</x:v>
+      </x:c>
+      <x:c r="H763" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I763" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J763" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K763" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L763" s="6" t="str"/>
+      <x:c r="M763" s="7" t="str"/>
+      <x:c r="N763" s="6" t="str"/>
+      <x:c r="O763" s="6" t="str">
+        <x:v>英文专业AutomaticTestandControl与中文名称不同，保留中文，授位未另核。</x:v>
+      </x:c>
+      <x:c r="P763" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q763" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WuYan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="764" ht="64" customHeight="1">
+      <x:c r="A764" s="6" t="str">
+        <x:v>吴艳</x:v>
+      </x:c>
+      <x:c r="B764" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C764" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D764" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E764" s="6" t="str">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="F764" s="6" t="str">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="G764" s="6" t="str">
+        <x:v>仪器科学与技术</x:v>
+      </x:c>
+      <x:c r="H764" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I764" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J764" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K764" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L764" s="6" t="str"/>
+      <x:c r="M764" s="7" t="str"/>
+      <x:c r="N764" s="6" t="str"/>
+      <x:c r="O764" s="6" t="str"/>
+      <x:c r="P764" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q764" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WuYan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="765" ht="64" customHeight="1">
+      <x:c r="A765" s="6" t="str">
+        <x:v>吴艳</x:v>
+      </x:c>
+      <x:c r="B765" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C765" s="6" t="str">
+        <x:v>教授级高级工程师</x:v>
+      </x:c>
+      <x:c r="D765" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E765" s="6" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="F765" s="6" t="str"/>
+      <x:c r="G765" s="6" t="str"/>
+      <x:c r="H765" s="6" t="str"/>
+      <x:c r="I765" s="6" t="str"/>
+      <x:c r="J765" s="6" t="str"/>
+      <x:c r="K765" s="6" t="str"/>
+      <x:c r="L765" s="6" t="str"/>
+      <x:c r="M765" s="7" t="str"/>
+      <x:c r="N765" s="6" t="str"/>
+      <x:c r="O765" s="6" t="str">
+        <x:v>英文Professor不可径译学术教授，采用中文具体职称。</x:v>
+      </x:c>
+      <x:c r="P765" s="6" t="str"/>
+      <x:c r="Q765" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WuYan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="766" ht="64" customHeight="1">
+      <x:c r="A766" s="6" t="str">
+        <x:v>吴艳</x:v>
+      </x:c>
+      <x:c r="B766" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C766" s="6" t="str">
+        <x:v>高级工程师</x:v>
+      </x:c>
+      <x:c r="D766" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E766" s="6" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="F766" s="6" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="G766" s="6" t="str"/>
+      <x:c r="H766" s="6" t="str"/>
+      <x:c r="I766" s="6" t="str"/>
+      <x:c r="J766" s="6" t="str"/>
+      <x:c r="K766" s="6" t="str"/>
+      <x:c r="L766" s="6" t="str"/>
+      <x:c r="M766" s="7" t="str"/>
+      <x:c r="N766" s="6" t="str"/>
+      <x:c r="O766" s="6" t="str"/>
+      <x:c r="P766" s="6" t="str"/>
+      <x:c r="Q766" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WuYan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="767" ht="64" customHeight="1">
+      <x:c r="A767" s="6" t="str">
+        <x:v>吴艳</x:v>
+      </x:c>
+      <x:c r="B767" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C767" s="6" t="str">
+        <x:v>工程师</x:v>
+      </x:c>
+      <x:c r="D767" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E767" s="6" t="str">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="F767" s="6" t="str">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="G767" s="6" t="str"/>
+      <x:c r="H767" s="6" t="str"/>
+      <x:c r="I767" s="6" t="str"/>
+      <x:c r="J767" s="6" t="str"/>
+      <x:c r="K767" s="6" t="str"/>
+      <x:c r="L767" s="6" t="str"/>
+      <x:c r="M767" s="7" t="str"/>
+      <x:c r="N767" s="6" t="str"/>
+      <x:c r="O767" s="6" t="str"/>
+      <x:c r="P767" s="6" t="str"/>
+      <x:c r="Q767" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WuYan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="768" ht="64" customHeight="1">
+      <x:c r="A768" s="6" t="str">
+        <x:v>吴艳</x:v>
+      </x:c>
+      <x:c r="B768" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C768" s="6" t="str">
+        <x:v>工程师</x:v>
+      </x:c>
+      <x:c r="D768" s="6" t="str">
+        <x:v>哈尔滨东安发动机集团有限公司</x:v>
+      </x:c>
+      <x:c r="E768" s="6" t="str">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="F768" s="6" t="str">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="G768" s="6" t="str"/>
+      <x:c r="H768" s="6" t="str"/>
+      <x:c r="I768" s="6" t="str"/>
+      <x:c r="J768" s="6" t="str"/>
+      <x:c r="K768" s="6" t="str"/>
+      <x:c r="L768" s="6" t="str"/>
+      <x:c r="M768" s="7" t="str"/>
+      <x:c r="N768" s="6" t="str"/>
+      <x:c r="O768" s="6" t="str"/>
+      <x:c r="P768" s="6" t="str"/>
+      <x:c r="Q768" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WuYan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="769" ht="64" customHeight="1">
+      <x:c r="A769" s="6" t="str">
+        <x:v>吴艳</x:v>
+      </x:c>
+      <x:c r="B769" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C769" s="6" t="str">
+        <x:v>应用工程师</x:v>
+      </x:c>
+      <x:c r="D769" s="6" t="str">
+        <x:v>美国国家仪器有限公司（NI）</x:v>
+      </x:c>
+      <x:c r="E769" s="6" t="str">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="F769" s="6" t="str">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="G769" s="6" t="str"/>
+      <x:c r="H769" s="6" t="str"/>
+      <x:c r="I769" s="6" t="str"/>
+      <x:c r="J769" s="6" t="str"/>
+      <x:c r="K769" s="6" t="str"/>
+      <x:c r="L769" s="6" t="str"/>
+      <x:c r="M769" s="7" t="str"/>
+      <x:c r="N769" s="6" t="str"/>
+      <x:c r="O769" s="6" t="str">
+        <x:v>公司名称含美国，不证明其本人任职地在美国。</x:v>
+      </x:c>
+      <x:c r="P769" s="6" t="str"/>
+      <x:c r="Q769" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WuYan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="770" ht="64" customHeight="1">
+      <x:c r="A770" s="6" t="str">
+        <x:v>郑文斌</x:v>
+      </x:c>
+      <x:c r="B770" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C770" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D770" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E770" s="6" t="str">
+        <x:v>2003-09</x:v>
+      </x:c>
+      <x:c r="F770" s="6" t="str">
+        <x:v>2007-07</x:v>
+      </x:c>
+      <x:c r="G770" s="6" t="str">
+        <x:v>测控技术与仪器</x:v>
+      </x:c>
+      <x:c r="H770" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I770" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J770" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K770" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L770" s="6" t="str"/>
+      <x:c r="M770" s="7" t="str"/>
+      <x:c r="N770" s="6" t="str"/>
+      <x:c r="O770" s="6" t="str"/>
+      <x:c r="P770" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q770" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhengwenbin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="771" ht="64" customHeight="1">
+      <x:c r="A771" s="6" t="str">
+        <x:v>郑文斌</x:v>
+      </x:c>
+      <x:c r="B771" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C771" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D771" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E771" s="6" t="str">
+        <x:v>2007-09</x:v>
+      </x:c>
+      <x:c r="F771" s="6" t="str">
+        <x:v>2009-07</x:v>
+      </x:c>
+      <x:c r="G771" s="6" t="str">
+        <x:v>仪器科学与技术</x:v>
+      </x:c>
+      <x:c r="H771" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I771" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J771" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K771" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L771" s="6" t="str"/>
+      <x:c r="M771" s="7" t="str"/>
+      <x:c r="N771" s="6" t="str"/>
+      <x:c r="O771" s="6" t="str"/>
+      <x:c r="P771" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q771" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhengwenbin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="772" ht="64" customHeight="1">
+      <x:c r="A772" s="6" t="str">
+        <x:v>郑文斌</x:v>
+      </x:c>
+      <x:c r="B772" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C772" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D772" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E772" s="6" t="str">
+        <x:v>2009-09</x:v>
+      </x:c>
+      <x:c r="F772" s="6" t="str">
+        <x:v>2014-07</x:v>
+      </x:c>
+      <x:c r="G772" s="6" t="str">
+        <x:v>仪器科学与技术</x:v>
+      </x:c>
+      <x:c r="H772" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I772" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J772" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K772" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L772" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M772" s="7" t="str"/>
+      <x:c r="N772" s="6" t="str"/>
+      <x:c r="O772" s="6" t="str">
+        <x:v>本人中英文简介明确PhD inEngineering，日期来自教育经历。</x:v>
+      </x:c>
+      <x:c r="P772" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q772" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhengwenbin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="773" ht="64" customHeight="1">
+      <x:c r="A773" s="6" t="str">
+        <x:v>郑文斌</x:v>
+      </x:c>
+      <x:c r="B773" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C773" s="6" t="str">
+        <x:v>高级工程师、硕士生导师</x:v>
+      </x:c>
+      <x:c r="D773" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E773" s="6" t="str"/>
+      <x:c r="F773" s="6" t="str"/>
+      <x:c r="G773" s="6" t="str"/>
+      <x:c r="H773" s="6" t="str"/>
+      <x:c r="I773" s="6" t="str"/>
+      <x:c r="J773" s="6" t="str"/>
+      <x:c r="K773" s="6" t="str"/>
+      <x:c r="L773" s="6" t="str"/>
+      <x:c r="M773" s="7" t="str"/>
+      <x:c r="N773" s="6" t="str"/>
+      <x:c r="O773" s="6" t="str">
+        <x:v>研究所教辅系列官方目录直接职称；不推首次任职时间。</x:v>
+      </x:c>
+      <x:c r="P773" s="6" t="str"/>
+      <x:c r="Q773" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/16428/list.htm</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1650e483b41d4a81"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra04bd8d785724c35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29557,10 +34609,216 @@
         <x:v>https://homepage.hit.edu.cn/pengxiyuan?lang=zh</x:v>
       </x:c>
     </x:row>
+    <x:row r="23" ht="64" customHeight="1">
+      <x:c r="A23" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
+        <x:v>付平</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D23" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E23" s="6" t="str">
+        <x:v>哈尔滨工业大学长聘教授、博士生导师，研究自动测试、信息检测处理与机器学习。</x:v>
+      </x:c>
+      <x:c r="F23" s="6" t="str">
+        <x:v>official_page_currently_listed</x:v>
+      </x:c>
+      <x:c r="G23" s="6" t="str">
+        <x:v>独立官方导师主页已读并与既有人员实体匹配。</x:v>
+      </x:c>
+      <x:c r="H23" s="6" t="str"/>
+      <x:c r="I23" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+      <x:c r="J23" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/fuping?lang=zh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="64" customHeight="1">
+      <x:c r="A24" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>王一平</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="str">
+        <x:v>硕士导师</x:v>
+      </x:c>
+      <x:c r="D24" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="E24" s="6" t="str">
+        <x:v>西安电子科技大学原教授、原副院长，电波传播与电磁理论学者，曾创建物理系。</x:v>
+      </x:c>
+      <x:c r="F24" s="6" t="str">
+        <x:v>deceased</x:v>
+      </x:c>
+      <x:c r="G24" s="6" t="str">
+        <x:v>西安电子科技大学署名的2026年搜狐文章记2011年去世；不是当前在职。</x:v>
+      </x:c>
+      <x:c r="H24" s="6" t="str"/>
+      <x:c r="I24" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+      <x:c r="J24" s="6" t="str">
+        <x:v>https://www.sohu.com/a/1080526727_407305</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="64" customHeight="1">
+      <x:c r="A25" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
+        <x:v>陈陆君</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="str">
+        <x:v>本科导师</x:v>
+      </x:c>
+      <x:c r="D25" s="6" t="str">
+        <x:v>本科</x:v>
+      </x:c>
+      <x:c r="E25" s="6" t="str"/>
+      <x:c r="F25" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G25" s="6" t="str">
+        <x:v>未取得可消歧的独立官方履历；未知不推断在职、退休或去世。</x:v>
+      </x:c>
+      <x:c r="H25" s="6" t="str"/>
+      <x:c r="I25" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+      <x:c r="J25" s="6" t="str"/>
+    </x:row>
+    <x:row r="26" ht="64" customHeight="1">
+      <x:c r="A26" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="str">
+        <x:v>彭宇</x:v>
+      </x:c>
+      <x:c r="C26" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D26" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E26" s="6" t="str">
+        <x:v>哈尔滨工业大学教授、博士生导师，从事自动测试、工业大数据与嵌入式智能研究。</x:v>
+      </x:c>
+      <x:c r="F26" s="6" t="str">
+        <x:v>official_page_currently_listed</x:v>
+      </x:c>
+      <x:c r="G26" s="6" t="str">
+        <x:v>独立官方机构当前页面列示，不推测退休或实际全职状态。</x:v>
+      </x:c>
+      <x:c r="H26" s="6" t="str"/>
+      <x:c r="I26" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/pengyu</x:v>
+      </x:c>
+      <x:c r="J26" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/pengyu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="64" customHeight="1">
+      <x:c r="A27" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B27" s="6" t="str">
+        <x:v>杨京礼</x:v>
+      </x:c>
+      <x:c r="C27" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D27" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E27" s="6" t="str">
+        <x:v>哈尔滨工业大学教授、博士生导师，研究智能感知、自主决策、数字孪生与类脑计算。</x:v>
+      </x:c>
+      <x:c r="F27" s="6" t="str">
+        <x:v>official_page_currently_listed</x:v>
+      </x:c>
+      <x:c r="G27" s="6" t="str">
+        <x:v>独立官方机构当前页面列示，不推测退休或实际全职状态。</x:v>
+      </x:c>
+      <x:c r="H27" s="6" t="str"/>
+      <x:c r="I27" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangchangdong</x:v>
+      </x:c>
+      <x:c r="J27" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yangjingli</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="64" customHeight="1">
+      <x:c r="A28" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="str">
+        <x:v>See Kye Yak</x:v>
+      </x:c>
+      <x:c r="C28" s="6" t="str">
+        <x:v>博士联合培养指导教师</x:v>
+      </x:c>
+      <x:c r="D28" s="6" t="str">
+        <x:v>joint_training</x:v>
+      </x:c>
+      <x:c r="E28" s="6" t="str">
+        <x:v>南洋理工大学副教授、电磁效应研究实验室主任。</x:v>
+      </x:c>
+      <x:c r="F28" s="6" t="str">
+        <x:v>official_page_currently_listed</x:v>
+      </x:c>
+      <x:c r="G28" s="6" t="str">
+        <x:v>独立官方机构当前页面列示，不推测退休或实际全职状态。</x:v>
+      </x:c>
+      <x:c r="H28" s="6" t="str"/>
+      <x:c r="I28" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangchangdong</x:v>
+      </x:c>
+      <x:c r="J28" s="6" t="str">
+        <x:v>https://www.ntu.edu.sg/emerl/about-us/contact-us</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="64" customHeight="1">
+      <x:c r="A29" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="str">
+        <x:v>李惠</x:v>
+      </x:c>
+      <x:c r="C29" s="6" t="str">
+        <x:v>博士后导师</x:v>
+      </x:c>
+      <x:c r="D29" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="E29" s="6" t="str">
+        <x:v>哈尔滨工业大学土木工程学院教授、中国科学院院士，研究桥梁安全监测与结构健康诊断。</x:v>
+      </x:c>
+      <x:c r="F29" s="6" t="str">
+        <x:v>official_page_currently_listed</x:v>
+      </x:c>
+      <x:c r="G29" s="6" t="str">
+        <x:v>独立官方机构当前页面列示，不推测退休或实际全职状态。</x:v>
+      </x:c>
+      <x:c r="H29" s="6" t="str"/>
+      <x:c r="I29" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangchangdong</x:v>
+      </x:c>
+      <x:c r="J29" s="6" t="str">
+        <x:v>https://civil.hit.edu.cn/kxyys/list.htm</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R258edb5dadcc4be0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97ae2612cd8e4f61"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -34957,10 +40215,1210 @@
         <x:v>同领域合著者李晓东哈尔滨工程大学官网逐名列Jingchao Zhang（张京超），与HIT稀疏采样研究方向及乔立岩合作网络对应；未声称逐篇出版社链接已读。 链接核验状态：Crossref 题名、作者及期刊元数据已核，文章落地页未检查。 Crossref 登记出版日期：2024；与官网年份分列，不自动推断差异原因。</x:v>
       </x:c>
     </x:row>
+    <x:row r="177" ht="64" customHeight="1">
+      <x:c r="A177" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B177" s="6" t="str">
+        <x:v>LLD: Lightweight Latency Decrease Scheme of LDPC Hard Decision Decoding for 3-D TLC NAND Flash Memory</x:v>
+      </x:c>
+      <x:c r="C177" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D177" s="6" t="str">
+        <x:v>10.1109/tcsi.2024.3438789</x:v>
+      </x:c>
+      <x:c r="E177" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tcsi.2024.3438789</x:v>
+      </x:c>
+      <x:c r="F177" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G177" s="6" t="str">
+        <x:v>https://api.crossref.org/works/10.1109/TCSI.2024.3438789</x:v>
+      </x:c>
+      <x:c r="H177" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/weidebao?lang=zh</x:v>
+      </x:c>
+      <x:c r="I177" s="6" t="str">
+        <x:v>registered_doi_metadata_verified_landing_unverified</x:v>
+      </x:c>
+      <x:c r="J177" s="6" t="str">
+        <x:v>官方书目与Crossref登记元数据的题名、作者核对；文章落地页未确认。 成果类型：期刊论文。 链接核验状态：登记书目元数据已核，文章落地页未核。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="64" customHeight="1">
+      <x:c r="A178" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B178" s="6" t="str">
+        <x:v>Edge Word-Line Reliability Problem in 3-D NAND Flash Memory: Observations, Analysis, and Solutions</x:v>
+      </x:c>
+      <x:c r="C178" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D178" s="6" t="str">
+        <x:v>10.1109/tvlsi.2023.3249183</x:v>
+      </x:c>
+      <x:c r="E178" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tvlsi.2023.3249183</x:v>
+      </x:c>
+      <x:c r="F178" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G178" s="6" t="str">
+        <x:v>https://api.crossref.org/works/10.1109/TVLSI.2023.3249183</x:v>
+      </x:c>
+      <x:c r="H178" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/weidebao?lang=zh</x:v>
+      </x:c>
+      <x:c r="I178" s="6" t="str">
+        <x:v>registered_doi_metadata_verified_landing_unverified</x:v>
+      </x:c>
+      <x:c r="J178" s="6" t="str">
+        <x:v>官方书目与Crossref登记元数据的题名、作者核对；文章落地页未确认。 成果类型：期刊论文。 链接核验状态：登记书目元数据已核，文章落地页未核。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="64" customHeight="1">
+      <x:c r="A179" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B179" s="6" t="str">
+        <x:v>TCSE: A Target Cell States Elimination Coding Strategy for Highly Reliable Data Storage Based on 3-D nand Flash Memory</x:v>
+      </x:c>
+      <x:c r="C179" s="6" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="D179" s="6" t="str">
+        <x:v>10.1109/tcad.2022.3155380</x:v>
+      </x:c>
+      <x:c r="E179" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tcad.2022.3155380</x:v>
+      </x:c>
+      <x:c r="F179" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G179" s="6" t="str">
+        <x:v>https://api.crossref.org/works/10.1109/TCAD.2022.3155380</x:v>
+      </x:c>
+      <x:c r="H179" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/weidebao?lang=zh</x:v>
+      </x:c>
+      <x:c r="I179" s="6" t="str">
+        <x:v>registered_doi_metadata_verified_landing_unverified</x:v>
+      </x:c>
+      <x:c r="J179" s="6" t="str">
+        <x:v>官方书目与Crossref登记元数据的题名、作者核对；文章落地页未确认。 成果类型：期刊论文。 链接核验状态：登记书目元数据已核，文章落地页未核。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="64" customHeight="1">
+      <x:c r="A180" s="6" t="str">
+        <x:v>刘晓东</x:v>
+      </x:c>
+      <x:c r="B180" s="6" t="str">
+        <x:v>A Hybrid Fault Diagnosis Framework Based on Test Stimulus Optimization and MPCNN for Analog Circuits</x:v>
+      </x:c>
+      <x:c r="C180" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D180" s="6" t="str">
+        <x:v>10.1109/tim.2025.3588964</x:v>
+      </x:c>
+      <x:c r="E180" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tim.2025.3588964</x:v>
+      </x:c>
+      <x:c r="F180" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G180" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=A%20Hybrid%20Fault%20Diagnosis%20Framework%20Based%20On%20Test%20Stimulus%20Optimization%20and%20MPCNN%20for%20Analogue%20Circuits&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="H180" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuxiaodong?lang=zh</x:v>
+      </x:c>
+      <x:c r="I180" s="6" t="str">
+        <x:v>registered_doi_metadata_verified_landing_unverified</x:v>
+      </x:c>
+      <x:c r="J180" s="6" t="str">
+        <x:v>选择IEEE正式期刊条目，而非检索首位的2024年SSRN预印本。官网写Analogue且刊名误写Instrument；Crossref正式登记为Analog及Instrumentation，题名其余内容和四位作者一致。 成果类型：期刊论文。 链接核验状态：登记书目元数据已核，文章落地页未核。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="64" customHeight="1">
+      <x:c r="A181" s="6" t="str">
+        <x:v>刘晓东</x:v>
+      </x:c>
+      <x:c r="B181" s="6" t="str">
+        <x:v>A Novel Incipient Fault Diagnosis Method for Analogue Circuits Based on an MLDLCN</x:v>
+      </x:c>
+      <x:c r="C181" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D181" s="6" t="str">
+        <x:v>10.1007/s00034-023-02524-x</x:v>
+      </x:c>
+      <x:c r="E181" s="6" t="str">
+        <x:v>https://doi.org/10.1007/s00034-023-02524-x</x:v>
+      </x:c>
+      <x:c r="F181" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G181" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=A%20Novel%20Incipient%20Fault%20Diagnosis%20Method%20for%20Analogue%20Circuits%20Based%20on%20an%20MLDLCN&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="H181" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuxiaodong?lang=zh</x:v>
+      </x:c>
+      <x:c r="I181" s="6" t="str">
+        <x:v>registered_doi_metadata_verified_landing_unverified</x:v>
+      </x:c>
+      <x:c r="J181" s="6" t="str">
+        <x:v>官网2023对应Crossref online date 2023-10-10；卷43期2的印刷出版月为2024-02。线上与印刷日期并存，不称二者矛盾。 成果类型：期刊论文。 链接核验状态：登记书目元数据已核，文章落地页未核。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="64" customHeight="1">
+      <x:c r="A182" s="6" t="str">
+        <x:v>刘晓东</x:v>
+      </x:c>
+      <x:c r="B182" s="6" t="str">
+        <x:v>UHA‐CycleGAN: Unpaired hybrid attention network based on CycleGAN for terahertz image super‐resolution</x:v>
+      </x:c>
+      <x:c r="C182" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D182" s="6" t="str">
+        <x:v>10.1049/ipr2.12804</x:v>
+      </x:c>
+      <x:c r="E182" s="6" t="str">
+        <x:v>https://doi.org/10.1049/ipr2.12804</x:v>
+      </x:c>
+      <x:c r="F182" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G182" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=UHA-CycleGAN%20unpaired%20hybrid%20attention%20network%20based%20on%20CycleGAN%20for%20terahertz%20image%20super-resolution&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="H182" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuxiaodong?lang=zh</x:v>
+      </x:c>
+      <x:c r="I182" s="6" t="str">
+        <x:v>registered_doi_metadata_verified_landing_unverified</x:v>
+      </x:c>
+      <x:c r="J182" s="6" t="str">
+        <x:v>官方书目与Crossref登记元数据的题名、作者核对；文章落地页未确认。 成果类型：期刊论文。 链接核验状态：登记书目元数据已核，文章落地页未核。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="64" customHeight="1">
+      <x:c r="A183" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B183" s="6" t="str">
+        <x:v>Particle estimation algorithm using correlation of observation for nonlinear system state</x:v>
+      </x:c>
+      <x:c r="C183" s="6" t="n">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="D183" s="6" t="str">
+        <x:v>10.1049/el:20080179</x:v>
+      </x:c>
+      <x:c r="E183" s="6" t="str">
+        <x:v>https://doi.org/10.1049/el:20080179</x:v>
+      </x:c>
+      <x:c r="F183" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G183" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Particle%20estimation%20algorithm%20using%20correlation%20of%20observation%20for%20nonlinear%20system%20state&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="H183" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ljzsylmy?lang=zh</x:v>
+      </x:c>
+      <x:c r="I183" s="6" t="str">
+        <x:v>registered_doi_metadata_verified_landing_unverified</x:v>
+      </x:c>
+      <x:c r="J183" s="6" t="str">
+        <x:v>官网期卷页为44(8):553-554且年份留空；Crossref精确题名及作者匹配，年份2008、页码553-555。采用登记元数据，官网页码差异保留。 成果类型：期刊论文。 链接核验状态：登记书目元数据已核，文章落地页未核。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="64" customHeight="1">
+      <x:c r="A184" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B184" s="6" t="str">
+        <x:v>Improved particle filter for nonlinear system state</x:v>
+      </x:c>
+      <x:c r="C184" s="6" t="n">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="D184" s="6" t="str">
+        <x:v>10.1049/el:20082403</x:v>
+      </x:c>
+      <x:c r="E184" s="6" t="str">
+        <x:v>https://doi.org/10.1049/el:20082403</x:v>
+      </x:c>
+      <x:c r="F184" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G184" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Improved%20particle%20filter%20for%20nonlinear%20system%20state&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="H184" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ljzsylmy?lang=zh</x:v>
+      </x:c>
+      <x:c r="I184" s="6" t="str">
+        <x:v>registered_doi_metadata_verified_landing_unverified</x:v>
+      </x:c>
+      <x:c r="J184" s="6" t="str">
+        <x:v>官方书目与Crossref登记元数据的题名、作者核对；文章落地页未确认。 成果类型：期刊论文。 链接核验状态：登记书目元数据已核，文章落地页未核。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="64" customHeight="1">
+      <x:c r="A185" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B185" s="6" t="str">
+        <x:v>Particle estimation algorithm using angle between observation vectors for nonlinear system state</x:v>
+      </x:c>
+      <x:c r="C185" s="6" t="str"/>
+      <x:c r="D185" s="6" t="str"/>
+      <x:c r="E185" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ljzsylmy?lang=zh</x:v>
+      </x:c>
+      <x:c r="F185" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G185" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ljzsylmy?lang=zh</x:v>
+      </x:c>
+      <x:c r="H185" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ljzsylmy?lang=zh</x:v>
+      </x:c>
+      <x:c r="I185" s="6" t="str">
+        <x:v>official_profile_bibliography_only</x:v>
+      </x:c>
+      <x:c r="J185" s="6" t="str">
+        <x:v>官网未填发表年份及DOI；Crossref题名检索仅返回其他论文，不能把correlation论文DOI嫁接本篇。保留官网书目及null年份/DOI。 成果类型：期刊论文。 链接核验状态：仅官方主页书目，尚未取得独立文章或 DOI 核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" ht="64" customHeight="1">
+      <x:c r="A186" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B186" s="6" t="str">
+        <x:v>基于LS-SVM和核密度估计的概率性风电功率预测</x:v>
+      </x:c>
+      <x:c r="C186" s="6" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D186" s="6" t="str">
+        <x:v>10.16526/j.cnki.11-4762/tp.2019.12.008</x:v>
+      </x:c>
+      <x:c r="E186" s="6" t="str">
+        <x:v>https://doi.org/10.16526/j.cnki.11-4762/tp.2019.12.008</x:v>
+      </x:c>
+      <x:c r="F186" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G186" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+      <x:c r="H186" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+      <x:c r="I186" s="6" t="str">
+        <x:v>official_profile_doi_unverified</x:v>
+      </x:c>
+      <x:c r="J186" s="6" t="str">
+        <x:v>DOI与书目来自官网；Crossref按DOI请求返回404。该错误不等于文章或DOI不存在；未独立核验。 成果类型：期刊论文。 链接核验状态：DOI 来自官方主页，未独立核验；Crossref 未收录或访问失败不等于 DOI 无效。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="64" customHeight="1">
+      <x:c r="A187" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B187" s="6" t="str">
+        <x:v>基于ARM和FPGA的LXI触发机制实现</x:v>
+      </x:c>
+      <x:c r="C187" s="6" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="D187" s="6" t="str">
+        <x:v>10.19651/j.cnki.emt.2013.06.019</x:v>
+      </x:c>
+      <x:c r="E187" s="6" t="str">
+        <x:v>https://doi.org/10.19651/j.cnki.emt.2013.06.019</x:v>
+      </x:c>
+      <x:c r="F187" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G187" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+      <x:c r="H187" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+      <x:c r="I187" s="6" t="str">
+        <x:v>official_profile_doi_unverified</x:v>
+      </x:c>
+      <x:c r="J187" s="6" t="str">
+        <x:v>DOI与书目来自官网；Crossref按DOI请求返回404，未独立核验，不据此认定DOI无效。 成果类型：期刊论文。 链接核验状态：DOI 来自官方主页，未独立核验；Crossref 未收录或访问失败不等于 DOI 无效。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="64" customHeight="1">
+      <x:c r="A188" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B188" s="6" t="str">
+        <x:v>超宽带穿墙雷达动目标跟踪成像算法研究</x:v>
+      </x:c>
+      <x:c r="C188" s="6" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="D188" s="6" t="str">
+        <x:v>10.19650/j.cnki.cjsi.2010.03.004</x:v>
+      </x:c>
+      <x:c r="E188" s="6" t="str">
+        <x:v>https://doi.org/10.19650/j.cnki.cjsi.2010.03.004</x:v>
+      </x:c>
+      <x:c r="F188" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G188" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+      <x:c r="H188" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+      <x:c r="I188" s="6" t="str">
+        <x:v>official_profile_doi_unverified</x:v>
+      </x:c>
+      <x:c r="J188" s="6" t="str">
+        <x:v>DOI与书目来自官网；Crossref按DOI请求返回404，未独立核验，不据此认定DOI无效。 成果类型：期刊论文。 链接核验状态：DOI 来自官方主页，未独立核验；Crossref 未收录或访问失败不等于 DOI 无效。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="64" customHeight="1">
+      <x:c r="A189" s="6" t="str">
+        <x:v>尹洪涛</x:v>
+      </x:c>
+      <x:c r="B189" s="6" t="str">
+        <x:v>人工智能基础创新与实践应用</x:v>
+      </x:c>
+      <x:c r="C189" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D189" s="6" t="str"/>
+      <x:c r="E189" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhengwenbin?lang=en</x:v>
+      </x:c>
+      <x:c r="F189" s="6" t="str">
+        <x:v>book</x:v>
+      </x:c>
+      <x:c r="G189" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhengwenbin?lang=en</x:v>
+      </x:c>
+      <x:c r="H189" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yinhongtao</x:v>
+      </x:c>
+      <x:c r="I189" s="6" t="str">
+        <x:v>coauthor_official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J189" s="6" t="str">
+        <x:v>共同作者郑文斌官方动态正文出版物栏目明确三位作者刘冰、郑文斌、尹洪涛；类型为书籍，不称期刊论文。 成果类型：书籍。 链接核验状态：共同作者官方成果列表佐证，未核独立出版页面。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="64" customHeight="1">
+      <x:c r="A190" s="6" t="str">
+        <x:v>马云彤</x:v>
+      </x:c>
+      <x:c r="B190" s="6" t="str">
+        <x:v>锂离子电池剩余寿命间接预测方法</x:v>
+      </x:c>
+      <x:c r="C190" s="6" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="D190" s="6" t="str"/>
+      <x:c r="E190" s="6" t="str">
+        <x:v>https://zkzx.cbpt.cnki.net/portal/journal/portal/client/paper/f0bd7e751c8b598182004df46d93c856</x:v>
+      </x:c>
+      <x:c r="F190" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G190" s="6" t="str">
+        <x:v>https://zkzx.cbpt.cnki.net/portal/journal/portal/client/paper/f0bd7e751c8b598182004df46d93c856</x:v>
+      </x:c>
+      <x:c r="H190" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mayuntong</x:v>
+      </x:c>
+      <x:c r="I190" s="6" t="str">
+        <x:v>article_metadata_verified</x:v>
+      </x:c>
+      <x:c r="J190" s="6" t="str">
+        <x:v>期刊官方CNKI托管题录直接列马云彤及HIT自动化测试与控制系署名；2014,9(1):28–36，仅元数据无需全文权限。 成果类型：期刊论文。 链接核验状态：期刊官方题录已核，仅确认元数据，不声称阅读全文。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" ht="64" customHeight="1">
+      <x:c r="A191" s="6" t="str">
+        <x:v>刘兆庆</x:v>
+      </x:c>
+      <x:c r="B191" s="6" t="str">
+        <x:v>Asymmetric Programming: A Highly Reliable Metadata Allocation Strategy for MLC NAND Flash Memory-Based Sensor Systems</x:v>
+      </x:c>
+      <x:c r="C191" s="6" t="n">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="D191" s="6" t="str">
+        <x:v>10.3390/s141018851</x:v>
+      </x:c>
+      <x:c r="E191" s="6" t="str">
+        <x:v>https://doi.org/10.3390/s141018851</x:v>
+      </x:c>
+      <x:c r="F191" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G191" s="6" t="str">
+        <x:v>https://doaj.org/article/ce60ba40229a4bf899e686c85fb34853</x:v>
+      </x:c>
+      <x:c r="H191" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuzhaoqing</x:v>
+      </x:c>
+      <x:c r="I191" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J191" s="6" t="str">
+        <x:v>DOAJ出版商提交元数据明确本人HIT自动化测试与控制系单位及同事乔立岩；仅核元数据。出版社落地页429、PubMed验证码页，不绕过也不声称文章页验证。 成果类型：期刊论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查。 Crossref 登记出版日期：2014-10-10；不自动作为全文访问或学位授予证据。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" ht="64" customHeight="1">
+      <x:c r="A192" s="6" t="str">
+        <x:v>刘旺</x:v>
+      </x:c>
+      <x:c r="B192" s="6" t="str">
+        <x:v>Research on digital balance technology based on wireless transmission</x:v>
+      </x:c>
+      <x:c r="C192" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D192" s="6" t="str">
+        <x:v>10.1088/1742-6596/3207/1/012104</x:v>
+      </x:c>
+      <x:c r="E192" s="6" t="str">
+        <x:v>https://doi.org/10.1088/1742-6596/3207/1/012104</x:v>
+      </x:c>
+      <x:c r="F192" s="6" t="str">
+        <x:v>conference_article</x:v>
+      </x:c>
+      <x:c r="G192" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuwang</x:v>
+      </x:c>
+      <x:c r="H192" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuwang</x:v>
+      </x:c>
+      <x:c r="I192" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J192" s="6" t="str">
+        <x:v>成果类型：会议论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查。 Crossref 登记出版日期：2026-04-01；不自动作为全文访问或学位授予证据。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" ht="64" customHeight="1">
+      <x:c r="A193" s="6" t="str">
+        <x:v>刘旺</x:v>
+      </x:c>
+      <x:c r="B193" s="6" t="str">
+        <x:v>Research on Fault Monitoring and Diagnosis Methods for Wind Tunnel Balance</x:v>
+      </x:c>
+      <x:c r="C193" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D193" s="6" t="str">
+        <x:v>10.1109/icetac65964.2025.11144012</x:v>
+      </x:c>
+      <x:c r="E193" s="6" t="str">
+        <x:v>https://doi.org/10.1109/icetac65964.2025.11144012</x:v>
+      </x:c>
+      <x:c r="F193" s="6" t="str">
+        <x:v>conference_paper</x:v>
+      </x:c>
+      <x:c r="G193" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuwang</x:v>
+      </x:c>
+      <x:c r="H193" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuwang</x:v>
+      </x:c>
+      <x:c r="I193" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J193" s="6" t="str">
+        <x:v>成果类型：会议论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查。 Crossref 登记出版日期：2025-06-20；不自动作为全文访问或学位授予证据。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" ht="64" customHeight="1">
+      <x:c r="A194" s="6" t="str">
+        <x:v>刘旺</x:v>
+      </x:c>
+      <x:c r="B194" s="6" t="str">
+        <x:v>Research on static calibration method of wind tunnel balance based on CNN</x:v>
+      </x:c>
+      <x:c r="C194" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D194" s="6" t="str">
+        <x:v>10.1088/1742-6596/2897/1/012027</x:v>
+      </x:c>
+      <x:c r="E194" s="6" t="str">
+        <x:v>https://doi.org/10.1088/1742-6596/2897/1/012027</x:v>
+      </x:c>
+      <x:c r="F194" s="6" t="str">
+        <x:v>conference_article</x:v>
+      </x:c>
+      <x:c r="G194" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuwang</x:v>
+      </x:c>
+      <x:c r="H194" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuwang</x:v>
+      </x:c>
+      <x:c r="I194" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J194" s="6" t="str">
+        <x:v>成果类型：会议论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查。 Crossref 登记出版日期：2024-11-01；不自动作为全文访问或学位授予证据。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" ht="64" customHeight="1">
+      <x:c r="A195" s="6" t="str">
+        <x:v>邹昕光</x:v>
+      </x:c>
+      <x:c r="B195" s="6" t="str">
+        <x:v>PN制导律多模型自适应辨识滤波方法</x:v>
+      </x:c>
+      <x:c r="C195" s="6" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="D195" s="6" t="str">
+        <x:v>10.3873/j.issn.1000-1328.2016.08.010</x:v>
+      </x:c>
+      <x:c r="E195" s="6" t="str">
+        <x:v>https://doi.org/10.3873/j.issn.1000-1328.2016.08.010</x:v>
+      </x:c>
+      <x:c r="F195" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G195" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zouxinguang</x:v>
+      </x:c>
+      <x:c r="H195" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zouxinguang</x:v>
+      </x:c>
+      <x:c r="I195" s="6" t="str">
+        <x:v>doi_explicitly_listed_on_official_profile</x:v>
+      </x:c>
+      <x:c r="J195" s="6" t="str">
+        <x:v>DOI来自官网英文栏目，原文全角点与空格仅做字符规范化。 成果类型：期刊论文。 链接核验状态：DOI 由官方主页明确列出，尚未独立确认文章落地页。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" ht="64" customHeight="1">
+      <x:c r="A196" s="6" t="str">
+        <x:v>邹昕光</x:v>
+      </x:c>
+      <x:c r="B196" s="6" t="str">
+        <x:v>Active Defense Guidance Law via Cooperative Identification and Estimation</x:v>
+      </x:c>
+      <x:c r="C196" s="6" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="D196" s="6" t="str">
+        <x:v>10.2514/1.g003372</x:v>
+      </x:c>
+      <x:c r="E196" s="6" t="str">
+        <x:v>https://doi.org/10.2514/1.g003372</x:v>
+      </x:c>
+      <x:c r="F196" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G196" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zouxinguang</x:v>
+      </x:c>
+      <x:c r="H196" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zouxinguang</x:v>
+      </x:c>
+      <x:c r="I196" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J196" s="6" t="str">
+        <x:v>官网doi栏实际填SCI索引号，未误当DOI；本次Crossref精确题名/作者/期刊匹配后补DOI。 成果类型：期刊论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查。 Crossref 登记出版日期：2018-11；不自动作为全文访问或学位授予证据。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" ht="64" customHeight="1">
+      <x:c r="A197" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B197" s="6" t="str">
+        <x:v>Uncertainty-oriented collaborative learning for on-orbit state-of-health estimation of satellite lithium-ion batteries considering multi-operating conditions</x:v>
+      </x:c>
+      <x:c r="C197" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D197" s="6" t="str">
+        <x:v>10.1016/j.apenergy.2026.127457</x:v>
+      </x:c>
+      <x:c r="E197" s="6" t="str">
+        <x:v>https://doi.org/10.1016/j.apenergy.2026.127457</x:v>
+      </x:c>
+      <x:c r="F197" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G197" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/songyuchen</x:v>
+      </x:c>
+      <x:c r="H197" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/songyuchen</x:v>
+      </x:c>
+      <x:c r="I197" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J197" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查，不等同阅读全文。 Crossref 登记出版日期：2026-04；保留登记精度，不改写官网年份。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="64" customHeight="1">
+      <x:c r="A198" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B198" s="6" t="str">
+        <x:v>PIAN: A physics-informed assimilation neural network for temporal super-resolution reconstruction of sensor data in satellite attitude control system</x:v>
+      </x:c>
+      <x:c r="C198" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D198" s="6" t="str">
+        <x:v>10.1016/j.aei.2025.103805</x:v>
+      </x:c>
+      <x:c r="E198" s="6" t="str">
+        <x:v>https://doi.org/10.1016/j.aei.2025.103805</x:v>
+      </x:c>
+      <x:c r="F198" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G198" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/songyuchen</x:v>
+      </x:c>
+      <x:c r="H198" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/songyuchen</x:v>
+      </x:c>
+      <x:c r="I198" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J198" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查，不等同阅读全文。 Crossref 登记出版日期：2025-11；保留登记精度，不改写官网年份。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="64" customHeight="1">
+      <x:c r="A199" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B199" s="6" t="str">
+        <x:v>Stress-informed transfer learning: Accelerated battery life evaluation model across diverse operating conditions and cell mechanisms</x:v>
+      </x:c>
+      <x:c r="C199" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D199" s="6" t="str">
+        <x:v>10.1016/j.egyai.2025.100629</x:v>
+      </x:c>
+      <x:c r="E199" s="6" t="str">
+        <x:v>https://doi.org/10.1016/j.egyai.2025.100629</x:v>
+      </x:c>
+      <x:c r="F199" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G199" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/songyuchen</x:v>
+      </x:c>
+      <x:c r="H199" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/songyuchen</x:v>
+      </x:c>
+      <x:c r="I199" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J199" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查，不等同阅读全文。 Crossref 登记出版日期：2025-12；保留登记精度，不改写官网年份。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" ht="64" customHeight="1">
+      <x:c r="A200" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B200" s="6" t="str">
+        <x:v>基于物理门控时频协同判别网络的喷水推进装置控制系统故障诊断方法</x:v>
+      </x:c>
+      <x:c r="C200" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D200" s="6" t="str"/>
+      <x:c r="E200" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaotianyu</x:v>
+      </x:c>
+      <x:c r="F200" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G200" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaotianyu</x:v>
+      </x:c>
+      <x:c r="H200" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaotianyu</x:v>
+      </x:c>
+      <x:c r="I200" s="6" t="str">
+        <x:v>official_selected_bibliography_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J200" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：仅官方精选书目，未独立核验文章或出版落地页。 Crossref 查询遇限流，未重试；不能据此认定 DOI 不存在。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="64" customHeight="1">
+      <x:c r="A201" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B201" s="6" t="str">
+        <x:v>Corrosion Detection of Gearbox Based on Wavelet Time-Frequency Attention Fusion Network</x:v>
+      </x:c>
+      <x:c r="C201" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D201" s="6" t="str">
+        <x:v>10.1109/tim.2025.3644553</x:v>
+      </x:c>
+      <x:c r="E201" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tim.2025.3644553</x:v>
+      </x:c>
+      <x:c r="F201" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G201" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaotianyu</x:v>
+      </x:c>
+      <x:c r="H201" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaotianyu</x:v>
+      </x:c>
+      <x:c r="I201" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J201" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查，不等同阅读全文。 Crossref 登记出版日期：2026；保留登记精度，不改写官网年份。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="64" customHeight="1">
+      <x:c r="A202" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B202" s="6" t="str">
+        <x:v>Analog Circuit Test Point Selection Method for Fault Diagnosis Based on Deep Reinforcement Learning</x:v>
+      </x:c>
+      <x:c r="C202" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D202" s="6" t="str">
+        <x:v>10.1016/j.engappai.2025.113294</x:v>
+      </x:c>
+      <x:c r="E202" s="6" t="str">
+        <x:v>https://doi.org/10.1016/j.engappai.2025.113294</x:v>
+      </x:c>
+      <x:c r="F202" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G202" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaotianyu</x:v>
+      </x:c>
+      <x:c r="H202" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaotianyu</x:v>
+      </x:c>
+      <x:c r="I202" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J202" s="6" t="str">
+        <x:v> 官网年与Crossref登记出版年不同，可能为在线/卷期差别但原因未独立核实，两者保留。 成果类型：期刊论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查，不等同阅读全文。 Crossref 登记出版日期：2026-01；保留登记精度，不改写官网年份。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="64" customHeight="1">
+      <x:c r="A203" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B203" s="6" t="str">
+        <x:v>Defect Detection and Classification of Railway Track System for In-Service MRT in Tropical Regions Using a Contactless TBMS and Adaptive-DBSCAN</x:v>
+      </x:c>
+      <x:c r="C203" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D203" s="6" t="str">
+        <x:v>10.1109/tits.2025.3597656</x:v>
+      </x:c>
+      <x:c r="E203" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tits.2025.3597656</x:v>
+      </x:c>
+      <x:c r="F203" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G203" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/changyongqi</x:v>
+      </x:c>
+      <x:c r="H203" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/changyongqi</x:v>
+      </x:c>
+      <x:c r="I203" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J203" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查，不等同阅读全文。 Crossref 登记出版日期：2025-11；保留登记精度，不改写官网年份。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="64" customHeight="1">
+      <x:c r="A204" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B204" s="6" t="str">
+        <x:v>EMAE-based Rail Structural Health Monitoring Using Doublelayer Signal Processing and Spectrum Information Entropy</x:v>
+      </x:c>
+      <x:c r="C204" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D204" s="6" t="str">
+        <x:v>10.1109/tits.2024.3358390</x:v>
+      </x:c>
+      <x:c r="E204" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tits.2024.3358390</x:v>
+      </x:c>
+      <x:c r="F204" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G204" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/changyongqi</x:v>
+      </x:c>
+      <x:c r="H204" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/changyongqi</x:v>
+      </x:c>
+      <x:c r="I204" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J204" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查，不等同阅读全文。 Crossref 登记出版日期：2024-09；保留登记精度，不改写官网年份。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="64" customHeight="1">
+      <x:c r="A205" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B205" s="6" t="str">
+        <x:v>Rail crack detection using optimal local mean decomposition and cepstral information coefficient based on electromagnetic acoustic emission technology</x:v>
+      </x:c>
+      <x:c r="C205" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D205" s="6" t="str">
+        <x:v>10.1109/tim.2024.3375420</x:v>
+      </x:c>
+      <x:c r="E205" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tim.2024.3375420</x:v>
+      </x:c>
+      <x:c r="F205" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G205" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/changyongqi</x:v>
+      </x:c>
+      <x:c r="H205" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/changyongqi</x:v>
+      </x:c>
+      <x:c r="I205" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J205" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查，不等同阅读全文。 Crossref 登记出版日期：2024；保留登记精度，不改写官网年份。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="64" customHeight="1">
+      <x:c r="A206" s="6" t="str">
+        <x:v>王俊凯</x:v>
+      </x:c>
+      <x:c r="B206" s="6" t="str">
+        <x:v>Physics-guided neural network integrating uncertainty evolution for spatiotemporal wind speed prediction</x:v>
+      </x:c>
+      <x:c r="C206" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D206" s="6" t="str">
+        <x:v>10.1038/s43247-026-03844-x</x:v>
+      </x:c>
+      <x:c r="E206" s="6" t="str">
+        <x:v>https://doi.org/10.1038/s43247-026-03844-x</x:v>
+      </x:c>
+      <x:c r="F206" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G206" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WangJunkai</x:v>
+      </x:c>
+      <x:c r="H206" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WangJunkai</x:v>
+      </x:c>
+      <x:c r="I206" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J206" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查，不等同阅读全文。 Crossref 登记出版日期：2026-07-28；保留登记精度，不改写官网年份。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="64" customHeight="1">
+      <x:c r="A207" s="6" t="str">
+        <x:v>王俊凯</x:v>
+      </x:c>
+      <x:c r="B207" s="6" t="str">
+        <x:v>Deep neural network based on dynamic attention and layer attention for meteorological data downscaling</x:v>
+      </x:c>
+      <x:c r="C207" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D207" s="6" t="str">
+        <x:v>10.1016/j.isprsjprs.2024.06.020</x:v>
+      </x:c>
+      <x:c r="E207" s="6" t="str">
+        <x:v>https://doi.org/10.1016/j.isprsjprs.2024.06.020</x:v>
+      </x:c>
+      <x:c r="F207" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G207" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WangJunkai</x:v>
+      </x:c>
+      <x:c r="H207" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WangJunkai</x:v>
+      </x:c>
+      <x:c r="I207" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J207" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查，不等同阅读全文。 Crossref 登记出版日期：2024-09；保留登记精度，不改写官网年份。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="64" customHeight="1">
+      <x:c r="A208" s="6" t="str">
+        <x:v>王俊凯</x:v>
+      </x:c>
+      <x:c r="B208" s="6" t="str">
+        <x:v>Neural network based on high freedom dynamic collaboration of flows for meteorological data temporal downscaling</x:v>
+      </x:c>
+      <x:c r="C208" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D208" s="6" t="str">
+        <x:v>10.1016/j.isprsjprs.2026.02.017</x:v>
+      </x:c>
+      <x:c r="E208" s="6" t="str">
+        <x:v>https://doi.org/10.1016/j.isprsjprs.2026.02.017</x:v>
+      </x:c>
+      <x:c r="F208" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G208" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WangJunkai</x:v>
+      </x:c>
+      <x:c r="H208" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WangJunkai</x:v>
+      </x:c>
+      <x:c r="I208" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J208" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查，不等同阅读全文。 Crossref 登记出版日期：2026-04；保留登记精度，不改写官网年份。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" ht="64" customHeight="1">
+      <x:c r="A209" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B209" s="6" t="str">
+        <x:v>A Virtual Domain-Driven Semi-Supervised Hyperbolic Metric Network with Domain-Class Adversarial Decoupling for Aircraft Engine Inter-Shaft Bearings Fault diagnosis</x:v>
+      </x:c>
+      <x:c r="C209" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D209" s="6" t="str">
+        <x:v>10.1109/tsmc.2025.3598790</x:v>
+      </x:c>
+      <x:c r="E209" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tsmc.2025.3598790</x:v>
+      </x:c>
+      <x:c r="F209" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G209" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yangjingli</x:v>
+      </x:c>
+      <x:c r="H209" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangchangdong</x:v>
+      </x:c>
+      <x:c r="I209" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J209" s="6" t="str">
+        <x:v>明确导师兼共同作者官方代表性论文栏目署名ChangdongWang，保留必要书目。 成果类型：期刊论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查，不等同阅读全文。 Crossref 登记出版日期：2025-11；保留登记精度，不改写官网年份。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="64" customHeight="1">
+      <x:c r="A210" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B210" s="6" t="str">
+        <x:v>Continuous Evolution Learning: A Lightweight Expansion-Based Continuous Learning Method for Train Transmission Systems Fault Diagnosis</x:v>
+      </x:c>
+      <x:c r="C210" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D210" s="6" t="str">
+        <x:v>10.1109/tii.2025.3588608</x:v>
+      </x:c>
+      <x:c r="E210" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tii.2025.3588608</x:v>
+      </x:c>
+      <x:c r="F210" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G210" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yangjingli</x:v>
+      </x:c>
+      <x:c r="H210" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangchangdong</x:v>
+      </x:c>
+      <x:c r="I210" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J210" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查，不等同阅读全文。 Crossref 登记出版日期：2025-11；保留登记精度，不改写官网年份。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="64" customHeight="1">
+      <x:c r="A211" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B211" s="6" t="str">
+        <x:v>A Shapelet-Driven Distillation Generation Method for Generalized Zero-Shot Learning in Compound Fault Diagnosis</x:v>
+      </x:c>
+      <x:c r="C211" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D211" s="6" t="str">
+        <x:v>10.1016/j.neucom.2025.131184</x:v>
+      </x:c>
+      <x:c r="E211" s="6" t="str">
+        <x:v>https://doi.org/10.1016/j.neucom.2025.131184</x:v>
+      </x:c>
+      <x:c r="F211" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G211" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yangjingli</x:v>
+      </x:c>
+      <x:c r="H211" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangchangdong</x:v>
+      </x:c>
+      <x:c r="I211" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J211" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 书目元数据已核，文章落地页未检查，不等同阅读全文。 Crossref 登记出版日期：2025-11；保留登记精度，不改写官网年份。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" ht="64" customHeight="1">
+      <x:c r="A212" s="6" t="str">
+        <x:v>吴艳</x:v>
+      </x:c>
+      <x:c r="B212" s="6" t="str">
+        <x:v>LabVIEW虚拟仪器设计指南</x:v>
+      </x:c>
+      <x:c r="C212" s="6" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="D212" s="6" t="str"/>
+      <x:c r="E212" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WuYan</x:v>
+      </x:c>
+      <x:c r="F212" s="6" t="str">
+        <x:v>book</x:v>
+      </x:c>
+      <x:c r="G212" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WuYan</x:v>
+      </x:c>
+      <x:c r="H212" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WuYan</x:v>
+      </x:c>
+      <x:c r="I212" s="6" t="str">
+        <x:v>official_selected_bibliography_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J212" s="6" t="str">
+        <x:v>成果类型：书籍。 链接核验状态：仅官方精选书目，未独立核验文章或出版落地页。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" ht="64" customHeight="1">
+      <x:c r="A213" s="6" t="str">
+        <x:v>吴艳</x:v>
+      </x:c>
+      <x:c r="B213" s="6" t="str">
+        <x:v>单片机原理级应用（第三版）</x:v>
+      </x:c>
+      <x:c r="C213" s="6" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="D213" s="6" t="str"/>
+      <x:c r="E213" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WuYan</x:v>
+      </x:c>
+      <x:c r="F213" s="6" t="str">
+        <x:v>book</x:v>
+      </x:c>
+      <x:c r="G213" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WuYan</x:v>
+      </x:c>
+      <x:c r="H213" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WuYan</x:v>
+      </x:c>
+      <x:c r="I213" s="6" t="str">
+        <x:v>official_selected_bibliography_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J213" s="6" t="str">
+        <x:v>按本人书目原文“级”保留，疑似“及”字错误，未核正式题名不静默修正。 成果类型：书籍。 链接核验状态：仅官方精选书目，未独立核验文章或出版落地页。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" ht="64" customHeight="1">
+      <x:c r="A214" s="6" t="str">
+        <x:v>郑文斌</x:v>
+      </x:c>
+      <x:c r="B214" s="6" t="str">
+        <x:v>人工智能基础创新与实践应用</x:v>
+      </x:c>
+      <x:c r="C214" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D214" s="6" t="str"/>
+      <x:c r="E214" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhengwenbin</x:v>
+      </x:c>
+      <x:c r="F214" s="6" t="str">
+        <x:v>book</x:v>
+      </x:c>
+      <x:c r="G214" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhengwenbin</x:v>
+      </x:c>
+      <x:c r="H214" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhengwenbin</x:v>
+      </x:c>
+      <x:c r="I214" s="6" t="str">
+        <x:v>official_selected_bibliography_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J214" s="6" t="str">
+        <x:v>成果类型：书籍。 链接核验状态：仅官方精选书目，未独立核验文章或出版落地页。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c121d6008884063"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b1683504f1243cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -39532,10 +45990,1676 @@
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
     </x:row>
+    <x:row r="269" ht="64" customHeight="1">
+      <x:c r="A269" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B269" s="6" t="str">
+        <x:v>weidebao-official</x:v>
+      </x:c>
+      <x:c r="C269" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/weidebao?lang=zh</x:v>
+      </x:c>
+      <x:c r="D269" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E269" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" ht="64" customHeight="1">
+      <x:c r="A270" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B270" s="6" t="str">
+        <x:v>harbin-measurement-engineering-roster</x:v>
+      </x:c>
+      <x:c r="C270" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D270" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E270" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271" ht="64" customHeight="1">
+      <x:c r="A271" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B271" s="6" t="str">
+        <x:v>weidebao-english-header</x:v>
+      </x:c>
+      <x:c r="C271" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/weidebao?lang=en</x:v>
+      </x:c>
+      <x:c r="D271" s="6" t="str">
+        <x:v>official_english_header_read</x:v>
+      </x:c>
+      <x:c r="E271" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" ht="64" customHeight="1">
+      <x:c r="A272" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B272" s="6" t="str">
+        <x:v>weidebao-2023-fund-news</x:v>
+      </x:c>
+      <x:c r="C272" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/2023/0612/c9262a313766/page.htm</x:v>
+      </x:c>
+      <x:c r="D272" s="6" t="str">
+        <x:v>official_dated_news_read</x:v>
+      </x:c>
+      <x:c r="E272" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" ht="64" customHeight="1">
+      <x:c r="A273" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B273" s="6" t="str">
+        <x:v>weidebao-lld-crossref</x:v>
+      </x:c>
+      <x:c r="C273" s="6" t="str">
+        <x:v>https://api.crossref.org/works/10.1109/TCSI.2024.3438789</x:v>
+      </x:c>
+      <x:c r="D273" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E273" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" ht="64" customHeight="1">
+      <x:c r="A274" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B274" s="6" t="str">
+        <x:v>weidebao-edge-crossref</x:v>
+      </x:c>
+      <x:c r="C274" s="6" t="str">
+        <x:v>https://api.crossref.org/works/10.1109/TVLSI.2023.3249183</x:v>
+      </x:c>
+      <x:c r="D274" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E274" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" ht="64" customHeight="1">
+      <x:c r="A275" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B275" s="6" t="str">
+        <x:v>weidebao-tcse-crossref</x:v>
+      </x:c>
+      <x:c r="C275" s="6" t="str">
+        <x:v>https://api.crossref.org/works/10.1109/TCAD.2022.3155380</x:v>
+      </x:c>
+      <x:c r="D275" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E275" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276" ht="64" customHeight="1">
+      <x:c r="A276" s="6" t="str">
+        <x:v>刘晓东</x:v>
+      </x:c>
+      <x:c r="B276" s="6" t="str">
+        <x:v>liuxiaodong-official</x:v>
+      </x:c>
+      <x:c r="C276" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuxiaodong?lang=zh</x:v>
+      </x:c>
+      <x:c r="D276" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E276" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" ht="64" customHeight="1">
+      <x:c r="A277" s="6" t="str">
+        <x:v>刘晓东</x:v>
+      </x:c>
+      <x:c r="B277" s="6" t="str">
+        <x:v>harbin-measurement-engineering-roster</x:v>
+      </x:c>
+      <x:c r="C277" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D277" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E277" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" ht="64" customHeight="1">
+      <x:c r="A278" s="6" t="str">
+        <x:v>刘晓东</x:v>
+      </x:c>
+      <x:c r="B278" s="6" t="str">
+        <x:v>liuxiaodong-english-header</x:v>
+      </x:c>
+      <x:c r="C278" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuxiaodong?lang=en</x:v>
+      </x:c>
+      <x:c r="D278" s="6" t="str">
+        <x:v>official_english_header_read</x:v>
+      </x:c>
+      <x:c r="E278" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279" ht="64" customHeight="1">
+      <x:c r="A279" s="6" t="str">
+        <x:v>刘晓东</x:v>
+      </x:c>
+      <x:c r="B279" s="6" t="str">
+        <x:v>liuxiaodong-hybrid-crossref</x:v>
+      </x:c>
+      <x:c r="C279" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=A%20Hybrid%20Fault%20Diagnosis%20Framework%20Based%20On%20Test%20Stimulus%20Optimization%20and%20MPCNN%20for%20Analogue%20Circuits&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D279" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E279" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280" ht="64" customHeight="1">
+      <x:c r="A280" s="6" t="str">
+        <x:v>刘晓东</x:v>
+      </x:c>
+      <x:c r="B280" s="6" t="str">
+        <x:v>liuxiaodong-incipient-crossref</x:v>
+      </x:c>
+      <x:c r="C280" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=A%20Novel%20Incipient%20Fault%20Diagnosis%20Method%20for%20Analogue%20Circuits%20Based%20on%20an%20MLDLCN&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D280" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E280" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" ht="64" customHeight="1">
+      <x:c r="A281" s="6" t="str">
+        <x:v>刘晓东</x:v>
+      </x:c>
+      <x:c r="B281" s="6" t="str">
+        <x:v>liuxiaodong-uha-crossref</x:v>
+      </x:c>
+      <x:c r="C281" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=UHA-CycleGAN%20unpaired%20hybrid%20attention%20network%20based%20on%20CycleGAN%20for%20terahertz%20image%20super-resolution&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D281" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E281" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" ht="64" customHeight="1">
+      <x:c r="A282" s="6" t="str">
+        <x:v>孙震</x:v>
+      </x:c>
+      <x:c r="B282" s="6" t="str">
+        <x:v>sunzhen-official</x:v>
+      </x:c>
+      <x:c r="C282" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/sunzhen?lang=zh</x:v>
+      </x:c>
+      <x:c r="D282" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E282" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" ht="64" customHeight="1">
+      <x:c r="A283" s="6" t="str">
+        <x:v>孙震</x:v>
+      </x:c>
+      <x:c r="B283" s="6" t="str">
+        <x:v>harbin-measurement-engineering-roster</x:v>
+      </x:c>
+      <x:c r="C283" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D283" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E283" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" ht="64" customHeight="1">
+      <x:c r="A284" s="6" t="str">
+        <x:v>孙震</x:v>
+      </x:c>
+      <x:c r="B284" s="6" t="str">
+        <x:v>sunzhen-english-header</x:v>
+      </x:c>
+      <x:c r="C284" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/sunzhen?lang=en</x:v>
+      </x:c>
+      <x:c r="D284" s="6" t="str">
+        <x:v>official_english_header_read</x:v>
+      </x:c>
+      <x:c r="E284" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" ht="64" customHeight="1">
+      <x:c r="A285" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B285" s="6" t="str">
+        <x:v>ljzsylmy-official</x:v>
+      </x:c>
+      <x:c r="C285" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ljzsylmy?lang=zh</x:v>
+      </x:c>
+      <x:c r="D285" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E285" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" ht="64" customHeight="1">
+      <x:c r="A286" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B286" s="6" t="str">
+        <x:v>harbin-measurement-engineering-roster</x:v>
+      </x:c>
+      <x:c r="C286" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D286" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E286" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" ht="64" customHeight="1">
+      <x:c r="A287" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B287" s="6" t="str">
+        <x:v>ljzsylmy-english-header</x:v>
+      </x:c>
+      <x:c r="C287" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ljzsylmy?lang=en</x:v>
+      </x:c>
+      <x:c r="D287" s="6" t="str">
+        <x:v>official_english_header_read</x:v>
+      </x:c>
+      <x:c r="E287" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" ht="64" customHeight="1">
+      <x:c r="A288" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B288" s="6" t="str">
+        <x:v>ljzsylmy-correlation-crossref</x:v>
+      </x:c>
+      <x:c r="C288" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Particle%20estimation%20algorithm%20using%20correlation%20of%20observation%20for%20nonlinear%20system%20state&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D288" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E288" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289" ht="64" customHeight="1">
+      <x:c r="A289" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B289" s="6" t="str">
+        <x:v>ljzsylmy-improved-crossref</x:v>
+      </x:c>
+      <x:c r="C289" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Improved%20particle%20filter%20for%20nonlinear%20system%20state&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D289" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E289" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290" ht="64" customHeight="1">
+      <x:c r="A290" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B290" s="6" t="str">
+        <x:v>ljzsylmy-angle-crossref</x:v>
+      </x:c>
+      <x:c r="C290" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Particle%20estimation%20algorithm%20using%20angle%20between%20observation%20vectors%20for%20nonlinear%20system%20state&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D290" s="6" t="str">
+        <x:v>crossref_exact_match_not_found</x:v>
+      </x:c>
+      <x:c r="E290" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291" ht="64" customHeight="1">
+      <x:c r="A291" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B291" s="6" t="str">
+        <x:v>mengsw-official</x:v>
+      </x:c>
+      <x:c r="C291" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=zh</x:v>
+      </x:c>
+      <x:c r="D291" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E291" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292" ht="64" customHeight="1">
+      <x:c r="A292" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B292" s="6" t="str">
+        <x:v>harbin-measurement-engineering-roster</x:v>
+      </x:c>
+      <x:c r="C292" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D292" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E292" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293" ht="64" customHeight="1">
+      <x:c r="A293" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B293" s="6" t="str">
+        <x:v>mengsw-english-header</x:v>
+      </x:c>
+      <x:c r="C293" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mengsw?lang=en</x:v>
+      </x:c>
+      <x:c r="D293" s="6" t="str">
+        <x:v>official_english_header_read</x:v>
+      </x:c>
+      <x:c r="E293" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" ht="64" customHeight="1">
+      <x:c r="A294" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B294" s="6" t="str">
+        <x:v>fuping-official</x:v>
+      </x:c>
+      <x:c r="C294" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/fuping?lang=zh</x:v>
+      </x:c>
+      <x:c r="D294" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E294" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" ht="64" customHeight="1">
+      <x:c r="A295" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B295" s="6" t="str">
+        <x:v>wangyiping-university-attributed-profile</x:v>
+      </x:c>
+      <x:c r="C295" s="6" t="str">
+        <x:v>https://www.sohu.com/a/1080526727_407305</x:v>
+      </x:c>
+      <x:c r="D295" s="6" t="str">
+        <x:v>university_attributed_external_profile_read</x:v>
+      </x:c>
+      <x:c r="E295" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296" ht="64" customHeight="1">
+      <x:c r="A296" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B296" s="6" t="str">
+        <x:v>mengsw-wind-crossref</x:v>
+      </x:c>
+      <x:c r="C296" s="6" t="str">
+        <x:v>https://api.crossref.org/works/10.16526/j.cnki.11-4762/tp.2019.12.008</x:v>
+      </x:c>
+      <x:c r="D296" s="6" t="str">
+        <x:v>crossref_metadata_unavailable</x:v>
+      </x:c>
+      <x:c r="E296" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297" ht="64" customHeight="1">
+      <x:c r="A297" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B297" s="6" t="str">
+        <x:v>mengsw-lxi-crossref</x:v>
+      </x:c>
+      <x:c r="C297" s="6" t="str">
+        <x:v>https://api.crossref.org/works/10.19651/j.cnki.emt.2013.06.019</x:v>
+      </x:c>
+      <x:c r="D297" s="6" t="str">
+        <x:v>crossref_metadata_unavailable</x:v>
+      </x:c>
+      <x:c r="E297" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" ht="64" customHeight="1">
+      <x:c r="A298" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B298" s="6" t="str">
+        <x:v>mengsw-radar-crossref</x:v>
+      </x:c>
+      <x:c r="C298" s="6" t="str">
+        <x:v>https://api.crossref.org/works/10.19650/j.cnki.cjsi.2010.03.004</x:v>
+      </x:c>
+      <x:c r="D298" s="6" t="str">
+        <x:v>crossref_metadata_unavailable</x:v>
+      </x:c>
+      <x:c r="E298" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299" ht="64" customHeight="1">
+      <x:c r="A299" s="6" t="str">
+        <x:v>尹洪涛</x:v>
+      </x:c>
+      <x:c r="B299" s="6" t="str">
+        <x:v>yinhongtao-official</x:v>
+      </x:c>
+      <x:c r="C299" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yinhongtao</x:v>
+      </x:c>
+      <x:c r="D299" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E299" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300" ht="64" customHeight="1">
+      <x:c r="A300" s="6" t="str">
+        <x:v>尹洪涛</x:v>
+      </x:c>
+      <x:c r="B300" s="6" t="str">
+        <x:v>harbin-measurement-roster</x:v>
+      </x:c>
+      <x:c r="C300" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D300" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E300" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301" ht="64" customHeight="1">
+      <x:c r="A301" s="6" t="str">
+        <x:v>尹洪涛</x:v>
+      </x:c>
+      <x:c r="B301" s="6" t="str">
+        <x:v>yinhongtao-source-3</x:v>
+      </x:c>
+      <x:c r="C301" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/2023/0227/c16426a289552/page.htm</x:v>
+      </x:c>
+      <x:c r="D301" s="6" t="str">
+        <x:v>official_institute_faculty_biography_read</x:v>
+      </x:c>
+      <x:c r="E301" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" ht="64" customHeight="1">
+      <x:c r="A302" s="6" t="str">
+        <x:v>尹洪涛</x:v>
+      </x:c>
+      <x:c r="B302" s="6" t="str">
+        <x:v>yinhongtao-source-4</x:v>
+      </x:c>
+      <x:c r="C302" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhengwenbin?lang=en</x:v>
+      </x:c>
+      <x:c r="D302" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E302" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" ht="64" customHeight="1">
+      <x:c r="A303" s="6" t="str">
+        <x:v>马云彤</x:v>
+      </x:c>
+      <x:c r="B303" s="6" t="str">
+        <x:v>mayuntong-official</x:v>
+      </x:c>
+      <x:c r="C303" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/mayuntong</x:v>
+      </x:c>
+      <x:c r="D303" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E303" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" ht="64" customHeight="1">
+      <x:c r="A304" s="6" t="str">
+        <x:v>马云彤</x:v>
+      </x:c>
+      <x:c r="B304" s="6" t="str">
+        <x:v>harbin-measurement-roster</x:v>
+      </x:c>
+      <x:c r="C304" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D304" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E304" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305" ht="64" customHeight="1">
+      <x:c r="A305" s="6" t="str">
+        <x:v>马云彤</x:v>
+      </x:c>
+      <x:c r="B305" s="6" t="str">
+        <x:v>mayuntong-source-3</x:v>
+      </x:c>
+      <x:c r="C305" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/2023/0227/c16426a289585/page.htm</x:v>
+      </x:c>
+      <x:c r="D305" s="6" t="str">
+        <x:v>official_institute_faculty_biography_read</x:v>
+      </x:c>
+      <x:c r="E305" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306" ht="64" customHeight="1">
+      <x:c r="A306" s="6" t="str">
+        <x:v>马云彤</x:v>
+      </x:c>
+      <x:c r="B306" s="6" t="str">
+        <x:v>mayuntong-source-4</x:v>
+      </x:c>
+      <x:c r="C306" s="6" t="str">
+        <x:v>https://zkzx.cbpt.cnki.net/portal/journal/portal/client/paper/f0bd7e751c8b598182004df46d93c856</x:v>
+      </x:c>
+      <x:c r="D306" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E306" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307" ht="64" customHeight="1">
+      <x:c r="A307" s="6" t="str">
+        <x:v>刘兆庆</x:v>
+      </x:c>
+      <x:c r="B307" s="6" t="str">
+        <x:v>liuzhaoqing-official</x:v>
+      </x:c>
+      <x:c r="C307" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuzhaoqing</x:v>
+      </x:c>
+      <x:c r="D307" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E307" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308" ht="64" customHeight="1">
+      <x:c r="A308" s="6" t="str">
+        <x:v>刘兆庆</x:v>
+      </x:c>
+      <x:c r="B308" s="6" t="str">
+        <x:v>harbin-measurement-roster</x:v>
+      </x:c>
+      <x:c r="C308" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D308" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E308" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309" ht="64" customHeight="1">
+      <x:c r="A309" s="6" t="str">
+        <x:v>刘兆庆</x:v>
+      </x:c>
+      <x:c r="B309" s="6" t="str">
+        <x:v>liuzhaoqing-source-3</x:v>
+      </x:c>
+      <x:c r="C309" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/2023/0227/c16426a289576/page.htm</x:v>
+      </x:c>
+      <x:c r="D309" s="6" t="str">
+        <x:v>official_institute_faculty_biography_read</x:v>
+      </x:c>
+      <x:c r="E309" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310" ht="64" customHeight="1">
+      <x:c r="A310" s="6" t="str">
+        <x:v>刘兆庆</x:v>
+      </x:c>
+      <x:c r="B310" s="6" t="str">
+        <x:v>liuzhaoqing-source-4</x:v>
+      </x:c>
+      <x:c r="C310" s="6" t="str">
+        <x:v>https://doaj.org/article/ce60ba40229a4bf899e686c85fb34853</x:v>
+      </x:c>
+      <x:c r="D310" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E310" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311" ht="64" customHeight="1">
+      <x:c r="A311" s="6" t="str">
+        <x:v>刘兆庆</x:v>
+      </x:c>
+      <x:c r="B311" s="6" t="str">
+        <x:v>liuzhaoqing-source-5</x:v>
+      </x:c>
+      <x:c r="C311" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Asymmetric%20Programming%3A%20A%20Highly%20Reliable%20Metadata%20Allocation%20Strategy%20for%20MLC%20NAND%20Flash%20Memory-Based%20Sensor%20Systems&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D311" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E311" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312" ht="64" customHeight="1">
+      <x:c r="A312" s="6" t="str">
+        <x:v>刘旺</x:v>
+      </x:c>
+      <x:c r="B312" s="6" t="str">
+        <x:v>liuwang-official</x:v>
+      </x:c>
+      <x:c r="C312" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liuwang</x:v>
+      </x:c>
+      <x:c r="D312" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E312" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313" ht="64" customHeight="1">
+      <x:c r="A313" s="6" t="str">
+        <x:v>刘旺</x:v>
+      </x:c>
+      <x:c r="B313" s="6" t="str">
+        <x:v>harbin-measurement-roster</x:v>
+      </x:c>
+      <x:c r="C313" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D313" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E313" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314" ht="64" customHeight="1">
+      <x:c r="A314" s="6" t="str">
+        <x:v>刘旺</x:v>
+      </x:c>
+      <x:c r="B314" s="6" t="str">
+        <x:v>liuwang-source-3</x:v>
+      </x:c>
+      <x:c r="C314" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Research%20on%20digital%20balance%20technology%20based%20on%20wireless%20transmission&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D314" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E314" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315" ht="64" customHeight="1">
+      <x:c r="A315" s="6" t="str">
+        <x:v>刘旺</x:v>
+      </x:c>
+      <x:c r="B315" s="6" t="str">
+        <x:v>liuwang-source-4</x:v>
+      </x:c>
+      <x:c r="C315" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Research%20on%20Fault%20Monitoring%20and%20Diagnosis%20Methods%20for%20Wind%20Tunnel%20Balance&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D315" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E315" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316" ht="64" customHeight="1">
+      <x:c r="A316" s="6" t="str">
+        <x:v>刘旺</x:v>
+      </x:c>
+      <x:c r="B316" s="6" t="str">
+        <x:v>liuwang-source-5</x:v>
+      </x:c>
+      <x:c r="C316" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Research%20on%20static%20calibration%20method%20of%20wind%20tunnel%20balance%20based%20on%20CNN&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D316" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E316" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317" ht="64" customHeight="1">
+      <x:c r="A317" s="6" t="str">
+        <x:v>邹昕光</x:v>
+      </x:c>
+      <x:c r="B317" s="6" t="str">
+        <x:v>zouxinguang-official</x:v>
+      </x:c>
+      <x:c r="C317" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zouxinguang</x:v>
+      </x:c>
+      <x:c r="D317" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E317" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318" ht="64" customHeight="1">
+      <x:c r="A318" s="6" t="str">
+        <x:v>邹昕光</x:v>
+      </x:c>
+      <x:c r="B318" s="6" t="str">
+        <x:v>harbin-measurement-roster</x:v>
+      </x:c>
+      <x:c r="C318" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D318" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E318" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319" ht="64" customHeight="1">
+      <x:c r="A319" s="6" t="str">
+        <x:v>邹昕光</x:v>
+      </x:c>
+      <x:c r="B319" s="6" t="str">
+        <x:v>zouxinguang-source-3</x:v>
+      </x:c>
+      <x:c r="C319" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/2023/0227/c16426a289583/page.htm</x:v>
+      </x:c>
+      <x:c r="D319" s="6" t="str">
+        <x:v>official_institute_faculty_biography_read</x:v>
+      </x:c>
+      <x:c r="E319" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320" ht="64" customHeight="1">
+      <x:c r="A320" s="6" t="str">
+        <x:v>邹昕光</x:v>
+      </x:c>
+      <x:c r="B320" s="6" t="str">
+        <x:v>zouxinguang-source-4</x:v>
+      </x:c>
+      <x:c r="C320" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Active%20Defense%20Guidance%20Law%20via%20Cooperative%20Identification%20and%20Estimation&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D320" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E320" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321" ht="64" customHeight="1">
+      <x:c r="A321" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B321" s="6" t="str">
+        <x:v>songyuchen-official</x:v>
+      </x:c>
+      <x:c r="C321" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/songyuchen</x:v>
+      </x:c>
+      <x:c r="D321" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E321" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322" ht="64" customHeight="1">
+      <x:c r="A322" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B322" s="6" t="str">
+        <x:v>harbin-measurement-roster</x:v>
+      </x:c>
+      <x:c r="C322" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D322" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E322" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323" ht="64" customHeight="1">
+      <x:c r="A323" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B323" s="6" t="str">
+        <x:v>songyuchen-source-3</x:v>
+      </x:c>
+      <x:c r="C323" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/pengyu</x:v>
+      </x:c>
+      <x:c r="D323" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E323" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324" ht="64" customHeight="1">
+      <x:c r="A324" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B324" s="6" t="str">
+        <x:v>songyuchen-source-4</x:v>
+      </x:c>
+      <x:c r="C324" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Uncertainty-oriented%20collaborative%20learning%20for%20on-orbit%20state-of-health%20estimation%20of%20satellite%20lithium-ion%20batteries%20considering%20multi-operating%20conditions&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D324" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E324" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325" ht="64" customHeight="1">
+      <x:c r="A325" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B325" s="6" t="str">
+        <x:v>songyuchen-source-5</x:v>
+      </x:c>
+      <x:c r="C325" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=PIAN%3A%20A%20physics-informed%20assimilation%20neural%20network%20for%20temporal%20super-resolution%20reconstruction%20of%20sensor%20data%20in%20satellite%20attitude%20control%20system&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D325" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E325" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326" ht="64" customHeight="1">
+      <x:c r="A326" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B326" s="6" t="str">
+        <x:v>songyuchen-source-6</x:v>
+      </x:c>
+      <x:c r="C326" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Stress-informed%20transfer%20learning%3A%20Accelerated%20battery%20life%20evaluation%20model%20across%20diverse%20operating%20conditions%20and%20cell%20mechanisms&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D326" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E326" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327" ht="64" customHeight="1">
+      <x:c r="A327" s="6" t="str">
+        <x:v>王本宽</x:v>
+      </x:c>
+      <x:c r="B327" s="6" t="str">
+        <x:v>wangbenkuan-official</x:v>
+      </x:c>
+      <x:c r="C327" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangbenkuan</x:v>
+      </x:c>
+      <x:c r="D327" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E327" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328" ht="64" customHeight="1">
+      <x:c r="A328" s="6" t="str">
+        <x:v>王本宽</x:v>
+      </x:c>
+      <x:c r="B328" s="6" t="str">
+        <x:v>harbin-measurement-roster</x:v>
+      </x:c>
+      <x:c r="C328" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D328" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E328" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329" ht="64" customHeight="1">
+      <x:c r="A329" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B329" s="6" t="str">
+        <x:v>gaotianyu-official</x:v>
+      </x:c>
+      <x:c r="C329" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaotianyu</x:v>
+      </x:c>
+      <x:c r="D329" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E329" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330" ht="64" customHeight="1">
+      <x:c r="A330" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B330" s="6" t="str">
+        <x:v>harbin-measurement-roster</x:v>
+      </x:c>
+      <x:c r="C330" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D330" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E330" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331" ht="64" customHeight="1">
+      <x:c r="A331" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B331" s="6" t="str">
+        <x:v>gaotianyu-source-3</x:v>
+      </x:c>
+      <x:c r="C331" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/16427/list.htm</x:v>
+      </x:c>
+      <x:c r="D331" s="6" t="str">
+        <x:v>official_web_body_read</x:v>
+      </x:c>
+      <x:c r="E331" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332" ht="64" customHeight="1">
+      <x:c r="A332" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B332" s="6" t="str">
+        <x:v>gaotianyu-source-4</x:v>
+      </x:c>
+      <x:c r="C332" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yangjingli</x:v>
+      </x:c>
+      <x:c r="D332" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E332" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333" ht="64" customHeight="1">
+      <x:c r="A333" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B333" s="6" t="str">
+        <x:v>gaotianyu-source-5</x:v>
+      </x:c>
+      <x:c r="C333" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Corrosion%20Detection%20of%20Gearbox%20Based%20on%20Wavelet%20Time-Frequency%20Attention%20Fusion%20Network&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D333" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E333" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334" ht="64" customHeight="1">
+      <x:c r="A334" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B334" s="6" t="str">
+        <x:v>gaotianyu-source-6</x:v>
+      </x:c>
+      <x:c r="C334" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Analog%20Circuit%20Test%20Point%20Selection%20Method%20for%20Fault%20Diagnosis%20Based%20on%20Deep%20Reinforcement%20Learning&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D334" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E334" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335" ht="64" customHeight="1">
+      <x:c r="A335" s="6" t="str">
+        <x:v>尉志良</x:v>
+      </x:c>
+      <x:c r="B335" s="6" t="str">
+        <x:v>WeiZhiliang-official</x:v>
+      </x:c>
+      <x:c r="C335" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WeiZhiliang</x:v>
+      </x:c>
+      <x:c r="D335" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E335" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336" ht="64" customHeight="1">
+      <x:c r="A336" s="6" t="str">
+        <x:v>尉志良</x:v>
+      </x:c>
+      <x:c r="B336" s="6" t="str">
+        <x:v>harbin-measurement-roster</x:v>
+      </x:c>
+      <x:c r="C336" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D336" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E336" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337" ht="64" customHeight="1">
+      <x:c r="A337" s="6" t="str">
+        <x:v>尉志良</x:v>
+      </x:c>
+      <x:c r="B337" s="6" t="str">
+        <x:v>WeiZhiliang-source-3</x:v>
+      </x:c>
+      <x:c r="C337" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/16427/list.htm</x:v>
+      </x:c>
+      <x:c r="D337" s="6" t="str">
+        <x:v>official_web_body_read</x:v>
+      </x:c>
+      <x:c r="E337" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338" ht="64" customHeight="1">
+      <x:c r="A338" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B338" s="6" t="str">
+        <x:v>changyongqi-official</x:v>
+      </x:c>
+      <x:c r="C338" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/changyongqi</x:v>
+      </x:c>
+      <x:c r="D338" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E338" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339" ht="64" customHeight="1">
+      <x:c r="A339" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B339" s="6" t="str">
+        <x:v>harbin-measurement-roster</x:v>
+      </x:c>
+      <x:c r="C339" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D339" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E339" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340" ht="64" customHeight="1">
+      <x:c r="A340" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B340" s="6" t="str">
+        <x:v>changyongqi-source-3</x:v>
+      </x:c>
+      <x:c r="C340" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/16427/list.htm</x:v>
+      </x:c>
+      <x:c r="D340" s="6" t="str">
+        <x:v>official_web_body_read</x:v>
+      </x:c>
+      <x:c r="E340" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341" ht="64" customHeight="1">
+      <x:c r="A341" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B341" s="6" t="str">
+        <x:v>changyongqi-source-4</x:v>
+      </x:c>
+      <x:c r="C341" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Defect%20Detection%20and%20Classification%20of%20Railway%20Track%20System%20for%20In-Service%20MRT%20in%20Tropical%20Regions%20Using%20a%20Contactless%20TBMS%20and%20Adaptive-DBSCAN&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D341" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E341" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342" ht="64" customHeight="1">
+      <x:c r="A342" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B342" s="6" t="str">
+        <x:v>changyongqi-source-5</x:v>
+      </x:c>
+      <x:c r="C342" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=EMAE-based%20Rail%20Structural%20Health%20Monitoring%20Using%20Doublelayer%20Signal%20Processing%20and%20Spectrum%20Information%20Entropy&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D342" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E342" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343" ht="64" customHeight="1">
+      <x:c r="A343" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B343" s="6" t="str">
+        <x:v>changyongqi-source-6</x:v>
+      </x:c>
+      <x:c r="C343" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Rail%20crack%20detection%20using%20optimal%20local%20mean%20decomposition%20and%20cepstral%20information%20coefficient%20based%20on%20electromagnetic%20acoustic%20emission%20technology&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D343" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E343" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344" ht="64" customHeight="1">
+      <x:c r="A344" s="6" t="str">
+        <x:v>王俊凯</x:v>
+      </x:c>
+      <x:c r="B344" s="6" t="str">
+        <x:v>WangJunkai-official</x:v>
+      </x:c>
+      <x:c r="C344" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WangJunkai</x:v>
+      </x:c>
+      <x:c r="D344" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E344" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345" ht="64" customHeight="1">
+      <x:c r="A345" s="6" t="str">
+        <x:v>王俊凯</x:v>
+      </x:c>
+      <x:c r="B345" s="6" t="str">
+        <x:v>harbin-measurement-roster</x:v>
+      </x:c>
+      <x:c r="C345" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D345" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E345" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346" ht="64" customHeight="1">
+      <x:c r="A346" s="6" t="str">
+        <x:v>王俊凯</x:v>
+      </x:c>
+      <x:c r="B346" s="6" t="str">
+        <x:v>WangJunkai-source-3</x:v>
+      </x:c>
+      <x:c r="C346" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/16427/list.htm</x:v>
+      </x:c>
+      <x:c r="D346" s="6" t="str">
+        <x:v>official_web_body_read</x:v>
+      </x:c>
+      <x:c r="E346" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347" ht="64" customHeight="1">
+      <x:c r="A347" s="6" t="str">
+        <x:v>王俊凯</x:v>
+      </x:c>
+      <x:c r="B347" s="6" t="str">
+        <x:v>WangJunkai-source-4</x:v>
+      </x:c>
+      <x:c r="C347" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/linlianlei</x:v>
+      </x:c>
+      <x:c r="D347" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E347" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348" ht="64" customHeight="1">
+      <x:c r="A348" s="6" t="str">
+        <x:v>王俊凯</x:v>
+      </x:c>
+      <x:c r="B348" s="6" t="str">
+        <x:v>WangJunkai-source-5</x:v>
+      </x:c>
+      <x:c r="C348" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Physics-guided%20neural%20network%20integrating%20uncertainty%20evolution%20for%20spatiotemporal%20wind%20speed%20prediction&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D348" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E348" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349" ht="64" customHeight="1">
+      <x:c r="A349" s="6" t="str">
+        <x:v>王俊凯</x:v>
+      </x:c>
+      <x:c r="B349" s="6" t="str">
+        <x:v>WangJunkai-source-6</x:v>
+      </x:c>
+      <x:c r="C349" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Deep%20neural%20network%20based%20on%20dynamic%20attention%20and%20layer%20attention%20for%20meteorological%20data%20downscaling&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D349" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E349" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350" ht="64" customHeight="1">
+      <x:c r="A350" s="6" t="str">
+        <x:v>王俊凯</x:v>
+      </x:c>
+      <x:c r="B350" s="6" t="str">
+        <x:v>WangJunkai-source-7</x:v>
+      </x:c>
+      <x:c r="C350" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Neural%20network%20based%20on%20high%20freedom%20dynamic%20collaboration%20of%20flows%20for%20meteorological%20data%20temporal%20downscaling&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D350" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E350" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351" ht="64" customHeight="1">
+      <x:c r="A351" s="6" t="str">
+        <x:v>姚博文</x:v>
+      </x:c>
+      <x:c r="B351" s="6" t="str">
+        <x:v>yaobowen-official</x:v>
+      </x:c>
+      <x:c r="C351" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yaobowen</x:v>
+      </x:c>
+      <x:c r="D351" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E351" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352" ht="64" customHeight="1">
+      <x:c r="A352" s="6" t="str">
+        <x:v>姚博文</x:v>
+      </x:c>
+      <x:c r="B352" s="6" t="str">
+        <x:v>harbin-measurement-roster</x:v>
+      </x:c>
+      <x:c r="C352" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D352" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E352" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353" ht="64" customHeight="1">
+      <x:c r="A353" s="6" t="str">
+        <x:v>姚博文</x:v>
+      </x:c>
+      <x:c r="B353" s="6" t="str">
+        <x:v>yaobowen-source-3</x:v>
+      </x:c>
+      <x:c r="C353" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/16427/list.htm</x:v>
+      </x:c>
+      <x:c r="D353" s="6" t="str">
+        <x:v>official_web_body_read</x:v>
+      </x:c>
+      <x:c r="E353" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354" ht="64" customHeight="1">
+      <x:c r="A354" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B354" s="6" t="str">
+        <x:v>wangchangdong-official</x:v>
+      </x:c>
+      <x:c r="C354" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wangchangdong</x:v>
+      </x:c>
+      <x:c r="D354" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E354" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355" ht="64" customHeight="1">
+      <x:c r="A355" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B355" s="6" t="str">
+        <x:v>harbin-measurement-roster</x:v>
+      </x:c>
+      <x:c r="C355" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D355" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E355" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356" ht="64" customHeight="1">
+      <x:c r="A356" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B356" s="6" t="str">
+        <x:v>wangchangdong-source-3</x:v>
+      </x:c>
+      <x:c r="C356" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yangjingli</x:v>
+      </x:c>
+      <x:c r="D356" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E356" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357" ht="64" customHeight="1">
+      <x:c r="A357" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B357" s="6" t="str">
+        <x:v>wangchangdong-source-4</x:v>
+      </x:c>
+      <x:c r="C357" s="6" t="str">
+        <x:v>https://www.ntu.edu.sg/emerl/about-us/contact-us</x:v>
+      </x:c>
+      <x:c r="D357" s="6" t="str">
+        <x:v>official_web_body_read</x:v>
+      </x:c>
+      <x:c r="E357" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358" ht="64" customHeight="1">
+      <x:c r="A358" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B358" s="6" t="str">
+        <x:v>wangchangdong-source-5</x:v>
+      </x:c>
+      <x:c r="C358" s="6" t="str">
+        <x:v>https://civil.hit.edu.cn/kxyys/list.htm</x:v>
+      </x:c>
+      <x:c r="D358" s="6" t="str">
+        <x:v>official_web_body_read</x:v>
+      </x:c>
+      <x:c r="E358" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359" ht="64" customHeight="1">
+      <x:c r="A359" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B359" s="6" t="str">
+        <x:v>wangchangdong-source-6</x:v>
+      </x:c>
+      <x:c r="C359" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=A%20Virtual%20Domain-Driven%20Semi-Supervised%20Hyperbolic%20Metric%20Network%20with%20Domain-Class%20Adversarial%20Decoupling%20for%20Aircraft%20Engine%20Inter-Shaft%20Bearings%20Fault%20diagnosis&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D359" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E359" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360" ht="64" customHeight="1">
+      <x:c r="A360" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B360" s="6" t="str">
+        <x:v>wangchangdong-source-7</x:v>
+      </x:c>
+      <x:c r="C360" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Continuous%20Evolution%20Learning%3A%20A%20Lightweight%20Expansion-Based%20Continuous%20Learning%20Method%20for%20Train%20Transmission%20Systems%20Fault%20Diagnosis&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D360" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E360" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361" ht="64" customHeight="1">
+      <x:c r="A361" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B361" s="6" t="str">
+        <x:v>wangchangdong-source-8</x:v>
+      </x:c>
+      <x:c r="C361" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=A%20Shapelet-Driven%20Distillation%20Generation%20Method%20for%20Generalized%20Zero-Shot%20Learning%20in%20Compound%20Fault%20Diagnosis&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D361" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E361" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362" ht="64" customHeight="1">
+      <x:c r="A362" s="6" t="str">
+        <x:v>吴艳</x:v>
+      </x:c>
+      <x:c r="B362" s="6" t="str">
+        <x:v>WuYan-official</x:v>
+      </x:c>
+      <x:c r="C362" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/WuYan</x:v>
+      </x:c>
+      <x:c r="D362" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E362" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363" ht="64" customHeight="1">
+      <x:c r="A363" s="6" t="str">
+        <x:v>吴艳</x:v>
+      </x:c>
+      <x:c r="B363" s="6" t="str">
+        <x:v>harbin-measurement-roster</x:v>
+      </x:c>
+      <x:c r="C363" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D363" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E363" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364" ht="64" customHeight="1">
+      <x:c r="A364" s="6" t="str">
+        <x:v>郑文斌</x:v>
+      </x:c>
+      <x:c r="B364" s="6" t="str">
+        <x:v>zhengwenbin-official</x:v>
+      </x:c>
+      <x:c r="C364" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhengwenbin</x:v>
+      </x:c>
+      <x:c r="D364" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E364" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365" ht="64" customHeight="1">
+      <x:c r="A365" s="6" t="str">
+        <x:v>郑文斌</x:v>
+      </x:c>
+      <x:c r="B365" s="6" t="str">
+        <x:v>harbin-measurement-roster</x:v>
+      </x:c>
+      <x:c r="C365" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19283/list.htm</x:v>
+      </x:c>
+      <x:c r="D365" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E365" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="366" ht="64" customHeight="1">
+      <x:c r="A366" s="6" t="str">
+        <x:v>郑文斌</x:v>
+      </x:c>
+      <x:c r="B366" s="6" t="str">
+        <x:v>zhengwenbin-source-3</x:v>
+      </x:c>
+      <x:c r="C366" s="6" t="str">
+        <x:v>https://tce.hit.edu.cn/16428/list.htm</x:v>
+      </x:c>
+      <x:c r="D366" s="6" t="str">
+        <x:v>official_web_body_read</x:v>
+      </x:c>
+      <x:c r="E366" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb1a92ca2ea84352"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb1e4ace121445f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/hit-seie.xlsx
+++ b/site/exports/hit-seie.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re2532eb5601b446d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R3673877d0ca14e62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rda79ee985c174a4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R9274e9a79892498f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R0639878522ed414e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rcb8d0d4e7bd44b32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rc52ff6551b9d4ca8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R8c3581b1e22c4e32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R8ea7c4188e3f4479"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R04a9c03d37474048"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T1_0" displayName="T1_0" ref="A1:G104" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T1_0" displayName="T1_0" ref="A1:G124" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T1_1" displayName="T1_1" ref="A1:Q773" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T1_1" displayName="T1_1" ref="A1:Q926" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -179,7 +179,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T1_2" displayName="T1_2" ref="A1:J29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T1_2" displayName="T1_2" ref="A1:J37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="导师姓名"/>
@@ -197,7 +197,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T1_3" displayName="T1_3" ref="A1:J214" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T1_3" displayName="T1_3" ref="A1:J261" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -215,7 +215,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T1_4" displayName="T1_4" ref="A1:E366" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T1_4" displayName="T1_4" ref="A1:E469" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -2823,10 +2823,470 @@
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
     </x:row>
+    <x:row r="105" ht="64" customHeight="1">
+      <x:c r="A105" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B105" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C105" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D105" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+      <x:c r="E105" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F105" s="6" t="str">
+        <x:v>本次查阅未找到本人学位导师或合作导师的直接公开证据，未以合著、团队归属或学生名单推断师承。；精选成果不代表完整发表清单；不纳入私人联系方式、出生信息或学生名单，原始证据缓存不公开。；英文把1989.03–1996.06列为Assistant Professor，并另列1991.07–1996.06 Lecturer；与中文分段及职称不同。保留中文任职分段和英文晋升日期，不将重叠区间强行消除。；2003年访学机构中文为英国曼彻斯特大学理工学院，未强行归并其历史法人名称。；成果日期差异：MSDP-Net: A Multi-Scale Domain Perception Network for HRRP Target Recognition；官网日期2025-05，Crossref 登记日期2025-07-26，不擅自解释或覆盖。；成果日期差异：Inverse Synthetic Aperture Radar Image Multi-Modal Zero-Shot Learning Based on the Scattering Center Model and Neighbor-Adapted Locally Linear Embedding；官网日期2025-07，Crossref 登记日期2025-02-19，不擅自解释或覆盖。</x:v>
+      </x:c>
+      <x:c r="G105" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="64" customHeight="1">
+      <x:c r="A106" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B106" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C106" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D106" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+      <x:c r="E106" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F106" s="6" t="str">
+        <x:v>本次查阅未找到本人学位导师或合作导师的直接公开证据，未以合著、团队归属或学生名单推断师承。；精选成果不代表完整发表清单；不纳入私人联系方式、出生信息或学生名单，原始证据缓存不公开。；1992.09–1995.04哈工大研究生经历不能据其时间长度自动认定硕士学位。博士阶段内另有法国硕士，但来源未称联合培养，不擅标联培或双学位。</x:v>
+      </x:c>
+      <x:c r="G106" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="64" customHeight="1">
+      <x:c r="A107" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B107" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C107" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D107" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+      <x:c r="E107" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F107" s="6" t="str">
+        <x:v>本次查阅未找到本人学位导师或合作导师的直接公开证据，未以合著、团队归属或学生名单推断师承。；精选成果不代表完整发表清单；不纳入私人联系方式、出生信息或学生名单，原始证据缓存不公开。；本科授位校归属保留双校不明确状态，不参与单一学校本科背景或985确定性判断。博士后和访学未披露合作导师。；已获学士不等于授位机构已明确；两校并列仅保留原文，985分类显式未知，不按首项、任一候选或字典回填。</x:v>
+      </x:c>
+      <x:c r="G107" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="64" customHeight="1">
+      <x:c r="A108" s="6" t="str">
+        <x:v>朱兵</x:v>
+      </x:c>
+      <x:c r="B108" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C108" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D108" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhubing</x:v>
+      </x:c>
+      <x:c r="E108" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F108" s="6" t="str">
+        <x:v>本次查阅未找到本人学位导师或合作导师的直接公开证据，未以合著、团队归属或学生名单推断师承。；精选成果不代表完整发表清单；不纳入私人联系方式、出生信息或学生名单，原始证据缓存不公开。；本科、硕士、历史任职起讫及博士明确授位尚未披露。；仅成果数量，没有逐篇题名清单；未凭Bing Zhu同名搜索结果拼入论文。</x:v>
+      </x:c>
+      <x:c r="G108" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="64" customHeight="1">
+      <x:c r="A109" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B109" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C109" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D109" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guyf</x:v>
+      </x:c>
+      <x:c r="E109" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F109" s="6" t="str">
+        <x:v>本次查阅未找到本人学位导师或合作导师的直接公开证据，未以合著、团队归属或学生名单推断师承。；精选成果不代表完整发表清单；不纳入私人联系方式、出生信息或学生名单，原始证据缓存不公开。；本人当前主页不再列学历和早期工作经历；学士、硕士精确年月及博士入学时间仍无已核一手证据。；论文为官网图片展示的精选成果，不将2023图片上传时间误当发表年。；教育补证来自已审核官方讲座内容与本人署名论文作者简介；独审对华东师大网页复取超时，不声称该轮实时网页读取成功。</x:v>
+      </x:c>
+      <x:c r="G109" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="64" customHeight="1">
+      <x:c r="A110" s="6" t="str">
+        <x:v>侯成宇</x:v>
+      </x:c>
+      <x:c r="B110" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C110" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D110" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houchengyu</x:v>
+      </x:c>
+      <x:c r="E110" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F110" s="6" t="str">
+        <x:v>本科经历、博士是否授位和导师未知；2015博士候选不能升级为已获博士或仍在读。；未披露任职起讫；论文书目第一二篇官网作者姓名顺序不规范，保留元数据独立核验。；精选成果非完整论文全集，原始网页缓存不公开。；成果时间限制：HITrocket: Hadamard-vector inner-product transform of ROCKET for time series classification；登记卷期为2026年12月，晚于本次核验日；官网已列，未核实单独在线发表日期，不宣称该卷期已经出版。</x:v>
+      </x:c>
+      <x:c r="G110" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="64" customHeight="1">
+      <x:c r="A111" s="6" t="str">
+        <x:v>陈雨时</x:v>
+      </x:c>
+      <x:c r="B111" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C111" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D111" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chenyushi</x:v>
+      </x:c>
+      <x:c r="E111" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F111" s="6" t="str">
+        <x:v>本硕授位明确性、学位与博士后导师、教授晋升日期未知；合著张晔等不推师承。；不能合并上海交大同英文名YushiChen的能源专业博士生或其他同名人员。；精选成果非完整论文全集，原始网页缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G111" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="64" customHeight="1">
+      <x:c r="A112" s="6" t="str">
+        <x:v>尹振东</x:v>
+      </x:c>
+      <x:c r="B112" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C112" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D112" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yinzhendong</x:v>
+      </x:c>
+      <x:c r="E112" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F112" s="6" t="str">
+        <x:v>本科/硕士学历及2001毕业经历的学位层级不明确，不纳入确证本科985筛选；博士专业、入学年及各导师未知。；官网仅成果总量无逐篇列表，本批只补公开出版社原始书目样例。；精选成果非完整论文全集，原始网页缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G112" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="64" customHeight="1">
+      <x:c r="A113" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B113" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C113" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D113" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+      <x:c r="E113" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F113" s="6" t="str">
+        <x:v>本硕授位、各阶段导师与威斯康星具体校区未知；不合并其他同名陈浩或把合作者视作导师。；副教授仍今与后续教授记录冲突；系副主任与当前研究生教学主任不同标签保留。；精选成果非完整论文全集，原始网页缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G113" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="64" customHeight="1">
+      <x:c r="A114" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B114" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C114" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D114" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+      <x:c r="E114" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F114" s="6" t="str">
+        <x:v>本人学位及博士后导师未披露，邹斌仅合著证据不填导师。；网页AntoniBroquetasIbars为学生陈意钒的联合培养导师，明确不属于张腊梅本人经历。；博士生导师开始月中英2016.05/2016.04冲突，分段职称晋升日期未知。；精选成果非完整论文全集，原始网页缓存不公开。；DGS-CapNet期刊DOI仅官方搜索摘录支持，文章页本次403不可读；明确区别于逐页阅读。；成果时间限制：PELNet: A General Physics-Embedded Learning Framework for Polarimetric Target Decomposition；登记卷期为2026年12月，晚于本次核验日；官网已列，未核实单独在线发表日期，不宣称该卷期已经出版。</x:v>
+      </x:c>
+      <x:c r="G114" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="64" customHeight="1">
+      <x:c r="A115" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B115" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C115" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D115" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yangzhutian</x:v>
+      </x:c>
+      <x:c r="E115" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F115" s="6" t="str">
+        <x:v>仅收录本次公开可核职业资料及精选书目元数据；未纳入私人联系方式、出生资料、学生名单或论文全文。原始证据缓存不用于公开展示。；本科院校、学位与起讫未找到可靠直接证据，不能由硕博院校倒推本科背景或985标签。；本人硕士/博士及访问阶段导师均未找到明确direct角色证据。</x:v>
+      </x:c>
+      <x:c r="G115" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="64" customHeight="1">
+      <x:c r="A116" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B116" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C116" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D116" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huyue</x:v>
+      </x:c>
+      <x:c r="E116" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F116" s="6" t="str">
+        <x:v>仅收录本次公开可核职业资料及精选书目元数据；未纳入私人联系方式、出生资料、学生名单或论文全文。原始证据缓存不用于公开展示。；HIT主页学习区间结束为2014；论文署年2013、答辩为2013-08-02是不同日期类型，分别保留。确切博士授位日期仍未知。；未找到本科或硕士导师的明确直接证据。硕士单独起始、HIT入职与晋升年份未知。；博士论文作者简介与HIT官网对本科专业的英文表述不一致，未擅自消除差异。；指导关系当时导师机构为 University of Iowa；胡悦博士学位项目机构为 University of Rochester；所读当前导师简介为 University of Virginia。三者分别保存，指导起止未披露。</x:v>
+      </x:c>
+      <x:c r="G116" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="64" customHeight="1">
+      <x:c r="A117" s="6" t="str">
+        <x:v>刘金龙</x:v>
+      </x:c>
+      <x:c r="B117" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C117" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D117" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/JinlongLiu</x:v>
+      </x:c>
+      <x:c r="E117" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F117" s="6" t="str">
+        <x:v>仅收录本次公开可核职业资料及精选书目元数据；未纳入私人联系方式、出生资料、学生名单或论文全文。原始证据缓存不用于公开展示。；本人官网没有逐篇论文清单；本次不从同名数据库或他人主页拼接精选论文，publications暂空。；本科硕士经历来自公开原始论文的非出版社托管副本；未检得本人当前官网逐条复述，来源局限明确保留。；各学位导师、学习起始年份与具体专业未找到直接公开证据。多位材料、机械和土木领域同名刘金龙均未合并。</x:v>
+      </x:c>
+      <x:c r="G117" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="64" customHeight="1">
+      <x:c r="A118" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B118" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C118" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D118" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+      <x:c r="E118" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F118" s="6" t="str">
+        <x:v>仅收录本次公开可核职业资料及精选书目元数据；未纳入私人联系方式、出生资料、学生名单或论文全文。原始证据缓存不用于公开展示。；中文博导起始2023-06与英文2023-05冲突；中文研究员与英文Professor的职称翻译差异未消除。；未找到本人学位导师或博士后合作导师的直接角色声明；谷延锋为团队负责人、学生栏目出现本人、共同论文均不单独推断师承。；学士、硕士、博士履历为教育标签，授位状态均保留null；本科阶段院校可知，不将标签自动升级为已获学位。；Spectral Reconstruction From Satellite Multispectral Imagery Using Convolution and Transformer Joint Network：官网书目日期 Accepted；Crossref 登记日期 2023，不同日期原样保留，不推断差异原因。</x:v>
+      </x:c>
+      <x:c r="G118" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="64" customHeight="1">
+      <x:c r="A119" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B119" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C119" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D119" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+      <x:c r="E119" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F119" s="6" t="str">
+        <x:v>仅收录本次公开可核职业资料及精选书目元数据；未纳入私人联系方式、出生资料、学生名单或论文全文。原始证据缓存不用于公开展示。；NTU Research Fellow阶段只明确working with Shijian Lu，RIKEN阶段仅collaborating with Naoto Yokoya；普通合作不新增博士后导师边。；陈锐志的2026当前在职状态unknown；三位导师关系阶段明确，但各自精确指导起止未披露。；论文官网年份与Crossref可能为预印本/在线/卷期差异，未独断解释原因，保留双值。；Foundation Models for Remote Sensing and Earth Observation: A survey：书目年份冲突：官网 2026，Crossref 2025；双值保留，原因未核定。；A Survey of Label-Efficient Deep Learning for 3D Point Clouds：书目年份冲突：官网 2023，Crossref 2024；双值保留，原因未核定。</x:v>
+      </x:c>
+      <x:c r="G119" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="64" customHeight="1">
+      <x:c r="A120" s="6" t="str">
+        <x:v>胡航</x:v>
+      </x:c>
+      <x:c r="B120" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C120" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D120" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huhang</x:v>
+      </x:c>
+      <x:c r="E120" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F120" s="6" t="str">
+        <x:v>本科硕士履历、博士授位学校与年份、博士后机构及时间、本人各阶段导师未知。；其他同名教育学/材料物理研究者不合并；国外学术交流不算海外学位。；现代语音信号处理中文2014与英文另名著作2023可能不同版本，不强行合并，暂未选入。；精选成果非完整论文全集，原始网页缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G120" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="64" customHeight="1">
+      <x:c r="A121" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B121" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C121" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D121" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houyuguan</x:v>
+      </x:c>
+      <x:c r="E121" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F121" s="6" t="str">
+        <x:v>本科学位授予未独立确证；学位导师与博士后合作导师未知，不把合著沈一鹰、刘永坦、毛兴鹏等升级师承。；ScienceDirect相应2025论文落地页403；原始2013出版社作者简介已另有合法可读独立来源，未绕过403。；精选成果非完整论文全集，原始网页缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G121" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="64" customHeight="1">
+      <x:c r="A122" s="6" t="str">
+        <x:v>李宏博</x:v>
+      </x:c>
+      <x:c r="B122" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C122" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D122" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lihongbo</x:v>
+      </x:c>
+      <x:c r="E122" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F122" s="6" t="str">
+        <x:v>本硕经历、博士授位学校专业时间和导师均未知。；官网无逐篇成果列表；检索所得同名同单位雷达论文缺个人主页或更强身份链接，暂不归入确证个人成果。；不合并沈阳农业大学、山东农业大学、大庆师范学院同名教师及同名在读学生。；精选成果非完整论文全集，原始网页缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G122" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="64" customHeight="1">
+      <x:c r="A123" s="6" t="str">
+        <x:v>高建军</x:v>
+      </x:c>
+      <x:c r="B123" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C123" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D123" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/jjgao</x:v>
+      </x:c>
+      <x:c r="E123" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F123" s="6" t="str">
+        <x:v>本硕明确授位、各阶段专业和导师未知；不据合著宿富林等推师承。；其他期刊参考文献列高建军HIT博士论文《多径和海杂波干扰下的舰船ISAR成像及横向定标》2010，与本人教育结束2009可能是不同事件或记录冲突；未取得学位库原始题录，不确认为本人学位论文、不将2010当授位年。；不合并华东师范大学微电子、上海财经大学或其他机构同名研究者。；精选成果非完整论文全集，原始网页缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G123" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="64" customHeight="1">
+      <x:c r="A124" s="6" t="str">
+        <x:v>高国明</x:v>
+      </x:c>
+      <x:c r="B124" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C124" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D124" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaoguoming</x:v>
+      </x:c>
+      <x:c r="E124" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F124" s="6" t="str">
+        <x:v>本硕明确授位待核；导师未披露，谷延锋是团队负责人和合作者，不因此登记为博士导师。；副研究员开始月中英2022.01/2022.12冲突；职称中英不同按中文保留。；精选成果非完整论文全集，原始网页缓存不公开。；第3篇Crossref查询429，停止该查询；保持官网书目链接，不猜DOI。</x:v>
+      </x:c>
+      <x:c r="G124" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8293c13b76e848a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d83160e97284dab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33909,10 +34369,5859 @@
         <x:v>https://tce.hit.edu.cn/16428/list.htm</x:v>
       </x:c>
     </x:row>
+    <x:row r="774" ht="64" customHeight="1">
+      <x:c r="A774" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B774" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C774" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D774" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E774" s="6" t="str">
+        <x:v>1982-09</x:v>
+      </x:c>
+      <x:c r="F774" s="6" t="str">
+        <x:v>1986-07</x:v>
+      </x:c>
+      <x:c r="G774" s="6" t="str"/>
+      <x:c r="H774" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I774" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J774" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K774" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L774" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M774" s="7" t="str"/>
+      <x:c r="N774" s="6" t="str"/>
+      <x:c r="O774" s="6" t="str">
+        <x:v>明确获工学学士学位；来源只写电子与通信工程系，未把院系当作专业。</x:v>
+      </x:c>
+      <x:c r="P774" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q774" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="775" ht="64" customHeight="1">
+      <x:c r="A775" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B775" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C775" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D775" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E775" s="6" t="str">
+        <x:v>1986-09</x:v>
+      </x:c>
+      <x:c r="F775" s="6" t="str">
+        <x:v>1989-03</x:v>
+      </x:c>
+      <x:c r="G775" s="6" t="str"/>
+      <x:c r="H775" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I775" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J775" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K775" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L775" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M775" s="7" t="str"/>
+      <x:c r="N775" s="6" t="str"/>
+      <x:c r="O775" s="6" t="str">
+        <x:v>明确获工学硕士学位；具体专业未披露。</x:v>
+      </x:c>
+      <x:c r="P775" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q775" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="776" ht="64" customHeight="1">
+      <x:c r="A776" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B776" s="6" t="str">
+        <x:v>non_degree_training</x:v>
+      </x:c>
+      <x:c r="C776" s="6" t="str"/>
+      <x:c r="D776" s="6" t="str">
+        <x:v>北京语言大学</x:v>
+      </x:c>
+      <x:c r="E776" s="6" t="str">
+        <x:v>2002-09</x:v>
+      </x:c>
+      <x:c r="F776" s="6" t="str">
+        <x:v>2002-12</x:v>
+      </x:c>
+      <x:c r="G776" s="6" t="str"/>
+      <x:c r="H776" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I776" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J776" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K776" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L776" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M776" s="7" t="str"/>
+      <x:c r="N776" s="6" t="str"/>
+      <x:c r="O776" s="6" t="str">
+        <x:v>出国部高级班学习，非学位经历。 事件类型：非学位培训。</x:v>
+      </x:c>
+      <x:c r="P776" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q776" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="777" ht="64" customHeight="1">
+      <x:c r="A777" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B777" s="6" t="str">
+        <x:v>visiting_scholar</x:v>
+      </x:c>
+      <x:c r="C777" s="6" t="str"/>
+      <x:c r="D777" s="6" t="str">
+        <x:v>英国曼彻斯特大学理工学院（官网表述）</x:v>
+      </x:c>
+      <x:c r="E777" s="6" t="str">
+        <x:v>2003-01</x:v>
+      </x:c>
+      <x:c r="F777" s="6" t="str">
+        <x:v>2003-06</x:v>
+      </x:c>
+      <x:c r="G777" s="6" t="str"/>
+      <x:c r="H777" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="I777" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="J777" s="6" t="str">
+        <x:v>欧洲</x:v>
+      </x:c>
+      <x:c r="K777" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L777" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M777" s="7" t="str"/>
+      <x:c r="N777" s="6" t="str"/>
+      <x:c r="O777" s="6" t="str">
+        <x:v>访问学者，非授位。 事件类型：访问学者（非授位）。</x:v>
+      </x:c>
+      <x:c r="P777" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q777" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="778" ht="64" customHeight="1">
+      <x:c r="A778" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B778" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C778" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D778" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E778" s="6" t="str">
+        <x:v>2004-09</x:v>
+      </x:c>
+      <x:c r="F778" s="6" t="str">
+        <x:v>2009-01</x:v>
+      </x:c>
+      <x:c r="G778" s="6" t="str"/>
+      <x:c r="H778" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I778" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J778" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K778" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L778" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M778" s="7" t="str"/>
+      <x:c r="N778" s="6" t="str"/>
+      <x:c r="O778" s="6" t="str">
+        <x:v>明确获工学博士学位；具体专业未披露。</x:v>
+      </x:c>
+      <x:c r="P778" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q778" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="779" ht="64" customHeight="1">
+      <x:c r="A779" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B779" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C779" s="6" t="str">
+        <x:v>助教、讲师</x:v>
+      </x:c>
+      <x:c r="D779" s="6" t="str">
+        <x:v>哈尔滨工业大学计算中心图像室</x:v>
+      </x:c>
+      <x:c r="E779" s="6" t="str">
+        <x:v>1989-03</x:v>
+      </x:c>
+      <x:c r="F779" s="6" t="str">
+        <x:v>1994-03</x:v>
+      </x:c>
+      <x:c r="G779" s="6" t="str"/>
+      <x:c r="H779" s="6" t="str"/>
+      <x:c r="I779" s="6" t="str"/>
+      <x:c r="J779" s="6" t="str"/>
+      <x:c r="K779" s="6" t="str"/>
+      <x:c r="L779" s="6" t="str"/>
+      <x:c r="M779" s="7" t="str"/>
+      <x:c r="N779" s="6" t="str"/>
+      <x:c r="O779" s="6" t="str">
+        <x:v>中文合并列示，两个职称各自起讫未披露。</x:v>
+      </x:c>
+      <x:c r="P779" s="6" t="str"/>
+      <x:c r="Q779" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="780" ht="64" customHeight="1">
+      <x:c r="A780" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B780" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C780" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D780" s="6" t="str">
+        <x:v>哈尔滨工业大学航天学院电子与通信工程系</x:v>
+      </x:c>
+      <x:c r="E780" s="6" t="str">
+        <x:v>1994-03</x:v>
+      </x:c>
+      <x:c r="F780" s="6" t="str">
+        <x:v>1996-06</x:v>
+      </x:c>
+      <x:c r="G780" s="6" t="str"/>
+      <x:c r="H780" s="6" t="str"/>
+      <x:c r="I780" s="6" t="str"/>
+      <x:c r="J780" s="6" t="str"/>
+      <x:c r="K780" s="6" t="str"/>
+      <x:c r="L780" s="6" t="str"/>
+      <x:c r="M780" s="7" t="str"/>
+      <x:c r="N780" s="6" t="str"/>
+      <x:c r="O780" s="6" t="str"/>
+      <x:c r="P780" s="6" t="str"/>
+      <x:c r="Q780" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="781" ht="64" customHeight="1">
+      <x:c r="A781" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B781" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C781" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D781" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E781" s="6" t="str">
+        <x:v>1996-07</x:v>
+      </x:c>
+      <x:c r="F781" s="6" t="str">
+        <x:v>2009-12</x:v>
+      </x:c>
+      <x:c r="G781" s="6" t="str"/>
+      <x:c r="H781" s="6" t="str"/>
+      <x:c r="I781" s="6" t="str"/>
+      <x:c r="J781" s="6" t="str"/>
+      <x:c r="K781" s="6" t="str"/>
+      <x:c r="L781" s="6" t="str"/>
+      <x:c r="M781" s="7" t="str"/>
+      <x:c r="N781" s="6" t="str"/>
+      <x:c r="O781" s="6" t="str">
+        <x:v>英文任职表给出精确区间；中文将1996.7至今的副教授、教授、博导合并列示。</x:v>
+      </x:c>
+      <x:c r="P781" s="6" t="str"/>
+      <x:c r="Q781" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="782" ht="64" customHeight="1">
+      <x:c r="A782" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B782" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C782" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D782" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E782" s="6" t="str">
+        <x:v>2009-12</x:v>
+      </x:c>
+      <x:c r="F782" s="6" t="str"/>
+      <x:c r="G782" s="6" t="str"/>
+      <x:c r="H782" s="6" t="str"/>
+      <x:c r="I782" s="6" t="str"/>
+      <x:c r="J782" s="6" t="str"/>
+      <x:c r="K782" s="6" t="str"/>
+      <x:c r="L782" s="6" t="str"/>
+      <x:c r="M782" s="7" t="str"/>
+      <x:c r="N782" s="6" t="str"/>
+      <x:c r="O782" s="6" t="str">
+        <x:v>英文任职表明确2009.12至今。</x:v>
+      </x:c>
+      <x:c r="P782" s="6" t="str"/>
+      <x:c r="Q782" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="783" ht="64" customHeight="1">
+      <x:c r="A783" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B783" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C783" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D783" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E783" s="6" t="str"/>
+      <x:c r="F783" s="6" t="str"/>
+      <x:c r="G783" s="6" t="str"/>
+      <x:c r="H783" s="6" t="str"/>
+      <x:c r="I783" s="6" t="str"/>
+      <x:c r="J783" s="6" t="str"/>
+      <x:c r="K783" s="6" t="str"/>
+      <x:c r="L783" s="6" t="str"/>
+      <x:c r="M783" s="7" t="str"/>
+      <x:c r="N783" s="6" t="str"/>
+      <x:c r="O783" s="6" t="str">
+        <x:v>现任身份明确，未从1996.7至今混合职称区间推断博导起始。</x:v>
+      </x:c>
+      <x:c r="P783" s="6" t="str"/>
+      <x:c r="Q783" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="784" ht="64" customHeight="1">
+      <x:c r="A784" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B784" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C784" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D784" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E784" s="6" t="str">
+        <x:v>1986-09</x:v>
+      </x:c>
+      <x:c r="F784" s="6" t="str">
+        <x:v>1990-07</x:v>
+      </x:c>
+      <x:c r="G784" s="6" t="str">
+        <x:v>电子工程</x:v>
+      </x:c>
+      <x:c r="H784" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I784" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J784" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K784" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L784" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M784" s="7" t="str"/>
+      <x:c r="N784" s="6" t="str"/>
+      <x:c r="O784" s="6" t="str">
+        <x:v>官网提供学习区间；本人官网托管的署名论文简介明确1990获B.S.。</x:v>
+      </x:c>
+      <x:c r="P784" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q784" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="785" ht="64" customHeight="1">
+      <x:c r="A785" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B785" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C785" s="6" t="str"/>
+      <x:c r="D785" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E785" s="6" t="str">
+        <x:v>1992-09</x:v>
+      </x:c>
+      <x:c r="F785" s="6" t="str">
+        <x:v>1995-04</x:v>
+      </x:c>
+      <x:c r="G785" s="6" t="str"/>
+      <x:c r="H785" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I785" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J785" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K785" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L785" s="6" t="str"/>
+      <x:c r="M785" s="7" t="str"/>
+      <x:c r="N785" s="6" t="str"/>
+      <x:c r="O785" s="6" t="str">
+        <x:v>中文只写“研究生”，未明确硕士阶段或学位授予，保留未分类研究生经历。</x:v>
+      </x:c>
+      <x:c r="P785" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q785" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="786" ht="64" customHeight="1">
+      <x:c r="A786" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B786" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C786" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D786" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E786" s="6" t="str">
+        <x:v>1995-04</x:v>
+      </x:c>
+      <x:c r="F786" s="6" t="str">
+        <x:v>2001-04</x:v>
+      </x:c>
+      <x:c r="G786" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H786" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I786" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J786" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K786" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L786" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M786" s="7" t="str"/>
+      <x:c r="N786" s="6" t="str"/>
+      <x:c r="O786" s="6" t="str">
+        <x:v>学习区间据官网，2001获PhD及专业据本人署名论文简介。</x:v>
+      </x:c>
+      <x:c r="P786" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q786" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="787" ht="64" customHeight="1">
+      <x:c r="A787" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B787" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C787" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D787" s="6" t="str">
+        <x:v>国际宇航大学（International Space University）</x:v>
+      </x:c>
+      <x:c r="E787" s="6" t="str">
+        <x:v>1997-09</x:v>
+      </x:c>
+      <x:c r="F787" s="6" t="str">
+        <x:v>1998-08</x:v>
+      </x:c>
+      <x:c r="G787" s="6" t="str">
+        <x:v>空间研究（Space Studies）</x:v>
+      </x:c>
+      <x:c r="H787" s="6" t="str">
+        <x:v>法国</x:v>
+      </x:c>
+      <x:c r="I787" s="6" t="str">
+        <x:v>法国</x:v>
+      </x:c>
+      <x:c r="J787" s="6" t="str">
+        <x:v>欧洲</x:v>
+      </x:c>
+      <x:c r="K787" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L787" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M787" s="7" t="str"/>
+      <x:c r="N787" s="6" t="str"/>
+      <x:c r="O787" s="6" t="str">
+        <x:v>官网留学区间与署名论文明确1998获M.Sc.对应。</x:v>
+      </x:c>
+      <x:c r="P787" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q787" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="788" ht="64" customHeight="1">
+      <x:c r="A788" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B788" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="C788" s="6" t="str"/>
+      <x:c r="D788" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E788" s="6" t="str">
+        <x:v>2002-04</x:v>
+      </x:c>
+      <x:c r="F788" s="6" t="str">
+        <x:v>2005-12</x:v>
+      </x:c>
+      <x:c r="G788" s="6" t="str"/>
+      <x:c r="H788" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I788" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J788" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K788" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L788" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M788" s="7" t="str"/>
+      <x:c r="N788" s="6" t="str"/>
+      <x:c r="O788" s="6" t="str">
+        <x:v>博士后，不作为新学位。 事件类型：博士后研究（非授位）。</x:v>
+      </x:c>
+      <x:c r="P788" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q788" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="789" ht="64" customHeight="1">
+      <x:c r="A789" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B789" s="6" t="str">
+        <x:v>visiting_scholar</x:v>
+      </x:c>
+      <x:c r="C789" s="6" t="str"/>
+      <x:c r="D789" s="6" t="str">
+        <x:v>曼尼托巴大学</x:v>
+      </x:c>
+      <x:c r="E789" s="6" t="str">
+        <x:v>2003-10</x:v>
+      </x:c>
+      <x:c r="F789" s="6" t="str">
+        <x:v>2004-10</x:v>
+      </x:c>
+      <x:c r="G789" s="6" t="str"/>
+      <x:c r="H789" s="6" t="str">
+        <x:v>加拿大</x:v>
+      </x:c>
+      <x:c r="I789" s="6" t="str">
+        <x:v>加拿大</x:v>
+      </x:c>
+      <x:c r="J789" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K789" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L789" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M789" s="7" t="str"/>
+      <x:c r="N789" s="6" t="str"/>
+      <x:c r="O789" s="6" t="str">
+        <x:v>官网注明访问学者；署名论文同样列2003–2004访学。 事件类型：访问学者（非授位）。</x:v>
+      </x:c>
+      <x:c r="P789" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q789" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="790" ht="64" customHeight="1">
+      <x:c r="A790" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B790" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C790" s="6" t="str">
+        <x:v>助教</x:v>
+      </x:c>
+      <x:c r="D790" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E790" s="6" t="str">
+        <x:v>1990-07</x:v>
+      </x:c>
+      <x:c r="F790" s="6" t="str">
+        <x:v>1995-09</x:v>
+      </x:c>
+      <x:c r="G790" s="6" t="str"/>
+      <x:c r="H790" s="6" t="str"/>
+      <x:c r="I790" s="6" t="str"/>
+      <x:c r="J790" s="6" t="str"/>
+      <x:c r="K790" s="6" t="str"/>
+      <x:c r="L790" s="6" t="str"/>
+      <x:c r="M790" s="7" t="str"/>
+      <x:c r="N790" s="6" t="str"/>
+      <x:c r="O790" s="6" t="str"/>
+      <x:c r="P790" s="6" t="str"/>
+      <x:c r="Q790" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="791" ht="64" customHeight="1">
+      <x:c r="A791" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B791" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C791" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D791" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E791" s="6" t="str">
+        <x:v>1995-09</x:v>
+      </x:c>
+      <x:c r="F791" s="6" t="str">
+        <x:v>2000-09</x:v>
+      </x:c>
+      <x:c r="G791" s="6" t="str"/>
+      <x:c r="H791" s="6" t="str"/>
+      <x:c r="I791" s="6" t="str"/>
+      <x:c r="J791" s="6" t="str"/>
+      <x:c r="K791" s="6" t="str"/>
+      <x:c r="L791" s="6" t="str"/>
+      <x:c r="M791" s="7" t="str"/>
+      <x:c r="N791" s="6" t="str"/>
+      <x:c r="O791" s="6" t="str"/>
+      <x:c r="P791" s="6" t="str"/>
+      <x:c r="Q791" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="792" ht="64" customHeight="1">
+      <x:c r="A792" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B792" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C792" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D792" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E792" s="6" t="str">
+        <x:v>2000-09</x:v>
+      </x:c>
+      <x:c r="F792" s="6" t="str">
+        <x:v>2008-06</x:v>
+      </x:c>
+      <x:c r="G792" s="6" t="str"/>
+      <x:c r="H792" s="6" t="str"/>
+      <x:c r="I792" s="6" t="str"/>
+      <x:c r="J792" s="6" t="str"/>
+      <x:c r="K792" s="6" t="str"/>
+      <x:c r="L792" s="6" t="str"/>
+      <x:c r="M792" s="7" t="str"/>
+      <x:c r="N792" s="6" t="str"/>
+      <x:c r="O792" s="6" t="str"/>
+      <x:c r="P792" s="6" t="str"/>
+      <x:c r="Q792" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="793" ht="64" customHeight="1">
+      <x:c r="A793" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B793" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C793" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D793" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E793" s="6" t="str">
+        <x:v>2008-07</x:v>
+      </x:c>
+      <x:c r="F793" s="6" t="str"/>
+      <x:c r="G793" s="6" t="str"/>
+      <x:c r="H793" s="6" t="str"/>
+      <x:c r="I793" s="6" t="str"/>
+      <x:c r="J793" s="6" t="str"/>
+      <x:c r="K793" s="6" t="str"/>
+      <x:c r="L793" s="6" t="str"/>
+      <x:c r="M793" s="7" t="str"/>
+      <x:c r="N793" s="6" t="str"/>
+      <x:c r="O793" s="6" t="str"/>
+      <x:c r="P793" s="6" t="str"/>
+      <x:c r="Q793" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="794" ht="64" customHeight="1">
+      <x:c r="A794" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B794" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C794" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D794" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E794" s="6" t="str">
+        <x:v>2009-03</x:v>
+      </x:c>
+      <x:c r="F794" s="6" t="str"/>
+      <x:c r="G794" s="6" t="str"/>
+      <x:c r="H794" s="6" t="str"/>
+      <x:c r="I794" s="6" t="str"/>
+      <x:c r="J794" s="6" t="str"/>
+      <x:c r="K794" s="6" t="str"/>
+      <x:c r="L794" s="6" t="str"/>
+      <x:c r="M794" s="7" t="str"/>
+      <x:c r="N794" s="6" t="str"/>
+      <x:c r="O794" s="6" t="str"/>
+      <x:c r="P794" s="6" t="str"/>
+      <x:c r="Q794" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="795" ht="64" customHeight="1">
+      <x:c r="A795" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B795" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C795" s="6" t="str">
+        <x:v>研究员</x:v>
+      </x:c>
+      <x:c r="D795" s="6" t="str">
+        <x:v>新加坡国立大学</x:v>
+      </x:c>
+      <x:c r="E795" s="6" t="str">
+        <x:v>2006-11</x:v>
+      </x:c>
+      <x:c r="F795" s="6" t="str">
+        <x:v>2007-03</x:v>
+      </x:c>
+      <x:c r="G795" s="6" t="str"/>
+      <x:c r="H795" s="6" t="str"/>
+      <x:c r="I795" s="6" t="str"/>
+      <x:c r="J795" s="6" t="str"/>
+      <x:c r="K795" s="6" t="str"/>
+      <x:c r="L795" s="6" t="str"/>
+      <x:c r="M795" s="7" t="str"/>
+      <x:c r="N795" s="6" t="str"/>
+      <x:c r="O795" s="6" t="str">
+        <x:v>官网主要留学简历列研究员，不标学位。</x:v>
+      </x:c>
+      <x:c r="P795" s="6" t="str"/>
+      <x:c r="Q795" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="796" ht="64" customHeight="1">
+      <x:c r="A796" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B796" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C796" s="6" t="str">
+        <x:v>信息工程系副主任</x:v>
+      </x:c>
+      <x:c r="D796" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E796" s="6" t="str"/>
+      <x:c r="F796" s="6" t="str"/>
+      <x:c r="G796" s="6" t="str"/>
+      <x:c r="H796" s="6" t="str"/>
+      <x:c r="I796" s="6" t="str"/>
+      <x:c r="J796" s="6" t="str"/>
+      <x:c r="K796" s="6" t="str"/>
+      <x:c r="L796" s="6" t="str"/>
+      <x:c r="M796" s="7" t="str"/>
+      <x:c r="N796" s="6" t="str"/>
+      <x:c r="O796" s="6" t="str">
+        <x:v>2018作者简介现任表述；任期起讫及2026年是否仍任职未知。</x:v>
+      </x:c>
+      <x:c r="P796" s="6" t="str"/>
+      <x:c r="Q796" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ueditor/jsp/upload/file/20200505/1588688180750046569.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="797" ht="64" customHeight="1">
+      <x:c r="A797" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B797" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C797" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D797" s="6" t="str">
+        <x:v>哈尔滨工程大学/哈尔滨医科大学</x:v>
+      </x:c>
+      <x:c r="E797" s="6" t="str">
+        <x:v>1988</x:v>
+      </x:c>
+      <x:c r="F797" s="6" t="str">
+        <x:v>1993</x:v>
+      </x:c>
+      <x:c r="G797" s="6" t="str">
+        <x:v>生物医学工程与仪器</x:v>
+      </x:c>
+      <x:c r="H797" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I797" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J797" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K797" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L797" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M797" s="7" t="str"/>
+      <x:c r="N797" s="6" t="str"/>
+      <x:c r="O797" s="6" t="str">
+        <x:v>官网双校斜线并列，正式论文作者简介同样并列两校并明确获得B.S.。只能确认学位已获，不能据此推断双学位、具体授位法人或单一本科院校。 本科985/非985分类均为unknown，不纳入任一确证分组。</x:v>
+      </x:c>
+      <x:c r="P797" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q797" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="798" ht="64" customHeight="1">
+      <x:c r="A798" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B798" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C798" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D798" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E798" s="6" t="str">
+        <x:v>1996</x:v>
+      </x:c>
+      <x:c r="F798" s="6" t="str">
+        <x:v>1998</x:v>
+      </x:c>
+      <x:c r="G798" s="6" t="str">
+        <x:v>信号与信息处理</x:v>
+      </x:c>
+      <x:c r="H798" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I798" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J798" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K798" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L798" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M798" s="7" t="str"/>
+      <x:c r="N798" s="6" t="str"/>
+      <x:c r="O798" s="6" t="str">
+        <x:v>官网区间与正式论文received M.S.1998一致。</x:v>
+      </x:c>
+      <x:c r="P798" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q798" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="799" ht="64" customHeight="1">
+      <x:c r="A799" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B799" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C799" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D799" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E799" s="6" t="str">
+        <x:v>1998</x:v>
+      </x:c>
+      <x:c r="F799" s="6" t="str">
+        <x:v>2002</x:v>
+      </x:c>
+      <x:c r="G799" s="6" t="str">
+        <x:v>信号与信息处理</x:v>
+      </x:c>
+      <x:c r="H799" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I799" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J799" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K799" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L799" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M799" s="7" t="str"/>
+      <x:c r="N799" s="6" t="str"/>
+      <x:c r="O799" s="6" t="str">
+        <x:v>官网区间与正式论文received Ph.D.2002一致。</x:v>
+      </x:c>
+      <x:c r="P799" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q799" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="800" ht="64" customHeight="1">
+      <x:c r="A800" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B800" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="C800" s="6" t="str"/>
+      <x:c r="D800" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E800" s="6" t="str">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="F800" s="6" t="str">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="G800" s="6" t="str">
+        <x:v>仪器科学与技术</x:v>
+      </x:c>
+      <x:c r="H800" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I800" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J800" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K800" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L800" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M800" s="7" t="str"/>
+      <x:c r="N800" s="6" t="str"/>
+      <x:c r="O800" s="6" t="str">
+        <x:v>事件类型：博士后研究（非授位）。</x:v>
+      </x:c>
+      <x:c r="P800" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q800" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="801" ht="64" customHeight="1">
+      <x:c r="A801" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B801" s="6" t="str">
+        <x:v>visiting_scholar</x:v>
+      </x:c>
+      <x:c r="C801" s="6" t="str"/>
+      <x:c r="D801" s="6" t="str">
+        <x:v>密歇根州立大学（Michigan State University）</x:v>
+      </x:c>
+      <x:c r="E801" s="6" t="str">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="F801" s="6" t="str">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="G801" s="6" t="str"/>
+      <x:c r="H801" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I801" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J801" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K801" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L801" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M801" s="7" t="str"/>
+      <x:c r="N801" s="6" t="str"/>
+      <x:c r="O801" s="6" t="str">
+        <x:v>事件类型：访问学者（非授位）。</x:v>
+      </x:c>
+      <x:c r="P801" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q801" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="802" ht="64" customHeight="1">
+      <x:c r="A802" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B802" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C802" s="6" t="str">
+        <x:v>助教</x:v>
+      </x:c>
+      <x:c r="D802" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E802" s="6" t="str">
+        <x:v>1993</x:v>
+      </x:c>
+      <x:c r="F802" s="6" t="str">
+        <x:v>1998</x:v>
+      </x:c>
+      <x:c r="G802" s="6" t="str"/>
+      <x:c r="H802" s="6" t="str"/>
+      <x:c r="I802" s="6" t="str"/>
+      <x:c r="J802" s="6" t="str"/>
+      <x:c r="K802" s="6" t="str"/>
+      <x:c r="L802" s="6" t="str"/>
+      <x:c r="M802" s="7" t="str"/>
+      <x:c r="N802" s="6" t="str"/>
+      <x:c r="O802" s="6" t="str"/>
+      <x:c r="P802" s="6" t="str"/>
+      <x:c r="Q802" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="803" ht="64" customHeight="1">
+      <x:c r="A803" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B803" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C803" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D803" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E803" s="6" t="str">
+        <x:v>1998</x:v>
+      </x:c>
+      <x:c r="F803" s="6" t="str">
+        <x:v>2002</x:v>
+      </x:c>
+      <x:c r="G803" s="6" t="str"/>
+      <x:c r="H803" s="6" t="str"/>
+      <x:c r="I803" s="6" t="str"/>
+      <x:c r="J803" s="6" t="str"/>
+      <x:c r="K803" s="6" t="str"/>
+      <x:c r="L803" s="6" t="str"/>
+      <x:c r="M803" s="7" t="str"/>
+      <x:c r="N803" s="6" t="str"/>
+      <x:c r="O803" s="6" t="str"/>
+      <x:c r="P803" s="6" t="str"/>
+      <x:c r="Q803" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="804" ht="64" customHeight="1">
+      <x:c r="A804" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B804" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C804" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D804" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E804" s="6" t="str">
+        <x:v>2002</x:v>
+      </x:c>
+      <x:c r="F804" s="6" t="str">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="G804" s="6" t="str"/>
+      <x:c r="H804" s="6" t="str"/>
+      <x:c r="I804" s="6" t="str"/>
+      <x:c r="J804" s="6" t="str"/>
+      <x:c r="K804" s="6" t="str"/>
+      <x:c r="L804" s="6" t="str"/>
+      <x:c r="M804" s="7" t="str"/>
+      <x:c r="N804" s="6" t="str"/>
+      <x:c r="O804" s="6" t="str"/>
+      <x:c r="P804" s="6" t="str"/>
+      <x:c r="Q804" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="805" ht="64" customHeight="1">
+      <x:c r="A805" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B805" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C805" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D805" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E805" s="6" t="str">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="F805" s="6" t="str"/>
+      <x:c r="G805" s="6" t="str"/>
+      <x:c r="H805" s="6" t="str"/>
+      <x:c r="I805" s="6" t="str"/>
+      <x:c r="J805" s="6" t="str"/>
+      <x:c r="K805" s="6" t="str"/>
+      <x:c r="L805" s="6" t="str"/>
+      <x:c r="M805" s="7" t="str"/>
+      <x:c r="N805" s="6" t="str"/>
+      <x:c r="O805" s="6" t="str"/>
+      <x:c r="P805" s="6" t="str"/>
+      <x:c r="Q805" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="806" ht="64" customHeight="1">
+      <x:c r="A806" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B806" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C806" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D806" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E806" s="6" t="str">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="F806" s="6" t="str"/>
+      <x:c r="G806" s="6" t="str"/>
+      <x:c r="H806" s="6" t="str"/>
+      <x:c r="I806" s="6" t="str"/>
+      <x:c r="J806" s="6" t="str"/>
+      <x:c r="K806" s="6" t="str"/>
+      <x:c r="L806" s="6" t="str"/>
+      <x:c r="M806" s="7" t="str"/>
+      <x:c r="N806" s="6" t="str"/>
+      <x:c r="O806" s="6" t="str"/>
+      <x:c r="P806" s="6" t="str"/>
+      <x:c r="Q806" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="807" ht="64" customHeight="1">
+      <x:c r="A807" s="6" t="str">
+        <x:v>朱兵</x:v>
+      </x:c>
+      <x:c r="B807" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C807" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D807" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E807" s="6" t="str">
+        <x:v>2001-09</x:v>
+      </x:c>
+      <x:c r="F807" s="6" t="str">
+        <x:v>2006-10</x:v>
+      </x:c>
+      <x:c r="G807" s="6" t="str">
+        <x:v>信号与信息处理</x:v>
+      </x:c>
+      <x:c r="H807" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I807" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J807" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K807" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L807" s="6" t="str"/>
+      <x:c r="M807" s="7" t="str"/>
+      <x:c r="N807" s="6" t="str"/>
+      <x:c r="O807" s="6" t="str">
+        <x:v>仅教育经历表“学历：博士”，未见明确获得学位表述；不自动置degree_awarded=true。</x:v>
+      </x:c>
+      <x:c r="P807" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q807" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhubing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="808" ht="64" customHeight="1">
+      <x:c r="A808" s="6" t="str">
+        <x:v>朱兵</x:v>
+      </x:c>
+      <x:c r="B808" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C808" s="6" t="str">
+        <x:v>研究员</x:v>
+      </x:c>
+      <x:c r="D808" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E808" s="6" t="str"/>
+      <x:c r="F808" s="6" t="str"/>
+      <x:c r="G808" s="6" t="str"/>
+      <x:c r="H808" s="6" t="str"/>
+      <x:c r="I808" s="6" t="str"/>
+      <x:c r="J808" s="6" t="str"/>
+      <x:c r="K808" s="6" t="str"/>
+      <x:c r="L808" s="6" t="str"/>
+      <x:c r="M808" s="7" t="str"/>
+      <x:c r="N808" s="6" t="str"/>
+      <x:c r="O808" s="6" t="str">
+        <x:v>中文主页标题及正文同为研究员；英文正文为Associate Researcher，英文页面头部为Professor，保留翻译/职称不一致，不据此填晋升日期。</x:v>
+      </x:c>
+      <x:c r="P808" s="6" t="str"/>
+      <x:c r="Q808" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhubing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="809" ht="64" customHeight="1">
+      <x:c r="A809" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B809" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C809" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D809" s="6" t="str">
+        <x:v>大连理工大学</x:v>
+      </x:c>
+      <x:c r="E809" s="6" t="str"/>
+      <x:c r="F809" s="6" t="str"/>
+      <x:c r="G809" s="6" t="str">
+        <x:v>电子工程</x:v>
+      </x:c>
+      <x:c r="H809" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I809" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J809" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K809" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L809" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M809" s="7" t="str"/>
+      <x:c r="N809" s="6" t="str"/>
+      <x:c r="O809" s="6" t="str">
+        <x:v>官方讲座简介明确毕业并获学士；未列年月，不以年龄计算年份。</x:v>
+      </x:c>
+      <x:c r="P809" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q809" s="6" t="str">
+        <x:v>https://kjc.ecnu.edu.cn/28/54/c8151a272468/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="810" ht="64" customHeight="1">
+      <x:c r="A810" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B810" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C810" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D810" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E810" s="6" t="str"/>
+      <x:c r="F810" s="6" t="str"/>
+      <x:c r="G810" s="6" t="str">
+        <x:v>信号与信息处理</x:v>
+      </x:c>
+      <x:c r="H810" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I810" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J810" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K810" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L810" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M810" s="7" t="str"/>
+      <x:c r="N810" s="6" t="str"/>
+      <x:c r="O810" s="6" t="str">
+        <x:v>官方讲座简介明确获得硕士学位；未列年月。</x:v>
+      </x:c>
+      <x:c r="P810" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q810" s="6" t="str">
+        <x:v>https://kjc.ecnu.edu.cn/28/54/c8151a272468/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="811" ht="64" customHeight="1">
+      <x:c r="A811" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B811" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C811" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D811" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E811" s="6" t="str"/>
+      <x:c r="F811" s="6" t="str">
+        <x:v>2005</x:v>
+      </x:c>
+      <x:c r="G811" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H811" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I811" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J811" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K811" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L811" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M811" s="7" t="str"/>
+      <x:c r="N811" s="6" t="str"/>
+      <x:c r="O811" s="6" t="str">
+        <x:v>2016本人署名论文作者简介明确2005获PhD；华东师大讲座写信号与信息处理，可能是一级学科/二级学科口径，二者并列不删。</x:v>
+      </x:c>
+      <x:c r="P811" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q811" s="6" t="str">
+        <x:v>https://openremotesensing.net/wp-content/uploads/2019/11/TGRS_2016_MLK_Yanfeng_Gu.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="812" ht="64" customHeight="1">
+      <x:c r="A812" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B812" s="6" t="str">
+        <x:v>visiting_scholar</x:v>
+      </x:c>
+      <x:c r="C812" s="6" t="str"/>
+      <x:c r="D812" s="6" t="str">
+        <x:v>加利福尼亚大学伯克利分校</x:v>
+      </x:c>
+      <x:c r="E812" s="6" t="str">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="F812" s="6" t="str">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="G812" s="6" t="str"/>
+      <x:c r="H812" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I812" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J812" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K812" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L812" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M812" s="7" t="str"/>
+      <x:c r="N812" s="6" t="str"/>
+      <x:c r="O812" s="6" t="str">
+        <x:v>2016本人署名论文简介列电子工程与计算机科学系访问学者。 事件类型：访问学者（非授位）。</x:v>
+      </x:c>
+      <x:c r="P812" s="6" t="str">
+        <x:v>按所指院校所在地标准化，不代表国籍；学位与访学、博士后、非授位学习分开。</x:v>
+      </x:c>
+      <x:c r="Q812" s="6" t="str">
+        <x:v>https://openremotesensing.net/wp-content/uploads/2019/11/TGRS_2016_MLK_Yanfeng_Gu.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="813" ht="64" customHeight="1">
+      <x:c r="A813" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B813" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C813" s="6" t="str">
+        <x:v>二级教授</x:v>
+      </x:c>
+      <x:c r="D813" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E813" s="6" t="str"/>
+      <x:c r="F813" s="6" t="str"/>
+      <x:c r="G813" s="6" t="str"/>
+      <x:c r="H813" s="6" t="str"/>
+      <x:c r="I813" s="6" t="str"/>
+      <x:c r="J813" s="6" t="str"/>
+      <x:c r="K813" s="6" t="str"/>
+      <x:c r="L813" s="6" t="str"/>
+      <x:c r="M813" s="7" t="str"/>
+      <x:c r="N813" s="6" t="str"/>
+      <x:c r="O813" s="6" t="str"/>
+      <x:c r="P813" s="6" t="str"/>
+      <x:c r="Q813" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guyf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="814" ht="64" customHeight="1">
+      <x:c r="A814" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B814" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C814" s="6" t="str">
+        <x:v>电子与信息工程学院副院长</x:v>
+      </x:c>
+      <x:c r="D814" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E814" s="6" t="str"/>
+      <x:c r="F814" s="6" t="str"/>
+      <x:c r="G814" s="6" t="str"/>
+      <x:c r="H814" s="6" t="str"/>
+      <x:c r="I814" s="6" t="str"/>
+      <x:c r="J814" s="6" t="str"/>
+      <x:c r="K814" s="6" t="str"/>
+      <x:c r="L814" s="6" t="str"/>
+      <x:c r="M814" s="7" t="str"/>
+      <x:c r="N814" s="6" t="str"/>
+      <x:c r="O814" s="6" t="str"/>
+      <x:c r="P814" s="6" t="str"/>
+      <x:c r="Q814" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guyf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="815" ht="64" customHeight="1">
+      <x:c r="A815" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B815" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C815" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D815" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E815" s="6" t="str"/>
+      <x:c r="F815" s="6" t="str"/>
+      <x:c r="G815" s="6" t="str"/>
+      <x:c r="H815" s="6" t="str"/>
+      <x:c r="I815" s="6" t="str"/>
+      <x:c r="J815" s="6" t="str"/>
+      <x:c r="K815" s="6" t="str"/>
+      <x:c r="L815" s="6" t="str"/>
+      <x:c r="M815" s="7" t="str"/>
+      <x:c r="N815" s="6" t="str"/>
+      <x:c r="O815" s="6" t="str"/>
+      <x:c r="P815" s="6" t="str"/>
+      <x:c r="Q815" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guyf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="816" ht="64" customHeight="1">
+      <x:c r="A816" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B816" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C816" s="6" t="str">
+        <x:v>主任</x:v>
+      </x:c>
+      <x:c r="D816" s="6" t="str">
+        <x:v>黑龙江省天空地一体化智能遥感技术重点实验室</x:v>
+      </x:c>
+      <x:c r="E816" s="6" t="str"/>
+      <x:c r="F816" s="6" t="str"/>
+      <x:c r="G816" s="6" t="str"/>
+      <x:c r="H816" s="6" t="str"/>
+      <x:c r="I816" s="6" t="str"/>
+      <x:c r="J816" s="6" t="str"/>
+      <x:c r="K816" s="6" t="str"/>
+      <x:c r="L816" s="6" t="str"/>
+      <x:c r="M816" s="7" t="str"/>
+      <x:c r="N816" s="6" t="str"/>
+      <x:c r="O816" s="6" t="str"/>
+      <x:c r="P816" s="6" t="str"/>
+      <x:c r="Q816" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guyf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="817" ht="64" customHeight="1">
+      <x:c r="A817" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B817" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C817" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D817" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E817" s="6" t="str"/>
+      <x:c r="F817" s="6" t="str"/>
+      <x:c r="G817" s="6" t="str"/>
+      <x:c r="H817" s="6" t="str"/>
+      <x:c r="I817" s="6" t="str"/>
+      <x:c r="J817" s="6" t="str"/>
+      <x:c r="K817" s="6" t="str"/>
+      <x:c r="L817" s="6" t="str"/>
+      <x:c r="M817" s="7" t="str"/>
+      <x:c r="N817" s="6" t="str"/>
+      <x:c r="O817" s="6" t="str">
+        <x:v>2016作者简介称博士毕业后任讲师；精确起讫未给，不由“随后”推算日期。</x:v>
+      </x:c>
+      <x:c r="P817" s="6" t="str"/>
+      <x:c r="Q817" s="6" t="str">
+        <x:v>https://openremotesensing.net/wp-content/uploads/2019/11/TGRS_2016_MLK_Yanfeng_Gu.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="818" ht="64" customHeight="1">
+      <x:c r="A818" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B818" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C818" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D818" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E818" s="6" t="str">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="F818" s="6" t="str"/>
+      <x:c r="G818" s="6" t="str"/>
+      <x:c r="H818" s="6" t="str"/>
+      <x:c r="I818" s="6" t="str"/>
+      <x:c r="J818" s="6" t="str"/>
+      <x:c r="K818" s="6" t="str"/>
+      <x:c r="L818" s="6" t="str"/>
+      <x:c r="M818" s="7" t="str"/>
+      <x:c r="N818" s="6" t="str"/>
+      <x:c r="O818" s="6" t="str">
+        <x:v>2016作者简介明确2006任副教授，终止日期未披露；2016已为教授，不倒推晋升年份。</x:v>
+      </x:c>
+      <x:c r="P818" s="6" t="str"/>
+      <x:c r="Q818" s="6" t="str">
+        <x:v>https://openremotesensing.net/wp-content/uploads/2019/11/TGRS_2016_MLK_Yanfeng_Gu.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="819" ht="64" customHeight="1">
+      <x:c r="A819" s="6" t="str">
+        <x:v>侯成宇</x:v>
+      </x:c>
+      <x:c r="B819" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C819" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D819" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E819" s="6" t="str"/>
+      <x:c r="F819" s="6" t="str">
+        <x:v>2003</x:v>
+      </x:c>
+      <x:c r="G819" s="6" t="str">
+        <x:v>electronics and communication engineering</x:v>
+      </x:c>
+      <x:c r="H819" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I819" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J819" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K819" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L819" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M819" s="7" t="str"/>
+      <x:c r="N819" s="6" t="str"/>
+      <x:c r="O819" s="6" t="str">
+        <x:v>2015正式期刊作者简介明确receivedMS fromHIT in2003，同机构及HF雷达信号处理方向对应当前本人；不是从现任机构推学历。</x:v>
+      </x:c>
+      <x:c r="P819" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q819" s="6" t="str">
+        <x:v>https://article.nadiapub.com/IJSIP/vol8_no11/26.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="820" ht="64" customHeight="1">
+      <x:c r="A820" s="6" t="str">
+        <x:v>侯成宇</x:v>
+      </x:c>
+      <x:c r="B820" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C820" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D820" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E820" s="6" t="str"/>
+      <x:c r="F820" s="6" t="str"/>
+      <x:c r="G820" s="6" t="str">
+        <x:v>electronics and communication engineering</x:v>
+      </x:c>
+      <x:c r="H820" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I820" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J820" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K820" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L820" s="6" t="str"/>
+      <x:c r="M820" s="7" t="str"/>
+      <x:c r="N820" s="6" t="str"/>
+      <x:c r="O820" s="6" t="str">
+        <x:v>同篇2015作者简介仅doctoral candidate，表示历史在读证据，不代表目前仍在读或已获博士。</x:v>
+      </x:c>
+      <x:c r="P820" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q820" s="6" t="str">
+        <x:v>https://article.nadiapub.com/IJSIP/vol8_no11/26.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="821" ht="64" customHeight="1">
+      <x:c r="A821" s="6" t="str">
+        <x:v>侯成宇</x:v>
+      </x:c>
+      <x:c r="B821" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C821" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D821" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E821" s="6" t="str"/>
+      <x:c r="F821" s="6" t="str"/>
+      <x:c r="G821" s="6" t="str"/>
+      <x:c r="H821" s="6" t="str"/>
+      <x:c r="I821" s="6" t="str"/>
+      <x:c r="J821" s="6" t="str"/>
+      <x:c r="K821" s="6" t="str"/>
+      <x:c r="L821" s="6" t="str"/>
+      <x:c r="M821" s="7" t="str"/>
+      <x:c r="N821" s="6" t="str"/>
+      <x:c r="O821" s="6" t="str"/>
+      <x:c r="P821" s="6" t="str"/>
+      <x:c r="Q821" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houchengyu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="822" ht="64" customHeight="1">
+      <x:c r="A822" s="6" t="str">
+        <x:v>侯成宇</x:v>
+      </x:c>
+      <x:c r="B822" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C822" s="6" t="str">
+        <x:v>副主任（主管本科教学）</x:v>
+      </x:c>
+      <x:c r="D822" s="6" t="str">
+        <x:v>哈尔滨工业大学信息工程系</x:v>
+      </x:c>
+      <x:c r="E822" s="6" t="str"/>
+      <x:c r="F822" s="6" t="str"/>
+      <x:c r="G822" s="6" t="str"/>
+      <x:c r="H822" s="6" t="str"/>
+      <x:c r="I822" s="6" t="str"/>
+      <x:c r="J822" s="6" t="str"/>
+      <x:c r="K822" s="6" t="str"/>
+      <x:c r="L822" s="6" t="str"/>
+      <x:c r="M822" s="7" t="str"/>
+      <x:c r="N822" s="6" t="str"/>
+      <x:c r="O822" s="6" t="str"/>
+      <x:c r="P822" s="6" t="str"/>
+      <x:c r="Q822" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houchengyu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="823" ht="64" customHeight="1">
+      <x:c r="A823" s="6" t="str">
+        <x:v>陈雨时</x:v>
+      </x:c>
+      <x:c r="B823" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C823" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D823" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E823" s="6" t="str">
+        <x:v>1997-09</x:v>
+      </x:c>
+      <x:c r="F823" s="6" t="str">
+        <x:v>2001-07</x:v>
+      </x:c>
+      <x:c r="G823" s="6" t="str">
+        <x:v>电子信息工程</x:v>
+      </x:c>
+      <x:c r="H823" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I823" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J823" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K823" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L823" s="6" t="str"/>
+      <x:c r="M823" s="7" t="str"/>
+      <x:c r="N823" s="6" t="str"/>
+      <x:c r="O823" s="6" t="str"/>
+      <x:c r="P823" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q823" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chenyushi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="824" ht="64" customHeight="1">
+      <x:c r="A824" s="6" t="str">
+        <x:v>陈雨时</x:v>
+      </x:c>
+      <x:c r="B824" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C824" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D824" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E824" s="6" t="str">
+        <x:v>2001-09</x:v>
+      </x:c>
+      <x:c r="F824" s="6" t="str">
+        <x:v>2003-07</x:v>
+      </x:c>
+      <x:c r="G824" s="6" t="str">
+        <x:v>信号与信息处理</x:v>
+      </x:c>
+      <x:c r="H824" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I824" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J824" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K824" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L824" s="6" t="str"/>
+      <x:c r="M824" s="7" t="str"/>
+      <x:c r="N824" s="6" t="str"/>
+      <x:c r="O824" s="6" t="str"/>
+      <x:c r="P824" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q824" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chenyushi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="825" ht="64" customHeight="1">
+      <x:c r="A825" s="6" t="str">
+        <x:v>陈雨时</x:v>
+      </x:c>
+      <x:c r="B825" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C825" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D825" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E825" s="6" t="str">
+        <x:v>2003-09</x:v>
+      </x:c>
+      <x:c r="F825" s="6" t="str">
+        <x:v>2008-01</x:v>
+      </x:c>
+      <x:c r="G825" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H825" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I825" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J825" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K825" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L825" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M825" s="7" t="str"/>
+      <x:c r="N825" s="6" t="str"/>
+      <x:c r="O825" s="6" t="str">
+        <x:v>本人简介明确工学博士。</x:v>
+      </x:c>
+      <x:c r="P825" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q825" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chenyushi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="826" ht="64" customHeight="1">
+      <x:c r="A826" s="6" t="str">
+        <x:v>陈雨时</x:v>
+      </x:c>
+      <x:c r="B826" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="C826" s="6" t="str"/>
+      <x:c r="D826" s="6" t="str">
+        <x:v>北京市遥感信息研究所</x:v>
+      </x:c>
+      <x:c r="E826" s="6" t="str">
+        <x:v>2008-12</x:v>
+      </x:c>
+      <x:c r="F826" s="6" t="str">
+        <x:v>2012-05</x:v>
+      </x:c>
+      <x:c r="G826" s="6" t="str"/>
+      <x:c r="H826" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I826" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J826" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K826" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L826" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M826" s="7" t="str"/>
+      <x:c r="N826" s="6" t="str"/>
+      <x:c r="O826" s="6" t="str">
+        <x:v>按官网正式机构名保留，不无证猜测其他研究所名称或机构隶属。 事件类型：博士后研究（非授位）。</x:v>
+      </x:c>
+      <x:c r="P826" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q826" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chenyushi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="827" ht="64" customHeight="1">
+      <x:c r="A827" s="6" t="str">
+        <x:v>陈雨时</x:v>
+      </x:c>
+      <x:c r="B827" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C827" s="6" t="str">
+        <x:v>教师</x:v>
+      </x:c>
+      <x:c r="D827" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E827" s="6" t="str">
+        <x:v>2008-03</x:v>
+      </x:c>
+      <x:c r="F827" s="6" t="str"/>
+      <x:c r="G827" s="6" t="str"/>
+      <x:c r="H827" s="6" t="str"/>
+      <x:c r="I827" s="6" t="str"/>
+      <x:c r="J827" s="6" t="str"/>
+      <x:c r="K827" s="6" t="str"/>
+      <x:c r="L827" s="6" t="str"/>
+      <x:c r="M827" s="7" t="str"/>
+      <x:c r="N827" s="6" t="str"/>
+      <x:c r="O827" s="6" t="str"/>
+      <x:c r="P827" s="6" t="str"/>
+      <x:c r="Q827" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chenyushi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="828" ht="64" customHeight="1">
+      <x:c r="A828" s="6" t="str">
+        <x:v>陈雨时</x:v>
+      </x:c>
+      <x:c r="B828" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C828" s="6" t="str">
+        <x:v>长聘教授、博士生导师</x:v>
+      </x:c>
+      <x:c r="D828" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E828" s="6" t="str"/>
+      <x:c r="F828" s="6" t="str"/>
+      <x:c r="G828" s="6" t="str"/>
+      <x:c r="H828" s="6" t="str"/>
+      <x:c r="I828" s="6" t="str"/>
+      <x:c r="J828" s="6" t="str"/>
+      <x:c r="K828" s="6" t="str"/>
+      <x:c r="L828" s="6" t="str"/>
+      <x:c r="M828" s="7" t="str"/>
+      <x:c r="N828" s="6" t="str"/>
+      <x:c r="O828" s="6" t="str">
+        <x:v>当前简介列此职称，不能以2008教师起点当教授起点。</x:v>
+      </x:c>
+      <x:c r="P828" s="6" t="str"/>
+      <x:c r="Q828" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chenyushi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="829" ht="64" customHeight="1">
+      <x:c r="A829" s="6" t="str">
+        <x:v>尹振东</x:v>
+      </x:c>
+      <x:c r="B829" s="6" t="str">
+        <x:v>study_stage_unspecified</x:v>
+      </x:c>
+      <x:c r="C829" s="6" t="str"/>
+      <x:c r="D829" s="6" t="str">
+        <x:v>哈尔滨工业大学英才学院</x:v>
+      </x:c>
+      <x:c r="E829" s="6" t="str"/>
+      <x:c r="F829" s="6" t="str">
+        <x:v>2001</x:v>
+      </x:c>
+      <x:c r="G829" s="6" t="str"/>
+      <x:c r="H829" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I829" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J829" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K829" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L829" s="6" t="str"/>
+      <x:c r="M829" s="7" t="str"/>
+      <x:c r="N829" s="6" t="str"/>
+      <x:c r="O829" s="6" t="str">
+        <x:v>官网只说英才学院2001届毕业生，未明确该行学位与专业，不擅判本科授位；仅留毕业履历。</x:v>
+      </x:c>
+      <x:c r="P829" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q829" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yinzhendong</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="830" ht="64" customHeight="1">
+      <x:c r="A830" s="6" t="str">
+        <x:v>尹振东</x:v>
+      </x:c>
+      <x:c r="B830" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C830" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D830" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E830" s="6" t="str"/>
+      <x:c r="F830" s="6" t="str">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="G830" s="6" t="str"/>
+      <x:c r="H830" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I830" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J830" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K830" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L830" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M830" s="7" t="str"/>
+      <x:c r="N830" s="6" t="str"/>
+      <x:c r="O830" s="6" t="str">
+        <x:v>正式出版社论文作者简介直接He received his PhD degree fromHIT in2008；同名同单位同UWB/卫星通信研究方向，不合并河南电气工程同名作者。</x:v>
+      </x:c>
+      <x:c r="P830" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q830" s="6" t="str">
+        <x:v>https://www.ijiet.org/online/WA4003.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="831" ht="64" customHeight="1">
+      <x:c r="A831" s="6" t="str">
+        <x:v>尹振东</x:v>
+      </x:c>
+      <x:c r="B831" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C831" s="6" t="str">
+        <x:v>长聘教授、博士生导师</x:v>
+      </x:c>
+      <x:c r="D831" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E831" s="6" t="str"/>
+      <x:c r="F831" s="6" t="str"/>
+      <x:c r="G831" s="6" t="str"/>
+      <x:c r="H831" s="6" t="str"/>
+      <x:c r="I831" s="6" t="str"/>
+      <x:c r="J831" s="6" t="str"/>
+      <x:c r="K831" s="6" t="str"/>
+      <x:c r="L831" s="6" t="str"/>
+      <x:c r="M831" s="7" t="str"/>
+      <x:c r="N831" s="6" t="str"/>
+      <x:c r="O831" s="6" t="str"/>
+      <x:c r="P831" s="6" t="str"/>
+      <x:c r="Q831" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yinzhendong</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="832" ht="64" customHeight="1">
+      <x:c r="A832" s="6" t="str">
+        <x:v>尹振东</x:v>
+      </x:c>
+      <x:c r="B832" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C832" s="6" t="str">
+        <x:v>主任</x:v>
+      </x:c>
+      <x:c r="D832" s="6" t="str">
+        <x:v>哈尔滨工业大学信息工程系</x:v>
+      </x:c>
+      <x:c r="E832" s="6" t="str"/>
+      <x:c r="F832" s="6" t="str"/>
+      <x:c r="G832" s="6" t="str"/>
+      <x:c r="H832" s="6" t="str"/>
+      <x:c r="I832" s="6" t="str"/>
+      <x:c r="J832" s="6" t="str"/>
+      <x:c r="K832" s="6" t="str"/>
+      <x:c r="L832" s="6" t="str"/>
+      <x:c r="M832" s="7" t="str"/>
+      <x:c r="N832" s="6" t="str"/>
+      <x:c r="O832" s="6" t="str"/>
+      <x:c r="P832" s="6" t="str"/>
+      <x:c r="Q832" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yinzhendong</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="833" ht="64" customHeight="1">
+      <x:c r="A833" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B833" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C833" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D833" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E833" s="6" t="str">
+        <x:v>1997-09</x:v>
+      </x:c>
+      <x:c r="F833" s="6" t="str">
+        <x:v>2001-07</x:v>
+      </x:c>
+      <x:c r="G833" s="6" t="str">
+        <x:v>电子与通信工程</x:v>
+      </x:c>
+      <x:c r="H833" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I833" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J833" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K833" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L833" s="6" t="str"/>
+      <x:c r="M833" s="7" t="str"/>
+      <x:c r="N833" s="6" t="str"/>
+      <x:c r="O833" s="6" t="str"/>
+      <x:c r="P833" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q833" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="834" ht="64" customHeight="1">
+      <x:c r="A834" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B834" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C834" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D834" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E834" s="6" t="str">
+        <x:v>2001-09</x:v>
+      </x:c>
+      <x:c r="F834" s="6" t="str">
+        <x:v>2003-07</x:v>
+      </x:c>
+      <x:c r="G834" s="6" t="str">
+        <x:v>信号与信息处理</x:v>
+      </x:c>
+      <x:c r="H834" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I834" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J834" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K834" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L834" s="6" t="str"/>
+      <x:c r="M834" s="7" t="str"/>
+      <x:c r="N834" s="6" t="str"/>
+      <x:c r="O834" s="6" t="str"/>
+      <x:c r="P834" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q834" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="835" ht="64" customHeight="1">
+      <x:c r="A835" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B835" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C835" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D835" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E835" s="6" t="str">
+        <x:v>2003-09</x:v>
+      </x:c>
+      <x:c r="F835" s="6" t="str">
+        <x:v>2007-12</x:v>
+      </x:c>
+      <x:c r="G835" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H835" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I835" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J835" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K835" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L835" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M835" s="7" t="str"/>
+      <x:c r="N835" s="6" t="str"/>
+      <x:c r="O835" s="6" t="str">
+        <x:v>中文简介明确博士。</x:v>
+      </x:c>
+      <x:c r="P835" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q835" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="836" ht="64" customHeight="1">
+      <x:c r="A836" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B836" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="C836" s="6" t="str"/>
+      <x:c r="D836" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E836" s="6" t="str">
+        <x:v>2008-05</x:v>
+      </x:c>
+      <x:c r="F836" s="6" t="str">
+        <x:v>2011-05</x:v>
+      </x:c>
+      <x:c r="G836" s="6" t="str"/>
+      <x:c r="H836" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I836" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J836" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K836" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L836" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M836" s="7" t="str"/>
+      <x:c r="N836" s="6" t="str"/>
+      <x:c r="O836" s="6" t="str">
+        <x:v>事件类型：博士后研究（非授位）。</x:v>
+      </x:c>
+      <x:c r="P836" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q836" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="837" ht="64" customHeight="1">
+      <x:c r="A837" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B837" s="6" t="str">
+        <x:v>visiting_scholar</x:v>
+      </x:c>
+      <x:c r="C837" s="6" t="str"/>
+      <x:c r="D837" s="6" t="str">
+        <x:v>威斯康星大学（具体校区未披露）</x:v>
+      </x:c>
+      <x:c r="E837" s="6" t="str">
+        <x:v>2013-02</x:v>
+      </x:c>
+      <x:c r="F837" s="6" t="str">
+        <x:v>2014-02</x:v>
+      </x:c>
+      <x:c r="G837" s="6" t="str"/>
+      <x:c r="H837" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I837" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J837" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K837" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L837" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M837" s="7" t="str"/>
+      <x:c r="N837" s="6" t="str"/>
+      <x:c r="O837" s="6" t="str">
+        <x:v>官方只写美国威斯康星大学，不擅自指定Madison或Milwaukee等校区；美国地域明确，非授位。 事件类型：访问学者（非授位）。</x:v>
+      </x:c>
+      <x:c r="P837" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q837" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="838" ht="64" customHeight="1">
+      <x:c r="A838" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B838" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C838" s="6" t="str">
+        <x:v>助教</x:v>
+      </x:c>
+      <x:c r="D838" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E838" s="6" t="str">
+        <x:v>2004-10</x:v>
+      </x:c>
+      <x:c r="F838" s="6" t="str">
+        <x:v>2007-05</x:v>
+      </x:c>
+      <x:c r="G838" s="6" t="str"/>
+      <x:c r="H838" s="6" t="str"/>
+      <x:c r="I838" s="6" t="str"/>
+      <x:c r="J838" s="6" t="str"/>
+      <x:c r="K838" s="6" t="str"/>
+      <x:c r="L838" s="6" t="str"/>
+      <x:c r="M838" s="7" t="str"/>
+      <x:c r="N838" s="6" t="str"/>
+      <x:c r="O838" s="6" t="str">
+        <x:v>英文AssistantProfessor易误作助理教授，按中文助教职称。</x:v>
+      </x:c>
+      <x:c r="P838" s="6" t="str"/>
+      <x:c r="Q838" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="839" ht="64" customHeight="1">
+      <x:c r="A839" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B839" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C839" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D839" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E839" s="6" t="str">
+        <x:v>2007-06</x:v>
+      </x:c>
+      <x:c r="F839" s="6" t="str">
+        <x:v>2011-09</x:v>
+      </x:c>
+      <x:c r="G839" s="6" t="str"/>
+      <x:c r="H839" s="6" t="str"/>
+      <x:c r="I839" s="6" t="str"/>
+      <x:c r="J839" s="6" t="str"/>
+      <x:c r="K839" s="6" t="str"/>
+      <x:c r="L839" s="6" t="str"/>
+      <x:c r="M839" s="7" t="str"/>
+      <x:c r="N839" s="6" t="str"/>
+      <x:c r="O839" s="6" t="str"/>
+      <x:c r="P839" s="6" t="str"/>
+      <x:c r="Q839" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="840" ht="64" customHeight="1">
+      <x:c r="A840" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B840" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C840" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D840" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E840" s="6" t="str">
+        <x:v>2011-09</x:v>
+      </x:c>
+      <x:c r="F840" s="6" t="str"/>
+      <x:c r="G840" s="6" t="str"/>
+      <x:c r="H840" s="6" t="str"/>
+      <x:c r="I840" s="6" t="str"/>
+      <x:c r="J840" s="6" t="str"/>
+      <x:c r="K840" s="6" t="str"/>
+      <x:c r="L840" s="6" t="str"/>
+      <x:c r="M840" s="7" t="str"/>
+      <x:c r="N840" s="6" t="str"/>
+      <x:c r="O840" s="6" t="str">
+        <x:v>官网仍写今但2019.12又列教授，任职更新冲突未擅补2019结束。</x:v>
+      </x:c>
+      <x:c r="P840" s="6" t="str"/>
+      <x:c r="Q840" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="841" ht="64" customHeight="1">
+      <x:c r="A841" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B841" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C841" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D841" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E841" s="6" t="str">
+        <x:v>2019-12</x:v>
+      </x:c>
+      <x:c r="F841" s="6" t="str"/>
+      <x:c r="G841" s="6" t="str"/>
+      <x:c r="H841" s="6" t="str"/>
+      <x:c r="I841" s="6" t="str"/>
+      <x:c r="J841" s="6" t="str"/>
+      <x:c r="K841" s="6" t="str"/>
+      <x:c r="L841" s="6" t="str"/>
+      <x:c r="M841" s="7" t="str"/>
+      <x:c r="N841" s="6" t="str"/>
+      <x:c r="O841" s="6" t="str"/>
+      <x:c r="P841" s="6" t="str"/>
+      <x:c r="Q841" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="842" ht="64" customHeight="1">
+      <x:c r="A842" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B842" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C842" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D842" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E842" s="6" t="str">
+        <x:v>2010-05</x:v>
+      </x:c>
+      <x:c r="F842" s="6" t="str"/>
+      <x:c r="G842" s="6" t="str"/>
+      <x:c r="H842" s="6" t="str"/>
+      <x:c r="I842" s="6" t="str"/>
+      <x:c r="J842" s="6" t="str"/>
+      <x:c r="K842" s="6" t="str"/>
+      <x:c r="L842" s="6" t="str"/>
+      <x:c r="M842" s="7" t="str"/>
+      <x:c r="N842" s="6" t="str"/>
+      <x:c r="O842" s="6" t="str"/>
+      <x:c r="P842" s="6" t="str"/>
+      <x:c r="Q842" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="843" ht="64" customHeight="1">
+      <x:c r="A843" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B843" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C843" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D843" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E843" s="6" t="str">
+        <x:v>2016-04</x:v>
+      </x:c>
+      <x:c r="F843" s="6" t="str"/>
+      <x:c r="G843" s="6" t="str"/>
+      <x:c r="H843" s="6" t="str"/>
+      <x:c r="I843" s="6" t="str"/>
+      <x:c r="J843" s="6" t="str"/>
+      <x:c r="K843" s="6" t="str"/>
+      <x:c r="L843" s="6" t="str"/>
+      <x:c r="M843" s="7" t="str"/>
+      <x:c r="N843" s="6" t="str"/>
+      <x:c r="O843" s="6" t="str"/>
+      <x:c r="P843" s="6" t="str"/>
+      <x:c r="Q843" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="844" ht="64" customHeight="1">
+      <x:c r="A844" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B844" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C844" s="6" t="str">
+        <x:v>副主任</x:v>
+      </x:c>
+      <x:c r="D844" s="6" t="str">
+        <x:v>哈尔滨工业大学信息工程系</x:v>
+      </x:c>
+      <x:c r="E844" s="6" t="str">
+        <x:v>2012-05</x:v>
+      </x:c>
+      <x:c r="F844" s="6" t="str"/>
+      <x:c r="G844" s="6" t="str"/>
+      <x:c r="H844" s="6" t="str"/>
+      <x:c r="I844" s="6" t="str"/>
+      <x:c r="J844" s="6" t="str"/>
+      <x:c r="K844" s="6" t="str"/>
+      <x:c r="L844" s="6" t="str"/>
+      <x:c r="M844" s="7" t="str"/>
+      <x:c r="N844" s="6" t="str"/>
+      <x:c r="O844" s="6" t="str">
+        <x:v>工作表如此，现简介具体列研究生教学主任，保留两种表述不擅定职务变更日期。</x:v>
+      </x:c>
+      <x:c r="P844" s="6" t="str"/>
+      <x:c r="Q844" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="845" ht="64" customHeight="1">
+      <x:c r="A845" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B845" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C845" s="6" t="str">
+        <x:v>研究生教学主任</x:v>
+      </x:c>
+      <x:c r="D845" s="6" t="str">
+        <x:v>哈尔滨工业大学信息工程系</x:v>
+      </x:c>
+      <x:c r="E845" s="6" t="str"/>
+      <x:c r="F845" s="6" t="str"/>
+      <x:c r="G845" s="6" t="str"/>
+      <x:c r="H845" s="6" t="str"/>
+      <x:c r="I845" s="6" t="str"/>
+      <x:c r="J845" s="6" t="str"/>
+      <x:c r="K845" s="6" t="str"/>
+      <x:c r="L845" s="6" t="str"/>
+      <x:c r="M845" s="7" t="str"/>
+      <x:c r="N845" s="6" t="str"/>
+      <x:c r="O845" s="6" t="str"/>
+      <x:c r="P845" s="6" t="str"/>
+      <x:c r="Q845" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="846" ht="64" customHeight="1">
+      <x:c r="A846" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B846" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C846" s="6" t="str">
+        <x:v>团队负责人</x:v>
+      </x:c>
+      <x:c r="D846" s="6" t="str">
+        <x:v>哈尔滨工业大学图象与信息技术研究所</x:v>
+      </x:c>
+      <x:c r="E846" s="6" t="str"/>
+      <x:c r="F846" s="6" t="str"/>
+      <x:c r="G846" s="6" t="str"/>
+      <x:c r="H846" s="6" t="str"/>
+      <x:c r="I846" s="6" t="str"/>
+      <x:c r="J846" s="6" t="str"/>
+      <x:c r="K846" s="6" t="str"/>
+      <x:c r="L846" s="6" t="str"/>
+      <x:c r="M846" s="7" t="str"/>
+      <x:c r="N846" s="6" t="str"/>
+      <x:c r="O846" s="6" t="str"/>
+      <x:c r="P846" s="6" t="str"/>
+      <x:c r="Q846" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="847" ht="64" customHeight="1">
+      <x:c r="A847" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B847" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C847" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D847" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E847" s="6" t="str">
+        <x:v>2000-09</x:v>
+      </x:c>
+      <x:c r="F847" s="6" t="str">
+        <x:v>2004-07</x:v>
+      </x:c>
+      <x:c r="G847" s="6" t="str">
+        <x:v>电子信息工程</x:v>
+      </x:c>
+      <x:c r="H847" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I847" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J847" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K847" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L847" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M847" s="7" t="str"/>
+      <x:c r="N847" s="6" t="str"/>
+      <x:c r="O847" s="6" t="str">
+        <x:v>中文明确获学士学位；英文简介笼统把三学位专业都写InformationandCommunicationEngineering，取中文及英文AcademicQualifications细分专业。</x:v>
+      </x:c>
+      <x:c r="P847" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q847" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="848" ht="64" customHeight="1">
+      <x:c r="A848" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B848" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C848" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D848" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E848" s="6" t="str">
+        <x:v>2004-09</x:v>
+      </x:c>
+      <x:c r="F848" s="6" t="str">
+        <x:v>2006-07</x:v>
+      </x:c>
+      <x:c r="G848" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H848" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I848" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J848" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K848" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L848" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M848" s="7" t="str"/>
+      <x:c r="N848" s="6" t="str"/>
+      <x:c r="O848" s="6" t="str">
+        <x:v>中文明确获硕士学位。</x:v>
+      </x:c>
+      <x:c r="P848" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q848" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="849" ht="64" customHeight="1">
+      <x:c r="A849" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B849" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C849" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D849" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E849" s="6" t="str">
+        <x:v>2006-09</x:v>
+      </x:c>
+      <x:c r="F849" s="6" t="str">
+        <x:v>2010-04</x:v>
+      </x:c>
+      <x:c r="G849" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H849" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I849" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J849" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K849" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L849" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M849" s="7" t="str"/>
+      <x:c r="N849" s="6" t="str"/>
+      <x:c r="O849" s="6" t="str">
+        <x:v>中文明确获博士学位。</x:v>
+      </x:c>
+      <x:c r="P849" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q849" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="850" ht="64" customHeight="1">
+      <x:c r="A850" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B850" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="C850" s="6" t="str"/>
+      <x:c r="D850" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E850" s="6" t="str">
+        <x:v>2010-09</x:v>
+      </x:c>
+      <x:c r="F850" s="6" t="str">
+        <x:v>2013-05</x:v>
+      </x:c>
+      <x:c r="G850" s="6" t="str">
+        <x:v>仪器科学与技术</x:v>
+      </x:c>
+      <x:c r="H850" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I850" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J850" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K850" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L850" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M850" s="7" t="str"/>
+      <x:c r="N850" s="6" t="str"/>
+      <x:c r="O850" s="6" t="str">
+        <x:v>事件类型：博士后研究（非授位）。</x:v>
+      </x:c>
+      <x:c r="P850" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q850" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="851" ht="64" customHeight="1">
+      <x:c r="A851" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B851" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C851" s="6" t="str">
+        <x:v>讲师→副教授→教授（连续任职，分段晋升日期未列）</x:v>
+      </x:c>
+      <x:c r="D851" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E851" s="6" t="str">
+        <x:v>2010-12</x:v>
+      </x:c>
+      <x:c r="F851" s="6" t="str"/>
+      <x:c r="G851" s="6" t="str"/>
+      <x:c r="H851" s="6" t="str"/>
+      <x:c r="I851" s="6" t="str"/>
+      <x:c r="J851" s="6" t="str"/>
+      <x:c r="K851" s="6" t="str"/>
+      <x:c r="L851" s="6" t="str"/>
+      <x:c r="M851" s="7" t="str"/>
+      <x:c r="N851" s="6" t="str"/>
+      <x:c r="O851" s="6" t="str">
+        <x:v>原文一行合列三职称，不能把2010.12当教授任命时间。</x:v>
+      </x:c>
+      <x:c r="P851" s="6" t="str"/>
+      <x:c r="Q851" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="852" ht="64" customHeight="1">
+      <x:c r="A852" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B852" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C852" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D852" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E852" s="6" t="str"/>
+      <x:c r="F852" s="6" t="str"/>
+      <x:c r="G852" s="6" t="str"/>
+      <x:c r="H852" s="6" t="str"/>
+      <x:c r="I852" s="6" t="str"/>
+      <x:c r="J852" s="6" t="str"/>
+      <x:c r="K852" s="6" t="str"/>
+      <x:c r="L852" s="6" t="str"/>
+      <x:c r="M852" s="7" t="str"/>
+      <x:c r="N852" s="6" t="str"/>
+      <x:c r="O852" s="6" t="str">
+        <x:v>现任教授有明确简介，具体晋升日期未知。</x:v>
+      </x:c>
+      <x:c r="P852" s="6" t="str"/>
+      <x:c r="Q852" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="853" ht="64" customHeight="1">
+      <x:c r="A853" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B853" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C853" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D853" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E853" s="6" t="str">
+        <x:v>2013-05</x:v>
+      </x:c>
+      <x:c r="F853" s="6" t="str"/>
+      <x:c r="G853" s="6" t="str"/>
+      <x:c r="H853" s="6" t="str"/>
+      <x:c r="I853" s="6" t="str"/>
+      <x:c r="J853" s="6" t="str"/>
+      <x:c r="K853" s="6" t="str"/>
+      <x:c r="L853" s="6" t="str"/>
+      <x:c r="M853" s="7" t="str"/>
+      <x:c r="N853" s="6" t="str"/>
+      <x:c r="O853" s="6" t="str"/>
+      <x:c r="P853" s="6" t="str"/>
+      <x:c r="Q853" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="854" ht="64" customHeight="1">
+      <x:c r="A854" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B854" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C854" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D854" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E854" s="6" t="str">
+        <x:v>2016-05</x:v>
+      </x:c>
+      <x:c r="F854" s="6" t="str"/>
+      <x:c r="G854" s="6" t="str"/>
+      <x:c r="H854" s="6" t="str"/>
+      <x:c r="I854" s="6" t="str"/>
+      <x:c r="J854" s="6" t="str"/>
+      <x:c r="K854" s="6" t="str"/>
+      <x:c r="L854" s="6" t="str"/>
+      <x:c r="M854" s="7" t="str"/>
+      <x:c r="N854" s="6" t="str"/>
+      <x:c r="O854" s="6" t="str">
+        <x:v>英文ProfessionalExperience写2016.04；当前start取中文，月份冲突保留。</x:v>
+      </x:c>
+      <x:c r="P854" s="6" t="str"/>
+      <x:c r="Q854" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="855" ht="64" customHeight="1">
+      <x:c r="A855" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B855" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C855" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D855" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E855" s="6" t="str"/>
+      <x:c r="F855" s="6" t="str">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="G855" s="6" t="str"/>
+      <x:c r="H855" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I855" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J855" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K855" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L855" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M855" s="7" t="str"/>
+      <x:c r="N855" s="6" t="str"/>
+      <x:c r="O855" s="6" t="str">
+        <x:v>作者简介明确M.E.于2008年取得，专业和开始时间未披露。</x:v>
+      </x:c>
+      <x:c r="P855" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q855" s="6" t="str">
+        <x:v>https://wrap.warwick.ac.uk/id/eprint/94040/1/WRAP-proactive-jamming-towards-interference-alignment-networks-Chen-2017.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="856" ht="64" customHeight="1">
+      <x:c r="A856" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B856" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C856" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D856" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E856" s="6" t="str"/>
+      <x:c r="F856" s="6" t="str">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="G856" s="6" t="str"/>
+      <x:c r="H856" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I856" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J856" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K856" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L856" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M856" s="7" t="str"/>
+      <x:c r="N856" s="6" t="str"/>
+      <x:c r="O856" s="6" t="str">
+        <x:v>作者简介明确2013年取得Ph.D.，专业和开始时间未披露。</x:v>
+      </x:c>
+      <x:c r="P856" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q856" s="6" t="str">
+        <x:v>https://wrap.warwick.ac.uk/id/eprint/94040/1/WRAP-proactive-jamming-towards-interference-alignment-networks-Chen-2017.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="857" ht="64" customHeight="1">
+      <x:c r="A857" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B857" s="6" t="str">
+        <x:v>visiting_research</x:v>
+      </x:c>
+      <x:c r="C857" s="6" t="str"/>
+      <x:c r="D857" s="6" t="str">
+        <x:v>King’s College London</x:v>
+      </x:c>
+      <x:c r="E857" s="6" t="str">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="F857" s="6" t="str">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="G857" s="6" t="str"/>
+      <x:c r="H857" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="I857" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="J857" s="6" t="str">
+        <x:v>欧洲</x:v>
+      </x:c>
+      <x:c r="K857" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L857" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M857" s="7" t="str"/>
+      <x:c r="N857" s="6" t="str"/>
+      <x:c r="O857" s="6" t="str">
+        <x:v>访问研究任职，不是英国学位，也无直接导师证据。 事件类型：访问研究（非授位）。</x:v>
+      </x:c>
+      <x:c r="P857" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q857" s="6" t="str">
+        <x:v>https://wrap.warwick.ac.uk/id/eprint/94040/1/WRAP-proactive-jamming-towards-interference-alignment-networks-Chen-2017.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="858" ht="64" customHeight="1">
+      <x:c r="A858" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B858" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C858" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D858" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E858" s="6" t="str"/>
+      <x:c r="F858" s="6" t="str"/>
+      <x:c r="G858" s="6" t="str"/>
+      <x:c r="H858" s="6" t="str"/>
+      <x:c r="I858" s="6" t="str"/>
+      <x:c r="J858" s="6" t="str"/>
+      <x:c r="K858" s="6" t="str"/>
+      <x:c r="L858" s="6" t="str"/>
+      <x:c r="M858" s="7" t="str"/>
+      <x:c r="N858" s="6" t="str"/>
+      <x:c r="O858" s="6" t="str"/>
+      <x:c r="P858" s="6" t="str"/>
+      <x:c r="Q858" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yangzhutian</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="859" ht="64" customHeight="1">
+      <x:c r="A859" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B859" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C859" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D859" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E859" s="6" t="str"/>
+      <x:c r="F859" s="6" t="str"/>
+      <x:c r="G859" s="6" t="str"/>
+      <x:c r="H859" s="6" t="str"/>
+      <x:c r="I859" s="6" t="str"/>
+      <x:c r="J859" s="6" t="str"/>
+      <x:c r="K859" s="6" t="str"/>
+      <x:c r="L859" s="6" t="str"/>
+      <x:c r="M859" s="7" t="str"/>
+      <x:c r="N859" s="6" t="str"/>
+      <x:c r="O859" s="6" t="str"/>
+      <x:c r="P859" s="6" t="str"/>
+      <x:c r="Q859" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yangzhutian</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="860" ht="64" customHeight="1">
+      <x:c r="A860" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B860" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C860" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D860" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E860" s="6" t="str"/>
+      <x:c r="F860" s="6" t="str"/>
+      <x:c r="G860" s="6" t="str"/>
+      <x:c r="H860" s="6" t="str"/>
+      <x:c r="I860" s="6" t="str"/>
+      <x:c r="J860" s="6" t="str"/>
+      <x:c r="K860" s="6" t="str"/>
+      <x:c r="L860" s="6" t="str"/>
+      <x:c r="M860" s="7" t="str"/>
+      <x:c r="N860" s="6" t="str"/>
+      <x:c r="O860" s="6" t="str">
+        <x:v>2017作者稿简介列当时副教授，未披露起讫，不以此覆盖当前教授身份。</x:v>
+      </x:c>
+      <x:c r="P860" s="6" t="str"/>
+      <x:c r="Q860" s="6" t="str">
+        <x:v>https://wrap.warwick.ac.uk/id/eprint/94040/1/WRAP-proactive-jamming-towards-interference-alignment-networks-Chen-2017.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="861" ht="64" customHeight="1">
+      <x:c r="A861" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B861" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C861" s="6" t="str">
+        <x:v>Visiting Research Associate</x:v>
+      </x:c>
+      <x:c r="D861" s="6" t="str">
+        <x:v>King’s College London</x:v>
+      </x:c>
+      <x:c r="E861" s="6" t="str">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="F861" s="6" t="str">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="G861" s="6" t="str"/>
+      <x:c r="H861" s="6" t="str"/>
+      <x:c r="I861" s="6" t="str"/>
+      <x:c r="J861" s="6" t="str"/>
+      <x:c r="K861" s="6" t="str"/>
+      <x:c r="L861" s="6" t="str"/>
+      <x:c r="M861" s="7" t="str"/>
+      <x:c r="N861" s="6" t="str"/>
+      <x:c r="O861" s="6" t="str">
+        <x:v>作者简介只披露年份，不推断具体月份。</x:v>
+      </x:c>
+      <x:c r="P861" s="6" t="str"/>
+      <x:c r="Q861" s="6" t="str">
+        <x:v>https://wrap.warwick.ac.uk/id/eprint/94040/1/WRAP-proactive-jamming-towards-interference-alignment-networks-Chen-2017.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="862" ht="64" customHeight="1">
+      <x:c r="A862" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B862" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C862" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D862" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E862" s="6" t="str">
+        <x:v>2004</x:v>
+      </x:c>
+      <x:c r="F862" s="6" t="str">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="G862" s="6" t="str">
+        <x:v>通信工程</x:v>
+      </x:c>
+      <x:c r="H862" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I862" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J862" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K862" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L862" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M862" s="7" t="str"/>
+      <x:c r="N862" s="6" t="str"/>
+      <x:c r="O862" s="6" t="str">
+        <x:v>中文教育经历给区间，英文简介明确获得B.S.；学位论文简介将专业写作Electrical Engineering，与HIT官网Communication Engineering存在表述差异，保留官网专业并记录差异。</x:v>
+      </x:c>
+      <x:c r="P862" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q862" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huyue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="863" ht="64" customHeight="1">
+      <x:c r="A863" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B863" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C863" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D863" s="6" t="str">
+        <x:v>University of Rochester</x:v>
+      </x:c>
+      <x:c r="E863" s="6" t="str"/>
+      <x:c r="F863" s="6" t="str">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="G863" s="6" t="str"/>
+      <x:c r="H863" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I863" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J863" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K863" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L863" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M863" s="7" t="str"/>
+      <x:c r="N863" s="6" t="str"/>
+      <x:c r="O863" s="6" t="str">
+        <x:v>本人学位论文作者简介明确2011年获M.S.；硕士单独起始年份及精确专业未披露，不直接把博士2008起点赋给硕士。HIT官网英文简介也明确获得M.S.。</x:v>
+      </x:c>
+      <x:c r="P863" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q863" s="6" t="str">
+        <x:v>https://research.engineering.uiowa.edu/cbig/sites/research.engineering.uiowa.edu.cbig/files/files/YueHu_thesis(1).pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="864" ht="64" customHeight="1">
+      <x:c r="A864" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B864" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C864" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D864" s="6" t="str">
+        <x:v>University of Rochester</x:v>
+      </x:c>
+      <x:c r="E864" s="6" t="str">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="F864" s="6" t="str">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="G864" s="6" t="str">
+        <x:v>电子工程</x:v>
+      </x:c>
+      <x:c r="H864" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I864" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J864" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K864" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L864" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M864" s="7" t="str"/>
+      <x:c r="N864" s="6" t="str"/>
+      <x:c r="O864" s="6" t="str">
+        <x:v>HIT中文教育经历列2008–2014硕博连读，英文明确已获Ph.D.；这里end仅为官网所列学习区间结束年，不是授位日期。论文署年与答辩另列为独立文献/答辩事件。</x:v>
+      </x:c>
+      <x:c r="P864" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q864" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huyue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="865" ht="64" customHeight="1">
+      <x:c r="A865" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B865" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C865" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D865" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E865" s="6" t="str"/>
+      <x:c r="F865" s="6" t="str"/>
+      <x:c r="G865" s="6" t="str"/>
+      <x:c r="H865" s="6" t="str"/>
+      <x:c r="I865" s="6" t="str"/>
+      <x:c r="J865" s="6" t="str"/>
+      <x:c r="K865" s="6" t="str"/>
+      <x:c r="L865" s="6" t="str"/>
+      <x:c r="M865" s="7" t="str"/>
+      <x:c r="N865" s="6" t="str"/>
+      <x:c r="O865" s="6" t="str"/>
+      <x:c r="P865" s="6" t="str"/>
+      <x:c r="Q865" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huyue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="866" ht="64" customHeight="1">
+      <x:c r="A866" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B866" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C866" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D866" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E866" s="6" t="str"/>
+      <x:c r="F866" s="6" t="str"/>
+      <x:c r="G866" s="6" t="str"/>
+      <x:c r="H866" s="6" t="str"/>
+      <x:c r="I866" s="6" t="str"/>
+      <x:c r="J866" s="6" t="str"/>
+      <x:c r="K866" s="6" t="str"/>
+      <x:c r="L866" s="6" t="str"/>
+      <x:c r="M866" s="7" t="str"/>
+      <x:c r="N866" s="6" t="str"/>
+      <x:c r="O866" s="6" t="str"/>
+      <x:c r="P866" s="6" t="str"/>
+      <x:c r="Q866" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huyue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="867" ht="64" customHeight="1">
+      <x:c r="A867" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B867" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C867" s="6" t="str">
+        <x:v>青年科学家工作室学术带头人</x:v>
+      </x:c>
+      <x:c r="D867" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E867" s="6" t="str"/>
+      <x:c r="F867" s="6" t="str"/>
+      <x:c r="G867" s="6" t="str"/>
+      <x:c r="H867" s="6" t="str"/>
+      <x:c r="I867" s="6" t="str"/>
+      <x:c r="J867" s="6" t="str"/>
+      <x:c r="K867" s="6" t="str"/>
+      <x:c r="L867" s="6" t="str"/>
+      <x:c r="M867" s="7" t="str"/>
+      <x:c r="N867" s="6" t="str"/>
+      <x:c r="O867" s="6" t="str">
+        <x:v>官网明确当前身份；开始时间未披露。</x:v>
+      </x:c>
+      <x:c r="P867" s="6" t="str"/>
+      <x:c r="Q867" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huyue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="868" ht="64" customHeight="1">
+      <x:c r="A868" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B868" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C868" s="6" t="str">
+        <x:v>Teaching Assistant</x:v>
+      </x:c>
+      <x:c r="D868" s="6" t="str">
+        <x:v>University of Rochester</x:v>
+      </x:c>
+      <x:c r="E868" s="6" t="str"/>
+      <x:c r="F868" s="6" t="str"/>
+      <x:c r="G868" s="6" t="str"/>
+      <x:c r="H868" s="6" t="str"/>
+      <x:c r="I868" s="6" t="str"/>
+      <x:c r="J868" s="6" t="str"/>
+      <x:c r="K868" s="6" t="str"/>
+      <x:c r="L868" s="6" t="str"/>
+      <x:c r="M868" s="7" t="str"/>
+      <x:c r="N868" s="6" t="str"/>
+      <x:c r="O868" s="6" t="str">
+        <x:v>本人论文作者简介明确曾为Digital Logic Design及Introduction to Digital Communications助教，具体任职起讫未披露。</x:v>
+      </x:c>
+      <x:c r="P868" s="6" t="str"/>
+      <x:c r="Q868" s="6" t="str">
+        <x:v>https://research.engineering.uiowa.edu/cbig/sites/research.engineering.uiowa.edu.cbig/files/files/YueHu_thesis(1).pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="869" ht="64" customHeight="1">
+      <x:c r="A869" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B869" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C869" s="6" t="str">
+        <x:v>负责人</x:v>
+      </x:c>
+      <x:c r="D869" s="6" t="str">
+        <x:v>哈尔滨工业大学Intelligent Multimodal Image Processing Lab（IMIP）</x:v>
+      </x:c>
+      <x:c r="E869" s="6" t="str"/>
+      <x:c r="F869" s="6" t="str"/>
+      <x:c r="G869" s="6" t="str"/>
+      <x:c r="H869" s="6" t="str"/>
+      <x:c r="I869" s="6" t="str"/>
+      <x:c r="J869" s="6" t="str"/>
+      <x:c r="K869" s="6" t="str"/>
+      <x:c r="L869" s="6" t="str"/>
+      <x:c r="M869" s="7" t="str"/>
+      <x:c r="N869" s="6" t="str"/>
+      <x:c r="O869" s="6" t="str">
+        <x:v>官网英文简介明确heading该实验室；起始时间未披露。</x:v>
+      </x:c>
+      <x:c r="P869" s="6" t="str"/>
+      <x:c r="Q869" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huyue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="870" ht="64" customHeight="1">
+      <x:c r="A870" s="6" t="str">
+        <x:v>刘金龙</x:v>
+      </x:c>
+      <x:c r="B870" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C870" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D870" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E870" s="6" t="str"/>
+      <x:c r="F870" s="6" t="str">
+        <x:v>2007</x:v>
+      </x:c>
+      <x:c r="G870" s="6" t="str"/>
+      <x:c r="H870" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I870" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J870" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K870" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L870" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M870" s="7" t="str"/>
+      <x:c r="N870" s="6" t="str"/>
+      <x:c r="O870" s="6" t="str">
+        <x:v>2019年IEEE论文作者简介明确收到B.S.学位；未披露专业或起始时间。身份另由期刊官网作者简介与HIT个人主页核验。</x:v>
+      </x:c>
+      <x:c r="P870" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q870" s="6" t="str">
+        <x:v>https://www.researchgate.net/publication/331430708_Learning-Based_User_Association_for_Dual-UAV_Enabled_Wireless_Networks_With_D2D_Connections</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="871" ht="64" customHeight="1">
+      <x:c r="A871" s="6" t="str">
+        <x:v>刘金龙</x:v>
+      </x:c>
+      <x:c r="B871" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C871" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D871" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E871" s="6" t="str"/>
+      <x:c r="F871" s="6" t="str">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="G871" s="6" t="str"/>
+      <x:c r="H871" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I871" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J871" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K871" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L871" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M871" s="7" t="str"/>
+      <x:c r="N871" s="6" t="str"/>
+      <x:c r="O871" s="6" t="str">
+        <x:v>2019年IEEE论文作者简介明确收到M.S.学位；未披露专业或起始时间。</x:v>
+      </x:c>
+      <x:c r="P871" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q871" s="6" t="str">
+        <x:v>https://www.researchgate.net/publication/331430708_Learning-Based_User_Association_for_Dual-UAV_Enabled_Wireless_Networks_With_D2D_Connections</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="872" ht="64" customHeight="1">
+      <x:c r="A872" s="6" t="str">
+        <x:v>刘金龙</x:v>
+      </x:c>
+      <x:c r="B872" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C872" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D872" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E872" s="6" t="str"/>
+      <x:c r="F872" s="6" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="G872" s="6" t="str"/>
+      <x:c r="H872" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I872" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J872" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K872" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L872" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M872" s="7" t="str"/>
+      <x:c r="N872" s="6" t="str"/>
+      <x:c r="O872" s="6" t="str">
+        <x:v>期刊官网作者简介明确2019年获得博士学位，未披露专业或起始时间；不把所在学院视作专业。</x:v>
+      </x:c>
+      <x:c r="P872" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q872" s="6" t="str">
+        <x:v>https://www.ijiet.org/online/WA4003.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="873" ht="64" customHeight="1">
+      <x:c r="A873" s="6" t="str">
+        <x:v>刘金龙</x:v>
+      </x:c>
+      <x:c r="B873" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C873" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D873" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E873" s="6" t="str"/>
+      <x:c r="F873" s="6" t="str"/>
+      <x:c r="G873" s="6" t="str"/>
+      <x:c r="H873" s="6" t="str"/>
+      <x:c r="I873" s="6" t="str"/>
+      <x:c r="J873" s="6" t="str"/>
+      <x:c r="K873" s="6" t="str"/>
+      <x:c r="L873" s="6" t="str"/>
+      <x:c r="M873" s="7" t="str"/>
+      <x:c r="N873" s="6" t="str"/>
+      <x:c r="O873" s="6" t="str"/>
+      <x:c r="P873" s="6" t="str"/>
+      <x:c r="Q873" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/JinlongLiu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="874" ht="64" customHeight="1">
+      <x:c r="A874" s="6" t="str">
+        <x:v>刘金龙</x:v>
+      </x:c>
+      <x:c r="B874" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C874" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D874" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E874" s="6" t="str"/>
+      <x:c r="F874" s="6" t="str"/>
+      <x:c r="G874" s="6" t="str"/>
+      <x:c r="H874" s="6" t="str"/>
+      <x:c r="I874" s="6" t="str"/>
+      <x:c r="J874" s="6" t="str"/>
+      <x:c r="K874" s="6" t="str"/>
+      <x:c r="L874" s="6" t="str"/>
+      <x:c r="M874" s="7" t="str"/>
+      <x:c r="N874" s="6" t="str"/>
+      <x:c r="O874" s="6" t="str"/>
+      <x:c r="P874" s="6" t="str"/>
+      <x:c r="Q874" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/JinlongLiu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="875" ht="64" customHeight="1">
+      <x:c r="A875" s="6" t="str">
+        <x:v>刘金龙</x:v>
+      </x:c>
+      <x:c r="B875" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C875" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D875" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E875" s="6" t="str"/>
+      <x:c r="F875" s="6" t="str"/>
+      <x:c r="G875" s="6" t="str"/>
+      <x:c r="H875" s="6" t="str"/>
+      <x:c r="I875" s="6" t="str"/>
+      <x:c r="J875" s="6" t="str"/>
+      <x:c r="K875" s="6" t="str"/>
+      <x:c r="L875" s="6" t="str"/>
+      <x:c r="M875" s="7" t="str"/>
+      <x:c r="N875" s="6" t="str"/>
+      <x:c r="O875" s="6" t="str">
+        <x:v>作者稿2021年收修日期所载当时身份；任职起讫未披露，不覆盖当前教授。</x:v>
+      </x:c>
+      <x:c r="P875" s="6" t="str"/>
+      <x:c r="Q875" s="6" t="str">
+        <x:v>https://www.ijiet.org/online/WA4003.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="876" ht="64" customHeight="1">
+      <x:c r="A876" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B876" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C876" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D876" s="6" t="str">
+        <x:v>哈尔滨工业大学（威海）</x:v>
+      </x:c>
+      <x:c r="E876" s="6" t="str">
+        <x:v>2007-09</x:v>
+      </x:c>
+      <x:c r="F876" s="6" t="str">
+        <x:v>2011-07</x:v>
+      </x:c>
+      <x:c r="G876" s="6" t="str">
+        <x:v>电子与信息工程</x:v>
+      </x:c>
+      <x:c r="H876" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I876" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J876" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K876" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L876" s="6" t="str"/>
+      <x:c r="M876" s="7" t="str"/>
+      <x:c r="N876" s="6" t="str"/>
+      <x:c r="O876" s="6" t="str">
+        <x:v>教育履历仅列工学学士/Bachelor of Engineering Degree标签，没有明确授予动词，degree_awarded保持null。</x:v>
+      </x:c>
+      <x:c r="P876" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q876" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="877" ht="64" customHeight="1">
+      <x:c r="A877" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B877" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C877" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D877" s="6" t="str">
+        <x:v>哈尔滨工业大学（深圳）</x:v>
+      </x:c>
+      <x:c r="E877" s="6" t="str">
+        <x:v>2011-09</x:v>
+      </x:c>
+      <x:c r="F877" s="6" t="str">
+        <x:v>2014-01</x:v>
+      </x:c>
+      <x:c r="G877" s="6" t="str">
+        <x:v>电子与通信工程</x:v>
+      </x:c>
+      <x:c r="H877" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I877" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J877" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K877" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L877" s="6" t="str"/>
+      <x:c r="M877" s="7" t="str"/>
+      <x:c r="N877" s="6" t="str"/>
+      <x:c r="O877" s="6" t="str">
+        <x:v>教育履历仅列工程硕士/Master of Engineering Degree标签，degree_awarded保持null。</x:v>
+      </x:c>
+      <x:c r="P877" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q877" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="878" ht="64" customHeight="1">
+      <x:c r="A878" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B878" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C878" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D878" s="6" t="str">
+        <x:v>哈尔滨工业大学（哈尔滨）</x:v>
+      </x:c>
+      <x:c r="E878" s="6" t="str">
+        <x:v>2014-09</x:v>
+      </x:c>
+      <x:c r="F878" s="6" t="str">
+        <x:v>2019-09</x:v>
+      </x:c>
+      <x:c r="G878" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H878" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I878" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J878" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K878" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L878" s="6" t="str"/>
+      <x:c r="M878" s="7" t="str"/>
+      <x:c r="N878" s="6" t="str"/>
+      <x:c r="O878" s="6" t="str">
+        <x:v>教育履历仅列工学博士/Ph.D.标签；获优秀博士论文奖不作为本条授位证书，degree_awarded保持null。</x:v>
+      </x:c>
+      <x:c r="P878" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q878" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="879" ht="64" customHeight="1">
+      <x:c r="A879" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B879" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="C879" s="6" t="str"/>
+      <x:c r="D879" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E879" s="6" t="str">
+        <x:v>2019-11</x:v>
+      </x:c>
+      <x:c r="F879" s="6" t="str">
+        <x:v>2022-12</x:v>
+      </x:c>
+      <x:c r="G879" s="6" t="str">
+        <x:v>仪器科学与技术</x:v>
+      </x:c>
+      <x:c r="H879" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I879" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J879" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K879" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L879" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M879" s="7" t="str"/>
+      <x:c r="N879" s="6" t="str"/>
+      <x:c r="O879" s="6" t="str">
+        <x:v>师资博士后为非学位研究经历，兼列任职以保留职业时间线，不作为另一博士学位。 事件类型：博士后研究（非授位）。</x:v>
+      </x:c>
+      <x:c r="P879" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q879" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="880" ht="64" customHeight="1">
+      <x:c r="A880" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B880" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C880" s="6" t="str">
+        <x:v>师资博士后</x:v>
+      </x:c>
+      <x:c r="D880" s="6" t="str">
+        <x:v>哈尔滨工业大学仪器科学与技术学科</x:v>
+      </x:c>
+      <x:c r="E880" s="6" t="str">
+        <x:v>2019-11</x:v>
+      </x:c>
+      <x:c r="F880" s="6" t="str">
+        <x:v>2022-12</x:v>
+      </x:c>
+      <x:c r="G880" s="6" t="str"/>
+      <x:c r="H880" s="6" t="str"/>
+      <x:c r="I880" s="6" t="str"/>
+      <x:c r="J880" s="6" t="str"/>
+      <x:c r="K880" s="6" t="str"/>
+      <x:c r="L880" s="6" t="str"/>
+      <x:c r="M880" s="7" t="str"/>
+      <x:c r="N880" s="6" t="str"/>
+      <x:c r="O880" s="6" t="str"/>
+      <x:c r="P880" s="6" t="str"/>
+      <x:c r="Q880" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="881" ht="64" customHeight="1">
+      <x:c r="A881" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B881" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C881" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D881" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E881" s="6" t="str">
+        <x:v>2019-12</x:v>
+      </x:c>
+      <x:c r="F881" s="6" t="str">
+        <x:v>2022-12</x:v>
+      </x:c>
+      <x:c r="G881" s="6" t="str"/>
+      <x:c r="H881" s="6" t="str"/>
+      <x:c r="I881" s="6" t="str"/>
+      <x:c r="J881" s="6" t="str"/>
+      <x:c r="K881" s="6" t="str"/>
+      <x:c r="L881" s="6" t="str"/>
+      <x:c r="M881" s="7" t="str"/>
+      <x:c r="N881" s="6" t="str"/>
+      <x:c r="O881" s="6" t="str"/>
+      <x:c r="P881" s="6" t="str"/>
+      <x:c r="Q881" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="882" ht="64" customHeight="1">
+      <x:c r="A882" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B882" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C882" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D882" s="6" t="str">
+        <x:v>哈尔滨工业大学信息与通信工程学科</x:v>
+      </x:c>
+      <x:c r="E882" s="6" t="str">
+        <x:v>2021-05</x:v>
+      </x:c>
+      <x:c r="F882" s="6" t="str"/>
+      <x:c r="G882" s="6" t="str"/>
+      <x:c r="H882" s="6" t="str"/>
+      <x:c r="I882" s="6" t="str"/>
+      <x:c r="J882" s="6" t="str"/>
+      <x:c r="K882" s="6" t="str"/>
+      <x:c r="L882" s="6" t="str"/>
+      <x:c r="M882" s="7" t="str"/>
+      <x:c r="N882" s="6" t="str"/>
+      <x:c r="O882" s="6" t="str"/>
+      <x:c r="P882" s="6" t="str"/>
+      <x:c r="Q882" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="883" ht="64" customHeight="1">
+      <x:c r="A883" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B883" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C883" s="6" t="str">
+        <x:v>青年拔尖准聘副教授</x:v>
+      </x:c>
+      <x:c r="D883" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E883" s="6" t="str">
+        <x:v>2022-12</x:v>
+      </x:c>
+      <x:c r="F883" s="6" t="str">
+        <x:v>2024-12</x:v>
+      </x:c>
+      <x:c r="G883" s="6" t="str"/>
+      <x:c r="H883" s="6" t="str"/>
+      <x:c r="I883" s="6" t="str"/>
+      <x:c r="J883" s="6" t="str"/>
+      <x:c r="K883" s="6" t="str"/>
+      <x:c r="L883" s="6" t="str"/>
+      <x:c r="M883" s="7" t="str"/>
+      <x:c r="N883" s="6" t="str"/>
+      <x:c r="O883" s="6" t="str"/>
+      <x:c r="P883" s="6" t="str"/>
+      <x:c r="Q883" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="884" ht="64" customHeight="1">
+      <x:c r="A884" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B884" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C884" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D884" s="6" t="str">
+        <x:v>哈尔滨工业大学信息与通信工程学科</x:v>
+      </x:c>
+      <x:c r="E884" s="6" t="str">
+        <x:v>2023-06</x:v>
+      </x:c>
+      <x:c r="F884" s="6" t="str"/>
+      <x:c r="G884" s="6" t="str"/>
+      <x:c r="H884" s="6" t="str"/>
+      <x:c r="I884" s="6" t="str"/>
+      <x:c r="J884" s="6" t="str"/>
+      <x:c r="K884" s="6" t="str"/>
+      <x:c r="L884" s="6" t="str"/>
+      <x:c r="M884" s="7" t="str"/>
+      <x:c r="N884" s="6" t="str"/>
+      <x:c r="O884" s="6" t="str">
+        <x:v>中文工作经历为2023.06至今；英文Work Positions为05/2023，月份冲突未合并。</x:v>
+      </x:c>
+      <x:c r="P884" s="6" t="str"/>
+      <x:c r="Q884" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="885" ht="64" customHeight="1">
+      <x:c r="A885" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B885" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C885" s="6" t="str">
+        <x:v>青年拔尖研究员</x:v>
+      </x:c>
+      <x:c r="D885" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E885" s="6" t="str">
+        <x:v>2024-12</x:v>
+      </x:c>
+      <x:c r="F885" s="6" t="str"/>
+      <x:c r="G885" s="6" t="str"/>
+      <x:c r="H885" s="6" t="str"/>
+      <x:c r="I885" s="6" t="str"/>
+      <x:c r="J885" s="6" t="str"/>
+      <x:c r="K885" s="6" t="str"/>
+      <x:c r="L885" s="6" t="str"/>
+      <x:c r="M885" s="7" t="str"/>
+      <x:c r="N885" s="6" t="str"/>
+      <x:c r="O885" s="6" t="str">
+        <x:v>中文职称为研究员，英文Work Positions写Professor，保留中文主称与翻译差异，不把两者当作两个任职。</x:v>
+      </x:c>
+      <x:c r="P885" s="6" t="str"/>
+      <x:c r="Q885" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="886" ht="64" customHeight="1">
+      <x:c r="A886" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B886" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C886" s="6" t="str">
+        <x:v>研究人员（Research fellow）</x:v>
+      </x:c>
+      <x:c r="D886" s="6" t="str">
+        <x:v>黑龙江省天空地一体化智能遥感技术重点实验室</x:v>
+      </x:c>
+      <x:c r="E886" s="6" t="str">
+        <x:v>2019-12</x:v>
+      </x:c>
+      <x:c r="F886" s="6" t="str">
+        <x:v>2022-12</x:v>
+      </x:c>
+      <x:c r="G886" s="6" t="str"/>
+      <x:c r="H886" s="6" t="str"/>
+      <x:c r="I886" s="6" t="str"/>
+      <x:c r="J886" s="6" t="str"/>
+      <x:c r="K886" s="6" t="str"/>
+      <x:c r="L886" s="6" t="str"/>
+      <x:c r="M886" s="7" t="str"/>
+      <x:c r="N886" s="6" t="str"/>
+      <x:c r="O886" s="6" t="str">
+        <x:v>英文Work Positions随讲师任职并列此角色；具体是否独立聘任未知。</x:v>
+      </x:c>
+      <x:c r="P886" s="6" t="str"/>
+      <x:c r="Q886" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="887" ht="64" customHeight="1">
+      <x:c r="A887" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B887" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C887" s="6" t="str">
+        <x:v>副主任</x:v>
+      </x:c>
+      <x:c r="D887" s="6" t="str">
+        <x:v>黑龙江省天空地一体化智能遥感技术重点实验室</x:v>
+      </x:c>
+      <x:c r="E887" s="6" t="str">
+        <x:v>2022-12</x:v>
+      </x:c>
+      <x:c r="F887" s="6" t="str"/>
+      <x:c r="G887" s="6" t="str"/>
+      <x:c r="H887" s="6" t="str"/>
+      <x:c r="I887" s="6" t="str"/>
+      <x:c r="J887" s="6" t="str"/>
+      <x:c r="K887" s="6" t="str"/>
+      <x:c r="L887" s="6" t="str"/>
+      <x:c r="M887" s="7" t="str"/>
+      <x:c r="N887" s="6" t="str"/>
+      <x:c r="O887" s="6" t="str">
+        <x:v>英文Work Positions在2022.12–2024.12及2024.12至今两段均列Vice director，按连续时间列示。</x:v>
+      </x:c>
+      <x:c r="P887" s="6" t="str"/>
+      <x:c r="Q887" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="888" ht="64" customHeight="1">
+      <x:c r="A888" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B888" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C888" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D888" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+      <x:c r="E888" s="6" t="str">
+        <x:v>2012-09</x:v>
+      </x:c>
+      <x:c r="F888" s="6" t="str">
+        <x:v>2016-06</x:v>
+      </x:c>
+      <x:c r="G888" s="6" t="str">
+        <x:v>遥感科学与技术</x:v>
+      </x:c>
+      <x:c r="H888" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I888" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J888" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K888" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L888" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M888" s="7" t="str"/>
+      <x:c r="N888" s="6" t="str"/>
+      <x:c r="O888" s="6" t="str">
+        <x:v>英文About me明确获得Bachelor’s degree；中文教育经历给出日期及专业。</x:v>
+      </x:c>
+      <x:c r="P888" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q888" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="889" ht="64" customHeight="1">
+      <x:c r="A889" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B889" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C889" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D889" s="6" t="str">
+        <x:v>武汉大学</x:v>
+      </x:c>
+      <x:c r="E889" s="6" t="str">
+        <x:v>2016-09</x:v>
+      </x:c>
+      <x:c r="F889" s="6" t="str">
+        <x:v>2019-06</x:v>
+      </x:c>
+      <x:c r="G889" s="6" t="str">
+        <x:v>摄影测量与遥感</x:v>
+      </x:c>
+      <x:c r="H889" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I889" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J889" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K889" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L889" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M889" s="7" t="str"/>
+      <x:c r="N889" s="6" t="str"/>
+      <x:c r="O889" s="6" t="str">
+        <x:v>英文About me明确obtained Master’s degree，归属测绘遥感信息工程国家重点实验室。</x:v>
+      </x:c>
+      <x:c r="P889" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q889" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="890" ht="64" customHeight="1">
+      <x:c r="A890" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B890" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C890" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D890" s="6" t="str">
+        <x:v>Nanyang Technological University</x:v>
+      </x:c>
+      <x:c r="E890" s="6" t="str">
+        <x:v>2020-01</x:v>
+      </x:c>
+      <x:c r="F890" s="6" t="str">
+        <x:v>2024-01</x:v>
+      </x:c>
+      <x:c r="G890" s="6" t="str">
+        <x:v>计算机</x:v>
+      </x:c>
+      <x:c r="H890" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="I890" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="J890" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K890" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L890" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M890" s="7" t="str"/>
+      <x:c r="N890" s="6" t="str"/>
+      <x:c r="O890" s="6" t="str">
+        <x:v>英文About me明确received Ph.D.，中文教育经历给时间和专业。</x:v>
+      </x:c>
+      <x:c r="P890" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q890" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="891" ht="64" customHeight="1">
+      <x:c r="A891" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B891" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C891" s="6" t="str">
+        <x:v>Research Fellow</x:v>
+      </x:c>
+      <x:c r="D891" s="6" t="str">
+        <x:v>南洋理工大学计算机与数据科学学院</x:v>
+      </x:c>
+      <x:c r="E891" s="6" t="str">
+        <x:v>2024-01</x:v>
+      </x:c>
+      <x:c r="F891" s="6" t="str">
+        <x:v>2024-09</x:v>
+      </x:c>
+      <x:c r="G891" s="6" t="str"/>
+      <x:c r="H891" s="6" t="str"/>
+      <x:c r="I891" s="6" t="str"/>
+      <x:c r="J891" s="6" t="str"/>
+      <x:c r="K891" s="6" t="str"/>
+      <x:c r="L891" s="6" t="str"/>
+      <x:c r="M891" s="7" t="str"/>
+      <x:c r="N891" s="6" t="str"/>
+      <x:c r="O891" s="6" t="str">
+        <x:v>原文未明确postdoctoral，按研究任职列示，不新增博士后教育事件。</x:v>
+      </x:c>
+      <x:c r="P891" s="6" t="str"/>
+      <x:c r="Q891" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="892" ht="64" customHeight="1">
+      <x:c r="A892" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B892" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C892" s="6" t="str">
+        <x:v>特任研究员</x:v>
+      </x:c>
+      <x:c r="D892" s="6" t="str">
+        <x:v>日本理化学研究所先进智能项目中心（RIKEN AIP）</x:v>
+      </x:c>
+      <x:c r="E892" s="6" t="str">
+        <x:v>2024-10</x:v>
+      </x:c>
+      <x:c r="F892" s="6" t="str">
+        <x:v>2026-01</x:v>
+      </x:c>
+      <x:c r="G892" s="6" t="str"/>
+      <x:c r="H892" s="6" t="str"/>
+      <x:c r="I892" s="6" t="str"/>
+      <x:c r="J892" s="6" t="str"/>
+      <x:c r="K892" s="6" t="str"/>
+      <x:c r="L892" s="6" t="str"/>
+      <x:c r="M892" s="7" t="str"/>
+      <x:c r="N892" s="6" t="str"/>
+      <x:c r="O892" s="6" t="str">
+        <x:v>未把collaborating with解释为博士后合作导师。</x:v>
+      </x:c>
+      <x:c r="P892" s="6" t="str"/>
+      <x:c r="Q892" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="893" ht="64" customHeight="1">
+      <x:c r="A893" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B893" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C893" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D893" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E893" s="6" t="str">
+        <x:v>2026-02</x:v>
+      </x:c>
+      <x:c r="F893" s="6" t="str"/>
+      <x:c r="G893" s="6" t="str"/>
+      <x:c r="H893" s="6" t="str"/>
+      <x:c r="I893" s="6" t="str"/>
+      <x:c r="J893" s="6" t="str"/>
+      <x:c r="K893" s="6" t="str"/>
+      <x:c r="L893" s="6" t="str"/>
+      <x:c r="M893" s="7" t="str"/>
+      <x:c r="N893" s="6" t="str"/>
+      <x:c r="O893" s="6" t="str"/>
+      <x:c r="P893" s="6" t="str"/>
+      <x:c r="Q893" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="894" ht="64" customHeight="1">
+      <x:c r="A894" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B894" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C894" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D894" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E894" s="6" t="str">
+        <x:v>2026-02</x:v>
+      </x:c>
+      <x:c r="F894" s="6" t="str"/>
+      <x:c r="G894" s="6" t="str"/>
+      <x:c r="H894" s="6" t="str"/>
+      <x:c r="I894" s="6" t="str"/>
+      <x:c r="J894" s="6" t="str"/>
+      <x:c r="K894" s="6" t="str"/>
+      <x:c r="L894" s="6" t="str"/>
+      <x:c r="M894" s="7" t="str"/>
+      <x:c r="N894" s="6" t="str"/>
+      <x:c r="O894" s="6" t="str"/>
+      <x:c r="P894" s="6" t="str"/>
+      <x:c r="Q894" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="895" ht="64" customHeight="1">
+      <x:c r="A895" s="6" t="str">
+        <x:v>胡航</x:v>
+      </x:c>
+      <x:c r="B895" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C895" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D895" s="6" t="str"/>
+      <x:c r="E895" s="6" t="str"/>
+      <x:c r="F895" s="6" t="str"/>
+      <x:c r="G895" s="6" t="str"/>
+      <x:c r="H895" s="6" t="str"/>
+      <x:c r="I895" s="6" t="str"/>
+      <x:c r="J895" s="6" t="str"/>
+      <x:c r="K895" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L895" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M895" s="7" t="str"/>
+      <x:c r="N895" s="6" t="str"/>
+      <x:c r="O895" s="6" t="str">
+        <x:v>2009期刊作者简介明确博士，同名同单位同阵列处理研究方向并公开职业邮箱与本人官网一致；授位学校、专业和日期未列，不从任职学校推授位学校。</x:v>
+      </x:c>
+      <x:c r="P895" s="6" t="str">
+        <x:v>授位或研究机构未知，不从国籍、当前单位或姓名推断地域。</x:v>
+      </x:c>
+      <x:c r="Q895" s="6" t="str">
+        <x:v>https://www.sys-ele.com/CN/Y2009/V31/I4/733</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="896" ht="64" customHeight="1">
+      <x:c r="A896" s="6" t="str">
+        <x:v>胡航</x:v>
+      </x:c>
+      <x:c r="B896" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="C896" s="6" t="str"/>
+      <x:c r="D896" s="6" t="str"/>
+      <x:c r="E896" s="6" t="str"/>
+      <x:c r="F896" s="6" t="str"/>
+      <x:c r="G896" s="6" t="str"/>
+      <x:c r="H896" s="6" t="str"/>
+      <x:c r="I896" s="6" t="str"/>
+      <x:c r="J896" s="6" t="str"/>
+      <x:c r="K896" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L896" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M896" s="7" t="str"/>
+      <x:c r="N896" s="6" t="str"/>
+      <x:c r="O896" s="6" t="str">
+        <x:v>教育经历仅填博士后，无机构、时间或合作导师。 事件类型：博士后研究（非授位）。</x:v>
+      </x:c>
+      <x:c r="P896" s="6" t="str">
+        <x:v>授位或研究机构未知，不从国籍、当前单位或姓名推断地域。</x:v>
+      </x:c>
+      <x:c r="Q896" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huhang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="897" ht="64" customHeight="1">
+      <x:c r="A897" s="6" t="str">
+        <x:v>胡航</x:v>
+      </x:c>
+      <x:c r="B897" s="6" t="str">
+        <x:v>academic_exchange_or_training</x:v>
+      </x:c>
+      <x:c r="C897" s="6" t="str"/>
+      <x:c r="D897" s="6" t="str">
+        <x:v>Tohoku University（官网拼作Tokohu University）</x:v>
+      </x:c>
+      <x:c r="E897" s="6" t="str">
+        <x:v>2004</x:v>
+      </x:c>
+      <x:c r="F897" s="6" t="str"/>
+      <x:c r="G897" s="6" t="str"/>
+      <x:c r="H897" s="6" t="str">
+        <x:v>日本</x:v>
+      </x:c>
+      <x:c r="I897" s="6" t="str">
+        <x:v>日本</x:v>
+      </x:c>
+      <x:c r="J897" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K897" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L897" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M897" s="7" t="str"/>
+      <x:c r="N897" s="6" t="str"/>
+      <x:c r="O897" s="6" t="str">
+        <x:v>官网统一栏目为国外学术交流或进修，不能指定为访问学者、留学授位或多年经历；城市分别Sendai、Calgary、Vladivostok。俄罗斯此机构位于符拉迪沃斯托克，按机构实际地域归亚洲。 事件类型：学术交流或进修（非授位，未细分）。</x:v>
+      </x:c>
+      <x:c r="P897" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q897" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huhang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="898" ht="64" customHeight="1">
+      <x:c r="A898" s="6" t="str">
+        <x:v>胡航</x:v>
+      </x:c>
+      <x:c r="B898" s="6" t="str">
+        <x:v>academic_exchange_or_training</x:v>
+      </x:c>
+      <x:c r="C898" s="6" t="str"/>
+      <x:c r="D898" s="6" t="str">
+        <x:v>University of Calgary</x:v>
+      </x:c>
+      <x:c r="E898" s="6" t="str">
+        <x:v>2004</x:v>
+      </x:c>
+      <x:c r="F898" s="6" t="str"/>
+      <x:c r="G898" s="6" t="str"/>
+      <x:c r="H898" s="6" t="str">
+        <x:v>加拿大</x:v>
+      </x:c>
+      <x:c r="I898" s="6" t="str">
+        <x:v>加拿大</x:v>
+      </x:c>
+      <x:c r="J898" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K898" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L898" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M898" s="7" t="str"/>
+      <x:c r="N898" s="6" t="str"/>
+      <x:c r="O898" s="6" t="str">
+        <x:v>官网统一栏目为国外学术交流或进修，不能指定为访问学者、留学授位或多年经历；城市分别Sendai、Calgary、Vladivostok。俄罗斯此机构位于符拉迪沃斯托克，按机构实际地域归亚洲。 事件类型：学术交流或进修（非授位，未细分）。</x:v>
+      </x:c>
+      <x:c r="P898" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q898" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huhang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="899" ht="64" customHeight="1">
+      <x:c r="A899" s="6" t="str">
+        <x:v>胡航</x:v>
+      </x:c>
+      <x:c r="B899" s="6" t="str">
+        <x:v>academic_exchange_or_training</x:v>
+      </x:c>
+      <x:c r="C899" s="6" t="str"/>
+      <x:c r="D899" s="6" t="str">
+        <x:v>Far Eastern National Technical University</x:v>
+      </x:c>
+      <x:c r="E899" s="6" t="str">
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="F899" s="6" t="str"/>
+      <x:c r="G899" s="6" t="str"/>
+      <x:c r="H899" s="6" t="str">
+        <x:v>俄罗斯</x:v>
+      </x:c>
+      <x:c r="I899" s="6" t="str">
+        <x:v>俄罗斯</x:v>
+      </x:c>
+      <x:c r="J899" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K899" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L899" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M899" s="7" t="str"/>
+      <x:c r="N899" s="6" t="str"/>
+      <x:c r="O899" s="6" t="str">
+        <x:v>官网统一栏目为国外学术交流或进修，不能指定为访问学者、留学授位或多年经历；城市分别Sendai、Calgary、Vladivostok。俄罗斯此机构位于符拉迪沃斯托克，按机构实际地域归亚洲。 事件类型：学术交流或进修（非授位，未细分）。</x:v>
+      </x:c>
+      <x:c r="P899" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q899" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huhang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="900" ht="64" customHeight="1">
+      <x:c r="A900" s="6" t="str">
+        <x:v>胡航</x:v>
+      </x:c>
+      <x:c r="B900" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C900" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D900" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E900" s="6" t="str"/>
+      <x:c r="F900" s="6" t="str"/>
+      <x:c r="G900" s="6" t="str"/>
+      <x:c r="H900" s="6" t="str"/>
+      <x:c r="I900" s="6" t="str"/>
+      <x:c r="J900" s="6" t="str"/>
+      <x:c r="K900" s="6" t="str"/>
+      <x:c r="L900" s="6" t="str"/>
+      <x:c r="M900" s="7" t="str"/>
+      <x:c r="N900" s="6" t="str"/>
+      <x:c r="O900" s="6" t="str">
+        <x:v>当前官网页首明确副教授，日期未知。</x:v>
+      </x:c>
+      <x:c r="P900" s="6" t="str"/>
+      <x:c r="Q900" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huhang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="901" ht="64" customHeight="1">
+      <x:c r="A901" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B901" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C901" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D901" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E901" s="6" t="str">
+        <x:v>1996-09</x:v>
+      </x:c>
+      <x:c r="F901" s="6" t="str">
+        <x:v>2000-07</x:v>
+      </x:c>
+      <x:c r="G901" s="6" t="str">
+        <x:v>电子工程</x:v>
+      </x:c>
+      <x:c r="H901" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I901" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J901" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K901" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L901" s="6" t="str"/>
+      <x:c r="M901" s="7" t="str"/>
+      <x:c r="N901" s="6" t="str"/>
+      <x:c r="O901" s="6" t="str">
+        <x:v>中英教育表列本科/Bachelor’s Degree但没有明确授予陈述，保留学习记录。</x:v>
+      </x:c>
+      <x:c r="P901" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q901" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houyuguan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="902" ht="64" customHeight="1">
+      <x:c r="A902" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B902" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C902" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D902" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E902" s="6" t="str">
+        <x:v>2000-09</x:v>
+      </x:c>
+      <x:c r="F902" s="6" t="str">
+        <x:v>2003-07</x:v>
+      </x:c>
+      <x:c r="G902" s="6" t="str">
+        <x:v>通信与信息系统</x:v>
+      </x:c>
+      <x:c r="H902" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I902" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J902" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K902" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L902" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M902" s="7" t="str"/>
+      <x:c r="N902" s="6" t="str">
+        <x:v>https://gvpress.com/journals/IJSH/vol7_no3/21.pdf</x:v>
+      </x:c>
+      <x:c r="O902" s="6" t="str">
+        <x:v>2013原始出版社论文作者简介明确2003获硕士；表中月取本人官网，论文笼统信息与通信工程。</x:v>
+      </x:c>
+      <x:c r="P902" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q902" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houyuguan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="903" ht="64" customHeight="1">
+      <x:c r="A903" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B903" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C903" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D903" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E903" s="6" t="str">
+        <x:v>2003-09</x:v>
+      </x:c>
+      <x:c r="F903" s="6" t="str">
+        <x:v>2008-03</x:v>
+      </x:c>
+      <x:c r="G903" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H903" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I903" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J903" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K903" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L903" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M903" s="7" t="str"/>
+      <x:c r="N903" s="6" t="str">
+        <x:v>https://gvpress.com/journals/IJSH/vol7_no3/21.pdf</x:v>
+      </x:c>
+      <x:c r="O903" s="6" t="str">
+        <x:v>2013原始出版社PDF阅读器第10页作者简介明确2008获博士。</x:v>
+      </x:c>
+      <x:c r="P903" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q903" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houyuguan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="904" ht="64" customHeight="1">
+      <x:c r="A904" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B904" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="C904" s="6" t="str"/>
+      <x:c r="D904" s="6" t="str">
+        <x:v>总参第55研究所计算所博士后工作流动站</x:v>
+      </x:c>
+      <x:c r="E904" s="6" t="str">
+        <x:v>2009-04</x:v>
+      </x:c>
+      <x:c r="F904" s="6" t="str">
+        <x:v>2013-10</x:v>
+      </x:c>
+      <x:c r="G904" s="6" t="str"/>
+      <x:c r="H904" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I904" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J904" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K904" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L904" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M904" s="7" t="str"/>
+      <x:c r="N904" s="6" t="str"/>
+      <x:c r="O904" s="6" t="str">
+        <x:v>按官网原机构表述保留，不推当代机构隶属或合作导师。 事件类型：博士后研究（非授位）。</x:v>
+      </x:c>
+      <x:c r="P904" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q904" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houyuguan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="905" ht="64" customHeight="1">
+      <x:c r="A905" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B905" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C905" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D905" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E905" s="6" t="str">
+        <x:v>2008-05</x:v>
+      </x:c>
+      <x:c r="F905" s="6" t="str">
+        <x:v>2013-12</x:v>
+      </x:c>
+      <x:c r="G905" s="6" t="str"/>
+      <x:c r="H905" s="6" t="str"/>
+      <x:c r="I905" s="6" t="str"/>
+      <x:c r="J905" s="6" t="str"/>
+      <x:c r="K905" s="6" t="str"/>
+      <x:c r="L905" s="6" t="str"/>
+      <x:c r="M905" s="7" t="str"/>
+      <x:c r="N905" s="6" t="str"/>
+      <x:c r="O905" s="6" t="str"/>
+      <x:c r="P905" s="6" t="str"/>
+      <x:c r="Q905" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houyuguan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="906" ht="64" customHeight="1">
+      <x:c r="A906" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B906" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C906" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D906" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E906" s="6" t="str">
+        <x:v>2014-01</x:v>
+      </x:c>
+      <x:c r="F906" s="6" t="str"/>
+      <x:c r="G906" s="6" t="str"/>
+      <x:c r="H906" s="6" t="str"/>
+      <x:c r="I906" s="6" t="str"/>
+      <x:c r="J906" s="6" t="str"/>
+      <x:c r="K906" s="6" t="str"/>
+      <x:c r="L906" s="6" t="str"/>
+      <x:c r="M906" s="7" t="str"/>
+      <x:c r="N906" s="6" t="str"/>
+      <x:c r="O906" s="6" t="str"/>
+      <x:c r="P906" s="6" t="str"/>
+      <x:c r="Q906" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houyuguan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="907" ht="64" customHeight="1">
+      <x:c r="A907" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B907" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C907" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D907" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E907" s="6" t="str"/>
+      <x:c r="F907" s="6" t="str"/>
+      <x:c r="G907" s="6" t="str"/>
+      <x:c r="H907" s="6" t="str"/>
+      <x:c r="I907" s="6" t="str"/>
+      <x:c r="J907" s="6" t="str"/>
+      <x:c r="K907" s="6" t="str"/>
+      <x:c r="L907" s="6" t="str"/>
+      <x:c r="M907" s="7" t="str"/>
+      <x:c r="N907" s="6" t="str"/>
+      <x:c r="O907" s="6" t="str"/>
+      <x:c r="P907" s="6" t="str"/>
+      <x:c r="Q907" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houyuguan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="908" ht="64" customHeight="1">
+      <x:c r="A908" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B908" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C908" s="6" t="str">
+        <x:v>博士后</x:v>
+      </x:c>
+      <x:c r="D908" s="6" t="str">
+        <x:v>总参第55研究所计算所博士后工作流动站</x:v>
+      </x:c>
+      <x:c r="E908" s="6" t="str">
+        <x:v>2009-04</x:v>
+      </x:c>
+      <x:c r="F908" s="6" t="str">
+        <x:v>2013-10</x:v>
+      </x:c>
+      <x:c r="G908" s="6" t="str"/>
+      <x:c r="H908" s="6" t="str"/>
+      <x:c r="I908" s="6" t="str"/>
+      <x:c r="J908" s="6" t="str"/>
+      <x:c r="K908" s="6" t="str"/>
+      <x:c r="L908" s="6" t="str"/>
+      <x:c r="M908" s="7" t="str"/>
+      <x:c r="N908" s="6" t="str"/>
+      <x:c r="O908" s="6" t="str"/>
+      <x:c r="P908" s="6" t="str"/>
+      <x:c r="Q908" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houyuguan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="909" ht="64" customHeight="1">
+      <x:c r="A909" s="6" t="str">
+        <x:v>李宏博</x:v>
+      </x:c>
+      <x:c r="B909" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C909" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D909" s="6" t="str"/>
+      <x:c r="E909" s="6" t="str"/>
+      <x:c r="F909" s="6" t="str"/>
+      <x:c r="G909" s="6" t="str"/>
+      <x:c r="H909" s="6" t="str"/>
+      <x:c r="I909" s="6" t="str"/>
+      <x:c r="J909" s="6" t="str"/>
+      <x:c r="K909" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L909" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M909" s="7" t="str"/>
+      <x:c r="N909" s="6" t="str"/>
+      <x:c r="O909" s="6" t="str">
+        <x:v>本人官网明确工学博士，但授位院校、时间、专业未披露；不将当前HIT任职推为HIT授位。</x:v>
+      </x:c>
+      <x:c r="P909" s="6" t="str">
+        <x:v>授位或研究机构未知，不从国籍、当前单位或姓名推断地域。</x:v>
+      </x:c>
+      <x:c r="Q909" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lihongbo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="910" ht="64" customHeight="1">
+      <x:c r="A910" s="6" t="str">
+        <x:v>李宏博</x:v>
+      </x:c>
+      <x:c r="B910" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C910" s="6" t="str">
+        <x:v>正高级工程师</x:v>
+      </x:c>
+      <x:c r="D910" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E910" s="6" t="str"/>
+      <x:c r="F910" s="6" t="str"/>
+      <x:c r="G910" s="6" t="str"/>
+      <x:c r="H910" s="6" t="str"/>
+      <x:c r="I910" s="6" t="str"/>
+      <x:c r="J910" s="6" t="str"/>
+      <x:c r="K910" s="6" t="str"/>
+      <x:c r="L910" s="6" t="str"/>
+      <x:c r="M910" s="7" t="str"/>
+      <x:c r="N910" s="6" t="str"/>
+      <x:c r="O910" s="6" t="str"/>
+      <x:c r="P910" s="6" t="str"/>
+      <x:c r="Q910" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lihongbo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="911" ht="64" customHeight="1">
+      <x:c r="A911" s="6" t="str">
+        <x:v>李宏博</x:v>
+      </x:c>
+      <x:c r="B911" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C911" s="6" t="str">
+        <x:v>副研究员</x:v>
+      </x:c>
+      <x:c r="D911" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E911" s="6" t="str"/>
+      <x:c r="F911" s="6" t="str"/>
+      <x:c r="G911" s="6" t="str"/>
+      <x:c r="H911" s="6" t="str"/>
+      <x:c r="I911" s="6" t="str"/>
+      <x:c r="J911" s="6" t="str"/>
+      <x:c r="K911" s="6" t="str"/>
+      <x:c r="L911" s="6" t="str"/>
+      <x:c r="M911" s="7" t="str"/>
+      <x:c r="N911" s="6" t="str"/>
+      <x:c r="O911" s="6" t="str">
+        <x:v>中文此职称，英文Associate Professor不当作另一个副教授任命。</x:v>
+      </x:c>
+      <x:c r="P911" s="6" t="str"/>
+      <x:c r="Q911" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lihongbo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="912" ht="64" customHeight="1">
+      <x:c r="A912" s="6" t="str">
+        <x:v>李宏博</x:v>
+      </x:c>
+      <x:c r="B912" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C912" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D912" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E912" s="6" t="str"/>
+      <x:c r="F912" s="6" t="str"/>
+      <x:c r="G912" s="6" t="str"/>
+      <x:c r="H912" s="6" t="str"/>
+      <x:c r="I912" s="6" t="str"/>
+      <x:c r="J912" s="6" t="str"/>
+      <x:c r="K912" s="6" t="str"/>
+      <x:c r="L912" s="6" t="str"/>
+      <x:c r="M912" s="7" t="str"/>
+      <x:c r="N912" s="6" t="str"/>
+      <x:c r="O912" s="6" t="str"/>
+      <x:c r="P912" s="6" t="str"/>
+      <x:c r="Q912" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lihongbo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="913" ht="64" customHeight="1">
+      <x:c r="A913" s="6" t="str">
+        <x:v>高建军</x:v>
+      </x:c>
+      <x:c r="B913" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C913" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D913" s="6" t="str">
+        <x:v>吉林大学</x:v>
+      </x:c>
+      <x:c r="E913" s="6" t="str">
+        <x:v>1999</x:v>
+      </x:c>
+      <x:c r="F913" s="6" t="str">
+        <x:v>2003</x:v>
+      </x:c>
+      <x:c r="G913" s="6" t="str"/>
+      <x:c r="H913" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I913" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J913" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K913" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L913" s="6" t="str"/>
+      <x:c r="M913" s="7" t="str"/>
+      <x:c r="N913" s="6" t="str"/>
+      <x:c r="O913" s="6" t="str">
+        <x:v>来源仅就读及学士标签；通信工程学院是院系名称，不等同确证专业。</x:v>
+      </x:c>
+      <x:c r="P913" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q913" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/jjgao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="914" ht="64" customHeight="1">
+      <x:c r="A914" s="6" t="str">
+        <x:v>高建军</x:v>
+      </x:c>
+      <x:c r="B914" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C914" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D914" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E914" s="6" t="str">
+        <x:v>2003</x:v>
+      </x:c>
+      <x:c r="F914" s="6" t="str">
+        <x:v>2005</x:v>
+      </x:c>
+      <x:c r="G914" s="6" t="str"/>
+      <x:c r="H914" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I914" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J914" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K914" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L914" s="6" t="str"/>
+      <x:c r="M914" s="7" t="str"/>
+      <x:c r="N914" s="6" t="str"/>
+      <x:c r="O914" s="6" t="str">
+        <x:v>官网仅就读与学位标签，专业未披露。</x:v>
+      </x:c>
+      <x:c r="P914" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q914" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/jjgao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="915" ht="64" customHeight="1">
+      <x:c r="A915" s="6" t="str">
+        <x:v>高建军</x:v>
+      </x:c>
+      <x:c r="B915" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C915" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D915" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E915" s="6" t="str">
+        <x:v>2005</x:v>
+      </x:c>
+      <x:c r="F915" s="6" t="str">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="G915" s="6" t="str"/>
+      <x:c r="H915" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I915" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J915" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K915" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L915" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M915" s="7" t="str"/>
+      <x:c r="N915" s="6" t="str"/>
+      <x:c r="O915" s="6" t="str">
+        <x:v>本人英文简介Dr.明确持博士；2009为官网教育经历结束年，不另推精确授位日。公开其他论文参考文献将可能同一博士论文标2010，见unknowns，不用二手引文改本人记录。</x:v>
+      </x:c>
+      <x:c r="P915" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q915" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/jjgao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="916" ht="64" customHeight="1">
+      <x:c r="A916" s="6" t="str">
+        <x:v>高建军</x:v>
+      </x:c>
+      <x:c r="B916" s="6" t="str">
+        <x:v>visiting_scholar</x:v>
+      </x:c>
+      <x:c r="C916" s="6" t="str"/>
+      <x:c r="D916" s="6" t="str">
+        <x:v>University of Manitoba</x:v>
+      </x:c>
+      <x:c r="E916" s="6" t="str">
+        <x:v>2012-09</x:v>
+      </x:c>
+      <x:c r="F916" s="6" t="str">
+        <x:v>2013-08</x:v>
+      </x:c>
+      <x:c r="G916" s="6" t="str"/>
+      <x:c r="H916" s="6" t="str">
+        <x:v>加拿大</x:v>
+      </x:c>
+      <x:c r="I916" s="6" t="str">
+        <x:v>加拿大</x:v>
+      </x:c>
+      <x:c r="J916" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K916" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L916" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M916" s="7" t="str"/>
+      <x:c r="N916" s="6" t="str"/>
+      <x:c r="O916" s="6" t="str">
+        <x:v>事件类型：访问学者（非授位）。</x:v>
+      </x:c>
+      <x:c r="P916" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q916" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/jjgao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="917" ht="64" customHeight="1">
+      <x:c r="A917" s="6" t="str">
+        <x:v>高建军</x:v>
+      </x:c>
+      <x:c r="B917" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C917" s="6" t="str">
+        <x:v>教师（官网未列2010年具体职称）</x:v>
+      </x:c>
+      <x:c r="D917" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E917" s="6" t="str">
+        <x:v>2010-10</x:v>
+      </x:c>
+      <x:c r="F917" s="6" t="str"/>
+      <x:c r="G917" s="6" t="str"/>
+      <x:c r="H917" s="6" t="str"/>
+      <x:c r="I917" s="6" t="str"/>
+      <x:c r="J917" s="6" t="str"/>
+      <x:c r="K917" s="6" t="str"/>
+      <x:c r="L917" s="6" t="str"/>
+      <x:c r="M917" s="7" t="str"/>
+      <x:c r="N917" s="6" t="str"/>
+      <x:c r="O917" s="6" t="str"/>
+      <x:c r="P917" s="6" t="str"/>
+      <x:c r="Q917" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/jjgao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="918" ht="64" customHeight="1">
+      <x:c r="A918" s="6" t="str">
+        <x:v>高建军</x:v>
+      </x:c>
+      <x:c r="B918" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C918" s="6" t="str">
+        <x:v>副研究员</x:v>
+      </x:c>
+      <x:c r="D918" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E918" s="6" t="str"/>
+      <x:c r="F918" s="6" t="str"/>
+      <x:c r="G918" s="6" t="str"/>
+      <x:c r="H918" s="6" t="str"/>
+      <x:c r="I918" s="6" t="str"/>
+      <x:c r="J918" s="6" t="str"/>
+      <x:c r="K918" s="6" t="str"/>
+      <x:c r="L918" s="6" t="str"/>
+      <x:c r="M918" s="7" t="str"/>
+      <x:c r="N918" s="6" t="str"/>
+      <x:c r="O918" s="6" t="str">
+        <x:v>中文副研究员与英文Associate Professor措辞不同，按中文保留，不改成副教授。</x:v>
+      </x:c>
+      <x:c r="P918" s="6" t="str"/>
+      <x:c r="Q918" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/jjgao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="919" ht="64" customHeight="1">
+      <x:c r="A919" s="6" t="str">
+        <x:v>高建军</x:v>
+      </x:c>
+      <x:c r="B919" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C919" s="6" t="str">
+        <x:v>访问学者</x:v>
+      </x:c>
+      <x:c r="D919" s="6" t="str">
+        <x:v>University of Manitoba</x:v>
+      </x:c>
+      <x:c r="E919" s="6" t="str">
+        <x:v>2012-09</x:v>
+      </x:c>
+      <x:c r="F919" s="6" t="str">
+        <x:v>2013-08</x:v>
+      </x:c>
+      <x:c r="G919" s="6" t="str"/>
+      <x:c r="H919" s="6" t="str"/>
+      <x:c r="I919" s="6" t="str"/>
+      <x:c r="J919" s="6" t="str"/>
+      <x:c r="K919" s="6" t="str"/>
+      <x:c r="L919" s="6" t="str"/>
+      <x:c r="M919" s="7" t="str"/>
+      <x:c r="N919" s="6" t="str"/>
+      <x:c r="O919" s="6" t="str"/>
+      <x:c r="P919" s="6" t="str"/>
+      <x:c r="Q919" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/jjgao</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="920" ht="64" customHeight="1">
+      <x:c r="A920" s="6" t="str">
+        <x:v>高国明</x:v>
+      </x:c>
+      <x:c r="B920" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C920" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D920" s="6" t="str">
+        <x:v>中国民航大学</x:v>
+      </x:c>
+      <x:c r="E920" s="6" t="str">
+        <x:v>2006-09</x:v>
+      </x:c>
+      <x:c r="F920" s="6" t="str">
+        <x:v>2010-07</x:v>
+      </x:c>
+      <x:c r="G920" s="6" t="str">
+        <x:v>信息与计算科学</x:v>
+      </x:c>
+      <x:c r="H920" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I920" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J920" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K920" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L920" s="6" t="str"/>
+      <x:c r="M920" s="7" t="str"/>
+      <x:c r="N920" s="6" t="str"/>
+      <x:c r="O920" s="6" t="str"/>
+      <x:c r="P920" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q920" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaoguoming</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="921" ht="64" customHeight="1">
+      <x:c r="A921" s="6" t="str">
+        <x:v>高国明</x:v>
+      </x:c>
+      <x:c r="B921" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C921" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D921" s="6" t="str">
+        <x:v>广西师范大学</x:v>
+      </x:c>
+      <x:c r="E921" s="6" t="str">
+        <x:v>2010-09</x:v>
+      </x:c>
+      <x:c r="F921" s="6" t="str">
+        <x:v>2013-07</x:v>
+      </x:c>
+      <x:c r="G921" s="6" t="str">
+        <x:v>模式识别与智能系统</x:v>
+      </x:c>
+      <x:c r="H921" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I921" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J921" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K921" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L921" s="6" t="str"/>
+      <x:c r="M921" s="7" t="str"/>
+      <x:c r="N921" s="6" t="str"/>
+      <x:c r="O921" s="6" t="str"/>
+      <x:c r="P921" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q921" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaoguoming</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="922" ht="64" customHeight="1">
+      <x:c r="A922" s="6" t="str">
+        <x:v>高国明</x:v>
+      </x:c>
+      <x:c r="B922" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C922" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D922" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E922" s="6" t="str">
+        <x:v>2013-09</x:v>
+      </x:c>
+      <x:c r="F922" s="6" t="str">
+        <x:v>2018-07</x:v>
+      </x:c>
+      <x:c r="G922" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H922" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I922" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J922" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K922" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L922" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M922" s="7" t="str"/>
+      <x:c r="N922" s="6" t="str"/>
+      <x:c r="O922" s="6" t="str">
+        <x:v>本人中英文简介工学博士/obtained PhD 2018明确授位；英文简介Electronic and Communication Engineering与教育表Information and Communication Engineering表述不完全一致，专业取中英教育表。</x:v>
+      </x:c>
+      <x:c r="P922" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q922" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaoguoming</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="923" ht="64" customHeight="1">
+      <x:c r="A923" s="6" t="str">
+        <x:v>高国明</x:v>
+      </x:c>
+      <x:c r="B923" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C923" s="6" t="str">
+        <x:v>助理研究员</x:v>
+      </x:c>
+      <x:c r="D923" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E923" s="6" t="str">
+        <x:v>2018-10</x:v>
+      </x:c>
+      <x:c r="F923" s="6" t="str">
+        <x:v>2021-12</x:v>
+      </x:c>
+      <x:c r="G923" s="6" t="str"/>
+      <x:c r="H923" s="6" t="str"/>
+      <x:c r="I923" s="6" t="str"/>
+      <x:c r="J923" s="6" t="str"/>
+      <x:c r="K923" s="6" t="str"/>
+      <x:c r="L923" s="6" t="str"/>
+      <x:c r="M923" s="7" t="str"/>
+      <x:c r="N923" s="6" t="str"/>
+      <x:c r="O923" s="6" t="str">
+        <x:v>英文Lecturer，按中文职称。</x:v>
+      </x:c>
+      <x:c r="P923" s="6" t="str"/>
+      <x:c r="Q923" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaoguoming</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="924" ht="64" customHeight="1">
+      <x:c r="A924" s="6" t="str">
+        <x:v>高国明</x:v>
+      </x:c>
+      <x:c r="B924" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C924" s="6" t="str">
+        <x:v>副研究员</x:v>
+      </x:c>
+      <x:c r="D924" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E924" s="6" t="str">
+        <x:v>2022-01</x:v>
+      </x:c>
+      <x:c r="F924" s="6" t="str"/>
+      <x:c r="G924" s="6" t="str"/>
+      <x:c r="H924" s="6" t="str"/>
+      <x:c r="I924" s="6" t="str"/>
+      <x:c r="J924" s="6" t="str"/>
+      <x:c r="K924" s="6" t="str"/>
+      <x:c r="L924" s="6" t="str"/>
+      <x:c r="M924" s="7" t="str"/>
+      <x:c r="N924" s="6" t="str"/>
+      <x:c r="O924" s="6" t="str">
+        <x:v>英文Work Positions写12/2022，当前start采用中文01/2022，冲突保留；英文Associate Professor不作额外副教授职务。</x:v>
+      </x:c>
+      <x:c r="P924" s="6" t="str"/>
+      <x:c r="Q924" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaoguoming</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="925" ht="64" customHeight="1">
+      <x:c r="A925" s="6" t="str">
+        <x:v>高国明</x:v>
+      </x:c>
+      <x:c r="B925" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C925" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D925" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E925" s="6" t="str">
+        <x:v>2022-04</x:v>
+      </x:c>
+      <x:c r="F925" s="6" t="str"/>
+      <x:c r="G925" s="6" t="str"/>
+      <x:c r="H925" s="6" t="str"/>
+      <x:c r="I925" s="6" t="str"/>
+      <x:c r="J925" s="6" t="str"/>
+      <x:c r="K925" s="6" t="str"/>
+      <x:c r="L925" s="6" t="str"/>
+      <x:c r="M925" s="7" t="str"/>
+      <x:c r="N925" s="6" t="str"/>
+      <x:c r="O925" s="6" t="str">
+        <x:v>中文学科信息与通信工程，英文Signal and Information Processing，不擅定学科变更。</x:v>
+      </x:c>
+      <x:c r="P925" s="6" t="str"/>
+      <x:c r="Q925" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaoguoming</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="926" ht="64" customHeight="1">
+      <x:c r="A926" s="6" t="str">
+        <x:v>高国明</x:v>
+      </x:c>
+      <x:c r="B926" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C926" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D926" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E926" s="6" t="str">
+        <x:v>2025-09</x:v>
+      </x:c>
+      <x:c r="F926" s="6" t="str"/>
+      <x:c r="G926" s="6" t="str"/>
+      <x:c r="H926" s="6" t="str"/>
+      <x:c r="I926" s="6" t="str"/>
+      <x:c r="J926" s="6" t="str"/>
+      <x:c r="K926" s="6" t="str"/>
+      <x:c r="L926" s="6" t="str"/>
+      <x:c r="M926" s="7" t="str"/>
+      <x:c r="N926" s="6" t="str"/>
+      <x:c r="O926" s="6" t="str">
+        <x:v>中英学科名称层级不同。</x:v>
+      </x:c>
+      <x:c r="P926" s="6" t="str"/>
+      <x:c r="Q926" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaoguoming</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra04bd8d785724c35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c4708181ee54769"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -34815,10 +41124,218 @@
         <x:v>https://civil.hit.edu.cn/kxyys/list.htm</x:v>
       </x:c>
     </x:row>
+    <x:row r="30" ht="64" customHeight="1">
+      <x:c r="A30" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B30" s="6" t="str">
+        <x:v>Mathews Jacob</x:v>
+      </x:c>
+      <x:c r="C30" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D30" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E30" s="6" t="str">
+        <x:v>弗吉尼亚大学电气与计算机工程教授，负责计算生物医学成像团队；研究MRI图像重建、分析和量化。</x:v>
+      </x:c>
+      <x:c r="F30" s="6" t="str">
+        <x:v>official_page_currently_listed</x:v>
+      </x:c>
+      <x:c r="G30" s="6" t="str">
+        <x:v>本次官方页面列示的职业身份，不等同独立人事核验。 指导关系当时导师机构为 University of Iowa；胡悦博士学位项目机构为 University of Rochester；所读当前导师简介为 University of Virginia。三者分别保存，指导起止未披露。</x:v>
+      </x:c>
+      <x:c r="H30" s="6" t="str"/>
+      <x:c r="I30" s="6" t="str">
+        <x:v>https://research.engineering.uiowa.edu/cbig/sites/research.engineering.uiowa.edu.cbig/files/files/YueHu_thesis(1).pdf</x:v>
+      </x:c>
+      <x:c r="J30" s="6" t="str">
+        <x:v>https://engineering.virginia.edu/faculty/mathews-jacob</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="64" customHeight="1">
+      <x:c r="A31" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B31" s="6" t="str">
+        <x:v>Marvin Doyley</x:v>
+      </x:c>
+      <x:c r="C31" s="6" t="str">
+        <x:v>博士论文委员会成员（非导师认定）</x:v>
+      </x:c>
+      <x:c r="D31" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E31" s="6" t="str"/>
+      <x:c r="F31" s="6" t="str"/>
+      <x:c r="G31" s="6" t="str"/>
+      <x:c r="H31" s="6" t="str"/>
+      <x:c r="I31" s="6" t="str">
+        <x:v>https://research.engineering.uiowa.edu/cbig/sites/research.engineering.uiowa.edu.cbig/files/files/YueHu_thesis(1).pdf</x:v>
+      </x:c>
+      <x:c r="J31" s="6" t="str"/>
+    </x:row>
+    <x:row r="32" ht="64" customHeight="1">
+      <x:c r="A32" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B32" s="6" t="str">
+        <x:v>Nathan Cahill</x:v>
+      </x:c>
+      <x:c r="C32" s="6" t="str">
+        <x:v>博士论文委员会成员（非导师认定）</x:v>
+      </x:c>
+      <x:c r="D32" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E32" s="6" t="str"/>
+      <x:c r="F32" s="6" t="str"/>
+      <x:c r="G32" s="6" t="str"/>
+      <x:c r="H32" s="6" t="str"/>
+      <x:c r="I32" s="6" t="str">
+        <x:v>https://research.engineering.uiowa.edu/cbig/sites/research.engineering.uiowa.edu.cbig/files/files/YueHu_thesis(1).pdf</x:v>
+      </x:c>
+      <x:c r="J32" s="6" t="str"/>
+    </x:row>
+    <x:row r="33" ht="64" customHeight="1">
+      <x:c r="A33" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B33" s="6" t="str">
+        <x:v>Mark Bocko</x:v>
+      </x:c>
+      <x:c r="C33" s="6" t="str">
+        <x:v>博士论文委员会成员（非导师认定）</x:v>
+      </x:c>
+      <x:c r="D33" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E33" s="6" t="str"/>
+      <x:c r="F33" s="6" t="str"/>
+      <x:c r="G33" s="6" t="str"/>
+      <x:c r="H33" s="6" t="str"/>
+      <x:c r="I33" s="6" t="str">
+        <x:v>https://research.engineering.uiowa.edu/cbig/sites/research.engineering.uiowa.edu.cbig/files/files/YueHu_thesis(1).pdf</x:v>
+      </x:c>
+      <x:c r="J33" s="6" t="str"/>
+    </x:row>
+    <x:row r="34" ht="64" customHeight="1">
+      <x:c r="A34" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B34" s="6" t="str">
+        <x:v>Azadeh Vosoughi</x:v>
+      </x:c>
+      <x:c r="C34" s="6" t="str">
+        <x:v>博士论文委员会成员（非导师认定）</x:v>
+      </x:c>
+      <x:c r="D34" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E34" s="6" t="str"/>
+      <x:c r="F34" s="6" t="str"/>
+      <x:c r="G34" s="6" t="str"/>
+      <x:c r="H34" s="6" t="str"/>
+      <x:c r="I34" s="6" t="str">
+        <x:v>https://research.engineering.uiowa.edu/cbig/sites/research.engineering.uiowa.edu.cbig/files/files/YueHu_thesis(1).pdf</x:v>
+      </x:c>
+      <x:c r="J34" s="6" t="str"/>
+    </x:row>
+    <x:row r="35" ht="64" customHeight="1">
+      <x:c r="A35" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B35" s="6" t="str">
+        <x:v>Shijian Lu</x:v>
+      </x:c>
+      <x:c r="C35" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D35" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E35" s="6" t="str">
+        <x:v>南洋理工大学计算与数据科学学院副教授；研究计算机视觉与深度学习。</x:v>
+      </x:c>
+      <x:c r="F35" s="6" t="str">
+        <x:v>official_page_currently_listed</x:v>
+      </x:c>
+      <x:c r="G35" s="6" t="str">
+        <x:v>本次官方页面列示的职业身份，不等同独立人事核验。</x:v>
+      </x:c>
+      <x:c r="H35" s="6" t="str"/>
+      <x:c r="I35" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+      <x:c r="J35" s="6" t="str">
+        <x:v>https://personal.ntu.edu.sg/shijian.lu/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="64" customHeight="1">
+      <x:c r="A36" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B36" s="6" t="str">
+        <x:v>李德仁（Deren Li）</x:v>
+      </x:c>
+      <x:c r="C36" s="6" t="str">
+        <x:v>硕士导师</x:v>
+      </x:c>
+      <x:c r="D36" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="E36" s="6" t="str">
+        <x:v>武汉大学教授、博士生导师，中国科学院与中国工程院院士；研究地球空间信息科学。</x:v>
+      </x:c>
+      <x:c r="F36" s="6" t="str">
+        <x:v>official_page_currently_listed</x:v>
+      </x:c>
+      <x:c r="G36" s="6" t="str">
+        <x:v>2026-07-03武汉大学新闻仍明确教授身份；未推断其历史行政职务仍在任。</x:v>
+      </x:c>
+      <x:c r="H36" s="6" t="str"/>
+      <x:c r="I36" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+      <x:c r="J36" s="6" t="str">
+        <x:v>https://www.whu.edu.cn/info/7241/202104.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="64" customHeight="1">
+      <x:c r="A37" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B37" s="6" t="str">
+        <x:v>陈锐志（Ruizhi Chen）</x:v>
+      </x:c>
+      <x:c r="C37" s="6" t="str">
+        <x:v>硕士导师</x:v>
+      </x:c>
+      <x:c r="D37" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="E37" s="6" t="str">
+        <x:v>武汉大学2021年官方简介列教授、测绘遥感信息工程国家重点实验室主任；研究室内外导航定位及低轨卫星导航增强。</x:v>
+      </x:c>
+      <x:c r="F37" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G37" s="6" t="str">
+        <x:v>现有官方简介发布日期为2021年，2026当前在职与任职状态未核定。</x:v>
+      </x:c>
+      <x:c r="H37" s="6" t="str"/>
+      <x:c r="I37" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+      <x:c r="J37" s="6" t="str">
+        <x:v>https://news.whu.edu.cn/info/1002/64146.htm</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97ae2612cd8e4f61"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6e0a222fb804088"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41415,10 +47932,1504 @@
         <x:v>成果类型：书籍。 链接核验状态：仅官方精选书目，未独立核验文章或出版落地页。</x:v>
       </x:c>
     </x:row>
+    <x:row r="215" ht="64" customHeight="1">
+      <x:c r="A215" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B215" s="6" t="str">
+        <x:v>An End-to-End Multidomain Interaction Deep Unrolling Network Based on Block-Aware Optimization Model for ISAR Multitarget Separation</x:v>
+      </x:c>
+      <x:c r="C215" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D215" s="6" t="str">
+        <x:v>10.1109/tgrs.2025.3570322</x:v>
+      </x:c>
+      <x:c r="E215" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tgrs.2025.3570322</x:v>
+      </x:c>
+      <x:c r="F215" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G215" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+      <x:c r="H215" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+      <x:c r="I215" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J215" s="6" t="str">
+        <x:v>官网Multi-Domain/Multi-Target与Crossref Multidomain/Multitarget仅连字符形式不同，作者与期刊匹配。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2025；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" ht="64" customHeight="1">
+      <x:c r="A216" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B216" s="6" t="str">
+        <x:v>MSDP-Net: A Multi-Scale Domain Perception Network for HRRP Target Recognition</x:v>
+      </x:c>
+      <x:c r="C216" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D216" s="6" t="str">
+        <x:v>10.3390/rs17152601</x:v>
+      </x:c>
+      <x:c r="E216" s="6" t="str">
+        <x:v>https://doi.org/10.3390/rs17152601</x:v>
+      </x:c>
+      <x:c r="F216" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G216" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+      <x:c r="H216" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+      <x:c r="I216" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J216" s="6" t="str">
+        <x:v>官网英文成果月份与Crossref注册发表月份不同，保留两者，不声称日期已完全一致。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2025-07-26；保留原始精度。 成果日期差异：MSDP-Net: A Multi-Scale Domain Perception Network for HRRP Target Recognition；官网日期2025-05，Crossref 登记日期2025-07-26，不擅自解释或覆盖。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="64" customHeight="1">
+      <x:c r="A217" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B217" s="6" t="str">
+        <x:v>Inverse Synthetic Aperture Radar Image Multi-Modal Zero-Shot Learning Based on the Scattering Center Model and Neighbor-Adapted Locally Linear Embedding</x:v>
+      </x:c>
+      <x:c r="C217" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D217" s="6" t="str">
+        <x:v>10.3390/rs17040725</x:v>
+      </x:c>
+      <x:c r="E217" s="6" t="str">
+        <x:v>https://doi.org/10.3390/rs17040725</x:v>
+      </x:c>
+      <x:c r="F217" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G217" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+      <x:c r="H217" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+      <x:c r="I217" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J217" s="6" t="str">
+        <x:v>官网英文成果月份与Crossref注册发表月份不同，保留两者，不声称日期已完全一致。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2025-02-19；保留原始精度。 成果日期差异：Inverse Synthetic Aperture Radar Image Multi-Modal Zero-Shot Learning Based on the Scattering Center Model and Neighbor-Adapted Locally Linear Embedding；官网日期2025-07，Crossref 登记日期2025-02-19，不擅自解释或覆盖。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" ht="64" customHeight="1">
+      <x:c r="A218" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B218" s="6" t="str">
+        <x:v>Iterative PolInSAR Target Decomposition for Scattering Characterization and Building Detection</x:v>
+      </x:c>
+      <x:c r="C218" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D218" s="6" t="str">
+        <x:v>10.1109/jstars.2025.3554992</x:v>
+      </x:c>
+      <x:c r="E218" s="6" t="str">
+        <x:v>https://doi.org/10.1109/jstars.2025.3554992</x:v>
+      </x:c>
+      <x:c r="F218" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G218" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+      <x:c r="H218" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+      <x:c r="I218" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J218" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2025；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" ht="64" customHeight="1">
+      <x:c r="A219" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B219" s="6" t="str">
+        <x:v>Scattering Power Decomposition Based on PolInSAR Images and Sparse Representation</x:v>
+      </x:c>
+      <x:c r="C219" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D219" s="6" t="str">
+        <x:v>10.1109/lgrs.2025.3528313</x:v>
+      </x:c>
+      <x:c r="E219" s="6" t="str">
+        <x:v>https://doi.org/10.1109/lgrs.2025.3528313</x:v>
+      </x:c>
+      <x:c r="F219" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G219" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+      <x:c r="H219" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+      <x:c r="I219" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J219" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2025；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" ht="64" customHeight="1">
+      <x:c r="A220" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B220" s="6" t="str">
+        <x:v>Efficient End-to-End Diffusion Model for One-Step SAR-to-Optical Translation</x:v>
+      </x:c>
+      <x:c r="C220" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D220" s="6" t="str">
+        <x:v>10.1109/lgrs.2024.3506566</x:v>
+      </x:c>
+      <x:c r="E220" s="6" t="str">
+        <x:v>https://doi.org/10.1109/lgrs.2024.3506566</x:v>
+      </x:c>
+      <x:c r="F220" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G220" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+      <x:c r="H220" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+      <x:c r="I220" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J220" s="6" t="str">
+        <x:v>官网同时列2024-11及2025卷22版本；Crossref注册卷期年2025，未把两个记录当两篇。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2025；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" ht="64" customHeight="1">
+      <x:c r="A221" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B221" s="6" t="str">
+        <x:v>Exploring Lightweight Structures for Tiny Object Detection in Remote Sensing Images</x:v>
+      </x:c>
+      <x:c r="C221" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D221" s="6" t="str">
+        <x:v>10.1109/tgrs.2025.3567345</x:v>
+      </x:c>
+      <x:c r="E221" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tgrs.2025.3567345</x:v>
+      </x:c>
+      <x:c r="F221" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G221" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+      <x:c r="H221" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+      <x:c r="I221" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J221" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2025；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" ht="64" customHeight="1">
+      <x:c r="A222" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B222" s="6" t="str">
+        <x:v>UNMamba: Cascaded Spatial–Spectral Mamba for Blind Hyperspectral Unmixing</x:v>
+      </x:c>
+      <x:c r="C222" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D222" s="6" t="str">
+        <x:v>10.1109/lgrs.2025.3545505</x:v>
+      </x:c>
+      <x:c r="E222" s="6" t="str">
+        <x:v>https://doi.org/10.1109/lgrs.2025.3545505</x:v>
+      </x:c>
+      <x:c r="F222" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G222" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+      <x:c r="H222" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+      <x:c r="I222" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J222" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2025；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" ht="64" customHeight="1">
+      <x:c r="A223" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B223" s="6" t="str">
+        <x:v>Predictive Filtering Integrated Generative Remote Sensing Hyperspectral Image Inpainting</x:v>
+      </x:c>
+      <x:c r="C223" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D223" s="6" t="str">
+        <x:v>10.1109/lgrs.2025.3526177</x:v>
+      </x:c>
+      <x:c r="E223" s="6" t="str">
+        <x:v>https://doi.org/10.1109/lgrs.2025.3526177</x:v>
+      </x:c>
+      <x:c r="F223" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G223" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+      <x:c r="H223" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+      <x:c r="I223" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J223" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2025；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="64" customHeight="1">
+      <x:c r="A224" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B224" s="6" t="str">
+        <x:v>Multimodal hyperspectral remote sensing: an overview and perspective</x:v>
+      </x:c>
+      <x:c r="C224" s="6" t="n">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="D224" s="6" t="str">
+        <x:v>10.1007/s11432-020-3084-1</x:v>
+      </x:c>
+      <x:c r="E224" s="6" t="str">
+        <x:v>https://doi.org/10.1007/s11432-020-3084-1</x:v>
+      </x:c>
+      <x:c r="F224" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G224" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guyf</x:v>
+      </x:c>
+      <x:c r="H224" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guyf</x:v>
+      </x:c>
+      <x:c r="I224" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J224" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2021-01-21；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" ht="64" customHeight="1">
+      <x:c r="A225" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B225" s="6" t="str">
+        <x:v>Intrinsic Image Recovery From Remote Sensing Hyperspectral Images</x:v>
+      </x:c>
+      <x:c r="C225" s="6" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D225" s="6" t="str">
+        <x:v>10.1109/tgrs.2018.2853178</x:v>
+      </x:c>
+      <x:c r="E225" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tgrs.2018.2853178</x:v>
+      </x:c>
+      <x:c r="F225" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G225" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guyf</x:v>
+      </x:c>
+      <x:c r="H225" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guyf</x:v>
+      </x:c>
+      <x:c r="I225" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J225" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2019-01；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" ht="64" customHeight="1">
+      <x:c r="A226" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B226" s="6" t="str">
+        <x:v>Unsupervised Cross-Temporal Classification of Hyperspectral Images With Multiple Geodesic Flow Kernel Learning</x:v>
+      </x:c>
+      <x:c r="C226" s="6" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D226" s="6" t="str">
+        <x:v>10.1109/tgrs.2019.2928562</x:v>
+      </x:c>
+      <x:c r="E226" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tgrs.2019.2928562</x:v>
+      </x:c>
+      <x:c r="F226" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G226" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guyf</x:v>
+      </x:c>
+      <x:c r="H226" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guyf</x:v>
+      </x:c>
+      <x:c r="I226" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J226" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2019-12；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="64" customHeight="1">
+      <x:c r="A227" s="6" t="str">
+        <x:v>侯成宇</x:v>
+      </x:c>
+      <x:c r="B227" s="6" t="str">
+        <x:v>A TinyML System for Early Screening of CHD on ESP32</x:v>
+      </x:c>
+      <x:c r="C227" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D227" s="6" t="str">
+        <x:v>10.1109/jiot.2026.3687555</x:v>
+      </x:c>
+      <x:c r="E227" s="6" t="str">
+        <x:v>https://doi.org/10.1109/jiot.2026.3687555</x:v>
+      </x:c>
+      <x:c r="F227" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G227" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houchengyu</x:v>
+      </x:c>
+      <x:c r="H227" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houchengyu</x:v>
+      </x:c>
+      <x:c r="I227" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J227" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2026-07-15；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" ht="64" customHeight="1">
+      <x:c r="A228" s="6" t="str">
+        <x:v>侯成宇</x:v>
+      </x:c>
+      <x:c r="B228" s="6" t="str">
+        <x:v>HITrocket: Hadamard-vector inner-product transform of ROCKET for time series classification</x:v>
+      </x:c>
+      <x:c r="C228" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D228" s="6" t="str">
+        <x:v>10.1016/j.patcog.2026.114220</x:v>
+      </x:c>
+      <x:c r="E228" s="6" t="str">
+        <x:v>https://doi.org/10.1016/j.patcog.2026.114220</x:v>
+      </x:c>
+      <x:c r="F228" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G228" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houchengyu</x:v>
+      </x:c>
+      <x:c r="H228" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houchengyu</x:v>
+      </x:c>
+      <x:c r="I228" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J228" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2026-12；保留原始精度。 登记卷期为2026年12月，晚于本次核验日；官网已列，未核实单独在线发表日期，不宣称该卷期已经出版。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" ht="64" customHeight="1">
+      <x:c r="A229" s="6" t="str">
+        <x:v>侯成宇</x:v>
+      </x:c>
+      <x:c r="B229" s="6" t="str">
+        <x:v>Target Recognition Algorithm Based on RCS Time Sequence</x:v>
+      </x:c>
+      <x:c r="C229" s="6" t="n">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="D229" s="6" t="str">
+        <x:v>10.14257/ijsip.2015.8.11.26</x:v>
+      </x:c>
+      <x:c r="E229" s="6" t="str">
+        <x:v>https://doi.org/10.14257/ijsip.2015.8.11.26</x:v>
+      </x:c>
+      <x:c r="F229" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G229" s="6" t="str">
+        <x:v>https://article.nadiapub.com/IJSIP/vol8_no11/26.pdf</x:v>
+      </x:c>
+      <x:c r="H229" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houchengyu</x:v>
+      </x:c>
+      <x:c r="I229" s="6" t="str">
+        <x:v>publisher_pdf_read_and_crossref_metadata_verified</x:v>
+      </x:c>
+      <x:c r="J229" s="6" t="str">
+        <x:v>原始期刊PDF题名作者所属单位及作者简介直接可读，仅保存书目及必要履历，不保存公开全文副本。 成果类型：期刊论文。 链接核验状态：原始出版社论文 PDF 与作者简介已读，Crossref 书目另核；不公开全文副本。 Crossref 登记出版日期：2015-11-30；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" ht="64" customHeight="1">
+      <x:c r="A230" s="6" t="str">
+        <x:v>陈雨时</x:v>
+      </x:c>
+      <x:c r="B230" s="6" t="str">
+        <x:v>Denoising-Guided SAR Foundation Model</x:v>
+      </x:c>
+      <x:c r="C230" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D230" s="6" t="str"/>
+      <x:c r="E230" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chenyushi</x:v>
+      </x:c>
+      <x:c r="F230" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G230" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chenyushi</x:v>
+      </x:c>
+      <x:c r="H230" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chenyushi</x:v>
+      </x:c>
+      <x:c r="I230" s="6" t="str">
+        <x:v>official_selected_bibliography_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J230" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：仅官方精选书目，未核独立文章落地页；不自动补同名 DOI。 Crossref 返回无关题名，未采用；不以错误匹配补 DOI。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" ht="64" customHeight="1">
+      <x:c r="A231" s="6" t="str">
+        <x:v>陈雨时</x:v>
+      </x:c>
+      <x:c r="B231" s="6" t="str">
+        <x:v>Multi-Sensor Hyperspectral Image Classification via Denoising-CAE and Dataset-Aware MAE</x:v>
+      </x:c>
+      <x:c r="C231" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D231" s="6" t="str">
+        <x:v>10.1109/lgrs.2026.3743370</x:v>
+      </x:c>
+      <x:c r="E231" s="6" t="str">
+        <x:v>https://doi.org/10.1109/lgrs.2026.3743370</x:v>
+      </x:c>
+      <x:c r="F231" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G231" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chenyushi</x:v>
+      </x:c>
+      <x:c r="H231" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chenyushi</x:v>
+      </x:c>
+      <x:c r="I231" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J231" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2026；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="64" customHeight="1">
+      <x:c r="A232" s="6" t="str">
+        <x:v>陈雨时</x:v>
+      </x:c>
+      <x:c r="B232" s="6" t="str">
+        <x:v>Multilevel Alignment-Based Domain Generalization Network for Cross-Scene Hyperspectral Image Classification</x:v>
+      </x:c>
+      <x:c r="C232" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D232" s="6" t="str">
+        <x:v>10.1109/jstars.2026.3662716</x:v>
+      </x:c>
+      <x:c r="E232" s="6" t="str">
+        <x:v>https://doi.org/10.1109/jstars.2026.3662716</x:v>
+      </x:c>
+      <x:c r="F232" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G232" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chenyushi</x:v>
+      </x:c>
+      <x:c r="H232" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chenyushi</x:v>
+      </x:c>
+      <x:c r="I232" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J232" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2026；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" ht="64" customHeight="1">
+      <x:c r="A233" s="6" t="str">
+        <x:v>尹振东</x:v>
+      </x:c>
+      <x:c r="B233" s="6" t="str">
+        <x:v>Research on the Talents Education Scheme Based on Integration of Science and Education for Information and Communication Engineering</x:v>
+      </x:c>
+      <x:c r="C233" s="6" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="D233" s="6" t="str">
+        <x:v>10.18178/ijiet.2022.12.4.1627</x:v>
+      </x:c>
+      <x:c r="E233" s="6" t="str">
+        <x:v>https://doi.org/10.18178/ijiet.2022.12.4.1627</x:v>
+      </x:c>
+      <x:c r="F233" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G233" s="6" t="str">
+        <x:v>https://www.ijiet.org/online/WA4003.pdf</x:v>
+      </x:c>
+      <x:c r="H233" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yinzhendong</x:v>
+      </x:c>
+      <x:c r="I233" s="6" t="str">
+        <x:v>publisher_pdf_read_and_crossref_metadata_verified</x:v>
+      </x:c>
+      <x:c r="J233" s="6" t="str">
+        <x:v>版权/收稿2021与正式登记出版2022区别明确，年份取Crossref正式出版登记。 成果类型：期刊论文。 链接核验状态：原始出版社论文 PDF 与作者简介已读，Crossref 书目另核；不公开全文副本。 Crossref 登记出版日期：2022；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" ht="64" customHeight="1">
+      <x:c r="A234" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B234" s="6" t="str">
+        <x:v>Contour Refinement and EG-GHT-Based Inshore Ship Detection in Optical Remote Sensing Image</x:v>
+      </x:c>
+      <x:c r="C234" s="6" t="n">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="D234" s="6" t="str">
+        <x:v>10.1109/tgrs.2019.2921242</x:v>
+      </x:c>
+      <x:c r="E234" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tgrs.2019.2921242</x:v>
+      </x:c>
+      <x:c r="F234" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G234" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+      <x:c r="H234" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+      <x:c r="I234" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J234" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2019-11；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" ht="64" customHeight="1">
+      <x:c r="A235" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B235" s="6" t="str">
+        <x:v>Coupled Heterogeneous Tucker Decomposition: A Feature extraction method for Multisource Fusion and Domain Adaptation using Multisource Heterogeneous Remote Sensing Data</x:v>
+      </x:c>
+      <x:c r="C235" s="6" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="D235" s="6" t="str">
+        <x:v>10.3390/rs14112553</x:v>
+      </x:c>
+      <x:c r="E235" s="6" t="str">
+        <x:v>https://doi.org/10.3390/rs14112553</x:v>
+      </x:c>
+      <x:c r="F235" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G235" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+      <x:c r="H235" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+      <x:c r="I235" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J235" s="6" t="str">
+        <x:v>本人英文书目列HaoChen在首位，但Crossref作者顺序TongGao、HaoChen、JunhongLu；保留登记顺序，不声称首作者身份。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2022-05-26；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="64" customHeight="1">
+      <x:c r="A236" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B236" s="6" t="str">
+        <x:v>A Generative Adversarial Network with Spatial Attention Mechanism for Building Structure Inference Based on Unmanned Aerial Vehicle Remote Sensing Images</x:v>
+      </x:c>
+      <x:c r="C236" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D236" s="6" t="str">
+        <x:v>10.3390/rs15184390</x:v>
+      </x:c>
+      <x:c r="E236" s="6" t="str">
+        <x:v>https://doi.org/10.3390/rs15184390</x:v>
+      </x:c>
+      <x:c r="F236" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G236" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+      <x:c r="H236" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+      <x:c r="I236" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J236" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2023-09-06；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="64" customHeight="1">
+      <x:c r="A237" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B237" s="6" t="str">
+        <x:v>PELNet: A General Physics-Embedded Learning Framework for Polarimetric Target Decomposition</x:v>
+      </x:c>
+      <x:c r="C237" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D237" s="6" t="str">
+        <x:v>10.1016/j.isprsjprs.2026.08.040</x:v>
+      </x:c>
+      <x:c r="E237" s="6" t="str">
+        <x:v>https://doi.org/10.1016/j.isprsjprs.2026.08.040</x:v>
+      </x:c>
+      <x:c r="F237" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G237" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+      <x:c r="H237" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+      <x:c r="I237" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J237" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2026-12；保留原始精度。 登记卷期为2026年12月，晚于本次核验日；官网已列，未核实单独在线发表日期，不宣称该卷期已经出版。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" ht="64" customHeight="1">
+      <x:c r="A238" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B238" s="6" t="str">
+        <x:v>DGS-CapNet：基于空间-频率感知的SAR图像描述模型</x:v>
+      </x:c>
+      <x:c r="C238" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D238" s="6" t="str">
+        <x:v>10.12000/JR25250</x:v>
+      </x:c>
+      <x:c r="E238" s="6" t="str">
+        <x:v>https://doi.org/10.12000/JR25250</x:v>
+      </x:c>
+      <x:c r="F238" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G238" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+      <x:c r="H238" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+      <x:c r="I238" s="6" t="str">
+        <x:v>publisher_search_excerpt_match_landing_timeout_and_403</x:v>
+      </x:c>
+      <x:c r="J238" s="6" t="str">
+        <x:v>期刊官方搜索摘录同题同作者同卷页给DOI；DOI打开timeout，直接期刊页403，未重试或冒称正文可读。 成果类型：期刊论文。 链接核验状态：仅期刊官方搜索摘录对应，文章页超时或403未读；不升级为文章正文核验。 Crossref 返回无关题名，未采用；不以错误匹配补 DOI。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="64" customHeight="1">
+      <x:c r="A239" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B239" s="6" t="str">
+        <x:v>Towards Interpretable PolSAR Image Classification: Polarimetric Scattering Mechanism Informed Concept Bottleneck and Kolmogorov-Arnold Network</x:v>
+      </x:c>
+      <x:c r="C239" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D239" s="6" t="str">
+        <x:v>10.1109/tgrs.2026.3652576</x:v>
+      </x:c>
+      <x:c r="E239" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tgrs.2026.3652576</x:v>
+      </x:c>
+      <x:c r="F239" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G239" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+      <x:c r="H239" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+      <x:c r="I239" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J239" s="6" t="str">
+        <x:v>本人官网Towards，登记题名Toward（单复拼写差别），同题其余文本、全部作者及期刊一致，保留两题名。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2026；保留原始精度。 登记题名异体：Toward Interpretable PolSAR Image Classification: Polarimetric Scattering Mechanism Informed Concept Bottleneck and Kolmogorov–Arnold Network。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="64" customHeight="1">
+      <x:c r="A240" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B240" s="6" t="str">
+        <x:v>Agentic AI-Empowered Reliable Routing in Interference-Aware UAV Networks</x:v>
+      </x:c>
+      <x:c r="C240" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D240" s="6" t="str">
+        <x:v>10.1109/tccn.2026.3706086</x:v>
+      </x:c>
+      <x:c r="E240" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tccn.2026.3706086</x:v>
+      </x:c>
+      <x:c r="F240" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G240" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yangzhutian</x:v>
+      </x:c>
+      <x:c r="H240" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yangzhutian</x:v>
+      </x:c>
+      <x:c r="I240" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J240" s="6" t="str">
+        <x:v>官网列入本人论文，Crossref标题、作者及期刊相符；DOI为真实注册元数据链接，不声称已打开出版社文章。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2026；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" ht="64" customHeight="1">
+      <x:c r="A241" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B241" s="6" t="str">
+        <x:v>Distance-Aware Hypergraph and Attention Network With Unimodal Assistance for Multimodal Sentiment Analysis</x:v>
+      </x:c>
+      <x:c r="C241" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D241" s="6" t="str">
+        <x:v>10.1109/tnse.2026.3668198</x:v>
+      </x:c>
+      <x:c r="E241" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tnse.2026.3668198</x:v>
+      </x:c>
+      <x:c r="F241" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G241" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yangzhutian</x:v>
+      </x:c>
+      <x:c r="H241" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yangzhutian</x:v>
+      </x:c>
+      <x:c r="I241" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J241" s="6" t="str">
+        <x:v>官网列入本人论文，Crossref标题、作者及期刊相符；DOI为真实注册元数据链接，不声称已打开出版社文章。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2026；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" ht="64" customHeight="1">
+      <x:c r="A242" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B242" s="6" t="str">
+        <x:v>NOMA-Enhanced Secure SWIPT-ISAC Against Internal and External Eavesdropping</x:v>
+      </x:c>
+      <x:c r="C242" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D242" s="6" t="str">
+        <x:v>10.1109/tcomm.2025.3573449</x:v>
+      </x:c>
+      <x:c r="E242" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tcomm.2025.3573449</x:v>
+      </x:c>
+      <x:c r="F242" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G242" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yangzhutian</x:v>
+      </x:c>
+      <x:c r="H242" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yangzhutian</x:v>
+      </x:c>
+      <x:c r="I242" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J242" s="6" t="str">
+        <x:v>官网列入本人论文，Crossref标题、作者及期刊相符；DOI为真实注册元数据链接，不声称已打开出版社文章。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2025-11；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" ht="64" customHeight="1">
+      <x:c r="A243" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B243" s="6" t="str">
+        <x:v>Deep graph embedding based on Laplacian eigenmaps for MR fingerprinting reconstruction</x:v>
+      </x:c>
+      <x:c r="C243" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D243" s="6" t="str">
+        <x:v>10.1016/j.media.2025.103481</x:v>
+      </x:c>
+      <x:c r="E243" s="6" t="str">
+        <x:v>https://doi.org/10.1016/j.media.2025.103481</x:v>
+      </x:c>
+      <x:c r="F243" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G243" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huyue</x:v>
+      </x:c>
+      <x:c r="H243" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huyue</x:v>
+      </x:c>
+      <x:c r="I243" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J243" s="6" t="str">
+        <x:v>官网列入本人论文，Crossref标题、作者及期刊相符；DOI为真实注册元数据链接，不声称已打开出版社文章。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2025-04；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" ht="64" customHeight="1">
+      <x:c r="A244" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B244" s="6" t="str">
+        <x:v>JotlasNet: Joint tensor low-rank and attention-based sparse unrolling network for accelerating dynamic MRI</x:v>
+      </x:c>
+      <x:c r="C244" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D244" s="6" t="str">
+        <x:v>10.1016/j.mri.2025.110337</x:v>
+      </x:c>
+      <x:c r="E244" s="6" t="str">
+        <x:v>https://doi.org/10.1016/j.mri.2025.110337</x:v>
+      </x:c>
+      <x:c r="F244" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G244" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huyue</x:v>
+      </x:c>
+      <x:c r="H244" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huyue</x:v>
+      </x:c>
+      <x:c r="I244" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J244" s="6" t="str">
+        <x:v>官网列入本人论文，Crossref标题、作者及期刊相符；DOI为真实注册元数据链接，不声称已打开出版社文章。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2025-05；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" ht="64" customHeight="1">
+      <x:c r="A245" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B245" s="6" t="str">
+        <x:v>Semi-Supervised Echocardiography Video Segmentation via Adaptive Spatio-Temporal Tensor Semantic Awareness and Memory Flow</x:v>
+      </x:c>
+      <x:c r="C245" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D245" s="6" t="str">
+        <x:v>10.1109/tmi.2025.3526955</x:v>
+      </x:c>
+      <x:c r="E245" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tmi.2025.3526955</x:v>
+      </x:c>
+      <x:c r="F245" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G245" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huyue</x:v>
+      </x:c>
+      <x:c r="H245" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huyue</x:v>
+      </x:c>
+      <x:c r="I245" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J245" s="6" t="str">
+        <x:v>官网列入本人论文，Crossref标题、作者及期刊相符；DOI为真实注册元数据链接，不声称已打开出版社文章。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2025-05；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" ht="64" customHeight="1">
+      <x:c r="A246" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B246" s="6" t="str">
+        <x:v>Spectral Reconstruction From Satellite Multispectral Imagery Using Convolution and Transformer Joint Network</x:v>
+      </x:c>
+      <x:c r="C246" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D246" s="6" t="str">
+        <x:v>10.1109/tgrs.2023.3285893</x:v>
+      </x:c>
+      <x:c r="E246" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tgrs.2023.3285893</x:v>
+      </x:c>
+      <x:c r="F246" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G246" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+      <x:c r="H246" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+      <x:c r="I246" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J246" s="6" t="str">
+        <x:v>官网列入本人论文，Crossref标题、作者及期刊相符；DOI为真实注册元数据链接，不声称已打开出版社文章。 官网仍写Accepted，Crossref给2023。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2023；保留原始精度。 官网书目日期 Accepted；Crossref 登记日期 2023，不同日期原样保留，不推断差异原因。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" ht="64" customHeight="1">
+      <x:c r="A247" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B247" s="6" t="str">
+        <x:v>Shadow-Less Intrinsic Hyperspectral Point Cloud Generation From HSIs and LiDAR</x:v>
+      </x:c>
+      <x:c r="C247" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D247" s="6" t="str">
+        <x:v>10.1109/tgrs.2023.3265080</x:v>
+      </x:c>
+      <x:c r="E247" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tgrs.2023.3265080</x:v>
+      </x:c>
+      <x:c r="F247" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G247" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+      <x:c r="H247" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+      <x:c r="I247" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J247" s="6" t="str">
+        <x:v>官网列入本人论文，Crossref标题、作者及期刊相符；DOI为真实注册元数据链接，不声称已打开出版社文章。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2023；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" ht="64" customHeight="1">
+      <x:c r="A248" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B248" s="6" t="str">
+        <x:v>Separable Coupled Dictionary Learning for Large-Scene Precise Classification of Multispectral Images</x:v>
+      </x:c>
+      <x:c r="C248" s="6" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="D248" s="6" t="str">
+        <x:v>10.1109/tgrs.2022.3217061</x:v>
+      </x:c>
+      <x:c r="E248" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tgrs.2022.3217061</x:v>
+      </x:c>
+      <x:c r="F248" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G248" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+      <x:c r="H248" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+      <x:c r="I248" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J248" s="6" t="str">
+        <x:v>官网列入本人论文，Crossref标题、作者及期刊相符；DOI为真实注册元数据链接，不声称已打开出版社文章。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2022；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" ht="64" customHeight="1">
+      <x:c r="A249" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B249" s="6" t="str">
+        <x:v>Foundation Models for Remote Sensing and Earth Observation: A survey</x:v>
+      </x:c>
+      <x:c r="C249" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D249" s="6" t="str">
+        <x:v>10.1109/mgrs.2025.3576766</x:v>
+      </x:c>
+      <x:c r="E249" s="6" t="str">
+        <x:v>https://doi.org/10.1109/mgrs.2025.3576766</x:v>
+      </x:c>
+      <x:c r="F249" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G249" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+      <x:c r="H249" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+      <x:c r="I249" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J249" s="6" t="str">
+        <x:v>官网列入本人论文，Crossref标题、作者及期刊相符；DOI为真实注册元数据链接，不声称已打开出版社文章。 官网年份与Crossref登记年份不一致，保留双值，原因未核定。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2025-12；保留原始精度。 书目年份冲突：官网 2026，Crossref 2025；双值保留，原因未核定。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" ht="64" customHeight="1">
+      <x:c r="A250" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B250" s="6" t="str">
+        <x:v>Unsupervised Point Cloud Representation Learning With Deep Neural Networks: A Survey</x:v>
+      </x:c>
+      <x:c r="C250" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D250" s="6" t="str">
+        <x:v>10.1109/tpami.2023.3262786</x:v>
+      </x:c>
+      <x:c r="E250" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tpami.2023.3262786</x:v>
+      </x:c>
+      <x:c r="F250" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G250" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+      <x:c r="H250" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+      <x:c r="I250" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J250" s="6" t="str">
+        <x:v>官网列入本人论文，Crossref标题、作者及期刊相符；DOI为真实注册元数据链接，不声称已打开出版社文章。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2023-09-01；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" ht="64" customHeight="1">
+      <x:c r="A251" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B251" s="6" t="str">
+        <x:v>A Survey of Label-Efficient Deep Learning for 3D Point Clouds</x:v>
+      </x:c>
+      <x:c r="C251" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D251" s="6" t="str">
+        <x:v>10.1109/tpami.2024.3416302</x:v>
+      </x:c>
+      <x:c r="E251" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tpami.2024.3416302</x:v>
+      </x:c>
+      <x:c r="F251" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G251" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+      <x:c r="H251" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+      <x:c r="I251" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J251" s="6" t="str">
+        <x:v>官网列入本人论文，Crossref标题、作者及期刊相符；DOI为真实注册元数据链接，不声称已打开出版社文章。 官网年份与Crossref登记年份不一致，保留双值，原因未核定。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2024-12；保留原始精度。 书目年份冲突：官网 2023，Crossref 2024；双值保留，原因未核定。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" ht="64" customHeight="1">
+      <x:c r="A252" s="6" t="str">
+        <x:v>胡航</x:v>
+      </x:c>
+      <x:c r="B252" s="6" t="str">
+        <x:v>Advances in Antenna Array Processing for Radar</x:v>
+      </x:c>
+      <x:c r="C252" s="6" t="n">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="D252" s="6" t="str">
+        <x:v>10.1155/2013/416096</x:v>
+      </x:c>
+      <x:c r="E252" s="6" t="str">
+        <x:v>https://doi.org/10.1155/2013/416096</x:v>
+      </x:c>
+      <x:c r="F252" s="6" t="str">
+        <x:v>editorial</x:v>
+      </x:c>
+      <x:c r="G252" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huhang</x:v>
+      </x:c>
+      <x:c r="H252" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huhang</x:v>
+      </x:c>
+      <x:c r="I252" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J252" s="6" t="str">
+        <x:v>官网期刊书目；专刊编辑引言非一般原创研究论文。 成果类型：编者按。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2013；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" ht="64" customHeight="1">
+      <x:c r="A253" s="6" t="str">
+        <x:v>胡航</x:v>
+      </x:c>
+      <x:c r="B253" s="6" t="str">
+        <x:v>现代相控阵雷达阵列处理技术</x:v>
+      </x:c>
+      <x:c r="C253" s="6" t="n">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="D253" s="6" t="str"/>
+      <x:c r="E253" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huhang</x:v>
+      </x:c>
+      <x:c r="F253" s="6" t="str">
+        <x:v>book</x:v>
+      </x:c>
+      <x:c r="G253" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huhang</x:v>
+      </x:c>
+      <x:c r="H253" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huhang</x:v>
+      </x:c>
+      <x:c r="I253" s="6" t="str">
+        <x:v>official_selected_bibliography_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J253" s="6" t="str">
+        <x:v>成果类型：著作。 链接核验状态：仅官方精选书目，未核独立文章落地页；不自动补同名 DOI。 Crossref 返回无关题名未采用，不按无关匹配补 DOI。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" ht="64" customHeight="1">
+      <x:c r="A254" s="6" t="str">
+        <x:v>胡航</x:v>
+      </x:c>
+      <x:c r="B254" s="6" t="str">
+        <x:v>相控阵的子阵级数字波束扫描方法研究</x:v>
+      </x:c>
+      <x:c r="C254" s="6" t="n">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="D254" s="6" t="str"/>
+      <x:c r="E254" s="6" t="str">
+        <x:v>https://www.sys-ele.com/CN/Y2009/V31/I4/733</x:v>
+      </x:c>
+      <x:c r="F254" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G254" s="6" t="str">
+        <x:v>https://www.sys-ele.com/CN/Y2009/V31/I4/733</x:v>
+      </x:c>
+      <x:c r="H254" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huhang</x:v>
+      </x:c>
+      <x:c r="I254" s="6" t="str">
+        <x:v>publisher_article_metadata_read</x:v>
+      </x:c>
+      <x:c r="J254" s="6" t="str">
+        <x:v>直接期刊页面读到题名、作者、单位及博士简介；出版日期2009-04-20，网站发布日期2010-01-03不替代出版年。 成果类型：期刊论文。 链接核验状态：期刊官方文章元数据已读，不等同全文读取。 Crossref 返回无关题名未采用，不按无关匹配补 DOI。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" ht="64" customHeight="1">
+      <x:c r="A255" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B255" s="6" t="str">
+        <x:v>Stokes parameters and DOA estimation for nested polarization sensitive array in unknown nonuniform noise environment</x:v>
+      </x:c>
+      <x:c r="C255" s="6" t="n">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="D255" s="6" t="str">
+        <x:v>10.1016/j.sigpro.2020.107630</x:v>
+      </x:c>
+      <x:c r="E255" s="6" t="str">
+        <x:v>https://doi.org/10.1016/j.sigpro.2020.107630</x:v>
+      </x:c>
+      <x:c r="F255" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G255" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houyuguan</x:v>
+      </x:c>
+      <x:c r="H255" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houyuguan</x:v>
+      </x:c>
+      <x:c r="I255" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J255" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2020-10；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" ht="64" customHeight="1">
+      <x:c r="A256" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B256" s="6" t="str">
+        <x:v>Importance Resampling Approach for Sensor Mutual Coupling Correction</x:v>
+      </x:c>
+      <x:c r="C256" s="6" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="D256" s="6" t="str">
+        <x:v>10.1109/jsen.2022.3175843</x:v>
+      </x:c>
+      <x:c r="E256" s="6" t="str">
+        <x:v>https://doi.org/10.1109/jsen.2022.3175843</x:v>
+      </x:c>
+      <x:c r="F256" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G256" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houyuguan</x:v>
+      </x:c>
+      <x:c r="H256" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houyuguan</x:v>
+      </x:c>
+      <x:c r="I256" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J256" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2022-07-01；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257" ht="64" customHeight="1">
+      <x:c r="A257" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B257" s="6" t="str">
+        <x:v>A two-stage detection method based on improved DP-TBD for marine weak extended targets</x:v>
+      </x:c>
+      <x:c r="C257" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D257" s="6" t="str">
+        <x:v>10.1016/j.dsp.2025.105054</x:v>
+      </x:c>
+      <x:c r="E257" s="6" t="str">
+        <x:v>https://doi.org/10.1016/j.dsp.2025.105054</x:v>
+      </x:c>
+      <x:c r="F257" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G257" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houyuguan</x:v>
+      </x:c>
+      <x:c r="H257" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houyuguan</x:v>
+      </x:c>
+      <x:c r="I257" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J257" s="6" t="str">
+        <x:v>官网只列前两位作者，Crossref完整四位登记署名保留；ScienceDirect落地403未冒称正文已读。 成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2025-05；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258" ht="64" customHeight="1">
+      <x:c r="A258" s="6" t="str">
+        <x:v>高建军</x:v>
+      </x:c>
+      <x:c r="B258" s="6" t="str">
+        <x:v>海杂波对ISAR成像的影响</x:v>
+      </x:c>
+      <x:c r="C258" s="6" t="n">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="D258" s="6" t="str"/>
+      <x:c r="E258" s="6" t="str">
+        <x:v>https://www.sys-ele.com/CN/Y2009/V31/I8/1851</x:v>
+      </x:c>
+      <x:c r="F258" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G258" s="6" t="str">
+        <x:v>https://www.sys-ele.com/CN/Y2009/V31/I8/1851</x:v>
+      </x:c>
+      <x:c r="H258" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/jjgao</x:v>
+      </x:c>
+      <x:c r="I258" s="6" t="str">
+        <x:v>publisher_article_metadata_read</x:v>
+      </x:c>
+      <x:c r="J258" s="6" t="str">
+        <x:v>直接期刊页同名同HIT院系同ISAR研究方向作者匹配；历史2009作者简介博士研究生不表示当前仍在读。 成果类型：期刊论文。 链接核验状态：期刊官方文章元数据已读，不等同全文读取。 Crossref 返回无关题名未采用，不按无关匹配补 DOI。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259" ht="64" customHeight="1">
+      <x:c r="A259" s="6" t="str">
+        <x:v>高国明</x:v>
+      </x:c>
+      <x:c r="B259" s="6" t="str">
+        <x:v>Dual-Path Self-Supervised Spatiotemporal Learning for Satellite Video Scene Understanding</x:v>
+      </x:c>
+      <x:c r="C259" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D259" s="6" t="str">
+        <x:v>10.1109/tgrs.2026.3660976</x:v>
+      </x:c>
+      <x:c r="E259" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tgrs.2026.3660976</x:v>
+      </x:c>
+      <x:c r="F259" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G259" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaoguoming</x:v>
+      </x:c>
+      <x:c r="H259" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaoguoming</x:v>
+      </x:c>
+      <x:c r="I259" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J259" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2026；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260" ht="64" customHeight="1">
+      <x:c r="A260" s="6" t="str">
+        <x:v>高国明</x:v>
+      </x:c>
+      <x:c r="B260" s="6" t="str">
+        <x:v>PESAT: A Parameter-Efficient Spatiotemporal Adapter Tuning Framework for Satellite Video Scene Classification</x:v>
+      </x:c>
+      <x:c r="C260" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D260" s="6" t="str">
+        <x:v>10.1109/tgrs.2025.3612049</x:v>
+      </x:c>
+      <x:c r="E260" s="6" t="str">
+        <x:v>https://doi.org/10.1109/tgrs.2025.3612049</x:v>
+      </x:c>
+      <x:c r="F260" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G260" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaoguoming</x:v>
+      </x:c>
+      <x:c r="H260" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaoguoming</x:v>
+      </x:c>
+      <x:c r="I260" s="6" t="str">
+        <x:v>crossref_metadata_verified_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J260" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：Crossref 登记书目元数据已核，文章落地页未核，不等同全文读取。 Crossref 登记出版日期：2025；保留原始精度。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261" ht="64" customHeight="1">
+      <x:c r="A261" s="6" t="str">
+        <x:v>高国明</x:v>
+      </x:c>
+      <x:c r="B261" s="6" t="str">
+        <x:v>Satellite Video Event of Interest Detection Using Deep Spatiotemporal Metric</x:v>
+      </x:c>
+      <x:c r="C261" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D261" s="6" t="str"/>
+      <x:c r="E261" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaoguoming</x:v>
+      </x:c>
+      <x:c r="F261" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G261" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaoguoming</x:v>
+      </x:c>
+      <x:c r="H261" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaoguoming</x:v>
+      </x:c>
+      <x:c r="I261" s="6" t="str">
+        <x:v>official_selected_bibliography_landing_page_not_checked</x:v>
+      </x:c>
+      <x:c r="J261" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：仅官方精选书目，未核独立文章落地页；不自动补同名 DOI。 Crossref 查询429后已停止，不补造 DOI 或声称核验成功。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b1683504f1243cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4a0f3d5f9364d71"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47656,10 +55667,1761 @@
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
     </x:row>
+    <x:row r="367" ht="64" customHeight="1">
+      <x:c r="A367" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B367" s="6" t="str">
+        <x:v>franklinsu-official</x:v>
+      </x:c>
+      <x:c r="C367" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/franklinsu</x:v>
+      </x:c>
+      <x:c r="D367" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E367" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368" ht="64" customHeight="1">
+      <x:c r="A368" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B368" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C368" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D368" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E368" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369" ht="64" customHeight="1">
+      <x:c r="A369" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B369" s="6" t="str">
+        <x:v>franklinsu-paper1-crossref</x:v>
+      </x:c>
+      <x:c r="C369" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=An%20End-to-End%20Multi-Domain%20Interaction%20Deep%20Unrolling%20Network%20Based%20on%20Block-Aware%20Optimization%20Model%20for%20ISAR%20Multi-Target%20Separation&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D369" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E369" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370" ht="64" customHeight="1">
+      <x:c r="A370" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B370" s="6" t="str">
+        <x:v>franklinsu-paper2-crossref</x:v>
+      </x:c>
+      <x:c r="C370" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=MSDP-Net%3A%20A%20Multi-Scale%20Domain%20Perception%20Network%20for%20HRRP%20Target%20Recognition&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D370" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E370" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371" ht="64" customHeight="1">
+      <x:c r="A371" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B371" s="6" t="str">
+        <x:v>franklinsu-paper3-crossref</x:v>
+      </x:c>
+      <x:c r="C371" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Inverse%20Synthetic%20Aperture%20Radar%20Image%20Multi-Modal%20Zero-Shot%20Learning%20Based%20on%20the%20Scattering%20Center%20Model%20and%20Neighbor-Adapted%20Locally%20Linear%20Embedding&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D371" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E371" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372" ht="64" customHeight="1">
+      <x:c r="A372" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B372" s="6" t="str">
+        <x:v>zoubin-official</x:v>
+      </x:c>
+      <x:c r="C372" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zoubin</x:v>
+      </x:c>
+      <x:c r="D372" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E372" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373" ht="64" customHeight="1">
+      <x:c r="A373" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B373" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C373" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D373" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E373" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374" ht="64" customHeight="1">
+      <x:c r="A374" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B374" s="6" t="str">
+        <x:v>zoubin-author-bio</x:v>
+      </x:c>
+      <x:c r="C374" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ueditor/jsp/upload/file/20200505/1588688180750046569.pdf</x:v>
+      </x:c>
+      <x:c r="D374" s="6" t="str">
+        <x:v>officially_hosted_authored_paper_biography_read</x:v>
+      </x:c>
+      <x:c r="E374" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375" ht="64" customHeight="1">
+      <x:c r="A375" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B375" s="6" t="str">
+        <x:v>zoubin-paper1-crossref</x:v>
+      </x:c>
+      <x:c r="C375" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Iterative%20PolInSAR%20Target%20Decomposition%20for%20Scattering%20Characterization%20and%20Building%20Detection&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D375" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E375" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376" ht="64" customHeight="1">
+      <x:c r="A376" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B376" s="6" t="str">
+        <x:v>zoubin-paper2-crossref</x:v>
+      </x:c>
+      <x:c r="C376" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Scattering%20Power%20Decomposition%20Based%20on%20PolInSAR%20Images%20and%20Sparse%20Representation&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D376" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E376" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377" ht="64" customHeight="1">
+      <x:c r="A377" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B377" s="6" t="str">
+        <x:v>zoubin-paper3-crossref</x:v>
+      </x:c>
+      <x:c r="C377" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Efficient%20End-to-End%20Diffusion%20Model%20for%20One-Step%20SAR-to-Optical%20Translation&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D377" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E377" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378" ht="64" customHeight="1">
+      <x:c r="A378" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B378" s="6" t="str">
+        <x:v>zhangjunping-official</x:v>
+      </x:c>
+      <x:c r="C378" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhangjunping</x:v>
+      </x:c>
+      <x:c r="D378" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E378" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379" ht="64" customHeight="1">
+      <x:c r="A379" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B379" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C379" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D379" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E379" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380" ht="64" customHeight="1">
+      <x:c r="A380" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B380" s="6" t="str">
+        <x:v>zhangjunping-author-bio</x:v>
+      </x:c>
+      <x:c r="C380" s="6" t="str">
+        <x:v>https://article.nadiapub.com/IJSIP/vol9_no9/12.pdf</x:v>
+      </x:c>
+      <x:c r="D380" s="6" t="str">
+        <x:v>publisher_authored_paper_biography_read</x:v>
+      </x:c>
+      <x:c r="E380" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381" ht="64" customHeight="1">
+      <x:c r="A381" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B381" s="6" t="str">
+        <x:v>zhangjunping-paper1-crossref</x:v>
+      </x:c>
+      <x:c r="C381" s="6" t="str">
+        <x:v>https://api.crossref.org/works/10.1109/TGRS.2025.3567345</x:v>
+      </x:c>
+      <x:c r="D381" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E381" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382" ht="64" customHeight="1">
+      <x:c r="A382" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B382" s="6" t="str">
+        <x:v>zhangjunping-paper2-crossref</x:v>
+      </x:c>
+      <x:c r="C382" s="6" t="str">
+        <x:v>https://api.crossref.org/works/10.1109/LGRS.2025.3545505</x:v>
+      </x:c>
+      <x:c r="D382" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E382" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383" ht="64" customHeight="1">
+      <x:c r="A383" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B383" s="6" t="str">
+        <x:v>zhangjunping-paper3-crossref</x:v>
+      </x:c>
+      <x:c r="C383" s="6" t="str">
+        <x:v>https://api.crossref.org/works/10.1109/LGRS.2025.3526177</x:v>
+      </x:c>
+      <x:c r="D383" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E383" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384" ht="64" customHeight="1">
+      <x:c r="A384" s="6" t="str">
+        <x:v>朱兵</x:v>
+      </x:c>
+      <x:c r="B384" s="6" t="str">
+        <x:v>zhubing-official</x:v>
+      </x:c>
+      <x:c r="C384" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhubing</x:v>
+      </x:c>
+      <x:c r="D384" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E384" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385" ht="64" customHeight="1">
+      <x:c r="A385" s="6" t="str">
+        <x:v>朱兵</x:v>
+      </x:c>
+      <x:c r="B385" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C385" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D385" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E385" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386" ht="64" customHeight="1">
+      <x:c r="A386" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B386" s="6" t="str">
+        <x:v>guyf-official</x:v>
+      </x:c>
+      <x:c r="C386" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guyf</x:v>
+      </x:c>
+      <x:c r="D386" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E386" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387" ht="64" customHeight="1">
+      <x:c r="A387" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B387" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C387" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D387" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E387" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388" ht="64" customHeight="1">
+      <x:c r="A388" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B388" s="6" t="str">
+        <x:v>guyf-ecnu-bio</x:v>
+      </x:c>
+      <x:c r="C388" s="6" t="str">
+        <x:v>https://kjc.ecnu.edu.cn/28/54/c8151a272468/page.htm</x:v>
+      </x:c>
+      <x:c r="D388" s="6" t="str">
+        <x:v>official_university_invited_speaker_biography_read</x:v>
+      </x:c>
+      <x:c r="E388" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389" ht="64" customHeight="1">
+      <x:c r="A389" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B389" s="6" t="str">
+        <x:v>guyf-author-bio</x:v>
+      </x:c>
+      <x:c r="C389" s="6" t="str">
+        <x:v>https://openremotesensing.net/wp-content/uploads/2019/11/TGRS_2016_MLK_Yanfeng_Gu.pdf</x:v>
+      </x:c>
+      <x:c r="D389" s="6" t="str">
+        <x:v>authored_journal_paper_biography_public_repository_read</x:v>
+      </x:c>
+      <x:c r="E389" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390" ht="64" customHeight="1">
+      <x:c r="A390" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B390" s="6" t="str">
+        <x:v>guyf-publications-image</x:v>
+      </x:c>
+      <x:c r="C390" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/ueditor/jsp/upload/image/20230216/1676520493341046292.jpg</x:v>
+      </x:c>
+      <x:c r="D390" s="6" t="str">
+        <x:v>official_profile_publication_image_visually_read</x:v>
+      </x:c>
+      <x:c r="E390" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391" ht="64" customHeight="1">
+      <x:c r="A391" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B391" s="6" t="str">
+        <x:v>guyf-paper1-crossref</x:v>
+      </x:c>
+      <x:c r="C391" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Multimodal%20hyperspectral%20remote%20sensing%3A%20an%20overview%20and%20perspective&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D391" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E391" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392" ht="64" customHeight="1">
+      <x:c r="A392" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B392" s="6" t="str">
+        <x:v>guyf-paper2-crossref</x:v>
+      </x:c>
+      <x:c r="C392" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Intrinsic%20Image%20Recovery%20From%20Remote%20Sensing%20Hyperspectral%20Images&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D392" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E392" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393" ht="64" customHeight="1">
+      <x:c r="A393" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B393" s="6" t="str">
+        <x:v>guyf-paper3-crossref</x:v>
+      </x:c>
+      <x:c r="C393" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Unsupervised%20Cross-Temporal%20Classification%20of%20Hyperspectral%20Images%20With%20Multiple%20Geodesic%20Flow%20Kernel%20Learning&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D393" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E393" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394" ht="64" customHeight="1">
+      <x:c r="A394" s="6" t="str">
+        <x:v>侯成宇</x:v>
+      </x:c>
+      <x:c r="B394" s="6" t="str">
+        <x:v>houchengyu-official</x:v>
+      </x:c>
+      <x:c r="C394" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houchengyu</x:v>
+      </x:c>
+      <x:c r="D394" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E394" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395" ht="64" customHeight="1">
+      <x:c r="A395" s="6" t="str">
+        <x:v>侯成宇</x:v>
+      </x:c>
+      <x:c r="B395" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C395" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D395" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E395" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396" ht="64" customHeight="1">
+      <x:c r="A396" s="6" t="str">
+        <x:v>侯成宇</x:v>
+      </x:c>
+      <x:c r="B396" s="6" t="str">
+        <x:v>houchengyu-source-3</x:v>
+      </x:c>
+      <x:c r="C396" s="6" t="str">
+        <x:v>https://article.nadiapub.com/IJSIP/vol8_no11/26.pdf</x:v>
+      </x:c>
+      <x:c r="D396" s="6" t="str">
+        <x:v>original_publisher_pdf_body_and_author_bio_read</x:v>
+      </x:c>
+      <x:c r="E396" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397" ht="64" customHeight="1">
+      <x:c r="A397" s="6" t="str">
+        <x:v>侯成宇</x:v>
+      </x:c>
+      <x:c r="B397" s="6" t="str">
+        <x:v>houchengyu-source-4</x:v>
+      </x:c>
+      <x:c r="C397" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=A%20TinyML%20System%20for%20Early%20Screening%20of%20CHD%20on%20ESP32&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D397" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E397" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" ht="64" customHeight="1">
+      <x:c r="A398" s="6" t="str">
+        <x:v>侯成宇</x:v>
+      </x:c>
+      <x:c r="B398" s="6" t="str">
+        <x:v>houchengyu-source-5</x:v>
+      </x:c>
+      <x:c r="C398" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=HITrocket%3A%20Hadamard-vector%20inner-product%20transform%20of%20ROCKET%20for%20time%20series%20classification&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D398" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E398" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399" ht="64" customHeight="1">
+      <x:c r="A399" s="6" t="str">
+        <x:v>侯成宇</x:v>
+      </x:c>
+      <x:c r="B399" s="6" t="str">
+        <x:v>houchengyu-source-6</x:v>
+      </x:c>
+      <x:c r="C399" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Target%20Recognition%20Algorithm%20Based%20on%20RCS%20Time%20Sequence&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D399" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E399" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400" ht="64" customHeight="1">
+      <x:c r="A400" s="6" t="str">
+        <x:v>陈雨时</x:v>
+      </x:c>
+      <x:c r="B400" s="6" t="str">
+        <x:v>chenyushi-official</x:v>
+      </x:c>
+      <x:c r="C400" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chenyushi</x:v>
+      </x:c>
+      <x:c r="D400" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E400" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401" ht="64" customHeight="1">
+      <x:c r="A401" s="6" t="str">
+        <x:v>陈雨时</x:v>
+      </x:c>
+      <x:c r="B401" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C401" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D401" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E401" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402" ht="64" customHeight="1">
+      <x:c r="A402" s="6" t="str">
+        <x:v>陈雨时</x:v>
+      </x:c>
+      <x:c r="B402" s="6" t="str">
+        <x:v>chenyushi-source-3</x:v>
+      </x:c>
+      <x:c r="C402" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Multi-Sensor%20Hyperspectral%20Image%20Classification%20via%20Denoising-CAE%20and%20Dataset-Aware%20MAE&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D402" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E402" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403" ht="64" customHeight="1">
+      <x:c r="A403" s="6" t="str">
+        <x:v>陈雨时</x:v>
+      </x:c>
+      <x:c r="B403" s="6" t="str">
+        <x:v>chenyushi-source-4</x:v>
+      </x:c>
+      <x:c r="C403" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Multilevel%20Alignment-Based%20Domain%20Generalization%20Network%20for%20Cross-Scene%20Hyperspectral%20Image%20Classification&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D403" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E403" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404" ht="64" customHeight="1">
+      <x:c r="A404" s="6" t="str">
+        <x:v>尹振东</x:v>
+      </x:c>
+      <x:c r="B404" s="6" t="str">
+        <x:v>yinzhendong-official</x:v>
+      </x:c>
+      <x:c r="C404" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yinzhendong</x:v>
+      </x:c>
+      <x:c r="D404" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E404" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405" ht="64" customHeight="1">
+      <x:c r="A405" s="6" t="str">
+        <x:v>尹振东</x:v>
+      </x:c>
+      <x:c r="B405" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C405" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D405" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E405" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406" ht="64" customHeight="1">
+      <x:c r="A406" s="6" t="str">
+        <x:v>尹振东</x:v>
+      </x:c>
+      <x:c r="B406" s="6" t="str">
+        <x:v>yinzhendong-source-3</x:v>
+      </x:c>
+      <x:c r="C406" s="6" t="str">
+        <x:v>https://www.ijiet.org/online/WA4003.pdf</x:v>
+      </x:c>
+      <x:c r="D406" s="6" t="str">
+        <x:v>original_publisher_pdf_body_and_author_bio_read</x:v>
+      </x:c>
+      <x:c r="E406" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" ht="64" customHeight="1">
+      <x:c r="A407" s="6" t="str">
+        <x:v>尹振东</x:v>
+      </x:c>
+      <x:c r="B407" s="6" t="str">
+        <x:v>yinzhendong-source-4</x:v>
+      </x:c>
+      <x:c r="C407" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Research%20on%20the%20Talents%20Education%20Scheme%20Based%20on%20Integration%20of%20Science%20and%20Education%20for%20Information%20and%20Communication%20Engineering&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D407" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E407" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408" ht="64" customHeight="1">
+      <x:c r="A408" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B408" s="6" t="str">
+        <x:v>hithao-official</x:v>
+      </x:c>
+      <x:c r="C408" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/hithao</x:v>
+      </x:c>
+      <x:c r="D408" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E408" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" ht="64" customHeight="1">
+      <x:c r="A409" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B409" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C409" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D409" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E409" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" ht="64" customHeight="1">
+      <x:c r="A410" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B410" s="6" t="str">
+        <x:v>hithao-source-3</x:v>
+      </x:c>
+      <x:c r="C410" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Contour%20Refinement%20and%20EG-GHT-Based%20Inshore%20Ship%20Detection%20in%20Optical%20Remote%20Sensing%20Image&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D410" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E410" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" ht="64" customHeight="1">
+      <x:c r="A411" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B411" s="6" t="str">
+        <x:v>hithao-source-4</x:v>
+      </x:c>
+      <x:c r="C411" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Coupled%20Heterogeneous%20Tucker%20Decomposition%3A%20A%20Feature%20extraction%20method%20for%20Multisource%20Fusion%20and%20Domain%20Adaptation%20using%20Multisource%20Heterogeneous%20Remote%20Sensing%20Data&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D411" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E411" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" ht="64" customHeight="1">
+      <x:c r="A412" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B412" s="6" t="str">
+        <x:v>hithao-source-5</x:v>
+      </x:c>
+      <x:c r="C412" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=A%20Generative%20Adversarial%20Network%20with%20Spatial%20Attention%20Mechanism%20for%20Building%20Structure%20Inference%20Based%20on%20Unmanned%20Aerial%20Vehicle%20Remote%20Sensing%20Images&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D412" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E412" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" ht="64" customHeight="1">
+      <x:c r="A413" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B413" s="6" t="str">
+        <x:v>zhanglm-official</x:v>
+      </x:c>
+      <x:c r="C413" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+      <x:c r="D413" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E413" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" ht="64" customHeight="1">
+      <x:c r="A414" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B414" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C414" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D414" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E414" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" ht="64" customHeight="1">
+      <x:c r="A415" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B415" s="6" t="str">
+        <x:v>zhanglm-source-3</x:v>
+      </x:c>
+      <x:c r="C415" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=PELNet%3A%20A%20General%20Physics-Embedded%20Learning%20Framework%20for%20Polarimetric%20Target%20Decomposition&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D415" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E415" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" ht="64" customHeight="1">
+      <x:c r="A416" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B416" s="6" t="str">
+        <x:v>zhanglm-source-4</x:v>
+      </x:c>
+      <x:c r="C416" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Towards%20Interpretable%20PolSAR%20Image%20Classification%3A%20Polarimetric%20Scattering%20Mechanism%20Informed%20Concept%20Bottleneck%20and%20Kolmogorov-Arnold%20Network&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D416" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E416" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417" ht="64" customHeight="1">
+      <x:c r="A417" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B417" s="6" t="str">
+        <x:v>zhanglm-source-5</x:v>
+      </x:c>
+      <x:c r="C417" s="6" t="str">
+        <x:v>https://doi.org/10.12000/JR25250</x:v>
+      </x:c>
+      <x:c r="D417" s="6" t="str">
+        <x:v>official_journal_search_excerpt_only_landing_page_unreadable</x:v>
+      </x:c>
+      <x:c r="E417" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" ht="64" customHeight="1">
+      <x:c r="A418" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B418" s="6" t="str">
+        <x:v>yangzhutian-official</x:v>
+      </x:c>
+      <x:c r="C418" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/yangzhutian</x:v>
+      </x:c>
+      <x:c r="D418" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E418" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" ht="64" customHeight="1">
+      <x:c r="A419" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B419" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C419" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D419" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E419" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" ht="64" customHeight="1">
+      <x:c r="A420" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B420" s="6" t="str">
+        <x:v>yangzhutian-author-bio</x:v>
+      </x:c>
+      <x:c r="C420" s="6" t="str">
+        <x:v>https://wrap.warwick.ac.uk/id/eprint/94040/1/WRAP-proactive-jamming-towards-interference-alignment-networks-Chen-2017.pdf</x:v>
+      </x:c>
+      <x:c r="D420" s="6" t="str">
+        <x:v>university_repository_author_biography_read_via_web</x:v>
+      </x:c>
+      <x:c r="E420" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421" ht="64" customHeight="1">
+      <x:c r="A421" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B421" s="6" t="str">
+        <x:v>yangzhutian-paper1-crossref</x:v>
+      </x:c>
+      <x:c r="C421" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Agentic%20AI-Empowered%20Reliable%20Routing%20in%20Interference-Aware%20UAV%20Networks&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D421" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E421" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" ht="64" customHeight="1">
+      <x:c r="A422" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B422" s="6" t="str">
+        <x:v>yangzhutian-paper2-crossref</x:v>
+      </x:c>
+      <x:c r="C422" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Distance-Aware%20Hypergraph%20and%20Attention%20Network%20With%20Unimodal%20Assistance%20for%20Multimodal%20Sentiment%20Analysis&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D422" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E422" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423" ht="64" customHeight="1">
+      <x:c r="A423" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B423" s="6" t="str">
+        <x:v>yangzhutian-paper3-crossref</x:v>
+      </x:c>
+      <x:c r="C423" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=NOMA-Enhanced%20Secure%20SWIPT-ISAC%20Against%20Internal%20and%20External%20Eavesdropping&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D423" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E423" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" ht="64" customHeight="1">
+      <x:c r="A424" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B424" s="6" t="str">
+        <x:v>huyue-official</x:v>
+      </x:c>
+      <x:c r="C424" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huyue</x:v>
+      </x:c>
+      <x:c r="D424" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E424" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" ht="64" customHeight="1">
+      <x:c r="A425" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B425" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C425" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D425" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E425" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426" ht="64" customHeight="1">
+      <x:c r="A426" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B426" s="6" t="str">
+        <x:v>huyue-thesis</x:v>
+      </x:c>
+      <x:c r="C426" s="6" t="str">
+        <x:v>https://research.engineering.uiowa.edu/cbig/sites/research.engineering.uiowa.edu.cbig/files/files/YueHu_thesis(1).pdf</x:v>
+      </x:c>
+      <x:c r="D426" s="6" t="str">
+        <x:v>university_hosted_thesis_front_matter_read_via_web</x:v>
+      </x:c>
+      <x:c r="E426" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427" ht="64" customHeight="1">
+      <x:c r="A427" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B427" s="6" t="str">
+        <x:v>huyue-defense</x:v>
+      </x:c>
+      <x:c r="C427" s="6" t="str">
+        <x:v>https://www.hajim.rochester.edu/ece/news-events/events/ms-phd_defenses/assets/yuHue.pdf</x:v>
+      </x:c>
+      <x:c r="D427" s="6" t="str">
+        <x:v>official_doctoral_defense_notice_read</x:v>
+      </x:c>
+      <x:c r="E427" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" ht="64" customHeight="1">
+      <x:c r="A428" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B428" s="6" t="str">
+        <x:v>mathewsjacob-official</x:v>
+      </x:c>
+      <x:c r="C428" s="6" t="str">
+        <x:v>https://engineering.virginia.edu/faculty/mathews-jacob</x:v>
+      </x:c>
+      <x:c r="D428" s="6" t="str">
+        <x:v>official_faculty_profile_read_via_web</x:v>
+      </x:c>
+      <x:c r="E428" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" ht="64" customHeight="1">
+      <x:c r="A429" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B429" s="6" t="str">
+        <x:v>huyue-paper1-crossref</x:v>
+      </x:c>
+      <x:c r="C429" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Deep%20Graph%20Embedding%20based%20on%20Laplacian%20Eigenmaps%20for%20MR%20Fingerprinting%20Reconstruction&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D429" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E429" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" ht="64" customHeight="1">
+      <x:c r="A430" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B430" s="6" t="str">
+        <x:v>huyue-paper2-crossref</x:v>
+      </x:c>
+      <x:c r="C430" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=JotlasNet%3A%20Joint%20Tensor%20Low-Rank%20and%20Attention-based%20Sparse%20Unrolling%20Network%20for%20Accelerating%20Dynamic%20MRI&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D430" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E430" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431" ht="64" customHeight="1">
+      <x:c r="A431" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B431" s="6" t="str">
+        <x:v>huyue-paper3-crossref</x:v>
+      </x:c>
+      <x:c r="C431" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Semi-supervised%20echocardiography%20video%20segmentation%20via%20adaptive%20spatio-temporal%20tensor%20semantic%20awareness%20and%20memory%20flow&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D431" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E431" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" ht="64" customHeight="1">
+      <x:c r="A432" s="6" t="str">
+        <x:v>刘金龙</x:v>
+      </x:c>
+      <x:c r="B432" s="6" t="str">
+        <x:v>JinlongLiu-official</x:v>
+      </x:c>
+      <x:c r="C432" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/JinlongLiu</x:v>
+      </x:c>
+      <x:c r="D432" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E432" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" ht="64" customHeight="1">
+      <x:c r="A433" s="6" t="str">
+        <x:v>刘金龙</x:v>
+      </x:c>
+      <x:c r="B433" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C433" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D433" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E433" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" ht="64" customHeight="1">
+      <x:c r="A434" s="6" t="str">
+        <x:v>刘金龙</x:v>
+      </x:c>
+      <x:c r="B434" s="6" t="str">
+        <x:v>jinlongliu-author-bio</x:v>
+      </x:c>
+      <x:c r="C434" s="6" t="str">
+        <x:v>https://www.ijiet.org/online/WA4003.pdf</x:v>
+      </x:c>
+      <x:c r="D434" s="6" t="str">
+        <x:v>journal_official_author_biography_read</x:v>
+      </x:c>
+      <x:c r="E434" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435" ht="64" customHeight="1">
+      <x:c r="A435" s="6" t="str">
+        <x:v>刘金龙</x:v>
+      </x:c>
+      <x:c r="B435" s="6" t="str">
+        <x:v>jinlongliu-earlier-author-bio</x:v>
+      </x:c>
+      <x:c r="C435" s="6" t="str">
+        <x:v>https://www.researchgate.net/publication/331430708_Learning-Based_User_Association_for_Dual-UAV_Enabled_Wireless_Networks_With_D2D_Connections</x:v>
+      </x:c>
+      <x:c r="D435" s="6" t="str">
+        <x:v>published_article_author_biography_read_via_web_researchgate_copy</x:v>
+      </x:c>
+      <x:c r="E435" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436" ht="64" customHeight="1">
+      <x:c r="A436" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B436" s="6" t="str">
+        <x:v>liutianzhu-official</x:v>
+      </x:c>
+      <x:c r="C436" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liutianzhu</x:v>
+      </x:c>
+      <x:c r="D436" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E436" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437" ht="64" customHeight="1">
+      <x:c r="A437" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B437" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C437" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D437" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E437" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438" ht="64" customHeight="1">
+      <x:c r="A438" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B438" s="6" t="str">
+        <x:v>liutianzhu-paper1-crossref</x:v>
+      </x:c>
+      <x:c r="C438" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Spectral%20Reconstruction%20From%20Satellite%20Multispectral%20Imagery%20Using%20Convolution%20and%20Transformer%20Joint%20Network&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D438" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E438" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439" ht="64" customHeight="1">
+      <x:c r="A439" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B439" s="6" t="str">
+        <x:v>liutianzhu-paper2-crossref</x:v>
+      </x:c>
+      <x:c r="C439" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Shadow-Less%20Intrinsic%20Hyperspectral%20Point%20Cloud%20Generation%20From%20HSIs%20and%20LiDAR&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D439" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E439" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440" ht="64" customHeight="1">
+      <x:c r="A440" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B440" s="6" t="str">
+        <x:v>liutianzhu-paper3-crossref</x:v>
+      </x:c>
+      <x:c r="C440" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Separable%20Coupled%20Dictionary%20Learning%20for%20Large-Scene%20Precise%20Classification%20of%20Multispectral%20Images&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D440" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E440" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="441" ht="64" customHeight="1">
+      <x:c r="A441" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B441" s="6" t="str">
+        <x:v>xiaoaoran-official</x:v>
+      </x:c>
+      <x:c r="C441" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/xiaoaoran</x:v>
+      </x:c>
+      <x:c r="D441" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E441" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442" ht="64" customHeight="1">
+      <x:c r="A442" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B442" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C442" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D442" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E442" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="443" ht="64" customHeight="1">
+      <x:c r="A443" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B443" s="6" t="str">
+        <x:v>shijianlu-official</x:v>
+      </x:c>
+      <x:c r="C443" s="6" t="str">
+        <x:v>https://personal.ntu.edu.sg/shijian.lu/</x:v>
+      </x:c>
+      <x:c r="D443" s="6" t="str">
+        <x:v>official_faculty_profile_read</x:v>
+      </x:c>
+      <x:c r="E443" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="444" ht="64" customHeight="1">
+      <x:c r="A444" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B444" s="6" t="str">
+        <x:v>lideren-official</x:v>
+      </x:c>
+      <x:c r="C444" s="6" t="str">
+        <x:v>https://www.whu.edu.cn/info/7241/202104.htm</x:v>
+      </x:c>
+      <x:c r="D444" s="6" t="str">
+        <x:v>official_faculty_profile_read_via_web</x:v>
+      </x:c>
+      <x:c r="E444" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="445" ht="64" customHeight="1">
+      <x:c r="A445" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B445" s="6" t="str">
+        <x:v>lideren-2026-news</x:v>
+      </x:c>
+      <x:c r="C445" s="6" t="str">
+        <x:v>https://news.whu.edu.cn/info/1013/499537.htm</x:v>
+      </x:c>
+      <x:c r="D445" s="6" t="str">
+        <x:v>official_university_news_read_via_web</x:v>
+      </x:c>
+      <x:c r="E445" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="446" ht="64" customHeight="1">
+      <x:c r="A446" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B446" s="6" t="str">
+        <x:v>chenruizhi-official-news</x:v>
+      </x:c>
+      <x:c r="C446" s="6" t="str">
+        <x:v>https://news.whu.edu.cn/info/1002/64146.htm</x:v>
+      </x:c>
+      <x:c r="D446" s="6" t="str">
+        <x:v>official_university_biographical_news_read_via_web</x:v>
+      </x:c>
+      <x:c r="E446" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="447" ht="64" customHeight="1">
+      <x:c r="A447" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B447" s="6" t="str">
+        <x:v>xiaoaoran-paper1-crossref</x:v>
+      </x:c>
+      <x:c r="C447" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Foundation%20Models%20for%20Remote%20Sensing%20and%20Earth%20Observation%3A%20A%20Survey&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D447" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E447" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448" ht="64" customHeight="1">
+      <x:c r="A448" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B448" s="6" t="str">
+        <x:v>xiaoaoran-paper2-crossref</x:v>
+      </x:c>
+      <x:c r="C448" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Unsupervised%20Point%20Cloud%20Representation%20Learning%20with%20Deep%20Neural%20Networks%3A%20A%20Survey&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D448" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E448" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449" ht="64" customHeight="1">
+      <x:c r="A449" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B449" s="6" t="str">
+        <x:v>xiaoaoran-paper3-crossref</x:v>
+      </x:c>
+      <x:c r="C449" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=A%20survey%20of%20label-efficient%20deep%20learning%20for%203D%20point%20clouds&amp;rows=2</x:v>
+      </x:c>
+      <x:c r="D449" s="6" t="str">
+        <x:v>crossref_registered_bibliographic_metadata_read</x:v>
+      </x:c>
+      <x:c r="E449" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="450" ht="64" customHeight="1">
+      <x:c r="A450" s="6" t="str">
+        <x:v>胡航</x:v>
+      </x:c>
+      <x:c r="B450" s="6" t="str">
+        <x:v>huhang-official</x:v>
+      </x:c>
+      <x:c r="C450" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huhang</x:v>
+      </x:c>
+      <x:c r="D450" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E450" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="451" ht="64" customHeight="1">
+      <x:c r="A451" s="6" t="str">
+        <x:v>胡航</x:v>
+      </x:c>
+      <x:c r="B451" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C451" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D451" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E451" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="452" ht="64" customHeight="1">
+      <x:c r="A452" s="6" t="str">
+        <x:v>胡航</x:v>
+      </x:c>
+      <x:c r="B452" s="6" t="str">
+        <x:v>huhang-source-3</x:v>
+      </x:c>
+      <x:c r="C452" s="6" t="str">
+        <x:v>https://www.sys-ele.com/CN/Y2009/V31/I4/733</x:v>
+      </x:c>
+      <x:c r="D452" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E452" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453" ht="64" customHeight="1">
+      <x:c r="A453" s="6" t="str">
+        <x:v>胡航</x:v>
+      </x:c>
+      <x:c r="B453" s="6" t="str">
+        <x:v>huhang-metadata-1</x:v>
+      </x:c>
+      <x:c r="C453" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Advances%20in%20Antenna%20Array%20Processing%20for%20Radar&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D453" s="6" t="str">
+        <x:v>crossref_registered_title_authors_venue_verified</x:v>
+      </x:c>
+      <x:c r="E453" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454" ht="64" customHeight="1">
+      <x:c r="A454" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B454" s="6" t="str">
+        <x:v>houyuguan-official</x:v>
+      </x:c>
+      <x:c r="C454" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/houyuguan</x:v>
+      </x:c>
+      <x:c r="D454" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E454" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455" ht="64" customHeight="1">
+      <x:c r="A455" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B455" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C455" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D455" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E455" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456" ht="64" customHeight="1">
+      <x:c r="A456" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B456" s="6" t="str">
+        <x:v>houyuguan-source-3</x:v>
+      </x:c>
+      <x:c r="C456" s="6" t="str">
+        <x:v>https://gvpress.com/journals/IJSH/vol7_no3/21.pdf</x:v>
+      </x:c>
+      <x:c r="D456" s="6" t="str">
+        <x:v>publisher_pdf_author_biography_read</x:v>
+      </x:c>
+      <x:c r="E456" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457" ht="64" customHeight="1">
+      <x:c r="A457" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B457" s="6" t="str">
+        <x:v>houyuguan-metadata-1</x:v>
+      </x:c>
+      <x:c r="C457" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Stokes%20parameters%20and%20DOA%20estimation%20for%20nested%20polarization%20sensitive%20array%20in%20unknown%20nonuniform%20noise%20environment&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D457" s="6" t="str">
+        <x:v>crossref_registered_title_authors_venue_verified</x:v>
+      </x:c>
+      <x:c r="E457" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458" ht="64" customHeight="1">
+      <x:c r="A458" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B458" s="6" t="str">
+        <x:v>houyuguan-metadata-2</x:v>
+      </x:c>
+      <x:c r="C458" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Importance%20Resampling%20Approach%20for%20Sensor%20Mutual%20Coupling%20Correction&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D458" s="6" t="str">
+        <x:v>crossref_registered_title_authors_venue_verified</x:v>
+      </x:c>
+      <x:c r="E458" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459" ht="64" customHeight="1">
+      <x:c r="A459" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B459" s="6" t="str">
+        <x:v>houyuguan-metadata-3</x:v>
+      </x:c>
+      <x:c r="C459" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=A%20two-stage%20detection%20method%20based%20on%20improved%20DP-TBD%20for%20marine%20weak%20extended%20targets&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D459" s="6" t="str">
+        <x:v>crossref_registered_title_authors_venue_verified</x:v>
+      </x:c>
+      <x:c r="E459" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="460" ht="64" customHeight="1">
+      <x:c r="A460" s="6" t="str">
+        <x:v>李宏博</x:v>
+      </x:c>
+      <x:c r="B460" s="6" t="str">
+        <x:v>lihongbo-official</x:v>
+      </x:c>
+      <x:c r="C460" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lihongbo</x:v>
+      </x:c>
+      <x:c r="D460" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E460" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461" ht="64" customHeight="1">
+      <x:c r="A461" s="6" t="str">
+        <x:v>李宏博</x:v>
+      </x:c>
+      <x:c r="B461" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C461" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D461" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E461" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462" ht="64" customHeight="1">
+      <x:c r="A462" s="6" t="str">
+        <x:v>高建军</x:v>
+      </x:c>
+      <x:c r="B462" s="6" t="str">
+        <x:v>jjgao-official</x:v>
+      </x:c>
+      <x:c r="C462" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/jjgao</x:v>
+      </x:c>
+      <x:c r="D462" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E462" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463" ht="64" customHeight="1">
+      <x:c r="A463" s="6" t="str">
+        <x:v>高建军</x:v>
+      </x:c>
+      <x:c r="B463" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C463" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D463" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E463" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464" ht="64" customHeight="1">
+      <x:c r="A464" s="6" t="str">
+        <x:v>高建军</x:v>
+      </x:c>
+      <x:c r="B464" s="6" t="str">
+        <x:v>jjgao-source-3</x:v>
+      </x:c>
+      <x:c r="C464" s="6" t="str">
+        <x:v>https://www.sys-ele.com/CN/Y2009/V31/I8/1851</x:v>
+      </x:c>
+      <x:c r="D464" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E464" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465" ht="64" customHeight="1">
+      <x:c r="A465" s="6" t="str">
+        <x:v>高建军</x:v>
+      </x:c>
+      <x:c r="B465" s="6" t="str">
+        <x:v>jjgao-source-4</x:v>
+      </x:c>
+      <x:c r="C465" s="6" t="str">
+        <x:v>https://radars.ac.cn/en/article/doi/10.12000/JR18077</x:v>
+      </x:c>
+      <x:c r="D465" s="6" t="str">
+        <x:v>official_journal_search_excerpt_only_landing_403</x:v>
+      </x:c>
+      <x:c r="E465" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466" ht="64" customHeight="1">
+      <x:c r="A466" s="6" t="str">
+        <x:v>高国明</x:v>
+      </x:c>
+      <x:c r="B466" s="6" t="str">
+        <x:v>gaoguoming-official</x:v>
+      </x:c>
+      <x:c r="C466" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/gaoguoming</x:v>
+      </x:c>
+      <x:c r="D466" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E466" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="467" ht="64" customHeight="1">
+      <x:c r="A467" s="6" t="str">
+        <x:v>高国明</x:v>
+      </x:c>
+      <x:c r="B467" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C467" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D467" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E467" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468" ht="64" customHeight="1">
+      <x:c r="A468" s="6" t="str">
+        <x:v>高国明</x:v>
+      </x:c>
+      <x:c r="B468" s="6" t="str">
+        <x:v>gaoguoming-metadata-1</x:v>
+      </x:c>
+      <x:c r="C468" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=Dual-Path%20Self-Supervised%20Spatiotemporal%20Learning%20for%20Satellite%20Video%20Scene%20Understanding&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D468" s="6" t="str">
+        <x:v>crossref_registered_title_authors_venue_verified</x:v>
+      </x:c>
+      <x:c r="E468" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="469" ht="64" customHeight="1">
+      <x:c r="A469" s="6" t="str">
+        <x:v>高国明</x:v>
+      </x:c>
+      <x:c r="B469" s="6" t="str">
+        <x:v>gaoguoming-metadata-2</x:v>
+      </x:c>
+      <x:c r="C469" s="6" t="str">
+        <x:v>https://api.crossref.org/works?query.title=PESAT%3A%20A%20Parameter-Efficient%20Spatiotemporal%20Adapter%20Tuning%20Framework%20for%20Satellite%20Video%20Scene%20Classification&amp;rows=1</x:v>
+      </x:c>
+      <x:c r="D469" s="6" t="str">
+        <x:v>crossref_registered_title_authors_venue_verified</x:v>
+      </x:c>
+      <x:c r="E469" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb1e4ace121445f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24786d4746e84880"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/hit-seie.xlsx
+++ b/site/exports/hit-seie.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rcb8d0d4e7bd44b32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rc52ff6551b9d4ca8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R8c3581b1e22c4e32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R8ea7c4188e3f4479"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R04a9c03d37474048"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rdc04b580cadd49ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R74eb212ece784a3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rfef87d7b389d4271"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R6659d0b1cb5b492b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Rcae10c57f50d48ec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T1_0" displayName="T1_0" ref="A1:G124" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T1_0" displayName="T1_0" ref="A1:G136" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T1_1" displayName="T1_1" ref="A1:Q926" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T1_1" displayName="T1_1" ref="A1:Q984" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -179,7 +179,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T1_2" displayName="T1_2" ref="A1:J37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T1_2" displayName="T1_2" ref="A1:J42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="导师姓名"/>
@@ -197,7 +197,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T1_3" displayName="T1_3" ref="A1:J261" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T1_3" displayName="T1_3" ref="A1:J287" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -215,7 +215,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T1_4" displayName="T1_4" ref="A1:E469" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T1_4" displayName="T1_4" ref="A1:E651" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -3283,10 +3283,286 @@
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
     </x:row>
+    <x:row r="125" ht="64" customHeight="1">
+      <x:c r="A125" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B125" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C125" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D125" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+      <x:c r="E125" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F125" s="6" t="str">
+        <x:v>仅收录本次公开可核职业资料及精选书目元数据；未纳入私人联系方式、出生资料、学生名单、GitHub链接或论文全文。原始证据缓存不用于公开展示。；本科与博士开始日期、具体专业及本科导师未公开核实；不推断是否存在单独硕士学位。；NTU博士后研究合作对象Alex Kot、Shijian Lu及HIT团队负责人谷延锋不自动升级为导师。；精选论文未逐篇完成出版商页面核验，DOI未据不确定检索结果填充。；未发现本人的学位答辩/论文委员会成员直接证据；committee_members为空，不代表不存在。；已读官方职业简介：哈尔滨工业大学副教授、博士生导师；研究场景理解、无监督学习及多模态视觉。 此简介不表示完整学历或任职履历。</x:v>
+      </x:c>
+      <x:c r="G125" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="64" customHeight="1">
+      <x:c r="A126" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B126" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C126" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D126" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+      <x:c r="E126" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F126" s="6" t="str">
+        <x:v>仅收录本次公开可核职业资料及精选书目元数据；未纳入私人联系方式、出生资料、学生名单、GitHub链接或论文全文。原始证据缓存不用于公开展示。；本科、硕士授位状态未明确；各阶段导师未获可直读正文证明，博士导师吴芝路线索单列待核。；访问机构的标准英文名与独立在访核证未取得；不将未来结束月当已完成经历。；论文DOI未核实，精选元数据来自本人官网，未标逐篇核验。；未发现本人的学位答辩/论文委员会成员直接证据；committee_members为空，不代表不存在。；已读官方职业简介：哈尔滨工业大学副研究员、硕士生导师；研究通感一体化信道编码、低空电磁频谱安全与抗干扰。 此简介不表示完整学历或任职履历。；待核导师线索：吴芝路；题录检索明确导师、学校、信息与通信工程及2022博士年份均匹配；正文未读，不计入mentors或已核关系。 不绘入师承图、不计确证导师。</x:v>
+      </x:c>
+      <x:c r="G126" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="64" customHeight="1">
+      <x:c r="A127" s="6" t="str">
+        <x:v>曹立新</x:v>
+      </x:c>
+      <x:c r="B127" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C127" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D127" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/caolixin</x:v>
+      </x:c>
+      <x:c r="E127" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F127" s="6" t="str">
+        <x:v>仅收录本次公开可核职业资料及精选书目元数据；未纳入私人联系方式、出生资料、学生名单、GitHub链接或论文全文。原始证据缓存不用于公开展示。；官方主页只有功率超声研究说明，未公开可核学位院校、起讫、职称、导师、履历和具体论文列表；相关字段保持空缺。；搜索出现HIT威海化工方向caolixin666及中科院物理研究所同名人员，学科/主页不符，未合并其教育、教授身份或论文。；未发现本人的学位答辩/论文委员会成员直接证据；committee_members为空，不代表不存在。；已读官方职业简介：哈尔滨工业大学电子与信息工程学院教师；研究功率超声工业应用、高功率超声系统及电子电路。 此简介不表示完整学历或任职履历。；已核公开职业事实稀疏，可结构化记录不等于完整详细履历；学历与任职未知项保持空缺。</x:v>
+      </x:c>
+      <x:c r="G127" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="64" customHeight="1">
+      <x:c r="A128" s="6" t="str">
+        <x:v>陈迪</x:v>
+      </x:c>
+      <x:c r="B128" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C128" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D128" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chendi</x:v>
+      </x:c>
+      <x:c r="E128" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F128" s="6" t="str">
+        <x:v>仅收录本次公开可核职业资料及精选书目元数据；未纳入私人联系方式、出生资料、学生名单、GitHub链接或论文全文。原始证据缓存不用于公开展示。；本科、硕士背景、博士专业与起讫、各阶段导师及历任工作未找到可靠直接公开证据。；官网说发表论文多篇但未提供题名列表；同名检索无法充分对人，故不猜填精选论文。；未发现本人的学位答辩/论文委员会成员直接证据；committee_members为空，不代表不存在。；已读官方职业简介：哈尔滨工业大学讲师、工学博士；研究信号处理、虚拟仿真及声音降噪。 此简介不表示完整学历或任职履历。；已核公开职业事实稀疏，可结构化记录不等于完整详细履历；学历与任职未知项保持空缺。</x:v>
+      </x:c>
+      <x:c r="G128" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="64" customHeight="1">
+      <x:c r="A129" s="6" t="str">
+        <x:v>李贤</x:v>
+      </x:c>
+      <x:c r="B129" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C129" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D129" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/XianLi</x:v>
+      </x:c>
+      <x:c r="E129" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F129" s="6" t="str">
+        <x:v>仅收录本次公开可核职业资料及精选书目元数据；未纳入私人联系方式、出生资料、学生名单、GitHub链接或论文全文。原始证据缓存不用于公开展示。；本科背景及硕博起始时间未找到直接证据。；根特留学条目括注Prof. Aleksandra Pizurica但未明确导师角色；谷延锋为团队负责人、丁明理为合著者均不足以建立导师边。；本人中文副研究员与英文Associate Professor口径不一致，未静默择一；其他教师团队页称博士后/硕导不覆盖本人当前博导简介。；中国博士后基金获资助不单独构成完整博士后任职起讫证据。；未发现本人的学位答辩/论文委员会成员直接证据；committee_members为空，不代表不存在。；已读官方职业简介：哈尔滨工业大学副研究员、博士生导师；研究低空高光谱与激光雷达探测、智能信息处理及深度学习。 此简介不表示完整学历或任职履历。</x:v>
+      </x:c>
+      <x:c r="G129" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="64" customHeight="1">
+      <x:c r="A130" s="6" t="str">
+        <x:v>李鹏</x:v>
+      </x:c>
+      <x:c r="B130" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C130" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D130" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lipeng</x:v>
+      </x:c>
+      <x:c r="E130" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F130" s="6" t="str">
+        <x:v>仅收录本次公开可核职业资料及精选书目元数据；未纳入私人联系方式、出生资料、学生名单、GitHub链接或论文全文。原始证据缓存不用于公开展示。；本科、博士开始日期、是否存在独立硕士学位、本科导师及副研究员起始时间未核定。；2024入选人才计划不等于明确2024副研究员任职起点；博士后基金资助不代替博士后任职证明。；未发现本人的学位答辩/论文委员会成员直接证据；committee_members为空，不代表不存在。；已读官方职业简介：哈尔滨工业大学副研究员、硕士生导师；研究可解释人工智能、多模态医学图像处理及多源遥感影像解译。 此简介不表示完整学历或任职履历。</x:v>
+      </x:c>
+      <x:c r="G130" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="64" customHeight="1">
+      <x:c r="A131" s="6" t="str">
+        <x:v>庄迪</x:v>
+      </x:c>
+      <x:c r="B131" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C131" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D131" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhuangdi</x:v>
+      </x:c>
+      <x:c r="E131" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F131" s="6" t="str">
+        <x:v>本科学位明确授予、硕士导师、博士后是否任职和导师未知；博士师承有直接表格证据。；本人主页正文空白，学历由官方教师页公开职业履历、毕业留校新闻及研究生院交叉核身份，不合并南开/南佛罗里达同英文名Di Zhuang。；博士后资助拟名单仅线索，本批不将拟资助视作已获资助或独立进站日期。；本批精选成果非完整论文库，缓存不公开。；本人主页是空模板；必要公开职业履历来自张腊梅官方教师页、毕业留校新闻与研究生院博士论文导师表交叉核验，仅保留庄迪本人事实，不发布其他学生名单。；硕士学习结束月份保留2020-07与旧栏目2020-06两值；获硕士证据不等同精确授位日期。；精选论文 PELNet: A General Physics-Embedded Learning Framework for Polarimetric Target Decomposition 的2026-12卷期晚于核验日；仅复用已审核Crossref元数据，不声称卷期已发行或出版社页面已读取。</x:v>
+      </x:c>
+      <x:c r="G131" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="64" customHeight="1">
+      <x:c r="A132" s="6" t="str">
+        <x:v>刘东洋</x:v>
+      </x:c>
+      <x:c r="B132" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C132" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D132" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liudongyang</x:v>
+      </x:c>
+      <x:c r="E132" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F132" s="6" t="str">
+        <x:v>本硕明确授位与全部学位专业未知；张钧萍仅共同作者和研究相关，不推定学位或博士后导师。；本批精选成果非完整论文库，缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G132" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="64" customHeight="1">
+      <x:c r="A133" s="6" t="str">
+        <x:v>李大森</x:v>
+      </x:c>
+      <x:c r="B133" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C133" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D133" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lidasen</x:v>
+      </x:c>
+      <x:c r="E133" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F133" s="6" t="str">
+        <x:v>本硕明确授位、各阶段导师未知；尹振东为合作作者与项目合作者，不由此推博士导师。；获博士后面上项目不自动证明进站起点、流动站名称或合作导师。；名录旧链接仅空页；补读同名同院系官方个人主页并保留两者实际读取记录。；本批精选成果非完整论文库，缓存不公开。；两篇Elsevier论文DOI候选仅第三方检索返回且DOI打开失败，未纳入已核主字段；MDPI落地429停止，不绕过。</x:v>
+      </x:c>
+      <x:c r="G133" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="64" customHeight="1">
+      <x:c r="A134" s="6" t="str">
+        <x:v>董喆</x:v>
+      </x:c>
+      <x:c r="B134" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C134" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D134" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+      <x:c r="E134" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F134" s="6" t="str">
+        <x:v>本硕明确授位、各阶段专业及导师未知，谷延锋团队负责人和共同作者不自动等同导师。；日期以官网截至2026.10实际列示记录，不从博士后岗位推第二博士学位。；本批精选成果非完整论文库，缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G134" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="64" customHeight="1">
+      <x:c r="A135" s="6" t="str">
+        <x:v>何胜阳</x:v>
+      </x:c>
+      <x:c r="B135" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C135" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D135" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/2024/0704/c19284a348197/page.htm</x:v>
+      </x:c>
+      <x:c r="E135" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F135" s="6" t="str">
+        <x:v>官方名录文章仅姓名，无个人学历正文；本硕博具体授位院校、日期和导师未知。；期刊官方检索摘录称博士、高级工程师，但文章页本次403，不据未能直接读取的正文补主学历。其他论文引用2013HIT博士论文仅是二手题录，未当授位证据。；不合并植物学同名院士或昆明理工大学同名学生。；本批精选成果非完整论文库，缓存不公开。；现有唯一已确认任职事实是2015-12-14校方教师新闻的历史快照；2026当前任职、职称和完整履历未核实，不从现名录或期刊搜索摘录补博士授位。；已核公开职业事实稀疏，可结构化记录不等于完整详细履历；学历与任职未知项保持空缺。</x:v>
+      </x:c>
+      <x:c r="G135" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="64" customHeight="1">
+      <x:c r="A136" s="6" t="str">
+        <x:v>吴龙文</x:v>
+      </x:c>
+      <x:c r="B136" s="6" t="str">
+        <x:v>哈尔滨</x:v>
+      </x:c>
+      <x:c r="C136" s="6" t="str">
+        <x:v>电子与信息工程学院·信息工程系</x:v>
+      </x:c>
+      <x:c r="D136" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wulongwen</x:v>
+      </x:c>
+      <x:c r="E136" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F136" s="6" t="str">
+        <x:v>学位导师均未找到直接角色说明；赵雅琴合著、团队内容不升级导师。；只取本人学历与精选成果，不复制学生栏目、政治面貌或联系资料。；本批精选成果非完整论文库，缓存不公开。</x:v>
+      </x:c>
+      <x:c r="G136" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d83160e97284dab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92a6b7a5e6e940ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40218,10 +40494,2288 @@
         <x:v>https://homepage.hit.edu.cn/gaoguoming</x:v>
       </x:c>
     </x:row>
+    <x:row r="927" ht="64" customHeight="1">
+      <x:c r="A927" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B927" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C927" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D927" s="6" t="str">
+        <x:v>中南大学</x:v>
+      </x:c>
+      <x:c r="E927" s="6" t="str"/>
+      <x:c r="F927" s="6" t="str">
+        <x:v>2014-06</x:v>
+      </x:c>
+      <x:c r="G927" s="6" t="str"/>
+      <x:c r="H927" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I927" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J927" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K927" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L927" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M927" s="7" t="str"/>
+      <x:c r="N927" s="6" t="str"/>
+      <x:c r="O927" s="6" t="str">
+        <x:v>官方英文简介明确obtained bachelor’s degree；开始时间与专业未披露。</x:v>
+      </x:c>
+      <x:c r="P927" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q927" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="928" ht="64" customHeight="1">
+      <x:c r="A928" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B928" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C928" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D928" s="6" t="str">
+        <x:v>浙江大学</x:v>
+      </x:c>
+      <x:c r="E928" s="6" t="str"/>
+      <x:c r="F928" s="6" t="str">
+        <x:v>2019-09</x:v>
+      </x:c>
+      <x:c r="G928" s="6" t="str"/>
+      <x:c r="H928" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I928" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J928" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K928" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L928" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M928" s="7" t="str"/>
+      <x:c r="N928" s="6" t="str"/>
+      <x:c r="O928" s="6" t="str">
+        <x:v>官方英文简介明确received PhD；开始时间与专业未披露。</x:v>
+      </x:c>
+      <x:c r="P928" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q928" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="929" ht="64" customHeight="1">
+      <x:c r="A929" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B929" s="6" t="str">
+        <x:v>postdoctoral_research</x:v>
+      </x:c>
+      <x:c r="C929" s="6" t="str"/>
+      <x:c r="D929" s="6" t="str">
+        <x:v>Nanyang Technological University</x:v>
+      </x:c>
+      <x:c r="E929" s="6" t="str">
+        <x:v>2019-11</x:v>
+      </x:c>
+      <x:c r="F929" s="6" t="str">
+        <x:v>2022-03</x:v>
+      </x:c>
+      <x:c r="G929" s="6" t="str"/>
+      <x:c r="H929" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="I929" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="J929" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K929" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L929" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M929" s="7" t="str"/>
+      <x:c r="N929" s="6" t="str"/>
+      <x:c r="O929" s="6" t="str">
+        <x:v>中文明确博士后，英文给Research Fellow任职月份；非新加坡授位事件。 事件类型：博士后研究（非授位）。</x:v>
+      </x:c>
+      <x:c r="P929" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q929" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="930" ht="64" customHeight="1">
+      <x:c r="A930" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B930" s="6" t="str">
+        <x:v>postdoctoral_research</x:v>
+      </x:c>
+      <x:c r="C930" s="6" t="str"/>
+      <x:c r="D930" s="6" t="str">
+        <x:v>Nanyang Technological University</x:v>
+      </x:c>
+      <x:c r="E930" s="6" t="str">
+        <x:v>2023-08</x:v>
+      </x:c>
+      <x:c r="F930" s="6" t="str">
+        <x:v>2024-03</x:v>
+      </x:c>
+      <x:c r="G930" s="6" t="str"/>
+      <x:c r="H930" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="I930" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="J930" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K930" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L930" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M930" s="7" t="str"/>
+      <x:c r="N930" s="6" t="str"/>
+      <x:c r="O930" s="6" t="str">
+        <x:v>中文明确博士后经历，英文给第二段Research Fellow月份；非新加坡授位事件。 事件类型：博士后研究（非授位）。</x:v>
+      </x:c>
+      <x:c r="P930" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q930" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="931" ht="64" customHeight="1">
+      <x:c r="A931" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B931" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C931" s="6" t="str">
+        <x:v>副教授</x:v>
+      </x:c>
+      <x:c r="D931" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E931" s="6" t="str"/>
+      <x:c r="F931" s="6" t="str"/>
+      <x:c r="G931" s="6" t="str"/>
+      <x:c r="H931" s="6" t="str"/>
+      <x:c r="I931" s="6" t="str"/>
+      <x:c r="J931" s="6" t="str"/>
+      <x:c r="K931" s="6" t="str"/>
+      <x:c r="L931" s="6" t="str"/>
+      <x:c r="M931" s="7" t="str"/>
+      <x:c r="N931" s="6" t="str"/>
+      <x:c r="O931" s="6" t="str">
+        <x:v>官网明确当前副教授；中文简介2024年加入团队不单独证明副教授晋升/起聘年份。</x:v>
+      </x:c>
+      <x:c r="P931" s="6" t="str"/>
+      <x:c r="Q931" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="932" ht="64" customHeight="1">
+      <x:c r="A932" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B932" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C932" s="6" t="str">
+        <x:v>加入研究团队</x:v>
+      </x:c>
+      <x:c r="D932" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院谷延锋团队</x:v>
+      </x:c>
+      <x:c r="E932" s="6" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="F932" s="6" t="str"/>
+      <x:c r="G932" s="6" t="str"/>
+      <x:c r="H932" s="6" t="str"/>
+      <x:c r="I932" s="6" t="str"/>
+      <x:c r="J932" s="6" t="str"/>
+      <x:c r="K932" s="6" t="str"/>
+      <x:c r="L932" s="6" t="str"/>
+      <x:c r="M932" s="7" t="str"/>
+      <x:c r="N932" s="6" t="str"/>
+      <x:c r="O932" s="6" t="str">
+        <x:v>中文简介明确2024年回国加入团队；不等同博士导师关系或副教授起聘日。</x:v>
+      </x:c>
+      <x:c r="P932" s="6" t="str"/>
+      <x:c r="Q932" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="933" ht="64" customHeight="1">
+      <x:c r="A933" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B933" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C933" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D933" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E933" s="6" t="str"/>
+      <x:c r="F933" s="6" t="str"/>
+      <x:c r="G933" s="6" t="str"/>
+      <x:c r="H933" s="6" t="str"/>
+      <x:c r="I933" s="6" t="str"/>
+      <x:c r="J933" s="6" t="str"/>
+      <x:c r="K933" s="6" t="str"/>
+      <x:c r="L933" s="6" t="str"/>
+      <x:c r="M933" s="7" t="str"/>
+      <x:c r="N933" s="6" t="str"/>
+      <x:c r="O933" s="6" t="str"/>
+      <x:c r="P933" s="6" t="str"/>
+      <x:c r="Q933" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="934" ht="64" customHeight="1">
+      <x:c r="A934" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B934" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C934" s="6" t="str">
+        <x:v>Research Fellow</x:v>
+      </x:c>
+      <x:c r="D934" s="6" t="str">
+        <x:v>Nanyang Technological University</x:v>
+      </x:c>
+      <x:c r="E934" s="6" t="str">
+        <x:v>2019-11</x:v>
+      </x:c>
+      <x:c r="F934" s="6" t="str">
+        <x:v>2022-03</x:v>
+      </x:c>
+      <x:c r="G934" s="6" t="str"/>
+      <x:c r="H934" s="6" t="str"/>
+      <x:c r="I934" s="6" t="str"/>
+      <x:c r="J934" s="6" t="str"/>
+      <x:c r="K934" s="6" t="str"/>
+      <x:c r="L934" s="6" t="str"/>
+      <x:c r="M934" s="7" t="str"/>
+      <x:c r="N934" s="6" t="str"/>
+      <x:c r="O934" s="6" t="str">
+        <x:v>英文About Me列精确月份；中文称博士后。working with不单独作为导师角色证据。</x:v>
+      </x:c>
+      <x:c r="P934" s="6" t="str"/>
+      <x:c r="Q934" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="935" ht="64" customHeight="1">
+      <x:c r="A935" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B935" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C935" s="6" t="str">
+        <x:v>Research Scientist</x:v>
+      </x:c>
+      <x:c r="D935" s="6" t="str">
+        <x:v>Mohamed bin Zayed University of Artificial Intelligence（MBZUAI）</x:v>
+      </x:c>
+      <x:c r="E935" s="6" t="str">
+        <x:v>2022-03</x:v>
+      </x:c>
+      <x:c r="F935" s="6" t="str">
+        <x:v>2023-07</x:v>
+      </x:c>
+      <x:c r="G935" s="6" t="str"/>
+      <x:c r="H935" s="6" t="str"/>
+      <x:c r="I935" s="6" t="str"/>
+      <x:c r="J935" s="6" t="str"/>
+      <x:c r="K935" s="6" t="str"/>
+      <x:c r="L935" s="6" t="str"/>
+      <x:c r="M935" s="7" t="str"/>
+      <x:c r="N935" s="6" t="str"/>
+      <x:c r="O935" s="6" t="str"/>
+      <x:c r="P935" s="6" t="str"/>
+      <x:c r="Q935" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="936" ht="64" customHeight="1">
+      <x:c r="A936" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B936" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C936" s="6" t="str">
+        <x:v>Research Fellow</x:v>
+      </x:c>
+      <x:c r="D936" s="6" t="str">
+        <x:v>Nanyang Technological University</x:v>
+      </x:c>
+      <x:c r="E936" s="6" t="str">
+        <x:v>2023-08</x:v>
+      </x:c>
+      <x:c r="F936" s="6" t="str">
+        <x:v>2024-03</x:v>
+      </x:c>
+      <x:c r="G936" s="6" t="str"/>
+      <x:c r="H936" s="6" t="str"/>
+      <x:c r="I936" s="6" t="str"/>
+      <x:c r="J936" s="6" t="str"/>
+      <x:c r="K936" s="6" t="str"/>
+      <x:c r="L936" s="6" t="str"/>
+      <x:c r="M936" s="7" t="str"/>
+      <x:c r="N936" s="6" t="str"/>
+      <x:c r="O936" s="6" t="str">
+        <x:v>英文About Me列精确月份；collaborating with Alex Kot不升级为导师关系。</x:v>
+      </x:c>
+      <x:c r="P936" s="6" t="str"/>
+      <x:c r="Q936" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="937" ht="64" customHeight="1">
+      <x:c r="A937" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B937" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C937" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D937" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E937" s="6" t="str">
+        <x:v>2010-09</x:v>
+      </x:c>
+      <x:c r="F937" s="6" t="str">
+        <x:v>2014-07</x:v>
+      </x:c>
+      <x:c r="G937" s="6" t="str">
+        <x:v>通信工程</x:v>
+      </x:c>
+      <x:c r="H937" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I937" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J937" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K937" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L937" s="6" t="str"/>
+      <x:c r="M937" s="7" t="str"/>
+      <x:c r="N937" s="6" t="str"/>
+      <x:c r="O937" s="6" t="str">
+        <x:v>教育经历列学士标签及区间，但未明确获得/授予，不以学历标签推断授位。</x:v>
+      </x:c>
+      <x:c r="P937" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q937" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="938" ht="64" customHeight="1">
+      <x:c r="A938" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B938" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C938" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D938" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E938" s="6" t="str">
+        <x:v>2014-09</x:v>
+      </x:c>
+      <x:c r="F938" s="6" t="str">
+        <x:v>2016-06</x:v>
+      </x:c>
+      <x:c r="G938" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H938" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I938" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J938" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K938" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L938" s="6" t="str"/>
+      <x:c r="M938" s="7" t="str"/>
+      <x:c r="N938" s="6" t="str"/>
+      <x:c r="O938" s="6" t="str">
+        <x:v>教育经历列硕士标签及区间，但未明确获得/授予。</x:v>
+      </x:c>
+      <x:c r="P938" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q938" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="939" ht="64" customHeight="1">
+      <x:c r="A939" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B939" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C939" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D939" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E939" s="6" t="str">
+        <x:v>2016-09</x:v>
+      </x:c>
+      <x:c r="F939" s="6" t="str">
+        <x:v>2022-12</x:v>
+      </x:c>
+      <x:c r="G939" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H939" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I939" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J939" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K939" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L939" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M939" s="7" t="str"/>
+      <x:c r="N939" s="6" t="str"/>
+      <x:c r="O939" s="6" t="str">
+        <x:v>基本信息明确本人持工学博士，教育经历给专业和起讫。</x:v>
+      </x:c>
+      <x:c r="P939" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q939" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="940" ht="64" customHeight="1">
+      <x:c r="A940" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B940" s="6" t="str">
+        <x:v>visiting_research</x:v>
+      </x:c>
+      <x:c r="C940" s="6" t="str"/>
+      <x:c r="D940" s="6" t="str">
+        <x:v>新加坡科学设计大学</x:v>
+      </x:c>
+      <x:c r="E940" s="6" t="str">
+        <x:v>2026-04</x:v>
+      </x:c>
+      <x:c r="F940" s="6" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="G940" s="6" t="str"/>
+      <x:c r="H940" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="I940" s="6" t="str">
+        <x:v>新加坡</x:v>
+      </x:c>
+      <x:c r="J940" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K940" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L940" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M940" s="7" t="str"/>
+      <x:c r="N940" s="6" t="str"/>
+      <x:c r="O940" s="6" t="str">
+        <x:v>工作经历中的访问学者，非授位；结束月份为未来计划。机构名称保留原文。 事件类型：访问研究（非授位）。</x:v>
+      </x:c>
+      <x:c r="P940" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q940" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="941" ht="64" customHeight="1">
+      <x:c r="A941" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B941" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C941" s="6" t="str">
+        <x:v>副研究员</x:v>
+      </x:c>
+      <x:c r="D941" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E941" s="6" t="str">
+        <x:v>2024-01</x:v>
+      </x:c>
+      <x:c r="F941" s="6" t="str"/>
+      <x:c r="G941" s="6" t="str"/>
+      <x:c r="H941" s="6" t="str"/>
+      <x:c r="I941" s="6" t="str"/>
+      <x:c r="J941" s="6" t="str"/>
+      <x:c r="K941" s="6" t="str"/>
+      <x:c r="L941" s="6" t="str"/>
+      <x:c r="M941" s="7" t="str"/>
+      <x:c r="N941" s="6" t="str"/>
+      <x:c r="O941" s="6" t="str">
+        <x:v>工作经历明确2024-01至今；2023入职不等于2023起即为副研究员。</x:v>
+      </x:c>
+      <x:c r="P941" s="6" t="str"/>
+      <x:c r="Q941" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="942" ht="64" customHeight="1">
+      <x:c r="A942" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B942" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C942" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D942" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E942" s="6" t="str"/>
+      <x:c r="F942" s="6" t="str"/>
+      <x:c r="G942" s="6" t="str"/>
+      <x:c r="H942" s="6" t="str"/>
+      <x:c r="I942" s="6" t="str"/>
+      <x:c r="J942" s="6" t="str"/>
+      <x:c r="K942" s="6" t="str"/>
+      <x:c r="L942" s="6" t="str"/>
+      <x:c r="M942" s="7" t="str"/>
+      <x:c r="N942" s="6" t="str"/>
+      <x:c r="O942" s="6" t="str"/>
+      <x:c r="P942" s="6" t="str"/>
+      <x:c r="Q942" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="943" ht="64" customHeight="1">
+      <x:c r="A943" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B943" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C943" s="6" t="str">
+        <x:v>助理研究员</x:v>
+      </x:c>
+      <x:c r="D943" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E943" s="6" t="str">
+        <x:v>2023-02</x:v>
+      </x:c>
+      <x:c r="F943" s="6" t="str">
+        <x:v>2024-01</x:v>
+      </x:c>
+      <x:c r="G943" s="6" t="str"/>
+      <x:c r="H943" s="6" t="str"/>
+      <x:c r="I943" s="6" t="str"/>
+      <x:c r="J943" s="6" t="str"/>
+      <x:c r="K943" s="6" t="str"/>
+      <x:c r="L943" s="6" t="str"/>
+      <x:c r="M943" s="7" t="str"/>
+      <x:c r="N943" s="6" t="str"/>
+      <x:c r="O943" s="6" t="str"/>
+      <x:c r="P943" s="6" t="str"/>
+      <x:c r="Q943" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="944" ht="64" customHeight="1">
+      <x:c r="A944" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B944" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C944" s="6" t="str">
+        <x:v>访问学者</x:v>
+      </x:c>
+      <x:c r="D944" s="6" t="str">
+        <x:v>新加坡科学设计大学</x:v>
+      </x:c>
+      <x:c r="E944" s="6" t="str">
+        <x:v>2026-04</x:v>
+      </x:c>
+      <x:c r="F944" s="6" t="str">
+        <x:v>2026-12</x:v>
+      </x:c>
+      <x:c r="G944" s="6" t="str"/>
+      <x:c r="H944" s="6" t="str"/>
+      <x:c r="I944" s="6" t="str"/>
+      <x:c r="J944" s="6" t="str"/>
+      <x:c r="K944" s="6" t="str"/>
+      <x:c r="L944" s="6" t="str"/>
+      <x:c r="M944" s="7" t="str"/>
+      <x:c r="N944" s="6" t="str"/>
+      <x:c r="O944" s="6" t="str">
+        <x:v>保留官网中文机构原文，未擅自改为另一校名；2026-12为页面计划结束时间，检索日仍未来，不声称已完成。</x:v>
+      </x:c>
+      <x:c r="P944" s="6" t="str"/>
+      <x:c r="Q944" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="945" ht="64" customHeight="1">
+      <x:c r="A945" s="6" t="str">
+        <x:v>曹立新</x:v>
+      </x:c>
+      <x:c r="B945" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C945" s="6" t="str"/>
+      <x:c r="D945" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E945" s="6" t="str"/>
+      <x:c r="F945" s="6" t="str"/>
+      <x:c r="G945" s="6" t="str"/>
+      <x:c r="H945" s="6" t="str"/>
+      <x:c r="I945" s="6" t="str"/>
+      <x:c r="J945" s="6" t="str"/>
+      <x:c r="K945" s="6" t="str"/>
+      <x:c r="L945" s="6" t="str"/>
+      <x:c r="M945" s="7" t="str"/>
+      <x:c r="N945" s="6" t="str"/>
+      <x:c r="O945" s="6" t="str">
+        <x:v>主页页头仅明确目前就职学院，未披露职称。</x:v>
+      </x:c>
+      <x:c r="P945" s="6" t="str"/>
+      <x:c r="Q945" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/caolixin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="946" ht="64" customHeight="1">
+      <x:c r="A946" s="6" t="str">
+        <x:v>陈迪</x:v>
+      </x:c>
+      <x:c r="B946" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C946" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D946" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E946" s="6" t="str"/>
+      <x:c r="F946" s="6" t="str"/>
+      <x:c r="G946" s="6" t="str"/>
+      <x:c r="H946" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I946" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J946" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K946" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L946" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M946" s="7" t="str"/>
+      <x:c r="N946" s="6" t="str"/>
+      <x:c r="O946" s="6" t="str">
+        <x:v>官网明确毕业于哈尔滨工业大学、工学博士；专业和起讫未披露。</x:v>
+      </x:c>
+      <x:c r="P946" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q946" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chendi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="947" ht="64" customHeight="1">
+      <x:c r="A947" s="6" t="str">
+        <x:v>陈迪</x:v>
+      </x:c>
+      <x:c r="B947" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C947" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D947" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E947" s="6" t="str"/>
+      <x:c r="F947" s="6" t="str"/>
+      <x:c r="G947" s="6" t="str"/>
+      <x:c r="H947" s="6" t="str"/>
+      <x:c r="I947" s="6" t="str"/>
+      <x:c r="J947" s="6" t="str"/>
+      <x:c r="K947" s="6" t="str"/>
+      <x:c r="L947" s="6" t="str"/>
+      <x:c r="M947" s="7" t="str"/>
+      <x:c r="N947" s="6" t="str"/>
+      <x:c r="O947" s="6" t="str"/>
+      <x:c r="P947" s="6" t="str"/>
+      <x:c r="Q947" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chendi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="948" ht="64" customHeight="1">
+      <x:c r="A948" s="6" t="str">
+        <x:v>李贤</x:v>
+      </x:c>
+      <x:c r="B948" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C948" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D948" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E948" s="6" t="str"/>
+      <x:c r="F948" s="6" t="str">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="G948" s="6" t="str"/>
+      <x:c r="H948" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I948" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J948" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K948" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L948" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M948" s="7" t="str"/>
+      <x:c r="N948" s="6" t="str"/>
+      <x:c r="O948" s="6" t="str">
+        <x:v>作者简介明确received M.S. degree；开始日期与硕士专业未披露。题名、作者及博士/根特经历与本人官网交叉吻合。</x:v>
+      </x:c>
+      <x:c r="P948" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q948" s="6" t="str">
+        <x:v>https://gaim.ugent.be/media/preprint/8638075.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="949" ht="64" customHeight="1">
+      <x:c r="A949" s="6" t="str">
+        <x:v>李贤</x:v>
+      </x:c>
+      <x:c r="B949" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C949" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D949" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E949" s="6" t="str"/>
+      <x:c r="F949" s="6" t="str">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="G949" s="6" t="str">
+        <x:v>仪器科学与技术</x:v>
+      </x:c>
+      <x:c r="H949" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I949" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J949" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K949" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L949" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M949" s="7" t="str"/>
+      <x:c r="N949" s="6" t="str"/>
+      <x:c r="O949" s="6" t="str">
+        <x:v>英文简介明确obtained Ph.D. degree in Instrument Science and Technology from HIT in 2021。</x:v>
+      </x:c>
+      <x:c r="P949" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q949" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/XianLi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="950" ht="64" customHeight="1">
+      <x:c r="A950" s="6" t="str">
+        <x:v>李贤</x:v>
+      </x:c>
+      <x:c r="B950" s="6" t="str">
+        <x:v>visiting_doctoral_research</x:v>
+      </x:c>
+      <x:c r="C950" s="6" t="str"/>
+      <x:c r="D950" s="6" t="str">
+        <x:v>Ghent University</x:v>
+      </x:c>
+      <x:c r="E950" s="6" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="F950" s="6" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="G950" s="6" t="str"/>
+      <x:c r="H950" s="6" t="str">
+        <x:v>比利时</x:v>
+      </x:c>
+      <x:c r="I950" s="6" t="str">
+        <x:v>比利时</x:v>
+      </x:c>
+      <x:c r="J950" s="6" t="str">
+        <x:v>欧洲</x:v>
+      </x:c>
+      <x:c r="K950" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L950" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M950" s="7" t="str"/>
+      <x:c r="N950" s="6" t="str"/>
+      <x:c r="O950" s="6" t="str">
+        <x:v>官方英文明确doctoral research，CSC资助；学位授予机构另为HIT，不将比利时访问博士研究当作比利时学位。 事件类型：博士阶段访问研究（非授位）。</x:v>
+      </x:c>
+      <x:c r="P950" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q950" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/XianLi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="951" ht="64" customHeight="1">
+      <x:c r="A951" s="6" t="str">
+        <x:v>李贤</x:v>
+      </x:c>
+      <x:c r="B951" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C951" s="6" t="str">
+        <x:v>副研究员</x:v>
+      </x:c>
+      <x:c r="D951" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E951" s="6" t="str"/>
+      <x:c r="F951" s="6" t="str"/>
+      <x:c r="G951" s="6" t="str"/>
+      <x:c r="H951" s="6" t="str"/>
+      <x:c r="I951" s="6" t="str"/>
+      <x:c r="J951" s="6" t="str"/>
+      <x:c r="K951" s="6" t="str"/>
+      <x:c r="L951" s="6" t="str"/>
+      <x:c r="M951" s="7" t="str"/>
+      <x:c r="N951" s="6" t="str"/>
+      <x:c r="O951" s="6" t="str">
+        <x:v>中文本人简介职称；英文Associate Professor并列保存，不能静默将二者视为同一中文职称。</x:v>
+      </x:c>
+      <x:c r="P951" s="6" t="str"/>
+      <x:c r="Q951" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/XianLi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="952" ht="64" customHeight="1">
+      <x:c r="A952" s="6" t="str">
+        <x:v>李贤</x:v>
+      </x:c>
+      <x:c r="B952" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C952" s="6" t="str">
+        <x:v>博士生导师</x:v>
+      </x:c>
+      <x:c r="D952" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E952" s="6" t="str"/>
+      <x:c r="F952" s="6" t="str"/>
+      <x:c r="G952" s="6" t="str"/>
+      <x:c r="H952" s="6" t="str"/>
+      <x:c r="I952" s="6" t="str"/>
+      <x:c r="J952" s="6" t="str"/>
+      <x:c r="K952" s="6" t="str"/>
+      <x:c r="L952" s="6" t="str"/>
+      <x:c r="M952" s="7" t="str"/>
+      <x:c r="N952" s="6" t="str"/>
+      <x:c r="O952" s="6" t="str"/>
+      <x:c r="P952" s="6" t="str"/>
+      <x:c r="Q952" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/XianLi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="953" ht="64" customHeight="1">
+      <x:c r="A953" s="6" t="str">
+        <x:v>李贤</x:v>
+      </x:c>
+      <x:c r="B953" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C953" s="6" t="str">
+        <x:v>Associate Professor</x:v>
+      </x:c>
+      <x:c r="D953" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E953" s="6" t="str"/>
+      <x:c r="F953" s="6" t="str"/>
+      <x:c r="G953" s="6" t="str"/>
+      <x:c r="H953" s="6" t="str"/>
+      <x:c r="I953" s="6" t="str"/>
+      <x:c r="J953" s="6" t="str"/>
+      <x:c r="K953" s="6" t="str"/>
+      <x:c r="L953" s="6" t="str"/>
+      <x:c r="M953" s="7" t="str"/>
+      <x:c r="N953" s="6" t="str"/>
+      <x:c r="O953" s="6" t="str">
+        <x:v>英文Basic Information原词；与中文副研究员存在翻译/职称口径差异，两者并列，不擅自覆盖。</x:v>
+      </x:c>
+      <x:c r="P953" s="6" t="str"/>
+      <x:c r="Q953" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/XianLi</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="954" ht="64" customHeight="1">
+      <x:c r="A954" s="6" t="str">
+        <x:v>李鹏</x:v>
+      </x:c>
+      <x:c r="B954" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C954" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D954" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E954" s="6" t="str"/>
+      <x:c r="F954" s="6" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="G954" s="6" t="str">
+        <x:v>电子信息工程</x:v>
+      </x:c>
+      <x:c r="H954" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I954" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J954" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K954" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L954" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M954" s="7" t="str"/>
+      <x:c r="N954" s="6" t="str"/>
+      <x:c r="O954" s="6" t="str">
+        <x:v>中文明确获学士学位；开始日期未披露。</x:v>
+      </x:c>
+      <x:c r="P954" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q954" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lipeng</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="955" ht="64" customHeight="1">
+      <x:c r="A955" s="6" t="str">
+        <x:v>李鹏</x:v>
+      </x:c>
+      <x:c r="B955" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C955" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D955" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E955" s="6" t="str"/>
+      <x:c r="F955" s="6" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="G955" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H955" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I955" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J955" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K955" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L955" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M955" s="7" t="str"/>
+      <x:c r="N955" s="6" t="str"/>
+      <x:c r="O955" s="6" t="str">
+        <x:v>中文明确获博士学位；未从2019学士年份倒推博士开始时间。</x:v>
+      </x:c>
+      <x:c r="P955" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；授位与非授位经历分开。</x:v>
+      </x:c>
+      <x:c r="Q955" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lipeng</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="956" ht="64" customHeight="1">
+      <x:c r="A956" s="6" t="str">
+        <x:v>李鹏</x:v>
+      </x:c>
+      <x:c r="B956" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C956" s="6" t="str">
+        <x:v>副研究员</x:v>
+      </x:c>
+      <x:c r="D956" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E956" s="6" t="str"/>
+      <x:c r="F956" s="6" t="str"/>
+      <x:c r="G956" s="6" t="str"/>
+      <x:c r="H956" s="6" t="str"/>
+      <x:c r="I956" s="6" t="str"/>
+      <x:c r="J956" s="6" t="str"/>
+      <x:c r="K956" s="6" t="str"/>
+      <x:c r="L956" s="6" t="str"/>
+      <x:c r="M956" s="7" t="str"/>
+      <x:c r="N956" s="6" t="str"/>
+      <x:c r="O956" s="6" t="str"/>
+      <x:c r="P956" s="6" t="str"/>
+      <x:c r="Q956" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lipeng</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="957" ht="64" customHeight="1">
+      <x:c r="A957" s="6" t="str">
+        <x:v>李鹏</x:v>
+      </x:c>
+      <x:c r="B957" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C957" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D957" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E957" s="6" t="str"/>
+      <x:c r="F957" s="6" t="str"/>
+      <x:c r="G957" s="6" t="str"/>
+      <x:c r="H957" s="6" t="str"/>
+      <x:c r="I957" s="6" t="str"/>
+      <x:c r="J957" s="6" t="str"/>
+      <x:c r="K957" s="6" t="str"/>
+      <x:c r="L957" s="6" t="str"/>
+      <x:c r="M957" s="7" t="str"/>
+      <x:c r="N957" s="6" t="str"/>
+      <x:c r="O957" s="6" t="str"/>
+      <x:c r="P957" s="6" t="str"/>
+      <x:c r="Q957" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lipeng</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="958" ht="64" customHeight="1">
+      <x:c r="A958" s="6" t="str">
+        <x:v>庄迪</x:v>
+      </x:c>
+      <x:c r="B958" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C958" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D958" s="6" t="str">
+        <x:v>哈尔滨工业大学（威海）</x:v>
+      </x:c>
+      <x:c r="E958" s="6" t="str">
+        <x:v>2014-09</x:v>
+      </x:c>
+      <x:c r="F958" s="6" t="str">
+        <x:v>2018-06</x:v>
+      </x:c>
+      <x:c r="G958" s="6" t="str">
+        <x:v>电子信息工程</x:v>
+      </x:c>
+      <x:c r="H958" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I958" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J958" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K958" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L958" s="6" t="str"/>
+      <x:c r="M958" s="7" t="str"/>
+      <x:c r="N958" s="6" t="str"/>
+      <x:c r="O958" s="6" t="str">
+        <x:v>张腊梅官网中的庄迪公开学术履历有本科标签，无明确学士授予声明；仅提取职业学历事实，不复制私人信息。</x:v>
+      </x:c>
+      <x:c r="P958" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q958" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="959" ht="64" customHeight="1">
+      <x:c r="A959" s="6" t="str">
+        <x:v>庄迪</x:v>
+      </x:c>
+      <x:c r="B959" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C959" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D959" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E959" s="6" t="str">
+        <x:v>2018-09</x:v>
+      </x:c>
+      <x:c r="F959" s="6" t="str">
+        <x:v>2020-07</x:v>
+      </x:c>
+      <x:c r="G959" s="6" t="str">
+        <x:v>电子与通信工程</x:v>
+      </x:c>
+      <x:c r="H959" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I959" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J959" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K959" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L959" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M959" s="7" t="str"/>
+      <x:c r="N959" s="6" t="str"/>
+      <x:c r="O959" s="6" t="str">
+        <x:v>最新博士栏目履历硕士止2020.07，课题组2020.07新闻明确获硕士；旧2018级硕士栏目止2020.06，两个结束月份保留，不作为精确授位日。</x:v>
+      </x:c>
+      <x:c r="P959" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q959" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="960" ht="64" customHeight="1">
+      <x:c r="A960" s="6" t="str">
+        <x:v>庄迪</x:v>
+      </x:c>
+      <x:c r="B960" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C960" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D960" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E960" s="6" t="str">
+        <x:v>2020-09</x:v>
+      </x:c>
+      <x:c r="F960" s="6" t="str">
+        <x:v>2025-03</x:v>
+      </x:c>
+      <x:c r="G960" s="6" t="str">
+        <x:v>信息与通信工程</x:v>
+      </x:c>
+      <x:c r="H960" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I960" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J960" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K960" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L960" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M960" s="7" t="str"/>
+      <x:c r="N960" s="6" t="str"/>
+      <x:c r="O960" s="6" t="str">
+        <x:v>张腊梅官方页202503明确博士毕业、欢迎庄迪博士留校任教；博士公开履历给2020.9–2025.3，研究生院博士论文表核学科及导师。</x:v>
+      </x:c>
+      <x:c r="P960" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q960" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="961" ht="64" customHeight="1">
+      <x:c r="A961" s="6" t="str">
+        <x:v>庄迪</x:v>
+      </x:c>
+      <x:c r="B961" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C961" s="6" t="str">
+        <x:v>教师（具体职称未披露）</x:v>
+      </x:c>
+      <x:c r="D961" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E961" s="6" t="str">
+        <x:v>2025-03</x:v>
+      </x:c>
+      <x:c r="F961" s="6" t="str"/>
+      <x:c r="G961" s="6" t="str"/>
+      <x:c r="H961" s="6" t="str"/>
+      <x:c r="I961" s="6" t="str"/>
+      <x:c r="J961" s="6" t="str"/>
+      <x:c r="K961" s="6" t="str"/>
+      <x:c r="L961" s="6" t="str"/>
+      <x:c r="M961" s="7" t="str"/>
+      <x:c r="N961" s="6" t="str"/>
+      <x:c r="O961" s="6" t="str">
+        <x:v>官方组内新闻明确2025.03博士毕业留校任教，未推断其具体职称或博士后身份。</x:v>
+      </x:c>
+      <x:c r="P961" s="6" t="str"/>
+      <x:c r="Q961" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="962" ht="64" customHeight="1">
+      <x:c r="A962" s="6" t="str">
+        <x:v>刘东洋</x:v>
+      </x:c>
+      <x:c r="B962" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C962" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D962" s="6" t="str">
+        <x:v>哈尔滨理工大学</x:v>
+      </x:c>
+      <x:c r="E962" s="6" t="str">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="F962" s="6" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="G962" s="6" t="str"/>
+      <x:c r="H962" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I962" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J962" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K962" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L962" s="6" t="str"/>
+      <x:c r="M962" s="7" t="str"/>
+      <x:c r="N962" s="6" t="str"/>
+      <x:c r="O962" s="6" t="str"/>
+      <x:c r="P962" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q962" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liudongyang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="963" ht="64" customHeight="1">
+      <x:c r="A963" s="6" t="str">
+        <x:v>刘东洋</x:v>
+      </x:c>
+      <x:c r="B963" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C963" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D963" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E963" s="6" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="F963" s="6" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="G963" s="6" t="str"/>
+      <x:c r="H963" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I963" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J963" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K963" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L963" s="6" t="str"/>
+      <x:c r="M963" s="7" t="str"/>
+      <x:c r="N963" s="6" t="str"/>
+      <x:c r="O963" s="6" t="str"/>
+      <x:c r="P963" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q963" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liudongyang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="964" ht="64" customHeight="1">
+      <x:c r="A964" s="6" t="str">
+        <x:v>刘东洋</x:v>
+      </x:c>
+      <x:c r="B964" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C964" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D964" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E964" s="6" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="F964" s="6" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="G964" s="6" t="str"/>
+      <x:c r="H964" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I964" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J964" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K964" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L964" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M964" s="7" t="str"/>
+      <x:c r="N964" s="6" t="str"/>
+      <x:c r="O964" s="6" t="str">
+        <x:v>本人简介明确工学博士，具体专业未披露。</x:v>
+      </x:c>
+      <x:c r="P964" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q964" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liudongyang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="965" ht="64" customHeight="1">
+      <x:c r="A965" s="6" t="str">
+        <x:v>刘东洋</x:v>
+      </x:c>
+      <x:c r="B965" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="C965" s="6" t="str"/>
+      <x:c r="D965" s="6" t="str">
+        <x:v>哈尔滨工业大学航天学院</x:v>
+      </x:c>
+      <x:c r="E965" s="6" t="str">
+        <x:v>2025-03</x:v>
+      </x:c>
+      <x:c r="F965" s="6" t="str"/>
+      <x:c r="G965" s="6" t="str"/>
+      <x:c r="H965" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I965" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J965" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K965" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L965" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M965" s="7" t="str"/>
+      <x:c r="N965" s="6" t="str"/>
+      <x:c r="O965" s="6" t="str">
+        <x:v>事件类型：博士后研究（非授位）。</x:v>
+      </x:c>
+      <x:c r="P965" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q965" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liudongyang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="966" ht="64" customHeight="1">
+      <x:c r="A966" s="6" t="str">
+        <x:v>刘东洋</x:v>
+      </x:c>
+      <x:c r="B966" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C966" s="6" t="str">
+        <x:v>助理研究员</x:v>
+      </x:c>
+      <x:c r="D966" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E966" s="6" t="str">
+        <x:v>2025-03</x:v>
+      </x:c>
+      <x:c r="F966" s="6" t="str"/>
+      <x:c r="G966" s="6" t="str"/>
+      <x:c r="H966" s="6" t="str"/>
+      <x:c r="I966" s="6" t="str"/>
+      <x:c r="J966" s="6" t="str"/>
+      <x:c r="K966" s="6" t="str"/>
+      <x:c r="L966" s="6" t="str"/>
+      <x:c r="M966" s="7" t="str"/>
+      <x:c r="N966" s="6" t="str"/>
+      <x:c r="O966" s="6" t="str"/>
+      <x:c r="P966" s="6" t="str"/>
+      <x:c r="Q966" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liudongyang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="967" ht="64" customHeight="1">
+      <x:c r="A967" s="6" t="str">
+        <x:v>刘东洋</x:v>
+      </x:c>
+      <x:c r="B967" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C967" s="6" t="str">
+        <x:v>博士后</x:v>
+      </x:c>
+      <x:c r="D967" s="6" t="str">
+        <x:v>哈尔滨工业大学航天学院</x:v>
+      </x:c>
+      <x:c r="E967" s="6" t="str">
+        <x:v>2025-03</x:v>
+      </x:c>
+      <x:c r="F967" s="6" t="str"/>
+      <x:c r="G967" s="6" t="str"/>
+      <x:c r="H967" s="6" t="str"/>
+      <x:c r="I967" s="6" t="str"/>
+      <x:c r="J967" s="6" t="str"/>
+      <x:c r="K967" s="6" t="str"/>
+      <x:c r="L967" s="6" t="str"/>
+      <x:c r="M967" s="7" t="str"/>
+      <x:c r="N967" s="6" t="str"/>
+      <x:c r="O967" s="6" t="str"/>
+      <x:c r="P967" s="6" t="str"/>
+      <x:c r="Q967" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liudongyang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="968" ht="64" customHeight="1">
+      <x:c r="A968" s="6" t="str">
+        <x:v>刘东洋</x:v>
+      </x:c>
+      <x:c r="B968" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C968" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D968" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E968" s="6" t="str"/>
+      <x:c r="F968" s="6" t="str"/>
+      <x:c r="G968" s="6" t="str"/>
+      <x:c r="H968" s="6" t="str"/>
+      <x:c r="I968" s="6" t="str"/>
+      <x:c r="J968" s="6" t="str"/>
+      <x:c r="K968" s="6" t="str"/>
+      <x:c r="L968" s="6" t="str"/>
+      <x:c r="M968" s="7" t="str"/>
+      <x:c r="N968" s="6" t="str"/>
+      <x:c r="O968" s="6" t="str"/>
+      <x:c r="P968" s="6" t="str"/>
+      <x:c r="Q968" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liudongyang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="969" ht="64" customHeight="1">
+      <x:c r="A969" s="6" t="str">
+        <x:v>李大森</x:v>
+      </x:c>
+      <x:c r="B969" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C969" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D969" s="6" t="str">
+        <x:v>哈尔滨工业大学（威海）</x:v>
+      </x:c>
+      <x:c r="E969" s="6" t="str">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="F969" s="6" t="str">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="G969" s="6" t="str">
+        <x:v>通信工程</x:v>
+      </x:c>
+      <x:c r="H969" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I969" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J969" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K969" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L969" s="6" t="str"/>
+      <x:c r="M969" s="7" t="str"/>
+      <x:c r="N969" s="6" t="str"/>
+      <x:c r="O969" s="6" t="str"/>
+      <x:c r="P969" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q969" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lidasen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="970" ht="64" customHeight="1">
+      <x:c r="A970" s="6" t="str">
+        <x:v>李大森</x:v>
+      </x:c>
+      <x:c r="B970" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C970" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D970" s="6" t="str">
+        <x:v>华南理工大学</x:v>
+      </x:c>
+      <x:c r="E970" s="6" t="str">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="F970" s="6" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="G970" s="6" t="str">
+        <x:v>计算机</x:v>
+      </x:c>
+      <x:c r="H970" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I970" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J970" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K970" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L970" s="6" t="str"/>
+      <x:c r="M970" s="7" t="str"/>
+      <x:c r="N970" s="6" t="str"/>
+      <x:c r="O970" s="6" t="str">
+        <x:v>专业按官网笼统计算机保留，不扩写成具体二级学科。</x:v>
+      </x:c>
+      <x:c r="P970" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q970" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lidasen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="971" ht="64" customHeight="1">
+      <x:c r="A971" s="6" t="str">
+        <x:v>李大森</x:v>
+      </x:c>
+      <x:c r="B971" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C971" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D971" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E971" s="6" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="F971" s="6" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="G971" s="6" t="str">
+        <x:v>先进制造</x:v>
+      </x:c>
+      <x:c r="H971" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I971" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J971" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K971" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L971" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M971" s="7" t="str"/>
+      <x:c r="N971" s="6" t="str"/>
+      <x:c r="O971" s="6" t="str">
+        <x:v>本人简介明确博士学位；不将其他论文作者所属电信学院替代本人学位专业先进制造。</x:v>
+      </x:c>
+      <x:c r="P971" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q971" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lidasen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="972" ht="64" customHeight="1">
+      <x:c r="A972" s="6" t="str">
+        <x:v>李大森</x:v>
+      </x:c>
+      <x:c r="B972" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C972" s="6" t="str">
+        <x:v>助理研究员</x:v>
+      </x:c>
+      <x:c r="D972" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E972" s="6" t="str">
+        <x:v>2025-07</x:v>
+      </x:c>
+      <x:c r="F972" s="6" t="str"/>
+      <x:c r="G972" s="6" t="str"/>
+      <x:c r="H972" s="6" t="str"/>
+      <x:c r="I972" s="6" t="str"/>
+      <x:c r="J972" s="6" t="str"/>
+      <x:c r="K972" s="6" t="str"/>
+      <x:c r="L972" s="6" t="str"/>
+      <x:c r="M972" s="7" t="str"/>
+      <x:c r="N972" s="6" t="str"/>
+      <x:c r="O972" s="6" t="str"/>
+      <x:c r="P972" s="6" t="str"/>
+      <x:c r="Q972" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lidasen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="973" ht="64" customHeight="1">
+      <x:c r="A973" s="6" t="str">
+        <x:v>董喆</x:v>
+      </x:c>
+      <x:c r="B973" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C973" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D973" s="6" t="str">
+        <x:v>中南大学</x:v>
+      </x:c>
+      <x:c r="E973" s="6" t="str">
+        <x:v>2015-09</x:v>
+      </x:c>
+      <x:c r="F973" s="6" t="str">
+        <x:v>2019-06</x:v>
+      </x:c>
+      <x:c r="G973" s="6" t="str"/>
+      <x:c r="H973" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I973" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J973" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K973" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L973" s="6" t="str"/>
+      <x:c r="M973" s="7" t="str"/>
+      <x:c r="N973" s="6" t="str"/>
+      <x:c r="O973" s="6" t="str">
+        <x:v>来源为化学化工学院，不等于确定具体专业。</x:v>
+      </x:c>
+      <x:c r="P973" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q973" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="974" ht="64" customHeight="1">
+      <x:c r="A974" s="6" t="str">
+        <x:v>董喆</x:v>
+      </x:c>
+      <x:c r="B974" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C974" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D974" s="6" t="str">
+        <x:v>哈尔滨工程大学</x:v>
+      </x:c>
+      <x:c r="E974" s="6" t="str">
+        <x:v>2019-09</x:v>
+      </x:c>
+      <x:c r="F974" s="6" t="str">
+        <x:v>2022-04</x:v>
+      </x:c>
+      <x:c r="G974" s="6" t="str"/>
+      <x:c r="H974" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I974" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J974" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K974" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L974" s="6" t="str"/>
+      <x:c r="M974" s="7" t="str"/>
+      <x:c r="N974" s="6" t="str"/>
+      <x:c r="O974" s="6" t="str">
+        <x:v>来源为计算机科学与技术学院，具体专业未知。</x:v>
+      </x:c>
+      <x:c r="P974" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q974" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="975" ht="64" customHeight="1">
+      <x:c r="A975" s="6" t="str">
+        <x:v>董喆</x:v>
+      </x:c>
+      <x:c r="B975" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C975" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D975" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E975" s="6" t="str">
+        <x:v>2022-09</x:v>
+      </x:c>
+      <x:c r="F975" s="6" t="str">
+        <x:v>2026-04</x:v>
+      </x:c>
+      <x:c r="G975" s="6" t="str"/>
+      <x:c r="H975" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I975" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J975" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K975" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L975" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M975" s="7" t="str"/>
+      <x:c r="N975" s="6" t="str"/>
+      <x:c r="O975" s="6" t="str">
+        <x:v>本人中英文简介明确工学博士/Dr，学位专业未单列。</x:v>
+      </x:c>
+      <x:c r="P975" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q975" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="976" ht="64" customHeight="1">
+      <x:c r="A976" s="6" t="str">
+        <x:v>董喆</x:v>
+      </x:c>
+      <x:c r="B976" s="6" t="str">
+        <x:v>postdoctoral</x:v>
+      </x:c>
+      <x:c r="C976" s="6" t="str"/>
+      <x:c r="D976" s="6" t="str">
+        <x:v>哈尔滨工业大学计算学部博士后流动站</x:v>
+      </x:c>
+      <x:c r="E976" s="6" t="str">
+        <x:v>2026-05</x:v>
+      </x:c>
+      <x:c r="F976" s="6" t="str"/>
+      <x:c r="G976" s="6" t="str"/>
+      <x:c r="H976" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I976" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J976" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K976" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L976" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M976" s="7" t="str"/>
+      <x:c r="N976" s="6" t="str"/>
+      <x:c r="O976" s="6" t="str">
+        <x:v>事件类型：博士后研究（非授位）。</x:v>
+      </x:c>
+      <x:c r="P976" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q976" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="977" ht="64" customHeight="1">
+      <x:c r="A977" s="6" t="str">
+        <x:v>董喆</x:v>
+      </x:c>
+      <x:c r="B977" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C977" s="6" t="str">
+        <x:v>副研究员</x:v>
+      </x:c>
+      <x:c r="D977" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E977" s="6" t="str">
+        <x:v>2026-05</x:v>
+      </x:c>
+      <x:c r="F977" s="6" t="str"/>
+      <x:c r="G977" s="6" t="str"/>
+      <x:c r="H977" s="6" t="str"/>
+      <x:c r="I977" s="6" t="str"/>
+      <x:c r="J977" s="6" t="str"/>
+      <x:c r="K977" s="6" t="str"/>
+      <x:c r="L977" s="6" t="str"/>
+      <x:c r="M977" s="7" t="str"/>
+      <x:c r="N977" s="6" t="str"/>
+      <x:c r="O977" s="6" t="str"/>
+      <x:c r="P977" s="6" t="str"/>
+      <x:c r="Q977" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="978" ht="64" customHeight="1">
+      <x:c r="A978" s="6" t="str">
+        <x:v>董喆</x:v>
+      </x:c>
+      <x:c r="B978" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C978" s="6" t="str">
+        <x:v>博士后</x:v>
+      </x:c>
+      <x:c r="D978" s="6" t="str">
+        <x:v>哈尔滨工业大学计算学部博士后流动站</x:v>
+      </x:c>
+      <x:c r="E978" s="6" t="str">
+        <x:v>2026-05</x:v>
+      </x:c>
+      <x:c r="F978" s="6" t="str"/>
+      <x:c r="G978" s="6" t="str"/>
+      <x:c r="H978" s="6" t="str"/>
+      <x:c r="I978" s="6" t="str"/>
+      <x:c r="J978" s="6" t="str"/>
+      <x:c r="K978" s="6" t="str"/>
+      <x:c r="L978" s="6" t="str"/>
+      <x:c r="M978" s="7" t="str"/>
+      <x:c r="N978" s="6" t="str"/>
+      <x:c r="O978" s="6" t="str"/>
+      <x:c r="P978" s="6" t="str"/>
+      <x:c r="Q978" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="979" ht="64" customHeight="1">
+      <x:c r="A979" s="6" t="str">
+        <x:v>董喆</x:v>
+      </x:c>
+      <x:c r="B979" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C979" s="6" t="str">
+        <x:v>硕士生导师</x:v>
+      </x:c>
+      <x:c r="D979" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E979" s="6" t="str">
+        <x:v>2026-09</x:v>
+      </x:c>
+      <x:c r="F979" s="6" t="str"/>
+      <x:c r="G979" s="6" t="str"/>
+      <x:c r="H979" s="6" t="str"/>
+      <x:c r="I979" s="6" t="str"/>
+      <x:c r="J979" s="6" t="str"/>
+      <x:c r="K979" s="6" t="str"/>
+      <x:c r="L979" s="6" t="str"/>
+      <x:c r="M979" s="7" t="str"/>
+      <x:c r="N979" s="6" t="str"/>
+      <x:c r="O979" s="6" t="str"/>
+      <x:c r="P979" s="6" t="str"/>
+      <x:c r="Q979" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="980" ht="64" customHeight="1">
+      <x:c r="A980" s="6" t="str">
+        <x:v>何胜阳</x:v>
+      </x:c>
+      <x:c r="B980" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C980" s="6" t="str">
+        <x:v>教师（2015年学校新闻列示）</x:v>
+      </x:c>
+      <x:c r="D980" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院</x:v>
+      </x:c>
+      <x:c r="E980" s="6" t="str"/>
+      <x:c r="F980" s="6" t="str"/>
+      <x:c r="G980" s="6" t="str"/>
+      <x:c r="H980" s="6" t="str"/>
+      <x:c r="I980" s="6" t="str"/>
+      <x:c r="J980" s="6" t="str"/>
+      <x:c r="K980" s="6" t="str"/>
+      <x:c r="L980" s="6" t="str"/>
+      <x:c r="M980" s="7" t="str"/>
+      <x:c r="N980" s="6" t="str"/>
+      <x:c r="O980" s="6" t="str">
+        <x:v>校内官方新闻直接称电信学院教师并报道2015年教师大赛获奖；职称、任职起讫与当前完整履历未披露。</x:v>
+      </x:c>
+      <x:c r="P980" s="6" t="str"/>
+      <x:c r="Q980" s="6" t="str">
+        <x:v>https://nydl.hit.edu.cn/2015/1214/c5681a146220/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="981" ht="64" customHeight="1">
+      <x:c r="A981" s="6" t="str">
+        <x:v>吴龙文</x:v>
+      </x:c>
+      <x:c r="B981" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C981" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D981" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E981" s="6" t="str">
+        <x:v>2008-09</x:v>
+      </x:c>
+      <x:c r="F981" s="6" t="str">
+        <x:v>2012-07</x:v>
+      </x:c>
+      <x:c r="G981" s="6" t="str">
+        <x:v>Information Countermeasure Technology</x:v>
+      </x:c>
+      <x:c r="H981" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I981" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J981" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K981" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L981" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M981" s="7" t="str"/>
+      <x:c r="N981" s="6" t="str">
+        <x:v>https://www.jocm.us/uploadfile/2016/0725/20160725033018142.pdf</x:v>
+      </x:c>
+      <x:c r="O981" s="6" t="str">
+        <x:v>2016原出版社PDF阅读器第7页作者简介明确2012获学士并给专业；起讫月取本人官网。</x:v>
+      </x:c>
+      <x:c r="P981" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q981" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wulongwen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="982" ht="64" customHeight="1">
+      <x:c r="A982" s="6" t="str">
+        <x:v>吴龙文</x:v>
+      </x:c>
+      <x:c r="B982" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C982" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D982" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E982" s="6" t="str">
+        <x:v>2012-09</x:v>
+      </x:c>
+      <x:c r="F982" s="6" t="str">
+        <x:v>2014-07</x:v>
+      </x:c>
+      <x:c r="G982" s="6" t="str">
+        <x:v>Electronics and Communication Engineering</x:v>
+      </x:c>
+      <x:c r="H982" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I982" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J982" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K982" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L982" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M982" s="7" t="str"/>
+      <x:c r="N982" s="6" t="str">
+        <x:v>https://www.jocm.us/uploadfile/2016/0725/20160725033018142.pdf</x:v>
+      </x:c>
+      <x:c r="O982" s="6" t="str">
+        <x:v>同原出版社PDF作者简介明确2014获硕士；起讫月取本人官网。</x:v>
+      </x:c>
+      <x:c r="P982" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q982" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wulongwen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="983" ht="64" customHeight="1">
+      <x:c r="A983" s="6" t="str">
+        <x:v>吴龙文</x:v>
+      </x:c>
+      <x:c r="B983" s="6" t="str">
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C983" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D983" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E983" s="6" t="str">
+        <x:v>2014-09</x:v>
+      </x:c>
+      <x:c r="F983" s="6" t="str">
+        <x:v>2019-11</x:v>
+      </x:c>
+      <x:c r="G983" s="6" t="str"/>
+      <x:c r="H983" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I983" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J983" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K983" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L983" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M983" s="7" t="str"/>
+      <x:c r="N983" s="6" t="str"/>
+      <x:c r="O983" s="6" t="str">
+        <x:v>本人官网明确工学博士，具体学位专业不以现研究方向替代。</x:v>
+      </x:c>
+      <x:c r="P983" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q983" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wulongwen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="984" ht="64" customHeight="1">
+      <x:c r="A984" s="6" t="str">
+        <x:v>吴龙文</x:v>
+      </x:c>
+      <x:c r="B984" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C984" s="6" t="str">
+        <x:v>教师</x:v>
+      </x:c>
+      <x:c r="D984" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
+      <x:c r="E984" s="6" t="str">
+        <x:v>2020-04</x:v>
+      </x:c>
+      <x:c r="F984" s="6" t="str"/>
+      <x:c r="G984" s="6" t="str"/>
+      <x:c r="H984" s="6" t="str"/>
+      <x:c r="I984" s="6" t="str"/>
+      <x:c r="J984" s="6" t="str"/>
+      <x:c r="K984" s="6" t="str"/>
+      <x:c r="L984" s="6" t="str"/>
+      <x:c r="M984" s="7" t="str"/>
+      <x:c r="N984" s="6" t="str"/>
+      <x:c r="O984" s="6" t="str">
+        <x:v>本人官网仅列教师；当前具体职称未在此页确定。</x:v>
+      </x:c>
+      <x:c r="P984" s="6" t="str"/>
+      <x:c r="Q984" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wulongwen</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c4708181ee54769"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88aa4d6259854d78"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41332,10 +43886,160 @@
         <x:v>https://news.whu.edu.cn/info/1002/64146.htm</x:v>
       </x:c>
     </x:row>
+    <x:row r="38" ht="64" customHeight="1">
+      <x:c r="A38" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B38" s="6" t="str">
+        <x:v>曹彦鹏（Yanpeng Cao）</x:v>
+      </x:c>
+      <x:c r="C38" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D38" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E38" s="6" t="str">
+        <x:v>浙江大学机械工程学院研究员、博士生导师，制造技术与系统工程研究所副所长；研究精密检测、红外热成像、机器视觉与无损检测。</x:v>
+      </x:c>
+      <x:c r="F38" s="6" t="str">
+        <x:v>official_page_currently_listed</x:v>
+      </x:c>
+      <x:c r="G38" s="6" t="str">
+        <x:v>仅反映所引官方页面公开列示，不等同独立人事核验。</x:v>
+      </x:c>
+      <x:c r="H38" s="6" t="str"/>
+      <x:c r="I38" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+      <x:c r="J38" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/caoyp/0.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="64" customHeight="1">
+      <x:c r="A39" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B39" s="6" t="str">
+        <x:v>杨将新（Jiangxin Yang）</x:v>
+      </x:c>
+      <x:c r="C39" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D39" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E39" s="6" t="str">
+        <x:v>贵州大学2025年官方新闻称浙江大学教授，参与机械制造专业培养方案、工程教育认证和联合培养交流。</x:v>
+      </x:c>
+      <x:c r="F39" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G39" s="6" t="str">
+        <x:v>2025年大学新闻明确教授身份，2026年当前在职与任职状态尚未核定。</x:v>
+      </x:c>
+      <x:c r="H39" s="6" t="str"/>
+      <x:c r="I39" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+      <x:c r="J39" s="6" t="str">
+        <x:v>https://mech.gzu.edu.cn/2025/0429/c11368a249480/page.htm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="64" customHeight="1">
+      <x:c r="A40" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B40" s="6" t="str">
+        <x:v>曹衍龙（Yanlong Cao）</x:v>
+      </x:c>
+      <x:c r="C40" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D40" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E40" s="6" t="str">
+        <x:v>浙江大学机械工程学院教授、博士生导师、制造所副所长；研究尺寸工程与视觉测量、机器人感知与控制、激光制造技术与装备。</x:v>
+      </x:c>
+      <x:c r="F40" s="6" t="str">
+        <x:v>official_page_currently_listed</x:v>
+      </x:c>
+      <x:c r="G40" s="6" t="str">
+        <x:v>仅反映所引官方页面公开列示，不等同独立人事核验。</x:v>
+      </x:c>
+      <x:c r="H40" s="6" t="str"/>
+      <x:c r="I40" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+      <x:c r="J40" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/sdcaoyl/0.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="64" customHeight="1">
+      <x:c r="A41" s="6" t="str">
+        <x:v>李鹏</x:v>
+      </x:c>
+      <x:c r="B41" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="C41" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D41" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E41" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院教授、博士生导师；研究人工智能、医学图像分析与计算磁共振、多源遥感图像处理。</x:v>
+      </x:c>
+      <x:c r="F41" s="6" t="str">
+        <x:v>official_page_currently_listed</x:v>
+      </x:c>
+      <x:c r="G41" s="6" t="str">
+        <x:v>仅反映所引官方页面公开列示，不等同独立人事核验。</x:v>
+      </x:c>
+      <x:c r="H41" s="6" t="str"/>
+      <x:c r="I41" s="6" t="str">
+        <x:v>https://hitgs.hit.edu.cn/2024/1226/c17460a361763/page.htm</x:v>
+      </x:c>
+      <x:c r="J41" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huyue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="64" customHeight="1">
+      <x:c r="A42" s="6" t="str">
+        <x:v>庄迪</x:v>
+      </x:c>
+      <x:c r="B42" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="C42" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D42" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E42" s="6" t="str">
+        <x:v>哈尔滨工业大学电子与信息工程学院教授、博士生导师，研究雷达信号和遥感图像处理。</x:v>
+      </x:c>
+      <x:c r="F42" s="6" t="str">
+        <x:v>official_page_currently_listed</x:v>
+      </x:c>
+      <x:c r="G42" s="6" t="str">
+        <x:v>本次官方个人主页仍列教授、博导。</x:v>
+      </x:c>
+      <x:c r="H42" s="6" t="str"/>
+      <x:c r="I42" s="6" t="str">
+        <x:v>https://hitgs.hit.edu.cn/2025/0326/c17343a365231/page.htm</x:v>
+      </x:c>
+      <x:c r="J42" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6e0a222fb804088"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re006e44c3720488e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49426,10 +52130,802 @@
         <x:v>成果类型：期刊论文。 链接核验状态：仅官方精选书目，未核独立文章落地页；不自动补同名 DOI。 Crossref 查询429后已停止，不补造 DOI 或声称核验成功。</x:v>
       </x:c>
     </x:row>
+    <x:row r="262" ht="64" customHeight="1">
+      <x:c r="A262" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B262" s="6" t="str">
+        <x:v>S2Match: Self-paced sampling for data-limited semi-supervised learning</x:v>
+      </x:c>
+      <x:c r="C262" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D262" s="6" t="str"/>
+      <x:c r="E262" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+      <x:c r="F262" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G262" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+      <x:c r="H262" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+      <x:c r="I262" s="6" t="str">
+        <x:v>official_profile_listed_individual_article_not_verified</x:v>
+      </x:c>
+      <x:c r="J262" s="6" t="str">
+        <x:v>本人官方主页列示的精选书目元数据；没有将整站主页视为逐篇落地页核验，也未收录论文全文。 成果类型：期刊论文。 链接核验状态：本人官网列示书目，独立文章页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263" ht="64" customHeight="1">
+      <x:c r="A263" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B263" s="6" t="str">
+        <x:v>Efficient Test-Time Adaptation of Vision-Language Models</x:v>
+      </x:c>
+      <x:c r="C263" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D263" s="6" t="str"/>
+      <x:c r="E263" s="6" t="str">
+        <x:v>https://openaccess.thecvf.com/content/CVPR2024/html/Karmanov_Efficient_Test-Time_Adaptation_of_Vision-Language_Models_CVPR_2024_paper.html</x:v>
+      </x:c>
+      <x:c r="F263" s="6" t="str">
+        <x:v>conference_paper</x:v>
+      </x:c>
+      <x:c r="G263" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+      <x:c r="H263" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+      <x:c r="I263" s="6" t="str">
+        <x:v>official_profile_link_target_fetch_returned_403</x:v>
+      </x:c>
+      <x:c r="J263" s="6" t="str">
+        <x:v>官网题名、作者、会议和链接已读；CVF落地页返回403，未绕过，也未标逐篇核验。 成果类型：会议论文。 链接核验状态：本人官网给出文章链接，目标页403未读，不宣称逐篇核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264" ht="64" customHeight="1">
+      <x:c r="A264" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B264" s="6" t="str">
+        <x:v>Unbiased Subclass Regularization for Semi-Supervised Semantic Segmentation</x:v>
+      </x:c>
+      <x:c r="C264" s="6" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="D264" s="6" t="str"/>
+      <x:c r="E264" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+      <x:c r="F264" s="6" t="str">
+        <x:v>conference_paper</x:v>
+      </x:c>
+      <x:c r="G264" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+      <x:c r="H264" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+      <x:c r="I264" s="6" t="str">
+        <x:v>official_profile_listed_individual_article_not_verified</x:v>
+      </x:c>
+      <x:c r="J264" s="6" t="str">
+        <x:v>本人官方主页列示的精选书目元数据；没有将整站主页视为逐篇落地页核验，也未收录论文全文。 成果类型：会议论文。 链接核验状态：本人官网列示书目，独立文章页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265" ht="64" customHeight="1">
+      <x:c r="A265" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B265" s="6" t="str">
+        <x:v>Generalized Constituent Nodes for Simplified Successive-Cancellation Decoding of Multi-Kernel Polar Codes</x:v>
+      </x:c>
+      <x:c r="C265" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D265" s="6" t="str"/>
+      <x:c r="E265" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+      <x:c r="F265" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G265" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+      <x:c r="H265" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+      <x:c r="I265" s="6" t="str">
+        <x:v>official_profile_listed_individual_article_not_verified</x:v>
+      </x:c>
+      <x:c r="J265" s="6" t="str">
+        <x:v>本人官方主页列示的精选书目元数据；没有将整站主页视为逐篇落地页核验，也未收录论文全文。 成果类型：期刊论文。 链接核验状态：本人官网列示书目，独立文章页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" ht="64" customHeight="1">
+      <x:c r="A266" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B266" s="6" t="str">
+        <x:v>Self-Sustainable IRS-Aided SWIPT: Beamforming Design and Resource Allocation</x:v>
+      </x:c>
+      <x:c r="C266" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D266" s="6" t="str"/>
+      <x:c r="E266" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+      <x:c r="F266" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G266" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+      <x:c r="H266" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+      <x:c r="I266" s="6" t="str">
+        <x:v>official_profile_listed_individual_article_not_verified</x:v>
+      </x:c>
+      <x:c r="J266" s="6" t="str">
+        <x:v>本人官方主页列示的精选书目元数据；没有将整站主页视为逐篇落地页核验，也未收录论文全文。 成果类型：期刊论文。 链接核验状态：本人官网列示书目，独立文章页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" ht="64" customHeight="1">
+      <x:c r="A267" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B267" s="6" t="str">
+        <x:v>Utilizing TOP2 Class for Hybrid Decision Making to Enhance TOP1 Accuracy of Ensemble Models</x:v>
+      </x:c>
+      <x:c r="C267" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D267" s="6" t="str"/>
+      <x:c r="E267" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+      <x:c r="F267" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G267" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+      <x:c r="H267" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+      <x:c r="I267" s="6" t="str">
+        <x:v>official_profile_listed_individual_article_not_verified</x:v>
+      </x:c>
+      <x:c r="J267" s="6" t="str">
+        <x:v>本人官方主页列示的精选书目元数据；没有将整站主页视为逐篇落地页核验，也未收录论文全文。 成果类型：期刊论文。 链接核验状态：本人官网列示书目，独立文章页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268" ht="64" customHeight="1">
+      <x:c r="A268" s="6" t="str">
+        <x:v>李贤</x:v>
+      </x:c>
+      <x:c r="B268" s="6" t="str">
+        <x:v>多模遥感立体信息获取发展现状与展望</x:v>
+      </x:c>
+      <x:c r="C268" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D268" s="6" t="str">
+        <x:v>10.7527/S1000-6893.2026.32870</x:v>
+      </x:c>
+      <x:c r="E268" s="6" t="str">
+        <x:v>https://hkxb.buaa.edu.cn/CN/abstract/abstract21205.shtml</x:v>
+      </x:c>
+      <x:c r="F268" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G268" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/XianLi</x:v>
+      </x:c>
+      <x:c r="H268" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/XianLi</x:v>
+      </x:c>
+      <x:c r="I268" s="6" t="str">
+        <x:v>publisher_article_metadata_verified</x:v>
+      </x:c>
+      <x:c r="J268" s="6" t="str">
+        <x:v>航空学报官网核验：47(10):532870，DOI及作者、题名相符；只收元数据。 成果类型：期刊论文。 链接核验状态：期刊官方文章元数据已核，不等同全文读取。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" ht="64" customHeight="1">
+      <x:c r="A269" s="6" t="str">
+        <x:v>李贤</x:v>
+      </x:c>
+      <x:c r="B269" s="6" t="str">
+        <x:v>An End-to-End Framework for Joint Denoising and Classification of Hyperspectral Images</x:v>
+      </x:c>
+      <x:c r="C269" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D269" s="6" t="str"/>
+      <x:c r="E269" s="6" t="str">
+        <x:v>https://ieeexplore.ieee.org/document/10101853/</x:v>
+      </x:c>
+      <x:c r="F269" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G269" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/XianLi</x:v>
+      </x:c>
+      <x:c r="H269" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/XianLi</x:v>
+      </x:c>
+      <x:c r="I269" s="6" t="str">
+        <x:v>official_profile_link_target_robot_verification</x:v>
+      </x:c>
+      <x:c r="J269" s="6" t="str">
+        <x:v>官网只列Xian Li、Yanfeng Gu et al.，此处仅记录已披露作者，非完整作者列表；IEEE打开停留机器人验证，未绕过、未核DOI。 成果类型：期刊论文。 链接核验状态：本人官网给出文章链接，访问停在机器人验证，不绕过、不声称文章已读。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" ht="64" customHeight="1">
+      <x:c r="A270" s="6" t="str">
+        <x:v>李贤</x:v>
+      </x:c>
+      <x:c r="B270" s="6" t="str">
+        <x:v>A Unified Multiview Spectral Feature Learning Framework for Hyperspectral Image Classification</x:v>
+      </x:c>
+      <x:c r="C270" s="6" t="n">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="D270" s="6" t="str"/>
+      <x:c r="E270" s="6" t="str">
+        <x:v>https://ieeexplore.ieee.org/document/9916307</x:v>
+      </x:c>
+      <x:c r="F270" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G270" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/XianLi</x:v>
+      </x:c>
+      <x:c r="H270" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/XianLi</x:v>
+      </x:c>
+      <x:c r="I270" s="6" t="str">
+        <x:v>official_profile_listed_individual_article_not_verified</x:v>
+      </x:c>
+      <x:c r="J270" s="6" t="str">
+        <x:v>官网只列Xian Li、Yanfeng Gu et al.，此处不是完整作者列表；真实官网所链文章地址，未逐篇打开核验。 成果类型：期刊论文。 链接核验状态：本人官网列示书目，独立文章页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271" ht="64" customHeight="1">
+      <x:c r="A271" s="6" t="str">
+        <x:v>李鹏</x:v>
+      </x:c>
+      <x:c r="B271" s="6" t="str">
+        <x:v>Improved MRF Reconstruction via Structure-Preserved Graph Embedding Framework</x:v>
+      </x:c>
+      <x:c r="C271" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D271" s="6" t="str">
+        <x:v>10.1109/TIP.2024.3477980</x:v>
+      </x:c>
+      <x:c r="E271" s="6" t="str">
+        <x:v>https://pubmed.ncbi.nlm.nih.gov/39412963/</x:v>
+      </x:c>
+      <x:c r="F271" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G271" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lipeng</x:v>
+      </x:c>
+      <x:c r="H271" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lipeng</x:v>
+      </x:c>
+      <x:c r="I271" s="6" t="str">
+        <x:v>pubmed_article_record_verified_publisher_landing_not_checked</x:v>
+      </x:c>
+      <x:c r="J271" s="6" t="str">
+        <x:v>PubMed逐篇记录核题名作者、2024年33卷5989–6001页及DOI；不声称IEEE落地页已打开。 成果类型：期刊论文。 链接核验状态：PubMed逐篇记录与DOI元数据已核，出版社落地页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" ht="64" customHeight="1">
+      <x:c r="A272" s="6" t="str">
+        <x:v>李鹏</x:v>
+      </x:c>
+      <x:c r="B272" s="6" t="str">
+        <x:v>Deep magnetic resonance fingerprinting based on Local and Global Vision Transformer</x:v>
+      </x:c>
+      <x:c r="C272" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D272" s="6" t="str">
+        <x:v>10.1016/j.media.2024.103198</x:v>
+      </x:c>
+      <x:c r="E272" s="6" t="str">
+        <x:v>https://pubmed.ncbi.nlm.nih.gov/38759259/</x:v>
+      </x:c>
+      <x:c r="F272" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G272" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lipeng</x:v>
+      </x:c>
+      <x:c r="H272" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lipeng</x:v>
+      </x:c>
+      <x:c r="I272" s="6" t="str">
+        <x:v>pubmed_article_record_verified_publisher_landing_not_checked</x:v>
+      </x:c>
+      <x:c r="J272" s="6" t="str">
+        <x:v>PubMed逐篇记录核题名、作者、HIT单位、2024年95卷103198及DOI；与2023同名会议论文分开。 成果类型：期刊论文。 链接核验状态：PubMed逐篇记录与DOI元数据已核，出版社落地页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" ht="64" customHeight="1">
+      <x:c r="A273" s="6" t="str">
+        <x:v>李鹏</x:v>
+      </x:c>
+      <x:c r="B273" s="6" t="str">
+        <x:v>Anatomical structure-guided joint spatiotemporal graph embedding framework for magnetic resonance fingerprint reconstruction</x:v>
+      </x:c>
+      <x:c r="C273" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D273" s="6" t="str">
+        <x:v>10.1016/j.media.2025.103816</x:v>
+      </x:c>
+      <x:c r="E273" s="6" t="str">
+        <x:v>https://doi.org/10.1016/j.media.2025.103816</x:v>
+      </x:c>
+      <x:c r="F273" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G273" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lipeng</x:v>
+      </x:c>
+      <x:c r="H273" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lipeng</x:v>
+      </x:c>
+      <x:c r="I273" s="6" t="str">
+        <x:v>official_profile_listed_individual_article_not_verified</x:v>
+      </x:c>
+      <x:c r="J273" s="6" t="str">
+        <x:v>本人官网列2026年107卷103816及DOI；DOI年份2025不强改正式出版年2026。未逐篇读出版商记录。 成果类型：期刊论文。 链接核验状态：本人官网列示书目，独立文章页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" ht="64" customHeight="1">
+      <x:c r="A274" s="6" t="str">
+        <x:v>庄迪</x:v>
+      </x:c>
+      <x:c r="B274" s="6" t="str">
+        <x:v>基于极化散射与干涉信息的SAR图像建筑提取与高程重建</x:v>
+      </x:c>
+      <x:c r="C274" s="6" t="str"/>
+      <x:c r="D274" s="6" t="str"/>
+      <x:c r="E274" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+      <x:c r="F274" s="6" t="str">
+        <x:v>doctoral_thesis</x:v>
+      </x:c>
+      <x:c r="G274" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+      <x:c r="H274" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhuangdi</x:v>
+      </x:c>
+      <x:c r="I274" s="6" t="str">
+        <x:v>official_selected_bibliography_only_landing_unchecked</x:v>
+      </x:c>
+      <x:c r="J274" s="6" t="str">
+        <x:v>张腊梅官网明确庄迪博士论文题名，2025.03为毕业/获奖报道时间，未另核论文出版日期。 成果类型：博士学位论文。 链接核验状态：仅官方精选书目，独立文章落地页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" ht="64" customHeight="1">
+      <x:c r="A275" s="6" t="str">
+        <x:v>庄迪</x:v>
+      </x:c>
+      <x:c r="B275" s="6" t="str">
+        <x:v>PELNet: A General Physics-Embedded Learning Framework for Polarimetric Target Decomposition</x:v>
+      </x:c>
+      <x:c r="C275" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D275" s="6" t="str">
+        <x:v>10.1016/j.isprsjprs.2026.08.040</x:v>
+      </x:c>
+      <x:c r="E275" s="6" t="str">
+        <x:v>https://doi.org/10.1016/j.isprsjprs.2026.08.040</x:v>
+      </x:c>
+      <x:c r="F275" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G275" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+      <x:c r="H275" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhuangdi</x:v>
+      </x:c>
+      <x:c r="I275" s="6" t="str">
+        <x:v>doi_verified_crossref_metadata_landing_unchecked</x:v>
+      </x:c>
+      <x:c r="J275" s="6" t="str">
+        <x:v>同一导师官网列作者Di Zhuang；已核第一批元数据可复用，卷期2026.12晚于核验日，不能声称卷期已发行。 成果类型：期刊论文。 链接核验状态：Crossref DOI元数据已核，独立文章落地页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276" ht="64" customHeight="1">
+      <x:c r="A276" s="6" t="str">
+        <x:v>刘东洋</x:v>
+      </x:c>
+      <x:c r="B276" s="6" t="str">
+        <x:v>RS-LLIC: A Lightweight Learned Image Compression Model with Knowledge Distillation for Onboard Remote Sensing</x:v>
+      </x:c>
+      <x:c r="C276" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D276" s="6" t="str">
+        <x:v>10.1109/TGRS.2026.3668020</x:v>
+      </x:c>
+      <x:c r="E276" s="6" t="str">
+        <x:v>https://doi.org/10.1109/TGRS.2026.3668020</x:v>
+      </x:c>
+      <x:c r="F276" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G276" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liudongyang</x:v>
+      </x:c>
+      <x:c r="H276" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liudongyang</x:v>
+      </x:c>
+      <x:c r="I276" s="6" t="str">
+        <x:v>publisher_indexed_metadata_direct_landing_unavailable</x:v>
+      </x:c>
+      <x:c r="J276" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：仅出版社索引/检索元数据，直接文章落地页不可读。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" ht="64" customHeight="1">
+      <x:c r="A277" s="6" t="str">
+        <x:v>刘东洋</x:v>
+      </x:c>
+      <x:c r="B277" s="6" t="str">
+        <x:v>Tiny Object Detection in Remote Sensing Images Based on Object Reconstruction and Multiple Receptive Field Adaptive Feature Enhancement</x:v>
+      </x:c>
+      <x:c r="C277" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D277" s="6" t="str"/>
+      <x:c r="E277" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liudongyang</x:v>
+      </x:c>
+      <x:c r="F277" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G277" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liudongyang</x:v>
+      </x:c>
+      <x:c r="H277" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liudongyang</x:v>
+      </x:c>
+      <x:c r="I277" s="6" t="str">
+        <x:v>official_selected_bibliography_only_landing_unchecked</x:v>
+      </x:c>
+      <x:c r="J277" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：仅官方精选书目，独立文章落地页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" ht="64" customHeight="1">
+      <x:c r="A278" s="6" t="str">
+        <x:v>刘东洋</x:v>
+      </x:c>
+      <x:c r="B278" s="6" t="str">
+        <x:v>Exploring Lightweight Structures for Tiny Object Detection in Remote Sensing Images</x:v>
+      </x:c>
+      <x:c r="C278" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D278" s="6" t="str"/>
+      <x:c r="E278" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liudongyang</x:v>
+      </x:c>
+      <x:c r="F278" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G278" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liudongyang</x:v>
+      </x:c>
+      <x:c r="H278" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liudongyang</x:v>
+      </x:c>
+      <x:c r="I278" s="6" t="str">
+        <x:v>official_selected_bibliography_only_landing_unchecked</x:v>
+      </x:c>
+      <x:c r="J278" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：仅官方精选书目，独立文章落地页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279" ht="64" customHeight="1">
+      <x:c r="A279" s="6" t="str">
+        <x:v>李大森</x:v>
+      </x:c>
+      <x:c r="B279" s="6" t="str">
+        <x:v>Rehearsal-based class-incremental learning approaches for plant disease classification</x:v>
+      </x:c>
+      <x:c r="C279" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="D279" s="6" t="str"/>
+      <x:c r="E279" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lidasen</x:v>
+      </x:c>
+      <x:c r="F279" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G279" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lidasen</x:v>
+      </x:c>
+      <x:c r="H279" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lidasen</x:v>
+      </x:c>
+      <x:c r="I279" s="6" t="str">
+        <x:v>official_selected_bibliography_only_landing_unchecked</x:v>
+      </x:c>
+      <x:c r="J279" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：仅官方精选书目，独立文章落地页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280" ht="64" customHeight="1">
+      <x:c r="A280" s="6" t="str">
+        <x:v>李大森</x:v>
+      </x:c>
+      <x:c r="B280" s="6" t="str">
+        <x:v>Non-exemplar class-incremental learning for continual plant diagnosis</x:v>
+      </x:c>
+      <x:c r="C280" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D280" s="6" t="str"/>
+      <x:c r="E280" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lidasen</x:v>
+      </x:c>
+      <x:c r="F280" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G280" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lidasen</x:v>
+      </x:c>
+      <x:c r="H280" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lidasen</x:v>
+      </x:c>
+      <x:c r="I280" s="6" t="str">
+        <x:v>official_selected_bibliography_only_landing_unchecked</x:v>
+      </x:c>
+      <x:c r="J280" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：仅官方精选书目，独立文章落地页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" ht="64" customHeight="1">
+      <x:c r="A281" s="6" t="str">
+        <x:v>李大森</x:v>
+      </x:c>
+      <x:c r="B281" s="6" t="str">
+        <x:v>MLFAnet: A Tomato Disease Classification Method Focusing on OOD Generalization</x:v>
+      </x:c>
+      <x:c r="C281" s="6" t="n">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="D281" s="6" t="str"/>
+      <x:c r="E281" s="6" t="str">
+        <x:v>https://www.mdpi.com/2077-0472/13/6/1140</x:v>
+      </x:c>
+      <x:c r="F281" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G281" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lidasen</x:v>
+      </x:c>
+      <x:c r="H281" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lidasen</x:v>
+      </x:c>
+      <x:c r="I281" s="6" t="str">
+        <x:v>publisher_indexed_metadata_direct_landing_unavailable</x:v>
+      </x:c>
+      <x:c r="J281" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：仅出版社索引/检索元数据，直接文章落地页不可读。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" ht="64" customHeight="1">
+      <x:c r="A282" s="6" t="str">
+        <x:v>董喆</x:v>
+      </x:c>
+      <x:c r="B282" s="6" t="str">
+        <x:v>HyperBridge: A Multi-Sensor Hyperspectral Benchmark with Geospatial Embedding Anchors for Cross-Sensor Representation Learning</x:v>
+      </x:c>
+      <x:c r="C282" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D282" s="6" t="str"/>
+      <x:c r="E282" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+      <x:c r="F282" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G282" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+      <x:c r="H282" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+      <x:c r="I282" s="6" t="str">
+        <x:v>official_selected_bibliography_only_landing_unchecked</x:v>
+      </x:c>
+      <x:c r="J282" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：仅官方精选书目，独立文章落地页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" ht="64" customHeight="1">
+      <x:c r="A283" s="6" t="str">
+        <x:v>董喆</x:v>
+      </x:c>
+      <x:c r="B283" s="6" t="str">
+        <x:v>PhyDAE: Physics-Guided Degradation-Adaptive Experts for All-in-One Remote Sensing Image Restoration</x:v>
+      </x:c>
+      <x:c r="C283" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D283" s="6" t="str"/>
+      <x:c r="E283" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+      <x:c r="F283" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G283" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+      <x:c r="H283" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+      <x:c r="I283" s="6" t="str">
+        <x:v>official_selected_bibliography_only_landing_unchecked</x:v>
+      </x:c>
+      <x:c r="J283" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：仅官方精选书目，独立文章落地页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" ht="64" customHeight="1">
+      <x:c r="A284" s="6" t="str">
+        <x:v>董喆</x:v>
+      </x:c>
+      <x:c r="B284" s="6" t="str">
+        <x:v>Cross-modal bidirectional interaction model for referring remote sensing image segmentation</x:v>
+      </x:c>
+      <x:c r="C284" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="D284" s="6" t="str"/>
+      <x:c r="E284" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+      <x:c r="F284" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G284" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+      <x:c r="H284" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+      <x:c r="I284" s="6" t="str">
+        <x:v>official_selected_bibliography_only_landing_unchecked</x:v>
+      </x:c>
+      <x:c r="J284" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：仅官方精选书目，独立文章落地页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" ht="64" customHeight="1">
+      <x:c r="A285" s="6" t="str">
+        <x:v>吴龙文</x:v>
+      </x:c>
+      <x:c r="B285" s="6" t="str">
+        <x:v>AWBIFS: An incremental fusion system for arrhythmia recognition on imbalanced ECG data with adaptive weighting</x:v>
+      </x:c>
+      <x:c r="C285" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D285" s="6" t="str"/>
+      <x:c r="E285" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wulongwen</x:v>
+      </x:c>
+      <x:c r="F285" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G285" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wulongwen</x:v>
+      </x:c>
+      <x:c r="H285" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wulongwen</x:v>
+      </x:c>
+      <x:c r="I285" s="6" t="str">
+        <x:v>official_selected_bibliography_only_landing_unchecked</x:v>
+      </x:c>
+      <x:c r="J285" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：仅官方精选书目，独立文章落地页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" ht="64" customHeight="1">
+      <x:c r="A286" s="6" t="str">
+        <x:v>吴龙文</x:v>
+      </x:c>
+      <x:c r="B286" s="6" t="str">
+        <x:v>IF Estimation in Multi-Component Signals Via Hough-Viterbi Algorithm With HGA-ADTFD</x:v>
+      </x:c>
+      <x:c r="C286" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D286" s="6" t="str"/>
+      <x:c r="E286" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wulongwen</x:v>
+      </x:c>
+      <x:c r="F286" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G286" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wulongwen</x:v>
+      </x:c>
+      <x:c r="H286" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wulongwen</x:v>
+      </x:c>
+      <x:c r="I286" s="6" t="str">
+        <x:v>official_selected_bibliography_only_landing_unchecked</x:v>
+      </x:c>
+      <x:c r="J286" s="6" t="str">
+        <x:v>成果类型：期刊论文。 链接核验状态：仅官方精选书目，独立文章落地页未核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" ht="64" customHeight="1">
+      <x:c r="A287" s="6" t="str">
+        <x:v>吴龙文</x:v>
+      </x:c>
+      <x:c r="B287" s="6" t="str">
+        <x:v>Sensor Pairing Optimization and Analytical Solution for Distributed TDOA Localization</x:v>
+      </x:c>
+      <x:c r="C287" s="6" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D287" s="6" t="str">
+        <x:v>10.1109/TVT.2025.3613346</x:v>
+      </x:c>
+      <x:c r="E287" s="6" t="str">
+        <x:v>https://doi.org/10.1109/TVT.2025.3613346</x:v>
+      </x:c>
+      <x:c r="F287" s="6" t="str">
+        <x:v>journal_article</x:v>
+      </x:c>
+      <x:c r="G287" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wulongwen</x:v>
+      </x:c>
+      <x:c r="H287" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wulongwen</x:v>
+      </x:c>
+      <x:c r="I287" s="6" t="str">
+        <x:v>official_selected_bibliography_only_landing_unchecked</x:v>
+      </x:c>
+      <x:c r="J287" s="6" t="str">
+        <x:v>官网明确2026卷期及2025 online DOI，年份不同是文献日期类型，保留而不改2026卷期。 成果类型：期刊论文。 链接核验状态：仅官方精选书目，独立文章落地页未核验。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4a0f3d5f9364d71"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R014bb8c9209942d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -57418,10 +60914,3104 @@
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
     </x:row>
+    <x:row r="470" ht="64" customHeight="1">
+      <x:c r="A470" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B470" s="6" t="str">
+        <x:v>guandayan-official</x:v>
+      </x:c>
+      <x:c r="C470" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan</x:v>
+      </x:c>
+      <x:c r="D470" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E470" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471" ht="64" customHeight="1">
+      <x:c r="A471" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B471" s="6" t="str">
+        <x:v>guandayan-official-header</x:v>
+      </x:c>
+      <x:c r="C471" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/guandayan?lang=zh</x:v>
+      </x:c>
+      <x:c r="D471" s="6" t="str">
+        <x:v>official_profile_shell_and_identity_read</x:v>
+      </x:c>
+      <x:c r="E471" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="472" ht="64" customHeight="1">
+      <x:c r="A472" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B472" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C472" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D472" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E472" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473" ht="64" customHeight="1">
+      <x:c r="A473" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B473" s="6" t="str">
+        <x:v>caoyanpeng-official</x:v>
+      </x:c>
+      <x:c r="C473" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/caoyp/0.html</x:v>
+      </x:c>
+      <x:c r="D473" s="6" t="str">
+        <x:v>official_profile_read_via_web_tool</x:v>
+      </x:c>
+      <x:c r="E473" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474" ht="64" customHeight="1">
+      <x:c r="A474" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B474" s="6" t="str">
+        <x:v>caoyanlong-official</x:v>
+      </x:c>
+      <x:c r="C474" s="6" t="str">
+        <x:v>https://person.zju.edu.cn/sdcaoyl/0.html</x:v>
+      </x:c>
+      <x:c r="D474" s="6" t="str">
+        <x:v>official_public_page_read</x:v>
+      </x:c>
+      <x:c r="E474" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="475" ht="64" customHeight="1">
+      <x:c r="A475" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B475" s="6" t="str">
+        <x:v>yangjiangxin-university-news</x:v>
+      </x:c>
+      <x:c r="C475" s="6" t="str">
+        <x:v>https://mech.gzu.edu.cn/2025/0429/c11368a249480/page.htm</x:v>
+      </x:c>
+      <x:c r="D475" s="6" t="str">
+        <x:v>official_university_news_read</x:v>
+      </x:c>
+      <x:c r="E475" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476" ht="64" customHeight="1">
+      <x:c r="A476" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B476" s="6" t="str">
+        <x:v>zhaoyanlong-official</x:v>
+      </x:c>
+      <x:c r="C476" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong</x:v>
+      </x:c>
+      <x:c r="D476" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E476" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477" ht="64" customHeight="1">
+      <x:c r="A477" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B477" s="6" t="str">
+        <x:v>zhaoyanlong-official-header</x:v>
+      </x:c>
+      <x:c r="C477" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhaoyanlong?lang=zh</x:v>
+      </x:c>
+      <x:c r="D477" s="6" t="str">
+        <x:v>official_profile_shell_and_identity_read</x:v>
+      </x:c>
+      <x:c r="E477" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478" ht="64" customHeight="1">
+      <x:c r="A478" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B478" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C478" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D478" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E478" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="479" ht="64" customHeight="1">
+      <x:c r="A479" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B479" s="6" t="str">
+        <x:v>zhaoyanlong-thesis-index-search</x:v>
+      </x:c>
+      <x:c r="C479" s="6" t="str">
+        <x:v>https://cnki.istiz.org.cn/kcms/detail/detail.aspx?dbcode=CDFD&amp;dbname=CDFD2025&amp;filename=1024586314.nh</x:v>
+      </x:c>
+      <x:c r="D479" s="6" t="str">
+        <x:v>search_index_only_primary_page_not_read</x:v>
+      </x:c>
+      <x:c r="E479" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480" ht="64" customHeight="1">
+      <x:c r="A480" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B480" s="6" t="str">
+        <x:v>wuzhilu-profile-unavailable</x:v>
+      </x:c>
+      <x:c r="C480" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wuzhilu</x:v>
+      </x:c>
+      <x:c r="D480" s="6" t="str">
+        <x:v>official_profile_redirects_to_not_opened</x:v>
+      </x:c>
+      <x:c r="E480" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="481" ht="64" customHeight="1">
+      <x:c r="A481" s="6" t="str">
+        <x:v>曹立新</x:v>
+      </x:c>
+      <x:c r="B481" s="6" t="str">
+        <x:v>caolixin-official</x:v>
+      </x:c>
+      <x:c r="C481" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/caolixin</x:v>
+      </x:c>
+      <x:c r="D481" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E481" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482" ht="64" customHeight="1">
+      <x:c r="A482" s="6" t="str">
+        <x:v>曹立新</x:v>
+      </x:c>
+      <x:c r="B482" s="6" t="str">
+        <x:v>caolixin-official-header</x:v>
+      </x:c>
+      <x:c r="C482" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/caolixin?lang=zh</x:v>
+      </x:c>
+      <x:c r="D482" s="6" t="str">
+        <x:v>official_profile_shell_and_identity_read</x:v>
+      </x:c>
+      <x:c r="E482" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483" ht="64" customHeight="1">
+      <x:c r="A483" s="6" t="str">
+        <x:v>曹立新</x:v>
+      </x:c>
+      <x:c r="B483" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C483" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D483" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E483" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484" ht="64" customHeight="1">
+      <x:c r="A484" s="6" t="str">
+        <x:v>陈迪</x:v>
+      </x:c>
+      <x:c r="B484" s="6" t="str">
+        <x:v>chendi-official</x:v>
+      </x:c>
+      <x:c r="C484" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chendi</x:v>
+      </x:c>
+      <x:c r="D484" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E484" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485" ht="64" customHeight="1">
+      <x:c r="A485" s="6" t="str">
+        <x:v>陈迪</x:v>
+      </x:c>
+      <x:c r="B485" s="6" t="str">
+        <x:v>chendi-official-header</x:v>
+      </x:c>
+      <x:c r="C485" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/chendi?lang=zh</x:v>
+      </x:c>
+      <x:c r="D485" s="6" t="str">
+        <x:v>official_profile_shell_and_identity_read</x:v>
+      </x:c>
+      <x:c r="E485" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486" ht="64" customHeight="1">
+      <x:c r="A486" s="6" t="str">
+        <x:v>陈迪</x:v>
+      </x:c>
+      <x:c r="B486" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C486" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D486" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E486" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="487" ht="64" customHeight="1">
+      <x:c r="A487" s="6" t="str">
+        <x:v>李贤</x:v>
+      </x:c>
+      <x:c r="B487" s="6" t="str">
+        <x:v>xianli-official</x:v>
+      </x:c>
+      <x:c r="C487" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/XianLi</x:v>
+      </x:c>
+      <x:c r="D487" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E487" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488" ht="64" customHeight="1">
+      <x:c r="A488" s="6" t="str">
+        <x:v>李贤</x:v>
+      </x:c>
+      <x:c r="B488" s="6" t="str">
+        <x:v>xianli-official-header</x:v>
+      </x:c>
+      <x:c r="C488" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/XianLi?lang=zh</x:v>
+      </x:c>
+      <x:c r="D488" s="6" t="str">
+        <x:v>official_profile_shell_and_identity_read</x:v>
+      </x:c>
+      <x:c r="E488" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489" ht="64" customHeight="1">
+      <x:c r="A489" s="6" t="str">
+        <x:v>李贤</x:v>
+      </x:c>
+      <x:c r="B489" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C489" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D489" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E489" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="490" ht="64" customHeight="1">
+      <x:c r="A490" s="6" t="str">
+        <x:v>李贤</x:v>
+      </x:c>
+      <x:c r="B490" s="6" t="str">
+        <x:v>xianli-author-bio</x:v>
+      </x:c>
+      <x:c r="C490" s="6" t="str">
+        <x:v>https://gaim.ugent.be/media/preprint/8638075.pdf</x:v>
+      </x:c>
+      <x:c r="D490" s="6" t="str">
+        <x:v>university_hosted_author_manuscript_biography_read</x:v>
+      </x:c>
+      <x:c r="E490" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491" ht="64" customHeight="1">
+      <x:c r="A491" s="6" t="str">
+        <x:v>李贤</x:v>
+      </x:c>
+      <x:c r="B491" s="6" t="str">
+        <x:v>xianli-paper-journal</x:v>
+      </x:c>
+      <x:c r="C491" s="6" t="str">
+        <x:v>https://hkxb.buaa.edu.cn/CN/abstract/abstract21205.shtml</x:v>
+      </x:c>
+      <x:c r="D491" s="6" t="str">
+        <x:v>publisher_article_metadata_read</x:v>
+      </x:c>
+      <x:c r="E491" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492" ht="64" customHeight="1">
+      <x:c r="A492" s="6" t="str">
+        <x:v>李鹏</x:v>
+      </x:c>
+      <x:c r="B492" s="6" t="str">
+        <x:v>lipeng-official</x:v>
+      </x:c>
+      <x:c r="C492" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lipeng</x:v>
+      </x:c>
+      <x:c r="D492" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E492" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493" ht="64" customHeight="1">
+      <x:c r="A493" s="6" t="str">
+        <x:v>李鹏</x:v>
+      </x:c>
+      <x:c r="B493" s="6" t="str">
+        <x:v>lipeng-official-header</x:v>
+      </x:c>
+      <x:c r="C493" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lipeng?lang=zh</x:v>
+      </x:c>
+      <x:c r="D493" s="6" t="str">
+        <x:v>official_profile_shell_and_identity_read</x:v>
+      </x:c>
+      <x:c r="E493" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494" ht="64" customHeight="1">
+      <x:c r="A494" s="6" t="str">
+        <x:v>李鹏</x:v>
+      </x:c>
+      <x:c r="B494" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C494" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D494" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E494" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495" ht="64" customHeight="1">
+      <x:c r="A495" s="6" t="str">
+        <x:v>李鹏</x:v>
+      </x:c>
+      <x:c r="B495" s="6" t="str">
+        <x:v>lipeng-phd-advisor</x:v>
+      </x:c>
+      <x:c r="C495" s="6" t="str">
+        <x:v>https://hitgs.hit.edu.cn/2024/1226/c17460a361763/page.htm</x:v>
+      </x:c>
+      <x:c r="D495" s="6" t="str">
+        <x:v>official_university_doctoral_dissertation_award_notice_read</x:v>
+      </x:c>
+      <x:c r="E495" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496" ht="64" customHeight="1">
+      <x:c r="A496" s="6" t="str">
+        <x:v>李鹏</x:v>
+      </x:c>
+      <x:c r="B496" s="6" t="str">
+        <x:v>huyue-official</x:v>
+      </x:c>
+      <x:c r="C496" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/huyue</x:v>
+      </x:c>
+      <x:c r="D496" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E496" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497" ht="64" customHeight="1">
+      <x:c r="A497" s="6" t="str">
+        <x:v>李鹏</x:v>
+      </x:c>
+      <x:c r="B497" s="6" t="str">
+        <x:v>lipeng-paper-pubmed1</x:v>
+      </x:c>
+      <x:c r="C497" s="6" t="str">
+        <x:v>https://pubmed.ncbi.nlm.nih.gov/39412963/</x:v>
+      </x:c>
+      <x:c r="D497" s="6" t="str">
+        <x:v>pubmed_article_metadata_read</x:v>
+      </x:c>
+      <x:c r="E497" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498" ht="64" customHeight="1">
+      <x:c r="A498" s="6" t="str">
+        <x:v>李鹏</x:v>
+      </x:c>
+      <x:c r="B498" s="6" t="str">
+        <x:v>lipeng-paper-pubmed2</x:v>
+      </x:c>
+      <x:c r="C498" s="6" t="str">
+        <x:v>https://pubmed.ncbi.nlm.nih.gov/38759259/</x:v>
+      </x:c>
+      <x:c r="D498" s="6" t="str">
+        <x:v>pubmed_article_metadata_read</x:v>
+      </x:c>
+      <x:c r="E498" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499" ht="64" customHeight="1">
+      <x:c r="A499" s="6" t="str">
+        <x:v>庄迪</x:v>
+      </x:c>
+      <x:c r="B499" s="6" t="str">
+        <x:v>zhuangdi-official</x:v>
+      </x:c>
+      <x:c r="C499" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhuangdi</x:v>
+      </x:c>
+      <x:c r="D499" s="6" t="str">
+        <x:v>official_profile_empty_or_name_only_read</x:v>
+      </x:c>
+      <x:c r="E499" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500" ht="64" customHeight="1">
+      <x:c r="A500" s="6" t="str">
+        <x:v>庄迪</x:v>
+      </x:c>
+      <x:c r="B500" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C500" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D500" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E500" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501" ht="64" customHeight="1">
+      <x:c r="A501" s="6" t="str">
+        <x:v>庄迪</x:v>
+      </x:c>
+      <x:c r="B501" s="6" t="str">
+        <x:v>zhuangdi-source-3</x:v>
+      </x:c>
+      <x:c r="C501" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/zhanglm</x:v>
+      </x:c>
+      <x:c r="D501" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E501" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502" ht="64" customHeight="1">
+      <x:c r="A502" s="6" t="str">
+        <x:v>庄迪</x:v>
+      </x:c>
+      <x:c r="B502" s="6" t="str">
+        <x:v>zhuangdi-source-4</x:v>
+      </x:c>
+      <x:c r="C502" s="6" t="str">
+        <x:v>https://hitgs.hit.edu.cn/2025/0326/c17343a365231/page.htm</x:v>
+      </x:c>
+      <x:c r="D502" s="6" t="str">
+        <x:v>official_graduate_school_advisor_table_read</x:v>
+      </x:c>
+      <x:c r="E502" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="503" ht="64" customHeight="1">
+      <x:c r="A503" s="6" t="str">
+        <x:v>庄迪</x:v>
+      </x:c>
+      <x:c r="B503" s="6" t="str">
+        <x:v>zhuangdi-publication-2-metadata</x:v>
+      </x:c>
+      <x:c r="C503" s="6" t="str">
+        <x:v>https://api.crossref.org/works/10.1016/j.isprsjprs.2026.08.040</x:v>
+      </x:c>
+      <x:c r="D503" s="6" t="str">
+        <x:v>previous_batch_crossref_selected_metadata_cache_reused</x:v>
+      </x:c>
+      <x:c r="E503" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504" ht="64" customHeight="1">
+      <x:c r="A504" s="6" t="str">
+        <x:v>刘东洋</x:v>
+      </x:c>
+      <x:c r="B504" s="6" t="str">
+        <x:v>liudongyang-official</x:v>
+      </x:c>
+      <x:c r="C504" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/liudongyang</x:v>
+      </x:c>
+      <x:c r="D504" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E504" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505" ht="64" customHeight="1">
+      <x:c r="A505" s="6" t="str">
+        <x:v>刘东洋</x:v>
+      </x:c>
+      <x:c r="B505" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C505" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D505" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E505" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="506" ht="64" customHeight="1">
+      <x:c r="A506" s="6" t="str">
+        <x:v>刘东洋</x:v>
+      </x:c>
+      <x:c r="B506" s="6" t="str">
+        <x:v>liudongyang-publication-1-metadata</x:v>
+      </x:c>
+      <x:c r="C506" s="6" t="str">
+        <x:v>https://xplorestaging.ieee.org/document/11411827</x:v>
+      </x:c>
+      <x:c r="D506" s="6" t="str">
+        <x:v>publisher_search_excerpt_read_direct_open_418</x:v>
+      </x:c>
+      <x:c r="E506" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507" ht="64" customHeight="1">
+      <x:c r="A507" s="6" t="str">
+        <x:v>李大森</x:v>
+      </x:c>
+      <x:c r="B507" s="6" t="str">
+        <x:v>lidasen-official</x:v>
+      </x:c>
+      <x:c r="C507" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/lidasen</x:v>
+      </x:c>
+      <x:c r="D507" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E507" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508" ht="64" customHeight="1">
+      <x:c r="A508" s="6" t="str">
+        <x:v>李大森</x:v>
+      </x:c>
+      <x:c r="B508" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C508" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D508" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E508" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="509" ht="64" customHeight="1">
+      <x:c r="A509" s="6" t="str">
+        <x:v>李大森</x:v>
+      </x:c>
+      <x:c r="B509" s="6" t="str">
+        <x:v>lidasen-publication-3-metadata</x:v>
+      </x:c>
+      <x:c r="C509" s="6" t="str">
+        <x:v>https://www.mdpi.com/2077-0472/13/6/1140</x:v>
+      </x:c>
+      <x:c r="D509" s="6" t="str">
+        <x:v>publisher_search_excerpt_read_direct_open_429</x:v>
+      </x:c>
+      <x:c r="E509" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510" ht="64" customHeight="1">
+      <x:c r="A510" s="6" t="str">
+        <x:v>董喆</x:v>
+      </x:c>
+      <x:c r="B510" s="6" t="str">
+        <x:v>dongzhe-official</x:v>
+      </x:c>
+      <x:c r="C510" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/dongzhe</x:v>
+      </x:c>
+      <x:c r="D510" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E510" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="511" ht="64" customHeight="1">
+      <x:c r="A511" s="6" t="str">
+        <x:v>董喆</x:v>
+      </x:c>
+      <x:c r="B511" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C511" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D511" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E511" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512" ht="64" customHeight="1">
+      <x:c r="A512" s="6" t="str">
+        <x:v>何胜阳</x:v>
+      </x:c>
+      <x:c r="B512" s="6" t="str">
+        <x:v>heshengyang-official</x:v>
+      </x:c>
+      <x:c r="C512" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/2024/0704/c19284a348197/page.htm</x:v>
+      </x:c>
+      <x:c r="D512" s="6" t="str">
+        <x:v>official_profile_empty_or_name_only_read</x:v>
+      </x:c>
+      <x:c r="E512" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513" ht="64" customHeight="1">
+      <x:c r="A513" s="6" t="str">
+        <x:v>何胜阳</x:v>
+      </x:c>
+      <x:c r="B513" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C513" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D513" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E513" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="514" ht="64" customHeight="1">
+      <x:c r="A514" s="6" t="str">
+        <x:v>何胜阳</x:v>
+      </x:c>
+      <x:c r="B514" s="6" t="str">
+        <x:v>heshengyang-source-3</x:v>
+      </x:c>
+      <x:c r="C514" s="6" t="str">
+        <x:v>https://nydl.hit.edu.cn/2015/1214/c5681a146220/page.htm</x:v>
+      </x:c>
+      <x:c r="D514" s="6" t="str">
+        <x:v>official_publisher_or_institution_metadata</x:v>
+      </x:c>
+      <x:c r="E514" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="515" ht="64" customHeight="1">
+      <x:c r="A515" s="6" t="str">
+        <x:v>何胜阳</x:v>
+      </x:c>
+      <x:c r="B515" s="6" t="str">
+        <x:v>heshengyang-journal-snippet</x:v>
+      </x:c>
+      <x:c r="C515" s="6" t="str">
+        <x:v>https://jeit.ac.cn/cn/article/doi/10.11999/JEIT220190</x:v>
+      </x:c>
+      <x:c r="D515" s="6" t="str">
+        <x:v>official_publisher_search_excerpt_only_landing_403</x:v>
+      </x:c>
+      <x:c r="E515" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="516" ht="64" customHeight="1">
+      <x:c r="A516" s="6" t="str">
+        <x:v>吴龙文</x:v>
+      </x:c>
+      <x:c r="B516" s="6" t="str">
+        <x:v>wulongwen-official</x:v>
+      </x:c>
+      <x:c r="C516" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/wulongwen</x:v>
+      </x:c>
+      <x:c r="D516" s="6" t="str">
+        <x:v>official_page_public_body_fetched</x:v>
+      </x:c>
+      <x:c r="E516" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517" ht="64" customHeight="1">
+      <x:c r="A517" s="6" t="str">
+        <x:v>吴龙文</x:v>
+      </x:c>
+      <x:c r="B517" s="6" t="str">
+        <x:v>harbin-information-roster</x:v>
+      </x:c>
+      <x:c r="C517" s="6" t="str">
+        <x:v>https://seie.hit.edu.cn/19284/list.htm</x:v>
+      </x:c>
+      <x:c r="D517" s="6" t="str">
+        <x:v>official_roster_read</x:v>
+      </x:c>
+      <x:c r="E517" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="518" ht="64" customHeight="1">
+      <x:c r="A518" s="6" t="str">
+        <x:v>吴龙文</x:v>
+      </x:c>
+      <x:c r="B518" s="6" t="str">
+        <x:v>wulongwen-source-3</x:v>
+      </x:c>
+      <x:c r="C518" s="6" t="str">
+        <x:v>https://www.jocm.us/uploadfile/2016/0725/20160725033018142.pdf</x:v>
+      </x:c>
+      <x:c r="D518" s="6" t="str">
+        <x:v>original_publisher_pdf_author_bio_read</x:v>
+      </x:c>
+      <x:c r="E518" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519" ht="64" customHeight="1">
+      <x:c r="A519" s="6" t="str">
+        <x:v>郭庆</x:v>
+      </x:c>
+      <x:c r="B519" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C519" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D519" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E519" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="520" ht="64" customHeight="1">
+      <x:c r="A520" s="6" t="str">
+        <x:v>沙学军</x:v>
+      </x:c>
+      <x:c r="B520" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C520" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D520" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E520" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521" ht="64" customHeight="1">
+      <x:c r="A521" s="6" t="str">
+        <x:v>孟维晓</x:v>
+      </x:c>
+      <x:c r="B521" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C521" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D521" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E521" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="522" ht="64" customHeight="1">
+      <x:c r="A522" s="6" t="str">
+        <x:v>赵洪林</x:v>
+      </x:c>
+      <x:c r="B522" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C522" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D522" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E522" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523" ht="64" customHeight="1">
+      <x:c r="A523" s="6" t="str">
+        <x:v>马永奎</x:v>
+      </x:c>
+      <x:c r="B523" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C523" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D523" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E523" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="524" ht="64" customHeight="1">
+      <x:c r="A524" s="6" t="str">
+        <x:v>杨明川</x:v>
+      </x:c>
+      <x:c r="B524" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C524" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D524" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E524" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="525" ht="64" customHeight="1">
+      <x:c r="A525" s="6" t="str">
+        <x:v>王振永</x:v>
+      </x:c>
+      <x:c r="B525" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C525" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D525" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E525" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="526" ht="64" customHeight="1">
+      <x:c r="A526" s="6" t="str">
+        <x:v>李卓明</x:v>
+      </x:c>
+      <x:c r="B526" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C526" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D526" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E526" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="527" ht="64" customHeight="1">
+      <x:c r="A527" s="6" t="str">
+        <x:v>吴少川</x:v>
+      </x:c>
+      <x:c r="B527" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C527" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D527" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E527" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="528" ht="64" customHeight="1">
+      <x:c r="A528" s="6" t="str">
+        <x:v>高玉龙</x:v>
+      </x:c>
+      <x:c r="B528" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C528" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D528" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E528" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="529" ht="64" customHeight="1">
+      <x:c r="A529" s="6" t="str">
+        <x:v>石硕</x:v>
+      </x:c>
+      <x:c r="B529" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C529" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D529" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E529" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="530" ht="64" customHeight="1">
+      <x:c r="A530" s="6" t="str">
+        <x:v>吴宣利</x:v>
+      </x:c>
+      <x:c r="B530" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C530" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D530" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E530" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="531" ht="64" customHeight="1">
+      <x:c r="A531" s="6" t="str">
+        <x:v>马琳</x:v>
+      </x:c>
+      <x:c r="B531" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C531" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D531" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E531" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="532" ht="64" customHeight="1">
+      <x:c r="A532" s="6" t="str">
+        <x:v>韩帅</x:v>
+      </x:c>
+      <x:c r="B532" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C532" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D532" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E532" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="533" ht="64" customHeight="1">
+      <x:c r="A533" s="6" t="str">
+        <x:v>何晨光</x:v>
+      </x:c>
+      <x:c r="B533" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C533" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D533" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E533" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="534" ht="64" customHeight="1">
+      <x:c r="A534" s="6" t="str">
+        <x:v>于启月</x:v>
+      </x:c>
+      <x:c r="B534" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C534" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D534" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E534" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="535" ht="64" customHeight="1">
+      <x:c r="A535" s="6" t="str">
+        <x:v>贾敏</x:v>
+      </x:c>
+      <x:c r="B535" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C535" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D535" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E535" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="536" ht="64" customHeight="1">
+      <x:c r="A536" s="6" t="str">
+        <x:v>史军</x:v>
+      </x:c>
+      <x:c r="B536" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C536" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D536" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E536" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="537" ht="64" customHeight="1">
+      <x:c r="A537" s="6" t="str">
+        <x:v>房宵杰</x:v>
+      </x:c>
+      <x:c r="B537" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C537" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D537" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E537" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="538" ht="64" customHeight="1">
+      <x:c r="A538" s="6" t="str">
+        <x:v>魏守明</x:v>
+      </x:c>
+      <x:c r="B538" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C538" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D538" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E538" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="539" ht="64" customHeight="1">
+      <x:c r="A539" s="6" t="str">
+        <x:v>迟永钢</x:v>
+      </x:c>
+      <x:c r="B539" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C539" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D539" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E539" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="540" ht="64" customHeight="1">
+      <x:c r="A540" s="6" t="str">
+        <x:v>张成文</x:v>
+      </x:c>
+      <x:c r="B540" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C540" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D540" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E540" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="541" ht="64" customHeight="1">
+      <x:c r="A541" s="6" t="str">
+        <x:v>张文彬</x:v>
+      </x:c>
+      <x:c r="B541" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C541" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D541" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E541" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="542" ht="64" customHeight="1">
+      <x:c r="A542" s="6" t="str">
+        <x:v>张佳岩</x:v>
+      </x:c>
+      <x:c r="B542" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C542" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D542" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E542" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="543" ht="64" customHeight="1">
+      <x:c r="A543" s="6" t="str">
+        <x:v>白旭</x:v>
+      </x:c>
+      <x:c r="B543" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C543" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D543" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E543" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="544" ht="64" customHeight="1">
+      <x:c r="A544" s="6" t="str">
+        <x:v>杨文超</x:v>
+      </x:c>
+      <x:c r="B544" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C544" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D544" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E544" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="545" ht="64" customHeight="1">
+      <x:c r="A545" s="6" t="str">
+        <x:v>叶亮</x:v>
+      </x:c>
+      <x:c r="B545" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C545" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D545" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E545" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="546" ht="64" customHeight="1">
+      <x:c r="A546" s="6" t="str">
+        <x:v>吴玮</x:v>
+      </x:c>
+      <x:c r="B546" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C546" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D546" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E546" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="547" ht="64" customHeight="1">
+      <x:c r="A547" s="6" t="str">
+        <x:v>梅林</x:v>
+      </x:c>
+      <x:c r="B547" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C547" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D547" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E547" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="548" ht="64" customHeight="1">
+      <x:c r="A548" s="6" t="str">
+        <x:v>陈舒怡</x:v>
+      </x:c>
+      <x:c r="B548" s="6" t="str">
+        <x:v>institution-classification-9</x:v>
+      </x:c>
+      <x:c r="C548" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D548" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E548" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="549" ht="64" customHeight="1">
+      <x:c r="A549" s="6" t="str">
+        <x:v>吴尘雨</x:v>
+      </x:c>
+      <x:c r="B549" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C549" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D549" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E549" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="550" ht="64" customHeight="1">
+      <x:c r="A550" s="6" t="str">
+        <x:v>王欣玉</x:v>
+      </x:c>
+      <x:c r="B550" s="6" t="str">
+        <x:v>institution-classification-9</x:v>
+      </x:c>
+      <x:c r="C550" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D550" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E550" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="551" ht="64" customHeight="1">
+      <x:c r="A551" s="6" t="str">
+        <x:v>单成兆</x:v>
+      </x:c>
+      <x:c r="B551" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C551" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D551" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E551" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="552" ht="64" customHeight="1">
+      <x:c r="A552" s="6" t="str">
+        <x:v>董衡</x:v>
+      </x:c>
+      <x:c r="B552" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C552" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D552" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E552" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="553" ht="64" customHeight="1">
+      <x:c r="A553" s="6" t="str">
+        <x:v>李志强</x:v>
+      </x:c>
+      <x:c r="B553" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C553" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D553" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E553" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="554" ht="64" customHeight="1">
+      <x:c r="A554" s="6" t="str">
+        <x:v>李德志</x:v>
+      </x:c>
+      <x:c r="B554" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C554" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D554" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E554" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="555" ht="64" customHeight="1">
+      <x:c r="A555" s="6" t="str">
+        <x:v>刘梅</x:v>
+      </x:c>
+      <x:c r="B555" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C555" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D555" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E555" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="556" ht="64" customHeight="1">
+      <x:c r="A556" s="6" t="str">
+        <x:v>姜义成</x:v>
+      </x:c>
+      <x:c r="B556" s="6" t="str">
+        <x:v>institution-classification-7</x:v>
+      </x:c>
+      <x:c r="C556" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D556" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E556" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="557" ht="64" customHeight="1">
+      <x:c r="A557" s="6" t="str">
+        <x:v>董英凝</x:v>
+      </x:c>
+      <x:c r="B557" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C557" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D557" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E557" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="558" ht="64" customHeight="1">
+      <x:c r="A558" s="6" t="str">
+        <x:v>赵彬</x:v>
+      </x:c>
+      <x:c r="B558" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C558" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D558" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E558" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="559" ht="64" customHeight="1">
+      <x:c r="A559" s="6" t="str">
+        <x:v>冀振元</x:v>
+      </x:c>
+      <x:c r="B559" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C559" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D559" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E559" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="560" ht="64" customHeight="1">
+      <x:c r="A560" s="6" t="str">
+        <x:v>谢俊好</x:v>
+      </x:c>
+      <x:c r="B560" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C560" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D560" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E560" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="561" ht="64" customHeight="1">
+      <x:c r="A561" s="6" t="str">
+        <x:v>毛兴鹏</x:v>
+      </x:c>
+      <x:c r="B561" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C561" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D561" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E561" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="562" ht="64" customHeight="1">
+      <x:c r="A562" s="6" t="str">
+        <x:v>位寅生</x:v>
+      </x:c>
+      <x:c r="B562" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C562" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D562" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E562" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="563" ht="64" customHeight="1">
+      <x:c r="A563" s="6" t="str">
+        <x:v>张云</x:v>
+      </x:c>
+      <x:c r="B563" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C563" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D563" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E563" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="564" ht="64" customHeight="1">
+      <x:c r="A564" s="6" t="str">
+        <x:v>李杨</x:v>
+      </x:c>
+      <x:c r="B564" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C564" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D564" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E564" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="565" ht="64" customHeight="1">
+      <x:c r="A565" s="6" t="str">
+        <x:v>周共健</x:v>
+      </x:c>
+      <x:c r="B565" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C565" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D565" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E565" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="566" ht="64" customHeight="1">
+      <x:c r="A566" s="6" t="str">
+        <x:v>王勇</x:v>
+      </x:c>
+      <x:c r="B566" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C566" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D566" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E566" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="567" ht="64" customHeight="1">
+      <x:c r="A567" s="6" t="str">
+        <x:v>于雷</x:v>
+      </x:c>
+      <x:c r="B567" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C567" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D567" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E567" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="568" ht="64" customHeight="1">
+      <x:c r="A568" s="6" t="str">
+        <x:v>张鑫</x:v>
+      </x:c>
+      <x:c r="B568" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C568" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D568" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E568" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="569" ht="64" customHeight="1">
+      <x:c r="A569" s="6" t="str">
+        <x:v>吴小川</x:v>
+      </x:c>
+      <x:c r="B569" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C569" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D569" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E569" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="570" ht="64" customHeight="1">
+      <x:c r="A570" s="6" t="str">
+        <x:v>索莹</x:v>
+      </x:c>
+      <x:c r="B570" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C570" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D570" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E570" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="571" ht="64" customHeight="1">
+      <x:c r="A571" s="6" t="str">
+        <x:v>耿钧</x:v>
+      </x:c>
+      <x:c r="B571" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C571" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D571" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E571" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="572" ht="64" customHeight="1">
+      <x:c r="A572" s="6" t="str">
+        <x:v>童鹏</x:v>
+      </x:c>
+      <x:c r="B572" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C572" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D572" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E572" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="573" ht="64" customHeight="1">
+      <x:c r="A573" s="6" t="str">
+        <x:v>李可毅</x:v>
+      </x:c>
+      <x:c r="B573" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C573" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D573" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E573" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="574" ht="64" customHeight="1">
+      <x:c r="A574" s="6" t="str">
+        <x:v>刘子滔</x:v>
+      </x:c>
+      <x:c r="B574" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C574" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D574" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E574" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="575" ht="64" customHeight="1">
+      <x:c r="A575" s="6" t="str">
+        <x:v>化青龙</x:v>
+      </x:c>
+      <x:c r="B575" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C575" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D575" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E575" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="576" ht="64" customHeight="1">
+      <x:c r="A576" s="6" t="str">
+        <x:v>袁浩轩</x:v>
+      </x:c>
+      <x:c r="B576" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C576" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D576" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E576" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="577" ht="64" customHeight="1">
+      <x:c r="A577" s="6" t="str">
+        <x:v>张君秋</x:v>
+      </x:c>
+      <x:c r="B577" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C577" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D577" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E577" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="578" ht="64" customHeight="1">
+      <x:c r="A578" s="6" t="str">
+        <x:v>丁明凯</x:v>
+      </x:c>
+      <x:c r="B578" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C578" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D578" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E578" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="579" ht="64" customHeight="1">
+      <x:c r="A579" s="6" t="str">
+        <x:v>彭喜元</x:v>
+      </x:c>
+      <x:c r="B579" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C579" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D579" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E579" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="580" ht="64" customHeight="1">
+      <x:c r="A580" s="6" t="str">
+        <x:v>姜守达</x:v>
+      </x:c>
+      <x:c r="B580" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C580" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D580" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E580" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="581" ht="64" customHeight="1">
+      <x:c r="A581" s="6" t="str">
+        <x:v>付平</x:v>
+      </x:c>
+      <x:c r="B581" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C581" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D581" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E581" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="582" ht="64" customHeight="1">
+      <x:c r="A582" s="6" t="str">
+        <x:v>彭宇</x:v>
+      </x:c>
+      <x:c r="B582" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C582" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D582" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E582" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="583" ht="64" customHeight="1">
+      <x:c r="A583" s="6" t="str">
+        <x:v>乔立岩</x:v>
+      </x:c>
+      <x:c r="B583" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C583" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D583" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E583" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="584" ht="64" customHeight="1">
+      <x:c r="A584" s="6" t="str">
+        <x:v>许永辉</x:v>
+      </x:c>
+      <x:c r="B584" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C584" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D584" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E584" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="585" ht="64" customHeight="1">
+      <x:c r="A585" s="6" t="str">
+        <x:v>许永辉</x:v>
+      </x:c>
+      <x:c r="B585" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C585" s="6" t="str">
+        <x:v>https://www.bit.edu.cn/gbxxgk/xxjj_sjb/index.htm</x:v>
+      </x:c>
+      <x:c r="D585" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E585" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="586" ht="64" customHeight="1">
+      <x:c r="A586" s="6" t="str">
+        <x:v>孙超</x:v>
+      </x:c>
+      <x:c r="B586" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C586" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D586" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E586" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="587" ht="64" customHeight="1">
+      <x:c r="A587" s="6" t="str">
+        <x:v>凤雷</x:v>
+      </x:c>
+      <x:c r="B587" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C587" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D587" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E587" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="588" ht="64" customHeight="1">
+      <x:c r="A588" s="6" t="str">
+        <x:v>赵光权</x:v>
+      </x:c>
+      <x:c r="B588" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C588" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D588" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E588" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="589" ht="64" customHeight="1">
+      <x:c r="A589" s="6" t="str">
+        <x:v>杨智明</x:v>
+      </x:c>
+      <x:c r="B589" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C589" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D589" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E589" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="590" ht="64" customHeight="1">
+      <x:c r="A590" s="6" t="str">
+        <x:v>俞洋</x:v>
+      </x:c>
+      <x:c r="B590" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C590" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D590" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E590" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="591" ht="64" customHeight="1">
+      <x:c r="A591" s="6" t="str">
+        <x:v>付宁</x:v>
+      </x:c>
+      <x:c r="B591" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C591" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D591" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E591" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="592" ht="64" customHeight="1">
+      <x:c r="A592" s="6" t="str">
+        <x:v>林连雷</x:v>
+      </x:c>
+      <x:c r="B592" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C592" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D592" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E592" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="593" ht="64" customHeight="1">
+      <x:c r="A593" s="6" t="str">
+        <x:v>魏长安</x:v>
+      </x:c>
+      <x:c r="B593" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C593" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D593" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E593" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="594" ht="64" customHeight="1">
+      <x:c r="A594" s="6" t="str">
+        <x:v>刘冰</x:v>
+      </x:c>
+      <x:c r="B594" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C594" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D594" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E594" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="595" ht="64" customHeight="1">
+      <x:c r="A595" s="6" t="str">
+        <x:v>刘大同</x:v>
+      </x:c>
+      <x:c r="B595" s="6" t="str">
+        <x:v>institution-classification-7</x:v>
+      </x:c>
+      <x:c r="C595" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D595" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E595" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="596" ht="64" customHeight="1">
+      <x:c r="A596" s="6" t="str">
+        <x:v>刘连胜</x:v>
+      </x:c>
+      <x:c r="B596" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C596" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D596" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E596" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="597" ht="64" customHeight="1">
+      <x:c r="A597" s="6" t="str">
+        <x:v>杨京礼</x:v>
+      </x:c>
+      <x:c r="B597" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C597" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D597" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E597" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="598" ht="64" customHeight="1">
+      <x:c r="A598" s="6" t="str">
+        <x:v>张京超</x:v>
+      </x:c>
+      <x:c r="B598" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C598" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D598" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E598" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="599" ht="64" customHeight="1">
+      <x:c r="A599" s="6" t="str">
+        <x:v>魏德宝</x:v>
+      </x:c>
+      <x:c r="B599" s="6" t="str">
+        <x:v>institution-classification-7</x:v>
+      </x:c>
+      <x:c r="C599" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D599" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E599" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="600" ht="64" customHeight="1">
+      <x:c r="A600" s="6" t="str">
+        <x:v>刘晓东</x:v>
+      </x:c>
+      <x:c r="B600" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C600" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D600" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E600" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="601" ht="64" customHeight="1">
+      <x:c r="A601" s="6" t="str">
+        <x:v>孙震</x:v>
+      </x:c>
+      <x:c r="B601" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C601" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D601" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E601" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="602" ht="64" customHeight="1">
+      <x:c r="A602" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B602" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C602" s="6" t="str">
+        <x:v>https://www.cqu.edu.cn/xqgk/xxjj.htm</x:v>
+      </x:c>
+      <x:c r="D602" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E602" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="603" ht="64" customHeight="1">
+      <x:c r="A603" s="6" t="str">
+        <x:v>梁军</x:v>
+      </x:c>
+      <x:c r="B603" s="6" t="str">
+        <x:v>institution-classification-7</x:v>
+      </x:c>
+      <x:c r="C603" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D603" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E603" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="604" ht="64" customHeight="1">
+      <x:c r="A604" s="6" t="str">
+        <x:v>孟升卫</x:v>
+      </x:c>
+      <x:c r="B604" s="6" t="str">
+        <x:v>institution-classification-8</x:v>
+      </x:c>
+      <x:c r="C604" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D604" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E604" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="605" ht="64" customHeight="1">
+      <x:c r="A605" s="6" t="str">
+        <x:v>刘兆庆</x:v>
+      </x:c>
+      <x:c r="B605" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C605" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D605" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E605" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="606" ht="64" customHeight="1">
+      <x:c r="A606" s="6" t="str">
+        <x:v>刘旺</x:v>
+      </x:c>
+      <x:c r="B606" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C606" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D606" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E606" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="607" ht="64" customHeight="1">
+      <x:c r="A607" s="6" t="str">
+        <x:v>邹昕光</x:v>
+      </x:c>
+      <x:c r="B607" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C607" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D607" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E607" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="608" ht="64" customHeight="1">
+      <x:c r="A608" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B608" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C608" s="6" t="str">
+        <x:v>https://www.uestc.edu.cn/xxgk/xxls.htm</x:v>
+      </x:c>
+      <x:c r="D608" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E608" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="609" ht="64" customHeight="1">
+      <x:c r="A609" s="6" t="str">
+        <x:v>宋宇晨</x:v>
+      </x:c>
+      <x:c r="B609" s="6" t="str">
+        <x:v>institution-classification-7</x:v>
+      </x:c>
+      <x:c r="C609" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D609" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E609" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="610" ht="64" customHeight="1">
+      <x:c r="A610" s="6" t="str">
+        <x:v>王本宽</x:v>
+      </x:c>
+      <x:c r="B610" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C610" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D610" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E610" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="611" ht="64" customHeight="1">
+      <x:c r="A611" s="6" t="str">
+        <x:v>高天宇</x:v>
+      </x:c>
+      <x:c r="B611" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C611" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D611" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E611" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="612" ht="64" customHeight="1">
+      <x:c r="A612" s="6" t="str">
+        <x:v>尉志良</x:v>
+      </x:c>
+      <x:c r="B612" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C612" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D612" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E612" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="613" ht="64" customHeight="1">
+      <x:c r="A613" s="6" t="str">
+        <x:v>常永祺</x:v>
+      </x:c>
+      <x:c r="B613" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C613" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D613" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E613" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614" ht="64" customHeight="1">
+      <x:c r="A614" s="6" t="str">
+        <x:v>王俊凯</x:v>
+      </x:c>
+      <x:c r="B614" s="6" t="str">
+        <x:v>institution-classification-7</x:v>
+      </x:c>
+      <x:c r="C614" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D614" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E614" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="615" ht="64" customHeight="1">
+      <x:c r="A615" s="6" t="str">
+        <x:v>姚博文</x:v>
+      </x:c>
+      <x:c r="B615" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C615" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D615" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E615" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="616" ht="64" customHeight="1">
+      <x:c r="A616" s="6" t="str">
+        <x:v>王厂东</x:v>
+      </x:c>
+      <x:c r="B616" s="6" t="str">
+        <x:v>institution-classification-8</x:v>
+      </x:c>
+      <x:c r="C616" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D616" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E616" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="617" ht="64" customHeight="1">
+      <x:c r="A617" s="6" t="str">
+        <x:v>吴艳</x:v>
+      </x:c>
+      <x:c r="B617" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C617" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D617" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E617" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="618" ht="64" customHeight="1">
+      <x:c r="A618" s="6" t="str">
+        <x:v>郑文斌</x:v>
+      </x:c>
+      <x:c r="B618" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C618" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D618" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E618" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="619" ht="64" customHeight="1">
+      <x:c r="A619" s="6" t="str">
+        <x:v>宿富林</x:v>
+      </x:c>
+      <x:c r="B619" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C619" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D619" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E619" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="620" ht="64" customHeight="1">
+      <x:c r="A620" s="6" t="str">
+        <x:v>邹斌</x:v>
+      </x:c>
+      <x:c r="B620" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C620" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D620" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E620" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="621" ht="64" customHeight="1">
+      <x:c r="A621" s="6" t="str">
+        <x:v>张钧萍</x:v>
+      </x:c>
+      <x:c r="B621" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C621" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D621" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E621" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="622" ht="64" customHeight="1">
+      <x:c r="A622" s="6" t="str">
+        <x:v>朱兵</x:v>
+      </x:c>
+      <x:c r="B622" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C622" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D622" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E622" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="623" ht="64" customHeight="1">
+      <x:c r="A623" s="6" t="str">
+        <x:v>谷延锋</x:v>
+      </x:c>
+      <x:c r="B623" s="6" t="str">
+        <x:v>institution-classification-8</x:v>
+      </x:c>
+      <x:c r="C623" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D623" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E623" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="624" ht="64" customHeight="1">
+      <x:c r="A624" s="6" t="str">
+        <x:v>侯成宇</x:v>
+      </x:c>
+      <x:c r="B624" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C624" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D624" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E624" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="625" ht="64" customHeight="1">
+      <x:c r="A625" s="6" t="str">
+        <x:v>陈雨时</x:v>
+      </x:c>
+      <x:c r="B625" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C625" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D625" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E625" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="626" ht="64" customHeight="1">
+      <x:c r="A626" s="6" t="str">
+        <x:v>尹振东</x:v>
+      </x:c>
+      <x:c r="B626" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C626" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D626" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E626" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="627" ht="64" customHeight="1">
+      <x:c r="A627" s="6" t="str">
+        <x:v>陈浩</x:v>
+      </x:c>
+      <x:c r="B627" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C627" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D627" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E627" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="628" ht="64" customHeight="1">
+      <x:c r="A628" s="6" t="str">
+        <x:v>张腊梅</x:v>
+      </x:c>
+      <x:c r="B628" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C628" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D628" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E628" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="629" ht="64" customHeight="1">
+      <x:c r="A629" s="6" t="str">
+        <x:v>杨柱天</x:v>
+      </x:c>
+      <x:c r="B629" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C629" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D629" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E629" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="630" ht="64" customHeight="1">
+      <x:c r="A630" s="6" t="str">
+        <x:v>胡悦</x:v>
+      </x:c>
+      <x:c r="B630" s="6" t="str">
+        <x:v>institution-classification-8</x:v>
+      </x:c>
+      <x:c r="C630" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D630" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E630" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="631" ht="64" customHeight="1">
+      <x:c r="A631" s="6" t="str">
+        <x:v>刘金龙</x:v>
+      </x:c>
+      <x:c r="B631" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C631" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D631" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E631" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="632" ht="64" customHeight="1">
+      <x:c r="A632" s="6" t="str">
+        <x:v>刘天竹</x:v>
+      </x:c>
+      <x:c r="B632" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C632" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D632" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E632" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="633" ht="64" customHeight="1">
+      <x:c r="A633" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B633" s="6" t="str">
+        <x:v>institution-classification-9</x:v>
+      </x:c>
+      <x:c r="C633" s="6" t="str">
+        <x:v>https://www.whu.edu.cn/xxgk/xxjj.htm</x:v>
+      </x:c>
+      <x:c r="D633" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E633" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="634" ht="64" customHeight="1">
+      <x:c r="A634" s="6" t="str">
+        <x:v>肖傲然</x:v>
+      </x:c>
+      <x:c r="B634" s="6" t="str">
+        <x:v>institution-classification-10</x:v>
+      </x:c>
+      <x:c r="C634" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D634" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E634" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="635" ht="64" customHeight="1">
+      <x:c r="A635" s="6" t="str">
+        <x:v>胡航</x:v>
+      </x:c>
+      <x:c r="B635" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C635" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D635" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E635" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="636" ht="64" customHeight="1">
+      <x:c r="A636" s="6" t="str">
+        <x:v>侯煜冠</x:v>
+      </x:c>
+      <x:c r="B636" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C636" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D636" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E636" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="637" ht="64" customHeight="1">
+      <x:c r="A637" s="6" t="str">
+        <x:v>高建军</x:v>
+      </x:c>
+      <x:c r="B637" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C637" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D637" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E637" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="638" ht="64" customHeight="1">
+      <x:c r="A638" s="6" t="str">
+        <x:v>高国明</x:v>
+      </x:c>
+      <x:c r="B638" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C638" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D638" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E638" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="639" ht="64" customHeight="1">
+      <x:c r="A639" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B639" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C639" s="6" t="str">
+        <x:v>https://www.csu.edu.cn/zjzn/xxgk.htm</x:v>
+      </x:c>
+      <x:c r="D639" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E639" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="640" ht="64" customHeight="1">
+      <x:c r="A640" s="6" t="str">
+        <x:v>官大衍</x:v>
+      </x:c>
+      <x:c r="B640" s="6" t="str">
+        <x:v>institution-classification-7</x:v>
+      </x:c>
+      <x:c r="C640" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D640" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E640" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="641" ht="64" customHeight="1">
+      <x:c r="A641" s="6" t="str">
+        <x:v>赵延龙</x:v>
+      </x:c>
+      <x:c r="B641" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C641" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D641" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E641" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="642" ht="64" customHeight="1">
+      <x:c r="A642" s="6" t="str">
+        <x:v>陈迪</x:v>
+      </x:c>
+      <x:c r="B642" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C642" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D642" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E642" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="643" ht="64" customHeight="1">
+      <x:c r="A643" s="6" t="str">
+        <x:v>李贤</x:v>
+      </x:c>
+      <x:c r="B643" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C643" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D643" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E643" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="644" ht="64" customHeight="1">
+      <x:c r="A644" s="6" t="str">
+        <x:v>李鹏</x:v>
+      </x:c>
+      <x:c r="B644" s="6" t="str">
+        <x:v>institution-classification-7</x:v>
+      </x:c>
+      <x:c r="C644" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D644" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E644" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="645" ht="64" customHeight="1">
+      <x:c r="A645" s="6" t="str">
+        <x:v>庄迪</x:v>
+      </x:c>
+      <x:c r="B645" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C645" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D645" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E645" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="646" ht="64" customHeight="1">
+      <x:c r="A646" s="6" t="str">
+        <x:v>刘东洋</x:v>
+      </x:c>
+      <x:c r="B646" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C646" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D646" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E646" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="647" ht="64" customHeight="1">
+      <x:c r="A647" s="6" t="str">
+        <x:v>李大森</x:v>
+      </x:c>
+      <x:c r="B647" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C647" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D647" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E647" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="648" ht="64" customHeight="1">
+      <x:c r="A648" s="6" t="str">
+        <x:v>李大森</x:v>
+      </x:c>
+      <x:c r="B648" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C648" s="6" t="str">
+        <x:v>https://xxgk.scut.edu.cn/_upload/article/files/f9/59/7229d8c64109b93efc60864c9f8f/715ab56f-79b5-46ff-afae-c75af81b2036.pdf</x:v>
+      </x:c>
+      <x:c r="D648" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E648" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="649" ht="64" customHeight="1">
+      <x:c r="A649" s="6" t="str">
+        <x:v>董喆</x:v>
+      </x:c>
+      <x:c r="B649" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C649" s="6" t="str">
+        <x:v>https://www.csu.edu.cn/zjzn/xxgk.htm</x:v>
+      </x:c>
+      <x:c r="D649" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E649" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="650" ht="64" customHeight="1">
+      <x:c r="A650" s="6" t="str">
+        <x:v>董喆</x:v>
+      </x:c>
+      <x:c r="B650" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C650" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D650" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E650" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="651" ht="64" customHeight="1">
+      <x:c r="A651" s="6" t="str">
+        <x:v>吴龙文</x:v>
+      </x:c>
+      <x:c r="B651" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C651" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D651" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E651" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24786d4746e84880"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb19dca357ad546b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>